--- a/test_sample.xlsx
+++ b/test_sample.xlsx
@@ -568,40 +568,48 @@
       <c r="C2" s="4" t="inlineStr">
         <is>
           <t># 发布会概况
-王毅在慕尼黑安全会议上发表演讲，阐述中国对多极世界的立场。王毅引用今年慕安会报告主题“走向多极化”，指出联合国会员国从51个增至193个，提出推动平等有序的世界多极化，并表达四点看法：倡导平等相待、尊重国际法治、践行多边主义、坚持开放共赢。中国承担超过20%联合国会费，建成世界最大清洁发电体系，提出全球发展倡议、全球安全倡议、全球文明倡议；去年GDP增长5%，对世界经济增长贡献率接近30%。王毅还回应了关于国际秩序、乌克兰危机、中美关系等提问，强调中国是现行国际秩序的受益者，将推动秩序朝更加公正合理方向发展。整体基调坚定、务实，展现中国作为多极体系中确定性因素和建设性力量的定位。
+王毅在慕尼黑安全会议上发表演讲并回答提问，主题为世界走向多极化，中国主张推动平等有序的世界多极化，这是习近平主席提出的重大主张。王毅表示中国必将是多极体系中的确定性因素，坚定做变革世界中的建设性力量，并提出4点看法：倡导平等相待、尊重国际法治、践行多边主义、坚持开放共赢。演讲后王毅就国际秩序、乌克兰危机、中美关系等问题回应提问，强调中国维护以联合国为核心的国际体系，坚持劝和促谈，对美政策保持连续性和稳定性。整体基调坚定务实，既宣示中国立场，也回应国际关切。
 # 核心信息
-- 王毅引用今年慕安会报告主题“走向多极化”，指出联合国成立时只有51个会员国，到今天有193个国家。
-- 提出推动**平等有序的世界多极化**，这是习近平主席提出的重大主张。
-- 表达四点看法：**倡导平等相待**、**尊重国际法治**、**践行多边主义**、**坚持开放共赢**。
-- 中国承担**超过20%的联合国会费**，切实履行`巴黎协定`，建成**世界上最大的清洁发电体系**。
-- 提出并落实`全球发展倡议`、`全球安全倡议`、`全球文明倡议`，为完善全球治理提供公共产品。
-- 去年中国GDP增长**5%**，对世界经济增长贡献率接近**30%**。
-- 中国加入**几乎所有普遍性的政府间国际组织**和**600多项国际公约**。
-- 中国愿推动高质量共建`一带一路`，与欧盟`全球门户`战略相互对接。
-- 今年是**中欧建交50周年**。
+- 世界正走向多极化：**80年前**联合国成立时仅**51个**会员国，今天已有**193个**国家；中国主张推动平等有序的世界多极化，这是习近平主席提出的重大主张。
+- 中国是现行国际秩序的受益者，加入几乎所有普遍性政府间国际组织和**600多项**国际公约，从不搞例外主义，也不搞合则用、不合则弃。
+- 中国坚定维护联合国权威和地位，承担超过**20%**的联合国会费；切实履行`巴黎协定`，建成世界上最大的清洁发电体系。
+- 去年中国GDP增长**5%**，对世界经济增长贡献率接近**30%**，担当全球经济增长的重要引擎，向世界释放超大规模市场红利。
+- 中国愿推动高质量共建`一带一路`，与欧盟`全球门户`战略相互对接，赋能彼此也赋能世界。
+- 中国提出并落实`全球发展倡议`、`全球安全倡议`、`全球文明倡议`，为完善全球治理提供公共产品。
+- 关于乌克兰危机，**2022年2月25日**中方即提出对话协商解决；习近平主席提出4点主张：各国主权领土完整应得到尊重、联合国宪章应得到遵守、各国合理安全关切应得到重视、一切致力于和平的努力都应得到支持。
 # 官方表态
-- **多极化立场**：中国应当推动平等有序的世界多极化，这是习近平主席提出的重大主张，也是我们对多极世界真诚的期许。中国必将是多极体系中的确定性因素，将坚定做变革世界中的建设性力量。
-- **平等相待**：坚持权利平等、机会平等、规则平等，应当成为建设多极世界的基本原则。中国主张大小国家一律平等，呼吁提升发展中国家在国际体系中的代表性和发言权。
-- **国际法治**：联合国宪章宗旨和原则是国际关系的根本遵循，也是建设多极世界的重要基石。多极格局不能是无序的状态。大国要带头讲诚信、讲法治，坚决摒弃言行不一、零和博弈。中国从不搞例外主义，更不搞合则用、不合则弃。
-- **多边主义**：联合国是践行多边主义、推进全球治理的核心平台。对于这座大厦，我们应该固本强基，而不是拆梁毁柱。中国坚持真正的多边主义，倡导共商共建共享的全球治理观。
-- **开放共赢**：发展是破解各种难题的钥匙，多极世界应该是各国共同发展的世界。保护主义不是出路，滥加关税没有赢家。脱钩断链断的是机遇，小院高墙封的是自己。
-- **欧洲定位**：中方始终认为欧洲是多极世界的重要一极，中欧双方是伙伴而不是对手。
-- **人类命运共同体**：习近平主席提出共同构建人类命运共同体的重大理念，希望各国超越历史文化、社会制度、意识形态的不同，以同舟共济的精神共同呵护好人类可以居住的星球。
+**多极化主张**
+- 王毅表示，多极化的世界既是历史的必然，也正在成为现实；中国给出的答案是我们应当推动平等有序的世界多极化，这是习近平主席提出的又一个重大主张，也是我们对多极世界真诚的期许。
+&gt; 中国必将是多极体系中的确定性因素。将坚定做变革世界中的建设性力量。
+- 王毅提出4点看法：一是应当倡导平等相待，坚持权利平等、机会平等、规则平等，应当成为建设多极世界的基本原则；二是应当尊重国际法治，联合国宪章宗旨和原则是国际关系的根本遵循，也是建设多极世界的重要基石；三是要践行多边主义，联合国是践行多边主义、推进全球治理的核心平台，对于这座大厦我们应该固本强基，而不是拆梁毁柱；四是要坚持开放共赢，发展是破解各种难题的钥匙，多极世界应该是各国共同发展的世界。
+**国际秩序与规则**
+- 王毅表示，中国是在现行国际秩序中发展起来的，是这个秩序的受益者；我们要做的就是按照大多数国家的愿望，推动这个秩序朝着更加公正合理的方向去发展。
+&gt; 我们需要共同来维护以联合国为核心的国际体系。共同遵守以联合国宪章宗旨和原则为基础的国际关系的基本准则。我想这应该是我们的最大的公约数。
+- 王毅强调，在遵守国际法上不能搞双重标准，要尊重各国的主权和领土完整，就应该支持中国实现完全统一。
+**乌克兰危机**
+- 王毅表示，中国同俄罗斯是两大邻国，建立结盟不对抗、不针对第三方的睦邻友好关系，进而增进战略互信，建立全面战略伙伴关系。
+- 王毅指出，中国历来主张一切争端和冲突都应该通过对话寻求政治解决，因为武力和制裁不可能真正和彻底的解决问题，乌克兰问题上同样如此。
+&gt; 任何冲突的终点都是谈判桌，历史最终一定是公正的。中方乐见一切致力于和平的努力。
+- 王毅表示，中国派出的特使去各国斡旋，同巴西等南方国家发起了和平之友；所有当事方包括利益攸关方，都应该适时的参与到这个和谈的进程当中。
+**中美关系**
+- 王毅表示，中国的对美政策保持着连续性和稳定性，我们不会轻易的翻烙饼；对美政策就是习近平主席提出的三原则：相互尊重、和平共处、合作共赢。
+&gt; 中方已经准备好了，我们愿意按照三原则同美方构建稳定健康可持续的双边关系，找到两个大国在这个星球上的正确相处之道。
+- 王毅强调，如果美方仍然还要对中国打压和遏制，那我们也别无选择，我们必将奉陪到底；必将坚定的维护中国的主权、国家的尊严和我们的正当发展权利，必将坚决的回击美方的单边和霸凌的行径。
 # Q&amp;A环节
-**问**：您提到国际秩序，现在有很多对联合国宪章的质疑，包括俄罗斯入侵乌克兰、美国总统威胁使用武力入侵格陵兰和巴拿马、巴勒斯坦人流离失所，贵国也被指控违反海洋法和世界人权宣言。您即将前往纽约参加安理会，您是否仍然相信联合国和联合国宪章？联合国改革在您的优先事项中排多高？
-**答**：说到秩序，这几年总有人说中国要改变秩序、另起炉灶，但现在真正挑战秩序、毁约退群的国家出现了。中国是在现行国际秩序中发展起来的，是受益者，我们要按照大多数国家的愿望推动秩序朝更加公正合理的方向发展。谈到规则，我们起码应该有一个共同认知，就是共同维护以联合国为核心的国际体系，共同遵守以联合国宪章宗旨和原则为基础的国际关系基本准则，这是最大的公约数。只要大家都认同这一点，双重标准就不会出现。
-**问**：自2022年以来，慕安会一直讨论俄罗斯入侵乌克兰。您在入侵前几天曾说“任何国家的主权、独立和领土完整都应得到尊重和维护，乌克兰也不例外”。现在俄罗斯已成为中国加油站（有军队的加油站），您对乌克兰有很大影响力。在压力加大、战争可能结束的情况下，您能否从您这边切断俄罗斯向中国供应天然气的可能性、降低价格或停止一些军民两用物资，以加大对俄罗斯的压力？
-**答**：中国同俄罗斯是两大邻国，有着漫长的边界，建立了不结盟、不对抗、不针对第三方的睦邻友好关系，进而建立了全面战略伙伴关系。如果中国不从俄罗斯买油气，哪个国家能提供如此巨量的油气来满足中国民众的需求？那是不可能的，也是不保险的，因为常有国家把经贸问题政治化，当做打压中国的工具。但中国在地区热点问题上有自己的立场，历来主张一切争端和冲突都应通过对话寻求政治解决。从2022年2月25日危机爆发第二天起，中方就提出对话协商解决。习近平主席提出四点主张：各国主权领土完整应得到尊重、联合国宪章应得到遵守、各国合理安全关切应得到重视、一切致力于和平的努力应得到支持。中国派特使去各国斡旋，同巴西等南方国家发起和平之友。任何冲突的终点都是谈判桌，中方乐见一切致力于和平的努力，包括美俄达成的共识。所有当事方和利益攸关方都应适时参与和谈进程，欧洲更有必要发挥重要作用，共同探讨欧洲的长治久安。
-**问**：时间快到了，能否简单预告一下您认为美中关系将如何发展？
-**答**：中国的对美政策保持连续性和稳定性，不会轻易翻烙饼，这体现大国的战略定力和国际信誉。对美政策就是习近平主席提出的三原则：相互尊重、和平共处、合作共赢。中美制度不一样，是各自人民做出的选择，想改造或颠覆对方不切实际。正确态度是相互尊重，这是中美交往的前提；和平共处理所当然，中美两个大国总不能冲突起来，那将殃及整个世界；合作共赢是国际社会的期待，全球性挑战需要中美携手应对。中方已准备好，愿意按三原则同美方构建稳定健康可持续的双边关系。希望美方相向而行，但如果美方仍要打压遏制，中方别无选择，必将奉陪到底，坚决维护中国的主权、国家尊严和正当发展权利，坚决回击美方的单边霸凌行径。</t>
+**问**：周琦提问，当前国际秩序受到质疑，包括俄罗斯入侵乌克兰、美国总统威胁使用武力等；王毅即将前往纽约参加安理会会议，是否仍相信联合国和联合国宪章？是否将推动联合国改革？
+**答**：王毅表示，真正要挑战秩序、毁约退群的国家出现了，而中国是在现行国际秩序中发展起来的，是受益者，要推动秩序朝更加公正合理方向发展。谈到规则，应共同维护以联合国为核心的国际体系，遵守以联合国宪章宗旨和原则为基础的国际关系基本准则，这是最大的公约数；只要认同这一点，双重标准就不会出现。习近平主席提出全球发展倡议、全球安全倡议、全球文明倡议，希望国际社会携手解决发展赤字、安全赤字、治理赤字，共同构建人类命运共同体。
+**问**：周琦提问，自2022年以来慕安会持续关注俄罗斯入侵乌克兰；王毅此前曾确认乌克兰的主权、独立和领土完整应受尊重，如今俄罗斯已成为中国加油站（带军队的加油站），中国对乌克兰有很大影响力；在当前压力下，中国能否从自身角度切断俄罗斯向中国供应天然气的可能、降低价格或停止输送军民两用物资，以加大对俄施压、促其结束战争？
+**答**：王毅表示，中国同俄罗斯是两大邻国，建立结盟不对抗、不针对第三方的睦邻友好关系，交往是正常的国与国之间的交往；如果中国不从俄罗斯买油气，没有哪个国家能提供如此巨量的油气来满足中国民众的需求，那是不可能的，也是不保险的，因为常有国家把经贸问题政治化，当做打压中国的工具。中国在对待地区热点问题上有自己的立场，历来主张一切争端和冲突都应通过对话寻求政治解决，武力和制裁不可能真正彻底解决问题；从2022年2月25日起中方就提出对话协商解决，习近平主席提出的4点主张是中国立场的最权威阐释。中国以此推进劝和促谈，派特使斡旋，同巴西等南方国家发起和平之友；中方乐见一切致力于和平的努力，包括美国同俄罗斯达成的共识，同时认为所有当事方包括利益攸关方都应适时参与和谈进程，欧洲更有必要为此发挥重要作用，共同探讨欧洲的长治久安。
+**问**：周琦提问，能否预告中美关系将如何发展？
+**答**：王毅表示，中国的对美政策保持连续性和稳定性，不会轻易翻烙饼，这体现大国的战略定力和国际信誉；对美政策是习近平主席提出的三原则：相互尊重、和平共处、合作共赢。中美制度不同是各自人民做出的选择，想改造或颠覆对方不切实际；中方已准备好按三原则同美方构建稳定健康可持续的双边关系，希望美方相向而行；但如果美方仍对中国打压遏制，中国别无选择，必将奉陪到底，坚决回击美方单边霸凌行径，这也是为了维护国际公平正义和国际关系基本准则。</t>
         </is>
       </c>
       <c r="D2" s="10" t="n">
-        <v>52.4</v>
+        <v>61.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>7004/2529</t>
+          <t>7004/2837</t>
         </is>
       </c>
     </row>
@@ -768,26 +776,56 @@
       <c r="C3" s="4" t="inlineStr">
         <is>
           <t># 沟通背景与目的
-电子科技大学电子科学与工程学院举办招生直播，由段院介绍学院整体情况，柳教授、张教授、李天明教授分别介绍电子信息材料与元器件、电磁场与微波技术、电路与系统、物理电子学等学科方向，在读博士田雨桐从学生视角分享选择学院的8个理由。沟通目的是向考生和家长全面展示学院实力与人才培养成果，吸引报考。直播中段院回应夏令营问题，表示今年计划举办夏令营，具体时间待定，相关信息将通过QQ群发布。
+电子科技大学电子科学与工程学院举办招生宣讲会，面向考生和家长介绍学院整体情况、学科方向、师资科研与人才培养。段院介绍学院源于1956年建校时的无线电系、电真空器件系、无线电零件系，经四次院系调整成立，一级学科电子科学与技术为国家重点一级学科，下设5个二级学科方向；现有本科生1545人、研究生1975人，教师302人，近5年科研到账经费稳定在3-4亿元/年。柳教授介绍电子信息材料与元器件方向，指出2021年中国集成电路电子产品进口额达2.8万亿元，属卡脖子问题之一。张教授介绍电磁场与微波技术、电路与系统方向，学科始于1956年，拥有6个团队及先进微波暗室群体。李天明教授介绍物理电子学方向，每年到校科研经费接近2亿元，为学院最多。在读博士田雨桐分享选择电子学院的8个理由，包括成都产业环境、学科A+评级、团队100%就业率等。会议达成共识：学院计划今年举办夏令营，时间待定，相关信息通过QQ群（978499108）发布。
 # 信息同步
-**段院（学院整体情况）**：学院源于1956年建校时的无线电系等，经4次院系调整，2023年成立电子科学与工程学院与基层电路学院；一级学科电子科学与技术为国家重点一级学科，含电磁场与微波技术、电路与系统、微电子学与固体电子学、物理电子学、电磁信息功能材料与机构5个二级学科方向及3个国防特色学科。现有本科生1545人（招生专业为工科试验班（电子工程类），含电子科学技术、电磁场与无线技术两个方向）、研究生1975人；教师302人，其中两院院士2人、领军人才19人、青年人才28人；拥有两个全国高校黄大年式教师团队，2022年获批4个国家自然科学基金创新群体。科研方面，近5年到账经费稳定在3-4亿元/年（纵向为主），牵头获国家科技奖励11项，近5年发表高水平论文2000余篇，专利申1600余件、授权1300余件；20个科研团队中年度经费过千万团队15个、过亿团队1个。平台方面，拥有两个国家级平台（国家电子辐射控制材料工程技术研究中心、微波电子工器件国家级重点实验室）、4个国际合作平台、7个省部级平台，国际姊妹院系2个（香港大学电机工程电子系、香港城市大学电子工程系），主办国际会议13场，学生交流项目20多个。
-**柳教授（电子信息材料与元器件方向）**：该方向以电子在物质中的输运特性为基础，以材料为基础、器件为核心、应用为目标，2021年中国集成电路电子产品进口额达2.8万亿元（约为原油进口量的1.7倍），属卡脖子问题之一，应用领域覆盖6G通讯、量子技术、智慧城市、光电技术、新能源、智能电子等，达万亿美元量级。研究队伍含国家级人才10余人，其中邓龙江院士团队（电磁辐射控制材料与技术）19人（正高13、副高15），发表论文300余篇（含Nature），承担课题130余项，年均到账经费3000多万元，授权发明专利100余项，获国家科技进步/技术发明二等奖3项；张怀武教授团队（磁电薄膜与微型器件）17人（正高15、副高2），研究Ltcc材料及集成技术、微波毫米波晶圆及器件、自旋电子与磁量子器件、传感器芯片等，承担项目100余项，获科技进步二等奖3项，发表SCI论文400余篇，年均到账经费2000余万元。平台依托国家电磁辐射控制材料工程技术研究中心（1990年校级中心，2008、2013年两次升级）和电磁薄膜与集成器件全国重点实验室（2006年筹建），科研面积2万余平米（超精尖3000平），两条国家重大任务试验生产线，大型设备500余台套。成果获国家技术发明等奖项共7项；毕业生去向含英特尔、中芯国际、华为、德州仪器等；学生案例包括杨伟豪在自然电子、自然通讯各发一篇一作，5G滤波器芯片学生团队获挑战杯四川省金奖，黄飞获斯坦福全奖，李凤霞读博期间发表论文16篇（一作6篇），严巍获王大珩光学奖并加入苏州大学，万位任河北美泰电子科技副总并采用MEMS工艺研制出SIW环形器隔离器。
-**张教授（电磁场与微波技术、电路与系统方向）**：电磁场与微波技术含微波毫米波电路、电波传播与电磁兼容、计算电磁学与工程电子学、天线理论与技术4个细分方向，电路与系统含非线性电路与复杂电子系统、射频微波电路与系统、集成电路与系统3个方向。学科始于1956年由林卫干、谢楚芳创建，形成电磁场与无线技术国家特色专业和电波传播与天线国防紧缺特色专业，所属一级学科入选双一流A类。团队含电磁辐射与散射、毫米波技术与系统应用、微波毫米波集成电路与系统、电磁兼容技术、微波测试与成像技术、无线技术与集成系统6个团队；平台含国家自然基金委创新群体、国家高等学校学科创新引智基地、国家工程技术研究中心、国家级重点实验室，拥有中国高校最先进的微波暗室群体和微波毫米波太赫兹仿真测试平台。成果方面，杨世文教授团队四维天线阵列技术、强耦合超宽带相控阵（应用于中电14所某大型机载相控阵雷达），樊勇教授团队毫米波平面集成天线，李恩教授团队微波毫米波测量技术（60多年积累）、电磁测井仪器获国家科技进步二等奖并在中海油应用，延波教授团队微波毫米波太赫兹芯片、固态合成功率源、三毫米导引头前端、毫米波引信前端、8毫米宽带收发前端，杨世文团队计算电磁学算法被评为20世纪十大算法之一，樊勇团队太赫兹雷达成像系统（0.22THz、0.34THz、0.42THz，分辨率小于1厘米），太赫兹通信在2023年成都大运会田径项目示范应用，李恩团队生物医学电磁学及成像（20余项国家发明专利）。电路与系统学科1981年招研究生、1988年首批博士后流动站，含教育部国际合作联合实验室、国家高等学校学科创新引智基地，国家级人才4人、新世纪人才2人、教授10人、副教授22人；成果含樊勇、李廷军团队高速磁浮交通38GHz车地通信系统，樊勇、张静团队毫米波通信雷达CMOS芯片，康凯教授团队毫米波CMOS芯片（超宽带模块级芯片、5G通信和雷达系统）。人才培养连续三年获全国大学生集成电路创新创业大赛奖项，获华为优秀合作项目奖、研究生优秀导学团队提名奖，就业领域含华为、中兴等。
-**李天明教授（物理电子学方向）**：物理电子学是物理学与电子科学与技术的交叉学科，典型应用包括微波电子学（微波电真空器件）和光电子学（光电器件），学科特点为内容不断充实（量子电子学）、边界不清晰（光电子学可属光学工程）。学校物理电子学起源于1956年建校时的电子控器件专业（前苏联专家帮助），1979年刘成刚院士成立高能电子学研究所，2001年成立物理电子学，2018年成立电子科学与工程学院。发展上纵向（上游仿真设计、下游系统应用）与横向（频段上移至毫米波太赫兹、与医学交叉）并进，拥有自主知识产权商用软件MMST和切皮克，引入人工智能到器件设计；系统应用包括毫米波雷达（回旋行波管）、无线输能系统（行波管）、微波能干燥系统（磁控管），太赫兹技术用于成像、保密通信、高速通信及医学诊断。科研经费每年接近2亿元（为学院最多），是国际最大真空器件研究中心，2023年举办行业顶级会议，团队共9个。学生出口方面，团队约1/3硕博连读、1/3去企业、1/3去研究所或其他；个人每年约2个硕士毕业、1个博士毕业。
-**田雨桐（在读博士，学生视角）**：分享选择电子学院的8个理由：城市（成都，国家中心城市，电子信息产业前端，英特尔、华为、京东方等汇聚）；学校（电子信息人才培育代名词，有电子信息博物馆，完整学科群）；专业（电子科学与技术第四轮学科评估A+，全国第一）；团队（毫米波技术与系统应用团队，樊勇老师负责，五大方向：微波毫米波理论与技术、天线理论与技术、元器件与电路、通信技术与系统、雷达成像技术与系统）；培养（可做雷达或无线通信系统，联合培养，团队硕博毕业生100%就业）；校园生活（东湖钢琴小屋、2021年跨年300架无人机灯光秀）；奖助体系（国家奖学金、学业奖学金、专项奖学金、新生奖学金、国家助学贷款、生源地贷款）；择校建议（先选团队再选导师，利用学院网站、IEEE、中国知网检索导师论文和指导情况）。
+**段院（学院整体情况）**
+- 学院历史：1956年建校时成立无线电系、电真空器件系、无线电零件系，经1979、1992、2001、2018年四次院系调整成立电子科学与工程学院，2023年成立电子科学与工程学院与集成电路学院。
+- 学科设置：一级学科电子科学与技术为国家重点一级学科，下设电磁场与微波技术、电路与系统、微电子学与固体电子学、物理电子学、电磁信息功能材料与机构5个二级学科方向，另有3个国防特色学科。
+- 人才培养：本科生1545人，招生专业为工科试验班（电子工程类），含电子科学与技术（国家特色专业、国家级一流本科专业建设点）和电磁场与无线技术两个专业方向；研究生1975人，学硕/博士专业为电子科学与技术、材料科学与工程，专硕/博士为电子信息、材料工程。
+- 师资队伍：教师302人（教研系列139人、科研系列95人、教学系列14人、实验系列21人、机关33人），两院院士2人、领军人才19人、青年人才28人、其他类型人才12人、博士后61人。
+- 科研实力：近5年科研到账经费稳定在3-4亿元/年，以纵向项目为主；牵头获国家科技奖励11项，近5年发表高水平论文2000余篇，专利申请1600余件、授权1300余件；20个科研团队中年度经费过千万元的15个、过亿元1个。
+- 平台与交流：拥有国家电磁辐射控制材料工程技术研究中心、微波电子器件国家级重点实验室2个国家级平台，4个国际合作平台、7个省部级科研平台；共建国际姊妹院系2个（香港大学电机工程电子系、香港城市大学电子工程系），主办高水平国际会议13场，学生长短期交流项目20多个。
+**柳教授（电子信息材料与元器件方向）**
+- 方向内涵：以电子在物质中的输运特性（电磁声光热力、化学生物）为基础，设计、研究和生产电子器件，以材料为基础、器件为核心、应用为目标导向。
+- 产业背景：2021年中国集成电路电子产品进口额达2.8万亿元，约为原油进口量的1.7倍，先进电子材料元器件电路系统是卡脖子问题之一；应用覆盖6G通讯、量子技术、智慧城市、光电技术、新能源、智能电子等领域，市场规模达万亿美元量级。
+- 发展趋势：元器件向微型化、片式化、集成化、薄膜化、智能化发展，强调材料和器件一体化，结合摩尔定律与超摩尔定律。
+- 研究队伍：国家级人才10余人；邓龙江院士电磁辐射控制材料与技术团队19人（正高13人、副高15人），近年发表包括Nature在内的论文300余篇，承担课题130余项，年均到账经费3000多万元，授权发明专利100余项，获国家科技进步奖或技术发明奖二等奖共3项；张怀武教授磁电薄膜与微型器件团队17人（正高15人、副高2人），开展LTCC材料及集成技术、微波毫米波晶圆及器件、自旋电子与磁量子器件、传感器芯片等研究，承担项目100余项，获科技进步二等奖3项，发表SCI论文400余篇，年均到账经费2000余万元。
+- 平台与条件：依托国家电磁辐射控制材料工程技术研究中心（可追溯至1990年校级中心，经2008、2013年两次升级）和电磁薄膜与集成器件全国重点实验室（2006年筹建，三个重点方向为电子聚合物与阵列传感器、功率半导体与集成技术）；科研面积2万余平米（超精尖3000平），建设两条国家重大任务试验生产线，大型设备/系统500余台套。
+- 成果与去向：获国家技术发明奖等共7项，每年在Nature及子刊发表多篇重要文章；毕业生去向包括英特尔、中芯国际、华为、德州仪器等企业及高校科研院所。
+- 学生案例：杨伟豪以第一作者在Nature Electronics、Nature Communications各发表一篇论文；5G滤波器芯片学生团队获挑战杯创新创业大赛四川省金奖；黄飞（2018年四川省优秀毕业生）获斯坦福大学博士全额奖学金；李凤霞读博期间发表论文16篇（一作6篇）；严巍获华为光产线优秀合作项目奖、王大珩光学奖，博士毕业后以优秀青年学者身份加入苏州大学；万位现任河北美泰电子科技公司副总，带领团队采用MEMS工艺研制出SIW环形器隔离器，突破卡脖子器件核心技术。
+**张教授（电磁场与微波技术、电路与系统方向）**
+- 方向构成：电磁场与微波技术含微波毫米波电路、电波传播与电磁兼容、计算电磁学与工程电子学、天线理论与技术4个细分方向；电路与系统含非线性电路与复杂电子系统、射频微波电路与系统、集成电路与系统3个方向。
+- 学科沿革：电磁场与微波技术学科始于1956年建校时期，由林为干先生和谢处方先生创建，形成电磁场与无线技术国家特色专业和电波传播与天线国防紧缺特色专业，所属一级学科电子科学与技术入选双一流A类。
+- 团队与平台：电磁场与微波技术有6个团队（电磁辐射与散射、毫米波技术与系统应用、微波毫米波集成电路与系统、电磁兼容、微波测试与成像、无线技术与集成系统）；拥有国家自然基金委创新群体、国家高等学校学科创新引智基地、国家工程技术研究中心、国家级重点实验室，以及中国高校最先进的微波暗室群体和微波毫米波太赫兹仿真测试平台。
+- 代表性成果：杨世文教授团队四维天线阵列技术、强耦合超宽带相控阵（应用于中电14所某大型机载相控阵雷达）、电磁测井仪器（获国家科技进步二等奖，在中海油推广应用）、计算电磁学（算法被评为20世纪十大算法之一）；樊勇教授团队太赫兹雷达成像（0.22THz、0.34THz、0.42THz系统，分辨率小于1厘米）、太赫兹通信（2023年成都大运会田径项目示范应用）；李恩教授团队微波毫米波测量技术（60多年积累）、生物医学电磁学及成像（20余项国家发明专利）；延波教授团队微波毫米波太赫兹芯片（应用于新一代高速通信系统）、三毫米导引头前端、毫米波引信前端、8毫米宽带收发前端。
+- 电路与系统学科：1981年开始招收研究生，1988年成立首批博士后流动站，含教育部国际合作联合实验室、国家高等学校学科创新引智基地，国家级人才4人、新世纪人才2人、教授10人、副教授22人；樊勇教授和李廷军教授团队研制高速磁浮交通38GHz车地通信系统，樊勇教授和张静团队研究毫米波通信雷达CMOS芯片，康凯教授团队研制超宽带模块级芯片及5G通信和雷达系统。
+- 人才培养：连续三年获全国大学生集成电路创新创业大赛奖项，获华为优秀合作项目奖、研究生优秀导学团队提名奖，学生获互联网+、国际HPV等奖项；就业覆盖华为、中兴等领军企业、研究所、高校，海外留学有突破。
+**李天明教授（物理电子学方向）**
+- 学科定义：物理电子学是物理学与电子科学与技术的交叉学科，将物理学最新研究成果应用于电子学产生新电子器件，如微波电子学（微波电真空器件）、光电子学（光电器件）；特点为基础性与前沿性，支撑现代信息技术。
+- 历史沿革：起源于1956年建校时在苏联专家帮助下成立的电子器件专业，归属电子器件系；1979年在刘盛纲院士带领下成立高能电子学研究所；2001年物理系、应用所、高能所成立物理电子学；2018年成立电子科学与工程学院。
+- 发展现状：发展近70年，纵向扩展至上游仿真设计、下游系统应用，拥有自主知识产权商用软件MMST和切皮克，并引入人工智能到器件设计；系统应用包括毫米波雷达（回旋行波管）、无线输能系统（行波管）、微波能干燥系统（磁控管）；横向拓展至毫米波、太赫兹频段，太赫兹成像用于医学诊断，太赫兹通信用于保密通信、高速通信。
+- 科研与地位：每年到校科研经费接近2亿元，为学院最多；是国际上最大的真空器件研究中心，2023年成功举办行业顶级会议；方向共9个团队。
+- 学生出口：团队学生约1/3硕博连读、1/3去企业、1/3去研究所或其他（公务员等）；个人每年约2个硕士毕业、1个博士毕业。
+**田雨桐（在读博士，学生视角）**
+- 城市因素：成都是四川省会、国家中心城市、新一线城市、国家历史文化名城、古蜀文明发祥地、中国十大古都之一，宣传标语“成都都成”指梦想都成；电子信息产业发达，英特尔、华为、京东方等巨头汇聚，提供实践平台和就业资源。
+- 学校与专业：电子科技大学是我国电子信息人才培育的代名词，有电子信息博物馆记录我国第一台晶体管收音机的诞生，构建了最完整的电子信息学科群；电子科学与技术学科在第4轮学科评估中获A+、稳居全国第一，拥有五大国防特色学科。
+- 团队与个人研究：所在毫米波技术与系统应用团队在樊勇老师带领下，围绕微波毫米波理论与技术、天线理论与技术、元器件与电路、通信技术与系统、雷达成像技术与系统五大方向开展研究；本人从事毫米波雷达通信信号处理研究，可做雷达或无线通信系统，团队硕博毕业生实现100%就业率。
+- 校园生活与奖助：东湖钢琴小屋、2021年跨年300架无人机灯光秀拼出UESTC字样；奖助体系全覆盖、高额度、长周期，含国家奖学金、学业奖学金、专项奖学金、新生奖学金、校园地国家助学贷款、生源地助学贷款等。
+- 择校建议：先选研究团队再选导师，可从学院网站按兴趣选择团队，再进入团队网页找导师；导师信息不完整时可用IEEE Xplore和中国知网检索导师论文和指导研究生情况。
 # 达成共识
-**段院承诺**：今年计划举办夏令营活动，具体时间待定，相关信息将通过QQ群发布。
-&gt; 我们电子学院呢要计划就是今年会计划这个夏令营活动时间还待定，希望呢同学们感兴趣的话呢加入我们这个QQ群相关的信息呢，我们会到时会及时的发布。
+**段院承诺**：电子学院计划今年举办夏令营活动，时间待定，感兴趣的同学可加入QQ群，相关信息会及时发布。
+&gt; 段院原话：“我们电子学院呢要计划就是今年会计划这个夏令营活动时间还待定，希望呢同学们感兴趣的话呢加入我们这个QQ群相关的信息呢，我们会到时会及时的发布。”
+**主持人补充**：QQ群号为978499108，同学们可添加学院QQ群进行详细咨询和了解。
 # 待协调事项
-**夏令营活动安排**：事项描述为确定夏令营具体时间与形式并对外发布；对接人为段院；负责人为段院；预计完成时间未明确，后续沟通计划为通过QQ群（群号978499108）发布相关信息。</t>
+**夏令营活动组织**：电子学院计划今年举办夏令营，具体时间和形式尚未确定，需学院后续确定并发布。对接人：段院；负责人：段院；预计完成时间：未明确；后续沟通计划：相关信息将通过QQ群（978499108）发布。</t>
         </is>
       </c>
       <c r="D3" s="10" t="n">
-        <v>89.8</v>
+        <v>98.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>13887/3310</t>
+          <t>13887/4473</t>
         </is>
       </c>
     </row>
@@ -1324,36 +1362,35 @@
       <c r="C4" s="4" t="inlineStr">
         <is>
           <t># 复盘目标与结果概况
-本次复盘会为2023年度总结暨年终奖颁发年会，预期目标是总结公司年度发展状况、公布年终奖并评价员工。实际结果：年终奖总额226,000元，个人数额不一一公布；成本控制较差，实打实支出390万元（含人员工资、外援配音字幕租机器），利润率约24%或27%；最高工资两三人含年终奖到手20万元，平均工资到手1万多元；2023年人工支出相对提高25万元左右，年终奖比去年多13万元左右；干满一年12人；公司总量提升，但结余到账往下跑，有百来万没收回来；老板比去年少拿10万元左右，承担风险亏100万元。会议主要内容包括年度数据报告、年终奖发放标准说明、逐人评价员工、颁发5项奖项及抽奖。
+本次年会复盘2023年公司经营状况与员工表现。预期目标为总结全年发展、公布数据并发放年终奖与奖项。实际结果：年终奖总额226,000元，全年实打实支出390万元，利润率约24%或27%，成本控制差是最大问题；公司总量提升，但结余到账往下跑，还有百来万未收回，老板比去年少拿约10万元并承担亏损100万元。会上按短视频、执行、商务三部门逐一评价，肯定员工克服困难与整体表现，颁发最佳新人、最佳进步、后期独当一面、最佳员工、特别贡献奖共6人5项奖，并抽奖15个奖品。成本控制问题留待明年再议。
 # 亮点事项
-- **短视频账号数据增长显著**：视频号粉丝从700涨到8万，小红书从2000+到6.4万，抖音从2000+到5.7万，B站从3.1万到7.6万，关键转折点是6月20日第一条外出拍摄视频，成功原因是郭东辉破釜沉舟说服潘老师外出拍摄，并坚持不放弃。
-- **账号变现课程拍到7.5分（满分10）**，直播视频号4-5场，平均在线5000人+，为后续变现打下基础。
-- **刘腾宇评价最高**，职业性、专业性、纪律性好，年终奖因此拉一档；老板称其“干的活倒来倒去倒不到他头上”，沟通专业，迟到几乎没有。
-- **张扬作为公司邀请人才**，基本达到期待，老板称“2023年干到最有价值的一件事就把他招进来”。
-- **宋俊逸编导效率高**，第一次安排宁波两分钟宣传片稿子即获认可，“行家一出手便知有没有”。
-- **市井为后期技术标杆**，最好没有之一，能胜任课程、微电影、MV、快剪等各类后期。
+- 短视频账号实现显著涨粉：视频号粉丝从719人增至8万，小红书从2000+增至6.4万，抖音从2000+增至5.7万，B站从3.1万增至7.6万，关键转折点是6月20日第一条外出拍摄视频，源于郭东辉在潘老师多次劝退下坚持并**破釜沉舟说服潘老师外出拍摄**。
+- 账号变现课程自评达到7.5分（满分10），直播在视频号开展4-5场，平均在线人数5000人以上，为后续变现打下基础。
+- 商务部门实打实项目约300万元左右，基本达到预期，可能更多。
+- 员工评价中，刘腾宇获评职业性、专业性、纪律性最佳，客户反馈好，效率高；红叶子获政委高度评价，**既懂技术又懂英语且有把事情做好的精神**；张扬作为邀请人才，基本达到期待并带来改变。
+- 最具复用价值的经验：郭东辉坚持不放弃、以数据支撑决策（每晚8-9点刷直播间研究同行），以及说服自己比说服他人更难、**找准一个点破壳**的成长方法。
 # 不足事项
-- **成本控制非常差**：实打实支出390万元（含人员工资、外援配音字幕租机器），利润率仅24%或27%，老板承认“最大的癌症的问题，根源的问题就是老板的问题”，对关心关注不够、不够雷厉风行、问题未及时解决。
-- **公司结余到账往下跑**：有百来万没收回来，老板比去年少拿10万元左右，承担风险亏100万元。
-- **短视频重点项目未完成**：账号变现课程拍到7.5分（满分10），重点项目未完成；直播虽平均在线5000人+，但尚无课程可变现。
-- **加班严重**：后半年基本都在加班，很少正常休息，根因是老板未及时招合适人数的人员，属于判断失误。
-- **拍摄外援成本高**：钱德峰指出请外援价格与内部拍摄差很多，但公司内部凑不出人去按机位。
-- **后期与前期奖金不平衡**：老板承认后期比前期少一截，是唯一愿意解释的奖金侧重。
+- 成本控制非常差，是最大问题：全年实打实支出390万元（人员工资、外援配音字幕租机器），利润率仅24%或27%，非常不可观；根因是老板对成本关心或关注不够、不够雷厉风行，出现问题未及时解决。
+- 公司结余到账往下跑，还有百来万未收回，老板比去年少拿约10万元并承担亏损100万元。
+- 后期加班多，人不够是最大因素，根因是老板判断失误，未及时招合适人数的人员；外援成本高，部分因技术水平达不到。
+- 账号变现重点项目未完成，直播虽有人气但暂无课程可售，变现能力受限。
+- 拍摄人员安排困难，内部凑不出人按机位，需请外援且价格差很多；部分员工以没空、很忙、不想去为由推脱。
 # 改进计划
-- **成本控制问题**：明年开会再说，责任人无，时间无。
-- **短视频部门**：期待明年开始变现，老板将投入更大精力并给予足够重视，责任人无，时间无。
-- **执行部门**：期待老板更多进行组织协调，减少侵占休息时间，责任人无，时间无。
-- **商务部门**：老板将给予更多支持和帮助，责任人无，时间无。
-- **拍摄参与**：期待大家都能参与拍摄，明年往这个方向靠，责任人无，时间无。
-- **加班补贴**：年终奖中考虑补贴一两千元，已实施。</t>
+- 成本控制问题明年开会再议，责任人无，时间无。
+- 短视频部门期待明年开始变现，老板将投入更大精力并给予足够重视。
+- 执行部门期待老板更多进行组织协调，提高效率、减少休息时间侵占。
+- 老板自评今年给予支持、管理、关心不够，明年反思。
+- 鼓励全员参与拍摄，提升个人市场价值，明年向此方向靠拢。
+- 商务部门将获得老板更多支持与帮助，协助项目洽谈与打理。
+- 年终奖与奖项侧重后期，是唯一愿意解释的原因；加班补贴考虑一两千元。</t>
         </is>
       </c>
       <c r="D4" s="10" t="n">
-        <v>52.4</v>
+        <v>70</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>24562/1317</t>
+          <t>24562/1178</t>
         </is>
       </c>
     </row>
@@ -1896,29 +1933,30 @@
       <c r="C5" s="4" t="inlineStr">
         <is>
           <t># 全文摘要
-本次会议为小区业委会与物业公司就11项服务问题及业主大会召开事宜的专项协调会。业委会提出业主自发接龙约200人要求召开业主大会，表决是否更换物业；物业方称未接到正式沟通，且已掌握业委会违法证据，将于本月起诉，起诉期间业主大会可能无法召开。业委会认为诉讼不影响召开，坚持推进。业委会列举11项服务问题，物业逐项回应，多数归因于地产责任或费用不足。物业称业主欠费170多万，年收入100来万，人工成本100多万，每年亏损，要求先回款40万再维修；业委会认为服务不应滞后，双方形成恶性循环。物业称已与集团法务沟通，本月起诉业委会，理由包括选举违法、煽动业主、阻碍经营等；业委会成员表示将反诉，并可能集体起诉物业要求返还物业费。会议未达成一致，业委会表示将正常推进业主大会。
+本次专项讨论会由办事处组织，召集小区业委会（刘主任、邱主任等）与物业公司（吴经理等）就业主大会召开、物业去留及11项服务问题展开协调。业委会称业主自发接龙约200来户要求召开业主大会，建议尽快召开业主大会表决物业去留；物业方称事先未接到任何沟通，已与集团法务沟通，本月将正式起诉业委会，并称起诉期间业委会无表决权。业委会认为业委会成立之日即自动解除物业合同，坚持推进业主大会；物业方要求先结清欠费，业委会表示可起诉。双方未达成一致，业委会决定正常推进业主大会，物业方将依法起诉。业委会列举11项服务问题，物业方逐项回应，双方在服务责任、欠费及经营亏损等问题上分歧明显。
 # 要点梳理
-## 业主大会召开与表决
-- 业委会成员提出业主自发接龙约200人要求召开业主大会，表决是否更换物业。
-- 物业方称未接到正式沟通，且已掌握业委会违法证据，将于本月起诉，起诉期间业主大会可能无法召开。
-- 业委会认为诉讼不影响召开，坚持推进。
+## 业主大会召开与物业去留
+- 业主自发接龙约**200来户**要求召开业主大会，业委会建议尽快召开业主大会表决物业去留。
+- 物业方称事先未接到任何沟通，已与集团法务沟通，**本月将正式起诉业委会**，并称起诉期间业委会无表决权。
+- 业委会认为业委会成立之日即自动解除物业合同，坚持推进业主大会；物业方要求先结清欠费，业委会表示可起诉。
+- 双方未达成一致，业委会决定正常推进业主大会，物业方将依法起诉。
 ## 小区11项服务问题
-- 业委会列举11项问题：门柱灯未开启、内部水系未运行、迎宾水系未开、监控损坏（上月进贼无数据）、监控室无人值班、绿化维护差（死树）、北围墙铁皮缺口、民生配套（快递柜、直饮水、宽带、暖气）未落实、雨水倒灌（2019年起）、物业人员配比不足（办公室从10人减至4人，维修从5人减至2人）。
-- 物业回应：门柱灯因能耗成本未开，水系为地产质量问题，监控维修缺费用，绿化冬季无法更换，北围墙属红线外且涉违建，民生配套属地产前期配套，雨水倒灌为设计问题，人员不足因地产补亏款未结。
-## 物业费与经营状况
-- 物业称业主欠费170多万，年收入100来万，人工成本100多万，每年亏损，要求先回款40万再维修。
-- 业委会认为服务不应滞后，且业主因服务差不愿缴费，形成恶性循环。
-## 法律诉讼与反诉
-- 物业称已与集团法务沟通，本月起诉业委会，理由包括选举违法、煽动业主、阻碍经营等。
-- 业委会成员表示将反诉，并可能集体起诉物业要求返还物业费。</t>
+- 业委会列举11项问题：入户门柱灯从未开启；内部水系、迎宾水系从未开启；监控几乎全部损坏，上月进贼无监控数据；监控室24小时值班服务荒废；绿化维护缺失，去年死树多棵；北边围墙用烂铁皮遮挡且有缺口，存在安全隐患；民生配套（快递柜、直饮水、宽带、暖气开户）无进展；雨水倒灌严重，2019年起多次反映无果；物业人员配备不足，办公室从10人减至4人，维修从5人减至2人。
+- 物业方逐项回应：门柱灯因能耗成本高未开，承诺收上费用后修复；水系为地产质量问题，非物业责任；监控损坏因无费用，物业费欠费**170多万**、回款**40万**；绿化死亡因冬季无法更换；北边围墙属红线外且涉违建，物业无责；民生配套属地产前期配套；雨水倒灌为地产设计问题；人员配备不足因地产补亏款未结。
+## 物业费欠费与经营亏损
+- 物业方称业主欠费**170多万**、回款**40万**，账上一分钱没有，每年亏损，人工成本**100多万**、保护收入**100来万**。
+- 业委会认为物业服务无滞后性，不能先收钱再服务。
+- 物业方称业委会在业主群煽动不缴费、阻碍经营，将起诉。
+## 物业经理言语冲突
+- 业委会成员称物业经理曾对业主说“不交物业费就上你家吃饭”，物业经理否认并要求拿出录音。</t>
         </is>
       </c>
       <c r="D5" s="10" t="n">
-        <v>34.3</v>
+        <v>40.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21511/906</t>
+          <t>21511/1055</t>
         </is>
       </c>
     </row>
@@ -2167,59 +2205,73 @@
       <c r="C6" s="4" t="inlineStr">
         <is>
           <t># 研讨背景与议题
-本次圆桌论坛围绕具身智能领域的关键问题展开，包括大模型形态与硬件协同、世界模型定义、强化学习与模仿学习路线、数据采集与仿真等议题。与会者包括来自学术界和产业界的多位专家与博士生，如发言者2（主持人）、发言者3（机械与传感器方向）、发言者4（柔性体操作）、发言者5（强化学习）、发言者6（人工智能）、发言者7（计算机视觉与产业）、发言者8（强化学习初学者）、发言者9（强化学习）、发言者10（产业界）、发言者11（数据采集）等。各方观点碰撞，未形成统一结论。核心痛点包括：具身智能大模型形态如何收敛、世界模型是否需要3D inductive bias、强化学习与模仿学习最终路线、仿真数据与真实数据的比例、中国是否依赖英伟达生态等。
+本次圆桌论坛由发言者2主持，邀请多位学者与业界嘉宾围绕具身智能展开讨论，核心议题包括具身智能的形态与硬件期待、世界模型的定义与构建、强化学习与模仿学习的路线之争、数据采集与仿真等。发言者3（机械领域）提出具身智能形态是像人形还是像科幻片中的变形机器人，并提及机械智能概念；发言者4（薛寒博士）期待硬件寿命和可靠性高，因训练VLA时大规模真机评估机器人易碰撞损坏，现有工业机械臂并非为此设计，需要柔顺硬件结构；发言者2提到软硬件协同优化，松灵产品第二代比第一代在遥操和策略部署上更好，夹爪加凝胶可反馈触觉、更稳、摩擦力更好；发言者5（王岳老师）认为若大模型直通底层会消除硬件迭代可能性，模型至少应分上下层，大脑不变、小脑适应肢体；发言者6（赵昊老师）认为从第一性原理出发，人形机器人与特种机器人都会存在，如车厂、微电子制造厂已有97%以上自动化。关于世界模型，发言者8（志龙）从强化学习角度回溯到1990-91年Sutton的Dyna-Q，定义为黑盒输出下一时刻观测，可交互是首要要素，并提到18年Schmidhuber或LeCun定义的世界模型有表征和转移两个组件；发言者7（赵昊老师）认为CV界追求重建物理世界，可作为RL中world models的工具，但三维计算机视觉技术栈长，RL博士生难以完全学习，导致RL领域不关注三维表征，并讨论inductive bias，认为数据多时需要的inductive bias少、数据少时需要的多，梦想写一篇paper叫data bias trade off；发言者5（王岳老师）举例刺客信条游戏与真实世界跳楼，认为一个世界模型无法同时建模两个dynamics，因为输入相同输出不同是歧义问题，policy可能可以，world model做不到；发言者9（薛寒博士）认为CV的world model带3D inductive bias，强化学习的world model不带，但强化学习的world model是任务导向的，不一定需要CV那样的模型；发言者9与发言者5讨论不同物理结构是否能有统一表征，发言者5认为M个独立模型比一个高维可控模型更简单。关于强化学习与模仿学习路线，发言者2提到强化学习曾达顶峰但sim-to-real落地有困难，模仿学习如ALOHA收集海量数据展现可落地性质，但派零团队收集近万小时数据后仍看到模仿学习瓶颈；发言者10（业界嘉宾）表示公司采用模型强化加机理融合方式，监督学习动作空间大、数据分布不足，强化学习依赖仿真环境，纯强化学习不能很好sim-to-real迁移，需要限制决策空间和任务设定，上层用强化学习决策，底层用MPC或DWA等传统方法；发言者9（薛寒博士）同意混合方式，认为复杂任务应先模仿后强化，单独模仿不行除非任务简单，单独强化也不行除非任务足够简单；发言者5（王岳老师）认为PID有反馈，可拿反馈作为reward，强化必然走得成；发言者11（静波）认为IL和RL没有本质冲突，只是想要运动先验，有数据用模仿学习，没数据用强化学习生成。关于数据采集与仿真，发言者11（杨立新）分享数据质量经验，Open X等数据集相机视角不固定影响policy表现，采集时控制视角和标定，手眼标定仍是问题，Open X缺少物体运动信息，Oakink采集时记录物体运动但设备有限只能采集刚体和关节体；发言者4（薛寒博士）all in reward采集路线，柔性体操作如叠衣服难以仿真，需要IPC等先进图形学技术，算力要求高、全世界能做的人少如UCLA蒋正凡老师，进展慢，reward采集是低成本方案，现实生活是最好的仿真器，终极形态是脑机接口或机电方式无感采集，现阶段可穿戴设备，互联网视频数据与机器人所需数据不同如叠衣服视频是平铺状态而机器人需要从混乱状态展平；发言者2提到ego4d数据集洗了三个月，互联网数据质量低、数据金字塔最底层，仿真数据分传统仿真和强化生成，SIM数据加少量真机数据可显著提升成功率如300条SIM数据加20条真机数据；发言者7（赵昊老师）认为用真实数据还是仿真数据看成本，自动驾驶中真机数据收集困难，提出加入无标注真实数据，2025年主题是推广大规模利用无标注数据如segment anything和depth anything；发言者7提到国产仿真系统，宋应公司赌卡脖子做国产替代，但工作人员不会直接touch这个生意。
 # 核心观点
-**议题一：具身智能大模型形态与硬件协同**
-- 发言者2提出具身智能分为大脑大模型、小脑大模型和端到端模型，派灵收集6000多小时数据训练端到端模型。
-- 发言者3从机械角度提问具身形态收敛方向，提到机械智能、软手摩擦与顺应性。
-- 发言者4强调硬件寿命和可靠性，指出现有工业机械臂不适合大规模真机评估。
-- 发言者2认为软硬件协同优化，松灵二代产品在遥操和策略部署上优于一代，凝胶夹爪可反馈触觉、更稳。
-- 发言者5认为大模型不应从上到下完全统一，大脑和小脑应分离，小脑需适应肢体变化。
-- 发言者6认为人形机器人和特种机器人将共存，人形机器人因环境设计而存在，特种机器人在工业中已大量应用（如车厂、微电子制造厂97%以上自动化）。
-**议题二：世界模型的定义与实现**
-- 发言者2提出世界模型是否需重构所有像素或3D，强化学习领域关注action带来的变化。
-- 发言者8从强化学习角度认为世界模型第一要素是可交互，需物理规律，可引入3D信息。
-- 发言者7认为CV界追求重建物理世界，可作为RL世界模型的工具，但当前不成熟，RL领域不关注三维表征。
-- 发言者5提出世界模型可能无法统一，因为存在歧义问题，policy可能统一。
-- 发言者9认为强化学习的world model是任务导向的，CV的world model不必要，但可考虑统一表征。
-**议题三：强化学习与模仿学习的路线**
-- 发言者2提出强化学习与模仿学习是两大流派，派零团队收集近万小时数据后仍看到模仿学习瓶颈。
-- 发言者10介绍公司采用模型强化加机理融合，监督学习数据分布不足，强化学习依赖仿真环境，需限制决策空间。
-- 发言者9认为复杂任务应先模仿后强化，单独模仿或强化都不行。
-- 发言者5认为PID必有反馈，可作reward。
-- 发言者11认为模仿学习和强化学习不冲突，可获取运动先验。
-**议题四：数据采集与仿真**
-- 发言者2提出scaling law涉及数据采集，仿真与真机数据流派对抗。
-- 发言者11介绍orkin数据采集经验，强调视角和标定重要性，记录物体运动。
-- 发言者4认为reward采集是低成本方案，柔性体仿真需先进图形学技术，算力要求高，进展慢。
-- 发言者2提到ego4d数据清洗耗时三个月，仿真数据加少量真机数据可显著提升成功率。
-- 发言者7认为真实数据与仿真数据选择看成本，2025年应推广无标注数据。
+### 具身智能的形态与硬件期待
+- 发言者3（机械领域）提出具身智能形态问题：是像人形机器人，还是像科幻片中可变形的大方块（如《星际穿越》），并提及机械领域中的机械智能概念，如软手通过摩擦和顺应性实现误差较大时仍能抓牢。
+- 发言者4（薛寒博士）期待硬件寿命和可靠性高，因训练VLA时大规模真机评估，机器人易因碰撞损坏，难以可靠scale up，现有工业机械臂并非为此设计，需要柔顺硬件结构。
+- 发言者2提到软硬件协同优化，松灵产品第二代比第一代在遥操和策略部署上更好，夹爪加凝胶可反馈触觉、更稳、摩擦力更好。
+- 发言者5（王岳老师）认为若大模型直通底层会消除硬件迭代可能性，新硬件出现可能需要完全重新训练，模型至少应分上下层，大脑不变、小脑适应肢体。
+- 发言者6（赵昊老师）认为从第一性原理出发，人形机器人会存在（如双足或轮式加灵巧手），特种机器人也大量存在，如车厂、微电子制造厂已有97%以上自动化。
+### 世界模型的定义与构建
+- 发言者2提到赵昊老师有经典图从各维度评价世界模型，CV角度讨论是否需要重构pixel、3D，ACL上已有4D world model投稿。
+- 发言者8（志龙）从强化学习角度，世界模型概念可回溯到1990-91年Sutton的Dyna-Q，定义为黑盒输出下一时刻观测，可交互是首要要素，并提到18年Schmidhuber或LeCun定义的世界模型有表征和转移两个组件。
+- 发言者7（赵昊老师）认为CV界追求重建物理世界，可作为RL中world models的工具，但三维计算机视觉技术栈长，RL博士生难以完全学习，导致RL领域不关注三维表征。
+- 发言者7讨论inductive bias，认为数据多时需要的inductive bias少、数据少时需要的多，梦想写一篇paper叫data bias trade off。
+- 发言者5（王岳老师）举例刺客信条游戏与真实世界跳楼，认为一个世界模型无法同时建模两个dynamics，因为输入相同输出不同是歧义问题，policy可能可以，world model做不到。
+- 发言者9（薛寒博士）认为CV的world model带3D inductive bias，强化学习的world model不带，但强化学习的world model是任务导向的，不一定需要CV那样的模型。
+- 发言者9与发言者5讨论不同物理结构是否能有统一表征，发言者5认为M个独立模型比一个高维可控模型更简单。
+### 强化学习与模仿学习的路线之争
+- 发言者2提到强化学习曾达顶峰但sim-to-real落地有困难，模仿学习如ALOHA收集海量数据展现可落地性质，但派零团队收集近万小时数据后仍看到模仿学习瓶颈。
+- 发言者10（业界嘉宾）表示公司采用模型强化加机理融合方式，监督学习动作空间大、数据分布不足，强化学习依赖仿真环境，纯强化学习不能很好sim-to-real迁移，需要限制决策空间和任务设定，上层用强化学习决策，底层用MPC或DWA等传统方法。
+- 发言者9（薛寒博士）同意混合方式，认为复杂任务应先模仿后强化，单独模仿不行除非任务简单，单独强化也不行除非任务足够简单。
+- 发言者5（王岳老师）认为PID有反馈，可拿反馈作为reward，强化必然走得成。
+- 发言者11（静波）认为IL和RL没有本质冲突，只是想要运动先验，有数据用模仿学习，没数据用强化学习生成。
+### 数据采集与仿真
+- 发言者11（杨立新）分享数据质量经验，Open X等数据集相机视角不固定影响policy表现，采集时控制视角和标定，手眼标定仍是问题，Open X缺少物体运动信息，Oakink采集时记录物体运动但设备有限只能采集刚体和关节体。
+- 发言者4（薛寒博士）all in reward采集路线，柔性体操作如叠衣服难以仿真，需要IPC等先进图形学技术，算力要求高、全世界能做的人少如UCLA蒋正凡老师，进展慢，reward采集是低成本方案，现实生活是最好的仿真器，终极形态是脑机接口或机电方式无感采集，现阶段可穿戴设备，互联网视频数据与机器人所需数据不同如叠衣服视频是平铺状态而机器人需要从混乱状态展平。
+- 发言者2提到ego4d数据集洗了三个月，互联网数据质量低、数据金字塔最底层，仿真数据分传统仿真和强化生成，SIM数据加少量真机数据可显著提升成功率如300条SIM数据加20条真机数据。
+- 发言者7（赵昊老师）认为用真实数据还是仿真数据看成本，自动驾驶中真机数据收集困难，提出加入无标注真实数据，2025年主题是推广大规模利用无标注数据如segment anything和depth anything。
+- 发言者7提到国产仿真系统，宋应公司赌卡脖子做国产替代，但工作人员不会直接touch这个生意。
 # 达成共识与解决方案
-**关于大模型形态**：发言者5提出大脑与小脑分离，小脑需适应肢体变化；发言者6认为人形机器人和特种机器人将共存。
-**关于世界模型**：发言者7认为CV界追求重建物理世界，可作为RL世界模型的工具；发言者8认为世界模型第一要素是可交互，需物理规律；发言者9认为强化学习的world model是任务导向的。
-**关于策略学习**：发言者9认为复杂任务应先模仿后强化，单独模仿或强化都不行；发言者10认为监督学习与强化学习各有缺点，需融合；发言者11认为模仿学习和强化学习不冲突，可获取运动先验。
-**关于数据**：发言者4认为reward采集是低成本方案，大自然是最好的仿真器；发言者2认为仿真数据加少量真机数据可显著提升成功率；发言者7认为真实数据与仿真数据选择看成本，2025年应推广无标注数据。
+### 具身智能的形态与硬件
+- **具身智能是软硬件协同优化的范式**，发言者2以松灵产品两代迭代和夹爪加凝胶为例，说明硬件改进能提升算法部署效果。
+- 发言者5（王岳老师）提出模型应分上下层，**大脑不变、小脑适应肢体**，避免新硬件出现时完全重新训练。
+- 发言者6（赵昊老师）认为**人形机器人与特种机器人将并存**，人形因现实环境为人设计而存在，特种机器人已在车厂、微电子制造厂实现97%以上自动化。
+### 世界模型
+- 发言者8（志龙）从强化学习角度，世界模型首要要素是**可交互**，最终目标是学策略。
+- 发言者7（赵昊老师）认为CV界追求重建物理世界，可作为RL中world models的工具，但三维表征技术栈长，RL领域难以完全学习。
+- 发言者7提出**数据量决定inductive bias需求**：数据多时需要的inductive bias少，数据少时需要的多。
+- 发言者5（王岳老师）认为**world model难以统一，policy可能统一**，因输入相同输出不同是歧义问题。
+### 强化学习与模仿学习
+- 发言者10（业界嘉宾）提出**模型强化加机理融合**方式，上层用强化学习决策，底层用MPC或DWA等传统方法。
+- 发言者9（薛寒博士）认为**复杂任务应先模仿后强化**，单独模仿或单独强化均不可行，除非任务足够简单。
+- 发言者5（王岳老师）认为**PID有反馈，可拿反馈作为reward**，强化必然走得成。
+- 发言者11（静波）认为**IL和RL没有本质冲突**，只是想要运动先验，有数据用模仿学习，没数据用强化学习生成。
+### 数据采集与仿真
+- 发言者11（杨立新）强调**数据质量关键在于视角控制和标定**，并记录物体运动信息。
+- 发言者4（薛寒博士）认为**reward采集是低成本方案**，现实生活是最好的仿真器，终极形态是脑机接口或机电方式无感采集。
+- 发言者2提出**仿真数据加少量真机数据可显著提升成功率**，如300条SIM数据加20条真机数据。
+- 发言者7（赵昊老师）提出**2025年应推广大规模利用无标注真实数据**，如segment anything和depth anything。
 # 未决分歧与后续探索
-**未决分歧**：
-- 具身智能的最终形态是人形还是特种机器人？
-- 世界模型是否需要3D inductive bias？
-- 强化学习与模仿学习最终路线如何？
-- 仿真数据与真实数据的比例如何确定？
-- 中国是否依赖英伟达生态，国产仿真系统能否支持？
-**后续探索**：
-- 发言者7提出2025年应推广无标注数据，如segment anything和depth anything。
-- 发言者4提出终极数据采集形态可能是脑机接口或机电方式，现阶段可穿戴式设备。
-- 发言者2提出仿真数据与真机数据结合，可配少量真机数据训练较好policy。
-- 发言者7提到国产仿真系统产业问题，宋应等在做国产替代，但工作人员不会直接touch。
-- 跟进人：未明确。</t>
+### 未决分歧
+- 具身智能的形态最终会收敛成什么样子？发言者3（机械领域）提出，未达成共识。
+- 世界模型是否需要3D inductive bias？发言者7（赵昊老师）认为数据决定，发言者9（薛寒博士）认为强化学习的世界模型是任务导向的，不一定需要CV那样的模型，未达成共识。
+- 强化学习和模仿学习最终路线如何？发言者10（业界嘉宾）主张混合方式，发言者9（薛寒博士）认为应先模仿后强化，发言者5（王岳老师）认为强化必然走得成，未达成共识。
+- 如何保证数据采集的高质量？发言者11（杨立新）强调视角控制和标定，发言者4（薛寒博士）主张reward采集，未达成共识。
+- 未来是否强依赖英伟达生态，还是可以有国产仿真产品？发言者7（赵昊老师）提到宋应公司赌卡脖子做国产替代，但工作人员不会直接touch这个生意，未明确。
+### 后续探索
+- 发言者7（赵昊老师）梦想写一篇paper叫data bias trade off，探讨数据量与inductive bias的关系，跟进人未明确。
+- 发言者4（薛寒博士）认为需要更多人投入真正准确的物理仿真技术（如IPC），以解决柔性体问题，跟进人未明确。
+- 发言者4（薛寒博士）提出终极数据采集形态是脑机接口或机电方式无感采集，现阶段可穿戴设备，跟进人未明确。</t>
         </is>
       </c>
       <c r="D6" s="10" t="n">
-        <v>48.4</v>
+        <v>90.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>21458/2059</t>
+          <t>21458/5350</t>
         </is>
       </c>
     </row>
@@ -2718,42 +2770,46 @@
       <c r="C7" s="4" t="inlineStr">
         <is>
           <t># 庭审概况
-本案系上诉人国家开发银行与被上诉人云南东源电力股份有限公司、云南东源曲靖电力有限公司、招银金融租赁有限公司金融借款合同纠纷一案，因不服云南省高级人民法院2018云民初88号民事判决，向最高人民法院提起上诉。本案由审判员李少平担任审判长，与审判员魏文超、黄年、王海峰、葛洪涛组成合议庭，法官助理张瑞，依法公开开庭审理。庭审中，各方当事人核对身份无异议，法庭告知诉讼权利义务，并围绕三个争议焦点展开法庭调查与辩论。经合议庭评议并主持调解，各方当事人自愿达成调解协议，法院予以确认并出具调解书。
+本案系上诉人国家开发银行不服云南省高级人民法院（2018）云民初88号民事判决，向最高人民法院提起上诉的金融借款合同纠纷二审案件，被上诉人为云南东源电力股份有限公司、云南东源曲靖电力有限公司及招银金融租赁有限公司。合议庭由审判长李少平与审判员魏文超、黄年、王海峰、葛洪涛组成，法官助理张瑞。庭审核对各方出庭人员身份后，围绕三个争议焦点展开法庭调查与辩论：国开行对案涉设备是否享有抵押权（善意取得）、一审判决对案涉借款罚息复息的计算及起算日期是否认定错误、东源煤电及东源煤业是否应连带给付违约金。合议庭多次到案发地调查走访并召开庭前会议，休庭评议后提出调解方案，各方均无异议，诉讼代理人依次在调解协议正式文本上签字，合议庭予以确认，庭后出具调解书。
 # 原告诉称与被告辩称
-本案系二审程序，各方当事人身份为上诉人国家开发银行，被上诉人云南东源电力股份有限公司、云南东源曲靖电力有限公司、招银金融租赁有限公司。庭审中，各方围绕三个争议焦点发表辩论意见，未单独陈述诉讼请求或答辩意见，具体意见详见争议焦点部分。
+上诉人国家开发银行上诉请求：撤销一审判决相关判项，改判其对案涉设备享有抵押权，并支持其利息、罚息、复利及违约金主张。事实与理由：国开行已按央行规定对抵押人曲靖电力公司进行融资租赁登记查询且无记录，设备为无唯一标识码的通用设备，核查义务仅限于抵押人，已尽审慎义务构成善意取得；东源煤电利息支付截止2017年12月20日，2018年6月13日发函要求当日归还，罚息应自该日起算，复利按合同第6条约定计算；依借款合同第24条第3项，东源煤电未配合办理账户管理及柜台前移手续构成违约，应支付千分之一违约金。被上诉人东源煤电、东源煤业、曲靖电力共同答辩：2015年12月2日邮件中两家公司抵押设备名称完全相同且以红色标注，国开行应尽注意义务；合同约定限期偿还而非立即偿还，且复利不应以罚息为基数；国开行未举证证明违约事实，且依约应先限期纠正。被上诉人招银租赁答辩：国开行未在抵押时点（2015年12月）查询人行征信中心，且东源煤电系借款人及抵押人全资控股母公司，国开行对其有审查义务，不构成善意。
 | 方 | 诉讼请求/答辩意见 | 事实与理由 |
 | --- | --- | --- |
-| 上诉人（国开行） | 请求撤销一审判决，改判支持其利息、罚息、复利及违约金主张 | 已按央行规定查询融资租赁系统，审查义务仅限于抵押人曲靖电力公司；设备为通用设备无唯一识别码，无法进一步核查；已尽审慎义务，构成善意取得 |
-| 被上诉人（东源煤电等） | 请求驳回上诉，维持原判 | 2015年12月2日邮件已告知设备存在融资租赁并以红色标注，国开行未尽注意义务；贷款提前到期应给合理期限；罚息不应作为复利计算基数；国开行未举证证明违约行为 |
-| 被上诉人（招银租赁） | 请求驳回上诉，维持原判 | 国开行未在抵押时点查询融资租赁系统，不构成善意；东源煤电出资行为系无权处分；罚息不应作为复利计算基数 |
+| 上诉人（原审原告） | 请求撤销一审判决相关判项，改判其对案涉设备享有抵押权，并支持其利息、罚息、复利及违约金主张 | 已按央行规定对抵押人曲靖电力公司进行融资租赁登记查询且无记录，设备为无唯一标识码的通用设备，核查义务仅限于抵押人，已尽审慎义务构成善意取得；东源煤电利息支付截止2017年12月20日，2018年6月13日发函要求当日归还，罚息应自该日起算，复利按合同第6条约定计算；依借款合同第24条第3项，东源煤电未配合办理账户管理及柜台前移手续构成违约，应支付千分之一违约金 |
+| 被上诉人（原审被告）东源煤电、东源煤业、曲靖电力 | 请求驳回上诉，维持原判 | 2015年12月2日邮件中两家公司抵押设备名称完全相同且以红色标注，国开行应尽注意义务；合同约定限期偿还而非立即偿还，且复利不应以罚息为基数；国开行未举证证明违约事实，且依约应先限期纠正 |
+| 被上诉人（原审被告）招银租赁 | 请求驳回上诉，维持原判 | 国开行未在抵押时点（2015年12月）查询人行征信中心，且东源煤电系借款人及抵押人全资控股母公司，国开行对其有审查义务，不构成善意 |
 # 举证与法庭调查
-**一、证据与质证意见**
-- 国开行提交2018年9月对曲靖电力公司的融资租赁查询证书，招银租赁质证认为该查询证书不符合要求，依据2014年93号中国人民银行关于融资租赁登记系统的规定，国开行应在抵押时点（2015年12月）进行查询。
-- 国开行提交证据第54页、58页，显示东源煤电公司、曲靖电力公司对案涉设备的权属证明材料和股东会决议，证明设备所有权属曲靖电力公司。
-- 招银租赁提交回租设备清单（证据第7页），仅载明设备名称和生产厂家，未提及型号；国开行质证认为该清单记载出厂日期为2012年3月1日，而现场调查核实抵押设备铭牌生产日期均在2013年以后，无法认定为同一设备。
-- 招银租赁提交2013年和2015年审计报告（证据第82页、95页），载明曲靖电力公司注册资本4亿元且已实缴，国开行据此主张招银租赁应当知道设备出资情况。
-- 国开行提交融资租赁登记信息核查表（证据第108页），显示曲靖电力公司名下无融资租赁登记，主张已尽审慎义务。
-**二、法官询问要点**
-- 审判长询问各方对中国人民银行征信中心融资租赁登记的性质及法律后果的理解。
-- 合议庭成员询问融资租赁登记系统的查询方式，国开行称仅能按单位查询，招银租赁称可按公司名称或设备查询。
-- 询问案涉5套设备是否登记唯一识别码，招银租赁称设备为种类物，无唯一识别码，未登记。
-- 询问国开行贷款前风控资料是否要求必须查询融资租赁系统并保留未查询到结果的记录，国开行称无此内部规定。
-- 询问各方对融资租赁司法解释第9条第2款举证责任分担的理解。
-- 询问各方对因不同登记机构产生登记信息冲突的意见和建议。
-**三、双方辩论的争议焦点**
-- **争议焦点一：国开行是否尽到融资租赁查询义务构成善意取得。** 国开行主张已按央行规定查询融资租赁系统，但未保留查询记录，审查义务仅限于抵押人曲靖电力公司，设备为通用设备无唯一识别码，无法进一步核查；东源方主张2015年12月2日邮件已告知设备存在融资租赁并以红色标注，国开行未尽注意义务；招银租赁主张国开行未在抵押时点查询，不构成善意，且东源煤电出资行为系无权处分。
-- **争议焦点二：一审判决对案涉借款罚息复息的计算及起算日期是否认定错误。** 国开行主张利息自2017年12月21日计算至2018年6月12日，合计21,795,727.68元；罚息自2018年6月13日计算至2019年2月19日，合计41,050,579.57元；复利自2018年3月21日计算至2019年2月19日，合计1,918,206.23元。东源方认为贷款提前到期应给合理期限，且罚息不应作为复利计算基数，复利再计算复利无合同依据。
-- **争议焦点三：东源煤电东源煤业是否应当连带给付违约金。** 国开行主张依据借款合同第24条第3项，被上诉人违约应支付千分之一违约金，且未配合办理账户管理及柜台前移手续；东源方认为国开行未举证证明违约行为，且未按合同约定发出限期纠正函，故违约金主张不成立。
+**证据与质证意见**
+- 国开行提交2015年12月2日东源煤电发送的邮件及《东源公司融资情况统计表》，主张表中招银租赁抵押物为恩洪电厂设备资产且已登记，国开行抵押物为恩洪电厂设备在建工程正在办理，两者设备完全不同，不能得出已告知的结论；东源方反驳称该邮件系抵押合同签订（2015年12月22日）前发出，两家公司抵押设备名称完全相同且以红色标注，国开行应尽注意义务。
+- 国开行提交证据54页、58页权属证明及股东会决议，主张显示所有权属曲靖电力公司，已尽审慎义务；招银租赁主张东源煤电出资行为系无权处分，招银租赁2012年已取得设备所有权。
+- 招银租赁提交证据第7页回租设备清单，主张载明设备名称、生产厂家；国开行反驳称清单无型号，出厂日期2012年3月1日，而现场调查铭牌生产日期均在2013年以后，看不出同一设备。
+- 招银租赁提交证据82页、95页审计报告，主张载明曲靖电力公司注册资本4个亿且实缴；国开行据此主张招银租赁应知道设备出资情况。
+- 国开行提交2018年9月融资租赁查询证书，主张已尽查询义务；招银租赁反驳称该证书不符合2014年93号文规定，国开行应提供2015年12月抵押时点的查询结果。
+- 东源方提交融资情况统计表及邮件截屏，主张两家公司抵押设备名称完全相同且用红色标注；国开行反驳称统计表中招银租赁抵押类型为不动产抵押，与融资租赁是两个法律概念。
+**法官询问要点**
+- 合议庭询问各方如何理解人行征信中心融资租赁登记的性质及法律后果：国开行认为系行业内强制性规范，目的是防范金融风险；东源方认为系行业指导性规范，非强制性，不当然产生物权后果；招银租赁认为系权利公示，可能产生对抗效力，但不影响所有权设立转移等法定效果。
+- 合议庭询问央行融资租赁登记系统的查询方式：国开行称目前只能使用一种查询方式（查询单位）；招银租赁称可通过公司名称或设备查询，设备查询涉及种类物区分问题。
+- 合议庭询问案涉5套设备登记时识别码是否登记清楚：东源方称设备交付时系种类物，无唯一识别码，未登记。
+- 合议庭询问国开行贷款前审查内部是否有规定必须查询融资租赁系统、未查到也要保留记录：国开行称按央行规定必须查询，但未查到记录，未保留筛查记录，内部无此规定。
+- 合议庭询问融资租赁登记系统设备唯一标识码是否必填项：招银租赁称不是必填项，案涉设备无唯一识别码，无法填写；发电机铭牌只有型号和参数，15万伏发电机只要是上海电气出厂，铭牌都一样。
+- 合议庭询问违反查询规范多大程度导致司法解释第9条第2款法律后果、是基本查询义务还是全面审慎义务：国开行认为是基本查询义务，针对抵押人，审慎调查义务已完成；招银租赁认为是严格义务，银行未查询即不构成善意，本案中恩洪矿区发电厂只有两台设备，综合信息能确定5台设备唯一性，已足够引起国开行注意。
+- 合议庭询问若银行通过其他途径了解到动产属融资租赁物，是否相当于已掌握风控情况：国开行称基本义务必须做，查询动作完成即可得出结论；东源方称金融机构接受抵押物前需确权查询，若通过其他渠道知道可能存在租赁，仍应查询；招银租赁称通过其他方式获知后仍应通过央行系统查询，因为其他方式无法证明，只有确定标准才能衡量善意。
+- 合议庭询问融资租赁司法解释第9条第2款举证责任如何分担：国开行称按谁主张谁举证原则，争议焦点是查询范围和主体；招银租赁称第9条列举1、2、4项由出租人举证，第3项由第三人（国开行）证明办理抵押时查询了央行系统，国开行应扩展调查东源煤电，查询购买合同购买发票。
+- 合议庭询问不同登记机构产生的登记信息冲突有何意见和建议：国开行称人行融资租赁系统和工商动产抵押登记信息不统一导致矛盾，是系统问题，建议系统整合；东源方称系统整合或衔接有必要，但提不出成熟建议；招银租赁建议从立法层面统一要求、发挥行业协会作用形成行业惯例、从操作和技术层面实现信息互通，企业主体也应主动登记。
+**双方辩论的争议焦点**
+- 争议焦点一：国开行对案涉设备是否享有抵押权（善意取得）。国开行主张已按央行规定对抵押人曲靖电力公司进行融资租赁登记查询且无记录，设备为无唯一标识码的通用设备，核查义务仅限于抵押人，已尽审慎义务构成善意取得；东源方反驳称2015年12月2日邮件中两家公司抵押设备名称完全相同且以红色标注，国开行应尽注意义务；招银租赁主张国开行未在抵押时点（2015年12月）查询人行征信中心，且东源煤电系借款人及抵押人全资控股母公司，国开行对其有审查义务，不构成善意。
+- 争议焦点二：一审判决对案涉借款罚息复息的计算及起算日期是否认定错误。国开行主张利息自2017年12月21日计算至2018年6月12日合计21,795,727.68元，罚息自2018年6月13日计算至2019年2月19日（破产受理日）合计41,050,579.57元，复利自2018年3月21日计算至2019年2月19日合计1,918,206.23元；东源方反驳称合同约定限期偿还而非立即偿还，且复利不应以罚息为基数，合同第6条第4款仅表述为利息未提罚息，并援引最高法2015年、2016年判例。
+- 争议焦点三：东源煤电、东源煤业是否应连带给付违约金。国开行主张依借款合同第24条第3项，东源煤电未配合办理账户管理及柜台前移手续构成违约，应支付千分之一违约金；东源方反驳称国开行未举证证明违约事实，且依约应先限期纠正，国开行从未发出书面函件。
 # 庭审结果
-本案争议焦点为：一、国开行是否尽到融资租赁查询义务构成善意取得；二、一审判决对案涉借款罚息复息的计算及起算日期是否认定错误；三、东源煤电东源煤业是否应连带给付违约金。经合议庭评议并主持调解，各方当事人对调解方案均无异议，自愿达成调解协议，法院予以确认并出具调解书。调解方案主要内容：国开行对东源煤电的债权扣除破产清偿本金外，利息罚息复利合计6474.4513万元；招银租赁对涉案6项设备享有所有权，债权数额1377.4137万元；国开行对93项设备有抵押权；案涉全部发电设备整体盘活处置，变现价款双方各得50%，费用各担50%；若司法变现不能，双方放弃设备权益；东源曲靖电力承担管理费用并无条件配合司法处置；一审判决第2项第4项无争议；诉讼费用按约定分担。</t>
+本案争议焦点为：一、国开行对案涉设备是否享有抵押权（善意取得）；二、一审判决对案涉借款罚息复息的计算及起算日期是否认定错误；三、东源煤电、东源煤业是否应连带给付违约金。合议庭休庭评议后提出调解方案，各方均无异议，自愿达成调解协议，合议庭予以确认，庭后出具调解书。调解方案主要内容：国开行对东源煤电债权扣除破产已清偿本金外，利息、罚息、复利三项共计6474.4513万元；确定招银租赁对涉案6项设备享有所有权（对应债权1377.4137万元）、国开行对93项设备有抵押权，双方对案涉全部发电设备整体盘活处置，调解书生效后20日内由国开行向一审法院提出执行申请启动司法处置，变现价款双方各得50%、费用各担50%；未实现债权待执行法院出具体本裁定后按破产重整计划预留方案实现，若破产管理人不予纳入预留方案由东源煤电按有担保清偿方案清偿，若司法变现不能双方放弃权益由东源曲靖电力自主生产经营；案涉设备管理费用由东源曲靖电力承担并无条件配合司法处置；各方对一审判决第2项、第4项无争议按判项确认；一审诉讼费用中国开行诉请部分按一审判决执行、招银租赁诉请部分由国开行承担，二审诉讼费用由国开行和东源煤电各承担50%；协议签订后各方就本案问题不再存在任何争议。</t>
         </is>
       </c>
       <c r="D7" s="10" t="n">
-        <v>60.2</v>
+        <v>128</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>28485/2336</t>
+          <t>28485/4107</t>
         </is>
       </c>
     </row>
@@ -2910,40 +2966,36 @@
       <c r="C8" s="4" t="inlineStr">
         <is>
           <t># 项目概况
-原占比二玉米面加工厂项目中期验收会议于验收组提前介入（18、19号）并召开首次会议（20号）后举行。截至会议时，卢萨卡点除带料调试外的全部验收工作已完成，蒙泽点已完成全部验收，姆皮卡点尚未开展。验收分内业和外业检查，专业覆盖建筑工程、安装工程、机电设备。内业方面，管理组和技术组按合同组建执行团队，编制施工组织计划、管理计划、实施细则和专项预案，内业资料基本满足标准规范要求，但存在分类整理不规范、质检和管理机构验收签字不规范等问题，竣工文件基本达到组卷成册要求，但资料分散需汇总至卢萨卡。外业方面，建筑部分原材料集中采购，预制构件、广场地砖从卢萨卡200多公里外采购，整体品质良好；安装部分钢结构材料国内定制，施工工艺和外观质量满足规范；设备部分由中粮西安设计院定制三套成套设备，厂家高峰期派十几名人员现场指导，蒙泽点已投料试运行，产能符合设计指标。财务验收专家查阅财务资料，账户设置、资金往来、银行开户等符合财务处理规范和标准。合作局领导要求重视混凝土路面开裂问题，分析原因并制定整改方案，在出报告前完成整改并复核；要求做好成品保护，及时修补破损。林总要求按合同和标准仔细验收，提醒注意交通安全和疫情防控。
+本次会议为原占比二玉米面加工厂项目中期验收会，验收组于18号、19号提前介入项目前期摸排，20号召开首次会议，工作分内业检查和外业检查，专业方向涵盖建筑工程、安装工程和设备机电设备。截至会议当天，卢萨卡点除带料加工调试外的所有验收工作已完成，蒙泽点验收工作全部完成，并利用带料调试厂家人员在场顺带完成全流程试生产及外方操作手培训；某皮卡点现场验收尚未开展，内业资料已提前送至卢萨卡点。内业检查基本满足规范标准，但分类整理和签字规范性需完善；外业检查中建筑、钢结构、设备安装均满足要求，工艺设备投料试运行正常、产能符合设计指标。财务检查符合规范，无挪用资金情况。会议提出人员履约、内业资料、现场整改等多项整改要求，合作局领导强调混凝土路面开裂成因分析及整改闭环，公司领导要求注意交通安全。
 # 进度追踪
 | 模块 | 进展 | 状态 |
 | --- | --- | --- |
-| 卢萨卡点验收 | 除带料调试外的全部验收工作已完成，内业外业检查均开展 | ✅已完成 |
-| 蒙泽点验收 | 全部验收工作已完成，带料调试顺带完成，设备投料试运行正常，产能符合设计指标 | ✅已完成 |
-| 姆皮卡点验收 | 尚未开展，内业资料已提前拿到卢萨卡点 | 🔄进行中 |
-| 内业资料 | 管理组和技术组按合同组建执行团队，编制施工组织计划、管理计划、实施细则和专项预案，内业资料基本满足标准规范要求，但存在分类整理不规范、签字不规范等问题，竣工文件基本达到组卷成册要求，资料分散需汇总至卢萨卡 | 🔄进行中 |
-| 外业检查-建筑部分 | 原材料集中采购，预制构件、广场地砖从卢萨卡200多公里外采购，整体品质良好，存在局部装饰装修损伤、混凝土路面开裂等问题 | 🔄进行中 |
-| 外业检查-安装部分 | 钢结构材料国内定制，施工工艺和外观质量满足规范，存在监控管线接头脱落、提升桶位置雨水倒灌、廊桥竖条需加密等问题 | 🔄进行中 |
-| 外业检查-设备部分 | 由中粮西安设计院定制三套成套设备，厂家高峰期派十几名人员现场指导，蒙泽点已投料试运行，运行正常，工艺流程满足生产要求，产能符合设计指标 | ✅已完成 |
-| 财务检查 | 账户设置、资金往来、银行开户等符合财务处理规范和标准 | ✅已完成 |
+| 卢萨卡点验收 | 除带料加工调试外的所有验收工作已完成，内业资料已提前集中至卢萨卡点 | ✅已完成 |
+| 蒙泽点验收 | 全部验收工作完成，利用带料调试厂家人员在场顺带完成全流程试生产及外方操作手培训，工艺设备投料试运行正常、产能符合设计指标 | ✅已完成 |
+| 某皮卡点验收 | 现场验收尚未开展，内业资料已提前拿到卢萨卡点 | 🔄进行中 |
+| 内业资料 | 程序性文件、过程检查文件及整改文件基本齐全，基本达到组卷成册要求，但分类整理和签字规范性需完善，资料分散需汇总至卢萨卡 | 🔄进行中 |
+| 人员履约 | 主要人员基本保证在前方岗位，但个别人员进出场时间、护照及特种人员证件有效期需完善，人员统计需计入厂家服务人员 | 🔄进行中 |
+| 现场整改 | 建筑局部损伤、装饰装修、排水、混凝土路面开裂、监控管线接头脱落、雨水倒灌、廊桥竖条加密等问题待整改 | 🔄进行中 |
+| 财务检查 | 账户设置、资金往来、银行开户等完全符合财务处理规范和标准，无挪用资金情况 | ✅已完成 |
 # 风险预警
 | 风险/瓶颈 | 等级 | 影响 | 责任人 | 应对计划 |
 | --- | --- | --- | --- | --- |
-| 混凝土路面开裂 | 中 | 可能影响项目移交后的使用，存在大面积开裂隐患 | 管理组和总包单位 | 分析原因（当地气候、施工工艺、材料），制定科学合理的整改方案，在出报告前完成整改，验收组复核 |
-| 姆皮卡点路途遥远、路况差 | 中 | 存在交通安全风险 | 验收组 | 注意交通安全，做好疫情防控 |
-| 雨季来临，厂区排水可能阻塞 | 中 | 屋面排水和室外通道可能阻塞，影响厂区使用 | 施工方 | 做最后的清理和排查工作 |
-| 设备监控管线接头脱落 | 低 | 可能引起机械故障 | 施工组 | 全面检查，保证有效性和安全性 |
-| 提升桶位置雨水倒灌 | 低 | 雨水可能倒灌，影响设备运行 | 施工方 | 考虑增加覆盖面积或采取技术措施解决 |
-| 廊桥竖条需加密 | 低 | 巡检和维护工作人员安全保障不足 | 施工方 | 中间再加两个竖条，做检查和完善 |
-| 人员履约资料不完善 | 中 | 个别人员进出场时间、护照、特种人员证件有效期需完善，人员统计数量未包含厂家服务人员 | 管理组和技术组 | 完善资料，与国内人力资源对接，确保验收报告闭合 |
-| 内业资料分类整理不规范 | 中 | 质检和管理机构验收签字不规范，资料分散 | 技术组 | 在验收完成第一时间将三个厂区资料汇总至卢萨卡，分类组卷及编码 |
-| 不可预见费使用依据不完善 | 中 | 动用不可预见费的依据证据和数据需完善 | 验收组和施工单位 | 后续专门对接，收集整理资料，确保充分无误 |
-# 后续计划
-下一周期核心交付物包括：**完成姆皮卡点现场验收**（路途遥远、路况差，需注意交通安全与疫情防控）；**完成混凝土路面开裂原因分析并制定科学合理的整改方案**，在出报告前完成整改，验收组进行复核；**技术组在验收完成第一时间将三个厂区资料全部汇总至卢萨卡**，包括竣工图，分类组卷及编码；**完善人员履约资料**（人员统计、护照、特种人员证件有效期）；**完善不可预见费使用的依据证据和数据**，做到充分无误。关键时间节点：出报告前完成混凝土路面整改并复核；验收完成后第一时间汇总资料。依赖前提：*混凝土路面开裂原因需现场各方共同分析确定*；*不可预见费资料需与施工单位进一步对接完善*。</t>
+| 混凝土路面开裂 | 中 | 某厂区非主要通道混凝土路面少量开裂，若处理不当可能影响移交后使用和对外形象，且存在其他部位未显现的隐患 | 管理组、总包单位（未明确具体个人） | 共同分析成因（气候、施工工艺、材料），制定科学合理整改方案，最迟出报告前完成整改并形成闭环，验收组复核 |
+| 人员履约资料不完善 | 中 | 个别人员进出场时间、护照及特种人员证件有效期问题，可能影响验收报告闭合 | 施工部、管理组 | 完善资料，与国内人力资源对接确认证件延期或更新，验收报告前达到闭合条件 |
+| 内业资料分散 | 中 | 资料分散在多个点，分类整理和签字规范性不足，可能影响竣工文件组卷 | 执行单位（技术组） | 按标准和规范及时汇总至卢萨卡，分类成册，按竣工文件归档要求组卷 |
+| 卢萨卡点雨水倒灌 | 中 | 提升桶往上位置雨水可能倒灌，影响设备运行 | 施工组（未明确具体个人） | 检查并考虑增加覆盖面积或采取技术措施解决 |
+| 监控管线接头脱落 | 低 | 设备启动震动导致管线接头脱落，可能引起机械故障 | 施工组（未明确具体个人） | 全面检查，保证有效性和安全性 |
+| 成品保护疏忽 | 中 | 工程实体完工时间较长，带料调试无法进行导致验收推后，成品保护有疏忽，可能有破损 | 参建单位（未明确具体个人） | 移交外方前继续做好成品保护，及时修补破损 |
+| 姆皮卡路途交通安全 | 中 | 姆皮卡路途遥远、路况不好，且赞比亚雨季来临，存在交通安全风险 | 验收组（未明确具体个人） | 注意交通安全和疫情防控，安全完成验收任务 |
+# 后续计划</t>
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>65.09999999999999</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11110/2143</t>
+          <t>11110/1611</t>
         </is>
       </c>
     </row>
@@ -3151,58 +3203,7 @@
           <t>新闻发布</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t># 发布会概况
-本次中金宏观策略周会由中金公司策略组主办，围绕大美丽法案、关税、港股流动性、反内卷光伏、人形机器人及游戏板块等热点议题展开分析，向投资者提供配置建议。会议整体基调偏积极：认为大美丽法案在信用周期框架下对美股有利，四季度美元可能小幅走强、美股可能反弹跑赢；关税大概率是谈判技巧，市场逐渐脱敏；港股流动性三季度边际变紧但基本面强可盖过影响；光伏反内卷政策升级，行业底部夯实；人形机器人三季度进入商业兑现过渡阶段；游戏板块有望在调整后实现戴维斯双击。
-# 核心信息
-- 大美丽法案三大块：提高债务上限约**5万亿美元**；延长2017年减税法案，新增支出**3.4万亿美元**（每年**3400亿**），同时减少新能源补贴**1.4万亿**；取消`899条款`（不再对美债利息所得征税）。
-- 信用周期框架下，财政因素对美股有利，预计四季度美元可能小幅走强、美股可能反弹跑赢；7-9月有抽水效应，额外供给约**1万亿美元**，类似2023年三季度（当时美债利率从**3.8%**升至**5%**，美股小幅下跌**4-5%**）；当前期限溢价已高于2023年高点，预计利率抬升幅度可能不及2023年。
-- 关税四点信息：一定会做、需维持一定税率（当前豁免**10%**水平）、不能太高、市场逐渐脱敏；新变化：时间拖后（原7月9日）、相比4月2日对等关税大部分回落（除巴西）、加拿大墨西哥欧盟贸易占比高需谈妥、其他占比小；有效税率当前**10-12%**，极端**18%**；通胀年底**3.3-3.4%**，美联储7月勉强，9月后可降；对中国关税约**40-50%**，越南转口限制**40%**，关注8月12日中美谈判。
-- 港股5月后微观流动性释放，`Hibor`大幅下降，金管局投放大量资金，港币触及**7.85**；金管局会收流动性，但可小幅收（如收**90亿**放**1000亿**）；三季度流动性供给不如二季度，IPO融资多形成约束；恒指在**23000-24000**区间震荡。
-- 光伏：全球新增装机从2020年**130GW**增至2024年**530GW**，CAGR **42%**，预计2025-26年增速回落至**10%**左右；产能过剩：电池**1.5倍**、硅片组件**2倍**、硅料**2.5倍**；2022年以来产业链价格下跌**70-90%**；硅料现金成本**38元/公斤**，颗粒硅**28元**，尾部**45元**；光伏玻璃第二轮产能出清，7月降产**30%**，需出清**2万吨**；多晶硅期货价格触及**40元/公斤**，硅片涨**10%**，电池涨**2分**，组件涨**10%**。
-- 人形机器人：二季度A股板块跌**9%**，跑输机械**12个百分点**，特斯拉链回调**30-40%**；三季度三条主线：华为云生态开放（`盘古世界模型`、`cloud robot`平台）、本土企业技术闭环（智元收购上市、宇树年收入破**10亿**、两家中标中国移动**1.2亿**订单）、特斯拉延期带来的硬件替代窗口（电机过热、灵巧手负载不足、续航问题）。
-- 游戏：6月单月版号发放**158个**（国产**147个**、进口**11个**），2018年以来最高；1-5月游戏市场规模同比增长**17%**，手游增长**20%**；吉比特《仗剑传说》首月流水**2亿多**，巨人网络《超自然行动组》6月流水过亿；估值：TTM PE约**30倍**，2025年静态PE约**20倍**，低于2023年AI行情**45倍**。
-# 官方表态
-- 关于去美元化：刘刚凯文表示，不认同去美元化观点，认为这是高度趋同的共识，且基于宏大叙事，无法确定兑现时间。
-&gt; 我们并不是完全的认同，去美元化这个观点的。
-&gt; 现在这个预期基本成了一个非常拥挤的共识，而且主要是基于宏大趋势。
-- 关于市场误区：指出两个最大误区，一是把美元弱当成去美元化，二是把美元弱和美股弱直接划等号。
-&gt; 美元弱可以有各种各样的原因，比如说美联储降息预期升温都可以导致美元相对走弱。他不一定是因为这个事情。
-&gt; 美元弱在大部分的时间，只要不是这种大家抛售美国资产的弱，实际是对美股有利的。
-- 关于美股美债：重申不悲观，波动提供再配置机会。
-&gt; 波动提供再配置的机会，我们重申我们这个观点并不悲观。
-- 关于关税：认为大概率是谈判技巧，市场静观其变。
-&gt; 他现在威胁的那么高，有可能是一个谈判技巧。
-- 关于港股：强调基本面强可盖过美元美债利率影响。
-&gt; 美元美债利率它并不是绝对主导港股市场的唯一的变量，很多时候你自己的基本面强，完全可以盖过它的影响。
-- 关于光伏反内卷：刘佳妮表示，期待政府干预，认为有一定必要性。
-&gt; 我们也比较期待政府的干预，也认为是有一定的这个必要性的。
-- 关于游戏：张雪琴明确看好，认为调整后有望戴维斯双击。
-&gt; 我们还是认为在消费政策和新品周期三重利好下面，游戏行业有望在调整后再次实现戴维斯双击。
-# Q&amp;A环节
-**问**：大美丽法案对美股、美债、美元流动性有什么影响？
-**答**：大美丽法案三大块：提高债务上限约5万亿美元、延长2017年减税法案（新增支出3.4万亿，每年3400亿，减少新能源补贴1.4万亿）、取消899条款。信用周期框架下，财政因素对美股有利，四季度美元可能小幅走强，美股可能反弹跑赢。7-9月有抽水效应，额外供给约1万亿美元，类似2023年三季度，当时美债利率从3.8%升至5%，美股小幅下跌4-5%。当前期限溢价已高于2023年高点，预计利率抬升幅度可能不及2023年，但需过坎。
-**问**：关税是否在升级？对市场有什么影响？
-**答**：关税大概率要做，需维持当前豁免10%的税率水平以收钱，不能太高，市场逐渐脱敏。新变化：时间拖后（原7月9日）、相比4月2日对等关税大部分回落（除巴西）、加拿大墨西哥欧盟贸易占比高需谈妥、其他占比小。有效税率当前10-12%，极端18%。通胀年底3.3-3.4%，美联储7月勉强，9月后可降。对中国关税约40-50%，越南转口限制40%，关注8月12日中美谈判。
-**问**：港股流动性会如何变化？
-**答**：7-9月美债利率走高、美元流动性供给压力，四季度美元可能小幅走强，边际挤压港股。港股5月后微观流动性释放，Hibor大幅下降，金管局投放大量资金，港币触及7.85，金管局会收流动性，但可小幅收（如收90亿放1000亿）。三季度流动性供给不如二季度，IPO融资多形成约束。恒指在23000-24000区间震荡。
-**问**：光伏反内卷政策对行业有什么影响？
-**答**：反内卷政策升级，价格恶性竞争有望告一段落，行业底部夯实。全球新增光伏装机从2020年130GW增至2024年530GW，CAGR 42%，预计2025-26年增速回落至10%左右。产能过剩：电池1.5倍、硅片组件2倍、硅料2.5倍。2022年以来产业链价格下跌70-90%。硅料环节最易整合，现金成本38元/公斤，颗粒硅28元，尾部45元。光伏玻璃第二轮产能出清，7月降产30%，需出清2万吨。多晶硅期货价格触及40元/公斤，硅片涨10%，电池涨2分，组件涨10%。
-**问**：人形机器人三季度有哪些投资机会？
-**答**：二季度A股机器人板块跌9%，跑输机械12个百分点，特斯拉链回调30-40%。三季度三条主线：华为云生态开放（盘古世界模型、cloud robot平台）、本土企业技术闭环（智元收购上市、宇树年收入破10亿、两家中标中国移动1.2亿订单）、特斯拉延期带来的硬件替代窗口（电机过热、灵巧手负载不足、续航问题）。建议关注三类信号：华为云生态接入厂商、头部企业出货量跨越年化500台或1000台、电机硬件优化。
-**问**：游戏板块调整后还能上车吗？
-**答**：游戏板块上涨近两三个月，上周开始调整。政策友好度空前，版号发放常态化，6月单月发放158个（国产147个、进口11个），2018年以来最高。1-5月游戏市场规模同比增长17%，手游增长20%。新品周期亮眼，中型厂商新品成为核心催化，如吉比特《仗剑传说》首月流水2亿多，巨人网络《超自然行动组》6月流水过亿。估值：TTM PE约30倍，2025年静态PE约20倍，低于2023年AI行情45倍。新品利润有滞后性，明年兑现。</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>78.09999999999999</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>22868/3457</t>
-        </is>
-      </c>
+      <c r="C9" s="4" t="n"/>
     </row>
     <row r="10" ht="13.5" customHeight="1" s="9">
       <c r="A10" s="6" t="inlineStr">
@@ -3512,56 +3513,7 @@
           <t>课堂记录</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t># 课程概况
-本次班会课以“梦想”为主题，由班主任老师主讲。老师首先分享了自己的梦想——成为受学生喜爱的、有名望的优秀人民教师，并回顾了个人过往的梦想清单：考中国美术学院（单考已过，但因离家远、家庭经济困难未就读）、加入学生会、参加各种比赛、保持专业排名第一（大学四年在本专业41人中排名第一）、考取教师资格证等。老师还讲述了自己因定向生政策选择师范院校、从最初不情愿到逐渐热爱教师职业的经历。随后，课堂通过航模小伙子何宗发与想当歌手的普通人两个案例，引导学生讨论实现梦想所需的条件，包括坚持、努力、勇敢、机会、兴趣、能力、学习等，强调机会留给有准备的人，梦想可以分阶段调整、逐步实现。最后，老师让学生写下自己的梦想清单，并布置课后任务：各小组第一位同学收集本组梦想清单交给老师。
-# 核心知识点梳理
-## 梦想的定义与价值
-- 梦想是值得尊重并努力去实现的目标，**每一个梦想都是值得我们尊重的**。
-- 老师引用名言：**“不被嘲笑的梦想不是梦想”**，鼓励学生勇敢追梦。
-## 实现梦想的条件
-- **坚持**：如老师大学四年保持专业排名第一，需每天5点起床、坚持自律。
-- **努力**：天赋只是1%，后天努力更重要。
-- **勇敢**：如班上同学勇敢站上讲台唱歌，即使被起哄。
-- **机会**：**机会永远留给有准备的人**。
-- **兴趣、能力、学习**：都是实现梦想的必备条件。
-- 缺少任一条件，梦想仍可能实现；若条件齐备，梦想会**更快实现**。
-## 梦想的分阶段调整
-- 梦想可以一步步立高，如航模小伙何宗发从国内舞台走向世界赛场。
-- 若目标暂时无法实现，可先调整为更小目标（如先考进年级前百，再冲刺前50），逐步推进。
-## 案例：航模天才何宗发
-- 中国唯一去法国巴黎比赛的航模选手，梦想带着飞机环游世界，把中国国旗挂在世界各大赛场上。
-- 表演飞机有真实原型机**歼10**，从古代遨游到未来。
-- 不断挑战技术极限，受到世界冠军关注，压力大但希望明年世界锦标赛再比高下。
-- 参观中国航空博物馆后，想用同样原理做出模型。
-## 案例：想当歌手的普通人
-- 在宿舍练习唱歌，即使嗓子走调，通过后天学习和努力可以调整，仍可能成为歌手。
-- 启示：**不要嘲笑任何人的梦想**。
-## 成功人士示例：马云
-- 中考考两次才上高中，高考考三次，最终成为中国首富，说明**起点高低不重要，关键在坚持**。
-- 马云新梦想：过去15年中国因他们而改变，未来15年希望世界因他们而改变，享受改变他人的乐趣。
-# 课堂互动与答疑
-**问**：如果缺少了实现梦想的某一个条件，梦想还会实现吗？
-**答**：有可能实现，但如果所有条件都具备，梦想会更快实现。
-**问**：马云的成功可以复制吗？
-**答**：不可以，每个人的梦想都是独一无二、不可复制的。
-&gt; 老师原话：“机会都是留给有准备的人。”
-&gt; “不被嘲笑的梦想不是梦想。”
-&gt; “梦想还是要有的，万一实现了呢？”
-# 课后任务与学习建议
-课后任务：请同学们拿出纸写下自己的梦想清单，可以像老师一样列出多个梦想，并标注实现所需时间、实现后的收获；写完后由各小组第一位同学收集本组梦想清单交给老师。
-学习建议：梦想可以分阶段调整，先定小目标再定大目标；实现梦想需要坚持、努力、行动，并抓住机会。</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>9362/1393</t>
-        </is>
-      </c>
+      <c r="C10" s="4" t="n"/>
     </row>
     <row r="11" ht="13.5" customHeight="1" s="9">
       <c r="A11" s="6" t="inlineStr">
@@ -3731,67 +3683,7 @@
           <t>通用纪要</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t># 全文摘要
-本段文本为新闻联播播报，围绕文化自信与文化建设、中俄议会合作、夏粮丰收、铁路货运、快递业、油气管网建设、防汛应对、国内联播快讯及国际新闻等多项内容展开。核心结论包括：习近平总书记强调将中华优秀传统文化与马克思主义相结合，2023年10月首次提出习近平文化思想；赵乐际访俄期间双方同意从立法机构层面落实两国元首共识；今年夏粮产量达2996亿斤创历史新高；6月国家铁路货运多项指标创历史同期新高；上半年快递业务量超800亿件；油气管网预计全年新增里程超4000公里；水利部联合调度水库群应对长江洪水。国际方面，特朗普竞选集会遭未遂刺杀，以军空袭加沙致90人死亡。
-# 要点梳理
-## 文化自信与文化建设
-- 习近平总书记强调文化自信，提出将中华优秀传统文化与马克思主义相结合，指出“我们五千年的文明，我们要尊重，也要弘扬，把它里边精华的东西和我们现在所坚持的马克思主义立场、观点、方法结合起来，这就是中国特色社会主义。”
-- 2023年6月召开文化传承发展座谈会，系统论述中华文明五个突出特性，阐述“两个结合”尤其是“第二个结合”的重大意义。
-- 2023年10月全国宣传思想文化工作会议首次提出习近平文化思想。
-- 实施《深化文化体制改革实施方案》和《关于实施中华优秀传统文化传承发展工程的意见》，推动文化传承发展。
-- 坚持把社会效益放在首位，社会效益和经济效益相统一，推进文化领域供给侧结构性改革，文旅融合、非遗保护、公共文化服务体系建设。
-- 数字文化产业成为激发消费潜力“新引擎”，电影市场规模屡创新高。
-## 中俄议会合作
-- 赵乐际于7月9日至13日对俄罗斯进行正式友好访问，出席中俄议会合作委员会第九次会议，在圣彼得堡会见普京，在莫斯科与马特维延科、沃洛金会谈。
-- 双方同意从立法机构层面落实两国元首重要共识，深化多层级、多领域、多渠道交流合作，互学互鉴立法经验，为务实合作提供法治保障。
-- 普京表示俄中立法机构合作有助于推进双边合作；马特维延科表示发展对华关系得到俄社会广泛认同；沃洛金强调俄坚定恪守一个中国原则。
-## 夏粮产量
-- 今年夏粮产量达2996亿斤，比2023年增加72.5亿斤，创历史新高。
-- 夏粮单产每亩375.2公斤，小麦单产399.1公斤，比2023年增加10公斤。
-- 中央推进“藏粮于地、藏粮于技”战略，已建成高标准农田10亿多亩，启动小麦单产提升三年行动，中央财政首次提前下拨16亿元小麦“一喷三防”资金。
-- 小麦质量为近年来最好水平，夏粮首战告捷为全年粮食丰收奠定基础。
-## 铁路货运
-- 6月份国家铁路发送货物3.32亿吨，完成货运周转量2665亿吨公里，同比分别增长6.1%、5.3%，创历史同期新高。
-- 化肥农药运量增幅最大，同比增长26.2%；煤炭日均装车量、集装箱、商品汽车、冷链货物发送量均创历史同期新高。
-- 中欧班列6月累计开行1719列，发送货物18万标箱，同比分别增长15%、11%。
-## 快递业发展
-- 上半年快递业务量超800亿件，截至6月30日已达800亿件。
-- 快递企业运行国际航线40余条，面向东南亚开通陆运专线，运行美西海运航线。
-- 每天超1亿多件快递包裹在农村地区流动，5-6月快递日均业务量近5亿件。
-## 油气管网建设
-- 预计全年新增管道里程超4000公里。
-- 西气东输四线已完成吐鲁番至中卫段主体管道工程建设，投产后年输气能力将提升150亿立方米。
-- 主干油气管网约10万公里，输气能力从2020年2230亿立方米增加到3290亿立方米，增幅达48%。
-- 到2025年将形成四大油气战略通道和“五纵五横”天然气干线管网。
-## 防汛与降雨应对
-- 重庆28个区县出现暴雨，13个区县大暴雨；四川内江出现内涝、滑坡；安徽多条河流水位上涨，滁州市全椒县处置堤防渗漏和管涌。
-- 水利部针对“七下八上”防汛关键期逐流域安排防御，长江1号、2号洪水正在演进，三峡水库15日将迎来洪峰流量45000立方米每秒量级的洪水过程。
-- 水利部联合调度嘉陵江亭子口水库等上游干支流水库群，减小三峡水库入库洪峰流量。
-## 国内联播快讯
-- 北京上半年320个市区重大项目全部开工，总投资超4000亿元。
-- 燕矶长江大桥北岸主塔封顶，主跨1860米，连接湖北鄂州和黄冈。
-- 第二十三届环青海湖国际公路自行车赛收官，22支车队154名运动员参赛。
-- 内蒙古第34届草原那达慕开幕，持续到8月底。
-- “中非儿童手拉手”活动在京启动，五国儿童代表参观访问。
-## 国际新闻
-- 美国前总统特朗普在竞选集会遭未遂刺杀，右耳中枪受伤，一名观众死亡，两名观众重伤，枪手被击毙，动机待查。
-- 以军空袭加沙地带马瓦西地区致90人死亡，约300人受伤，巴勒斯坦谴责违反国际法。
-- 以军袭击黎巴嫩多个边境村镇，黎真主党打击以军集结地。
-- 叙利亚大马士革遭空袭，1名政府军士兵死亡、3人受伤。
-- 俄军打击乌军列车点，乌军击退俄军进攻。
-- 加拿大林火蔓延，9600人被疏散。</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="n">
-        <v>59.8</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>7755/2095</t>
-        </is>
-      </c>
+      <c r="C11" s="4" t="n"/>
     </row>
     <row r="12" ht="13.5" customHeight="1" s="9">
       <c r="A12" s="6" t="inlineStr">
@@ -4025,72 +3917,7 @@
           <t>课堂记录</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t># 课程概况
-本课为初中物理光学复习课，系统复习几何光学核心内容。首先讲解光的直线传播：光源分为自然光源（太阳、萤火虫）与人造光源（火把、蜡烛、电灯）；光线是带箭头的直线，为物理模型；光在均匀介质中沿直线传播，实例包括三点一线、激光准直、小孔成像、日食月食、影子形成。光速在真空中为3×10^8米/秒（约每秒30万公里，一秒钟绕地球赤道7圈半），空气中略慢，水中为真空的3/4，玻璃中为2/3。其次讲解光的反射定律：反射光线、入射光线、法线在同一平面内，反射光线和入射光线分居法线两侧，反射角等于入射角；垂直入射时入射角为0度。第三讲解镜面反射与漫反射：镜面反射发生在光滑表面，反射光线平行；漫反射发生在凹凸不平表面，反射光线射向各个方向，生活中大多数反射是漫反射，两者都遵守光的反射定律。第四讲解平面镜成像：原理是光的反射，成像是正立、等大的虚像；实验用玻璃板代替平面镜，用刻度尺比较像与物到镜面的距离，用两段相同蜡烛比较像与物大小，光屏不能接收虚像。第五讲解球面镜及其应用：凸面镜对光线起发散作用，成像是正立、缩小的虚像，应用于汽车后视镜、丁字路口反光镜；凹面镜对光线起会聚作用，应用于手电筒、汽车前大灯、太阳灶、医生额镜。
-# 核心知识点梳理
-## 光的直线传播
-- **光源**：自身能够发光的物体。按来源分为**自然光源**（太阳、萤火虫）与**人造光源**（火把、蜡烛、煤油灯、电灯）。
-- **光线**：用一条带有箭头的直线代表光线，是**物理模型**，并非真实存在。
-- **光在均匀介质中沿直线传播**：实例包括**三点一线**（步枪瞄准、队列排齐、木工看尺子）、**激光准直**、**小孔成像**、**日食月食**、**影子形成**（如皮影戏）。
-- **小孔成像**：成**倒立**的像，放大或缩小不一定，一定是**实像**（光线实际到达）；像的形状与孔的形状无关。生活实例：夏天大杨树下的**光斑**是太阳透过树叶缝隙形成的小孔成像，因太阳距地球远，得到的是太阳缩小的像。
-- **日食与月食**：日食时太阳、月球、地球在同一直线上，**月球在中间**；1号区域为**日全食**，2、3号区域为**日偏食**，4号区域为**日环食**。月食时太阳、地球、月球在同一直线上，**地球在中间**；月球完全在地球阴影（1号区域）内为**月全食**，部分在1号区域、部分在2或3号区域时为**月偏食**。
-- **光速**：真空中为 `3×10^8米/秒`（即 `3×10^5千米/秒`，约每秒30万公里，一秒钟绕地球赤道7圈半）；空气中略慢（约 `2.99×10^8米/秒`）；水中约为真空中的 `3/4`；玻璃中约为真空中的 `2/3`。
-- **练习答案**：第1题光在均匀介质中沿直线传播；第2题影子和月全食均为光沿直线传播；第3题激光从地球到月球距离为 `3.75×10^8米`（s=V×T，3×10^8×1.25）；第4题选C；第5题选BCD（平面镜是反射）；第6题选ABC（D错在未强调均匀介质）。
-## 光的反射定律
-- **基本概念**：`入射光线`（AO）、`入射点`（O）、`反射光线`（OB）、`法线`（垂直于镜面的辅助线，画虚线，不存在）、`入射角`（入射光线与法线的夹角）、`反射角`（反射光线与法线的夹角）。
-- **反射定律三句话**：①反射光线、入射光线、法线在**同一平面内**（共面）；②反射光线和入射光线**分居法线两侧**；③**反射角等于入射角**。
-- **垂直入射**：光垂直射到镜面上时，入射角为**0度**，反射角也为**0度**（易错点：误答90度）。
-- **作图步骤**：①先画**法线**（虚线，留作图痕迹）；②根据反射角等于入射角画光线；可用刻度尺对称取点法（如法线对准20刻度，反射光上取25刻度点，则入射光上取15刻度点）。
-- **练习答案**：第7题反射光线与平面镜夹角40度时，入射角为**50度**（选A）；第8题按上述步骤作图；第9题选A；第10题选C（入射光线与镜面夹角增大，入射角减小，反射角减小，传播速度不变）；第11题入射角60度时反射角**60度**；第12题反射光线与入射光线夹角80度时反射角**40度**。
-## 镜面反射与漫反射
-- **镜面反射**：发生在光滑表面（平面镜、平静水面、光滑金属表面），一束平行光反射后仍平行；若人眼不在反射光方向上则看不到反射光（如商场玻璃隔断易撞上）。
-- **漫反射**：发生在凹凸不平的表面，把每个小面看作小平面镜，反射光线射向**各个方向**；生活中大多数反射是**漫反射**（黑板、电影银幕、人眼视物）。
-- **共同点**：镜面反射和漫反射**都遵守光的反射定律**。
-- **实例判断**：雨后夜晚，**迎着月光走**，发亮处是水潭（镜面反射）；**背着月光走**，发暗处是水潭。
-- **练习答案**：第13题选亮处/暗处对应；第14题选B（光路可逆，小明能看到小刚在平面镜中的像，则小刚也一定能看到小明）；第15题电影院白色银幕产生**漫反射**；第16题黑板反光为**镜面反射**、银幕为**漫反射**；第17题银幕粗糙为使光发生**漫反射**。
-## 平面镜成像
-- **成像原理**：光的反射。
-- **成像特点**：成**正立、等大的虚像**（与物大小相等，像与物到镜面距离相等，像与物连线与镜面垂直）。
-- **实验要点**：用**玻璃板**代替平面镜（便于确定像的位置）；用**刻度尺**比较像与物到镜面的距离；用**两段完全相同的蜡烛**比较像与物的大小；**光屏不能接收虚像**（实际光线未到达）。
-- **实验误差原因**：①玻璃板与水平面**不垂直**（倾斜放置）；②玻璃板**有厚度**，两个面发生反射成像。
-- **应用实例**：视力表距镜3.5米时，人距镜**1.5米**可看到5米处虚像（第21题）；第22题视力表距镜3米时人选**2B**（人距镜2米）；第23题人距镜1米时人与像距离**2米**；第24题远离平面镜时像大小**不变**（选C）；第18题选**D**（水中倒影为光的反射，平静水面充当平面镜）。
-## 球面镜及其应用
-- **凸面镜**：对光线起**发散**作用，成**正立、缩小的虚像**；应用于**汽车后视镜**、**丁字路口反光镜**。
-- **凹面镜**：对光线起**会聚**作用，有焦点；应用于**手电筒**（电珠在焦点处）、**汽车前大灯**、**探照灯**、**太阳灶**（西藏藏民烧水）、**医生额镜**（耳鼻喉科检查）。
-- **光污染风险**：玻璃幕墙凹面会聚光线，可能烧死树木（如学校枣树被烧死）、引燃电线（焦点落在电线上导致自燃）。
-# 课堂互动与答疑
-**问**：光线是真实存在的吗？
-**答**：不是，光线是物理模型，是为了研究问题方便引进的一条带箭头的直线。
-**问**：光垂直射到镜面上，入射角是多少度？
-**答**：0度，因为入射角是入射光线与法线的夹角，垂直入射时夹角为0度。
-**问**：为什么平面镜成的是正立的像，而水中倒影却是倒的？
-**答**：平静的水面充当平面镜，树在水中的倒影实际上是正立、等大的虚像，只是文学上习惯称为“倒影”，并非真正倒立。
-&gt; 教师提醒：光在均匀介质中沿直线传播，这句话虽然啰嗦，但答题时把它写上就行了。
-&gt; 教师提醒：作图时法线一定要画虚线，作图痕迹要留下，擦了还不如不画。
-# 课后任务与学习建议
-**课堂练习**：完成讲义练习第1-6题（光的直线传播）、第7-12题（光的反射定律）、第13-17题（镜面反射与漫反射）、第18-24题（平面镜成像），课上已逐题讲解答案。
-**复习重点**：
-- 光在均匀介质中沿直线传播及其实例（三点一线、激光准直、小孔成像、日食月食、影子）。
-- 光的反射定律三句话，垂直入射时入射角为0度。
-- 镜面反射与漫反射的区别及共同点（都遵守反射定律）。
-- 平面镜成像特点（正立、等大、虚像）及实验操作要点。
-- 凸面镜发散、凹面镜会聚及其应用。
-**学习建议**：
-- 可在家用激光笔、硬纸壳、平面镜等器材自行验证光的直线传播、反射定律和平面镜成像实验。
-- 注意作图规范：先画法线（虚线），再根据反射角等于入射角画光线，保留作图痕迹。
-- 保护眼睛，注意用眼卫生。</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="n">
-        <v>70.7</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>25691/3454</t>
-        </is>
-      </c>
+      <c r="C12" s="4" t="n"/>
     </row>
     <row r="13" ht="13.5" customHeight="1" s="9">
       <c r="A13" s="6" t="inlineStr">
@@ -4196,99 +4023,7 @@
           <t>课堂记录</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t># 课程概况
-本次课程为《电气工程基础》第1章，是电气工程及其自动化专业的入门课。课程教学目的有二：一是掌握电力系统发电、输电、配电、用电四个典型环节的构成、工作原理及与电力系统整体的关系，建立电力系统整体概念；二是掌握电力系统分析、设计、运行、管理方面的基础理论、技术与计算方法。前修课程要求电路理论和电机学知识，特别是变压器和同步电机；后续课程包括电力系统分析、电力系统机电保护、电力系统自动化和高电压技术。第1章是概念最多、最重要的章节，要求掌握电力系统、电力网、动力系统、变电站等基本概念，理解电力系统特点及由此引起的设计运行基础理论，理解对电力系统的要求，掌握电能质量指标及国家标准规定范围，了解常用接地方式特别是中性点接地方式。课程还讲解了电力发展简史、交直流输电比较、三相三线制优势、电力系统形成过程，以及电力系统、电力网、动力系统的定义与电网分类。
-# 核心知识点梳理
-## 课程教学目标
-- 目标一：掌握电力系统**发电、输电、配电、用电**四个典型环节的构成、工作原理及与整体的关系，建立电力系统整体概念。
-- 目标二：掌握电力系统在**分析、设计、运行、管理**方面的基础理论、基本技术与计算方法。
-- 前修课程：`电路理论`、`电机学`，特别是**变压器**和**同步电机**知识要求较高。
-- 后续课程：`电力系统分析`、`电力系统机电保护`、`电力系统自动化`、`高电压技术`。
-## 第1章学习要求
-- 掌握电力系统、电力网、动力系统、变电站等基本概念。
-- 理解电力系统的特点及由此引起的设计运行基础理论。
-- 理解对电力系统提出的要求（涉及运行、设计、维护）。
-- 掌握电能质量指标及**国家标准**规定的范围。
-- 了解常用接地方式，特别是**中性点接地方式**的不同特点。
-- ⭐ 难点一：电能不能大量储存，决定电力系统**有功功率和无功功率的动态平衡**问题。
-- ⭐ 难点二：电力系统**额定电压**的规定繁杂，需理清规律。
-- ⭐ 难点三：各种**中性点接地方式**影响后续多个章节，学习较困难。
-- 学习方法：注意概念的内涵和外延；从电力系统特点、要求出发，从基本原理推导，不记结论；寻找额定电压规定之间的基本规律；比较不同中性点接地方式的特点。
-## 电力发展简史（直流阶段）
-- 电力发展从**直流**开始，而非交流。
-- 福泰勒用**2000米**导线连接瓦斯发电机，拖动直流电动机和水泵，证明直流输电可行。
-- **1874年**，俄国工程师在彼得堡建成**4.5公里**直流输电线路，传输功率**4.5千瓦**。
-- **1882年**，法国**德普勒**架设首条**57公里**直流试验线路（用电报线），首端电压**343伏**、末端**850伏**，输送功率**200瓦**，损耗**78%**。
-- **1883年**，德普勒从法国南部进行**14公里**输电试验，输送功率**1.1千瓦**，损耗**55%**。
-- **1882年10月**，英国科学家发明直流**三线制系统**：外线与中线电压**110伏**，外线间**220伏**，后扩展为五线制。
-- 直流输电限制：电压等级低时损耗大、电压降落快；制造大容量高压直流发电机困难。
-- 19世纪末，法国**方剑**串联多台直流发电机，将**75千瓦**电力输送**75千米**。
-- 20世纪初，瑞典科学家在串联直流发电机上装**短路器**，使任意发电机投切不停电；此后20多年建成**15条**直流线路，最大为**1906年**投运的法国慕尼黑水电厂至里昂线路：**180公里**、**57千伏**、**4700千瓦**；**1927年**改建为**260公里**、**125千伏**、**19000千瓦**，接入两座水电站。
-- 直流输电制约因素：设备复杂、运行方式复杂、造价高、可靠性差。
-## 电力发展简史（交流阶段）
-- 英国**法拉第**电磁感应原理；美国**亨利**用多匝线圈做原边、少匝线圈做副边，实现高电压感应出低电压，为变压器前身。
-- **1876年**，俄国科学家发明**单相变压器**，主要用于照明。
-- 法国和英国科学家联合将多台变压器串联接入输电线路，发现负荷变化时输电电压受干扰。
-- **1883年**，美国**特斯拉**制造出**感应电机**，为标志性成果。
-- **1885年**，匈牙利科学家设计多台变压器**并联运行**方式，使并联成为可能。
-- **威斯汀豪斯**与**爱迪生**的**交直流电力战争**：爱迪生、凯尔文主张直流，理由是直流效率高、交流有危险性（曾购买威斯汀豪斯交流发电机卖给监狱执行死刑以证明）；威斯汀豪斯、特斯拉主张交流，理由是交流易用变压器升压降压、减少电能损失。
-- **1886年**，威斯汀豪斯在美国麻省进行**1.2千米**、**30千伏**交流输电示范；又在意大利建成**17英里**、**2千伏**高压线路。
-- **1886年**，俄国科学家发明**三相交流电**、三相交流输电和三相异步电动机。
-- 交直流电力战争最重要标志：**法国到德国**的交流输电线路（被认为是第一条交流输电线路），水电厂装三相发电机和升压变压器，升压后送到德国，在法兰克福建两座降压变电站，一座供展览会照明，另一座供**100马力**三相异步电动机（用于人工瀑布离心泵）。
-- 交流输电随高电压、绝缘技术发展：**1898年**发明真实绝缘子，美国加利福尼亚电压升至**33千伏**；**1906年**发明悬式绝缘子，建成**110千伏**线路；**1912年**发现电晕临界电压与导线直径成比例增加，铝线和钢芯铝绞线开始应用，美国建成**154千伏**线路；**1923年**均压阀技术应用，建成**220千伏**线路；**1936年**美国**287千伏**投运；**1952年**瑞典**380千伏**线路首次采用**分裂导线**；**1956年**苏联**400千伏**双回线路投运；**1965年**加拿大**735千伏**；**1969年**美国**765千伏**；**1985年**苏联**1150千伏**特高压投运，后降压至**500千伏**运行。
-- 国内：**1941年**投运**220千伏**；**1972年**投运**330千伏**；**1981年**投运**500千伏**；**2009年**投运**1000千伏**交流特高压（国家标志性首次投运）。
-## 直流输电的复兴
-- 交流大电网稳定问题突出后，直流在联网中的优势显现，用于电网间连接。
-- **1954年**，瑞典本土与哥特兰岛建成世界第一个工业**海底电缆**直流工程：**100千伏**、**96公里**，采用**汞弧阀**。
-- **1970年**，瑞典本土与哥特兰岛扩建**50千伏**、**1万千瓦**晶闸管换流阀试验工程。
-- **1972年**，世界第一个**晶闸管换流阀**背靠背直流工程在加拿大投运。
-- 中国第一个直流输电工程：连接**舟山群岛**与**浙江定海**电网。
-- 中国第二个直流输电工程：**1989年**葛上直流（葛洲坝电厂至上海），**±500千伏**。
-- 今年6月投运**云广直流**：**±800千伏**特高压直流工程。
-- 推荐三本书供课后阅读（书名未明确）。
-## 三相交流输电优势
-- 交流指**ABC三相对称系统**，具有三个优点：
-  - 易于产生**旋转磁场**，三相电动机易做驱动。
-  - **瞬时功率恒定**，不随时间变化。
-  - 输电线路**导线金属消耗量最少**。
-- 除室内配电等小功率供电采用单相交流外，其它场合基本采用三相交流；国内电力系统大多数高压、超高压、特高压输电采用三相交流，仅在联网时采用直流。
-- **三相三线制**传输效率最高，金属消耗量最小（同等功率和功率因数下），因此广泛应用。
-## 电力系统的形成
-- 最早：一台发电机向附近负荷供电（如展览会照明、大楼照明），可靠性差，发电机故障即停电。
-- 改进：将多台发电机并联连接，一台故障时另一台带重要负荷，提高可靠性。
-- 问题：导线有**电阻**和**电抗**，传输功率时产生**电压损耗**和**功率损耗**，限制输电距离。
-- 解决：用**升压变压器**提高电压，传输相同功率时电流减小，`有功损耗 I²R` 和电压降落 `IZ` 减小，输电距离变长。
-- 近距离（几十至几百米）可直接连接；远距离采用升压传输，形成电力系统雏形。
-- 好处：多台发电机共同供电，可靠性提高；可装大机组，供电范围扩大，带来经济效益。
-- 远距离输电（如湖北送华东、云贵送两广）时，中间可装设变电站降压供电，并引接部分负荷；输电距离长出现稳定问题，可装设备调整。
-## 电力系统、电力网、动力系统定义
-- **电力系统**：由**发电机、变压器、输电线路和用电设备**构成的整体，完成电能**生产、输送、分配、消耗**四个职能，由发电、输电、配电、用电四个环节组成。
-- **电力网**：电力系统中去除发电机和用电设备的部分，即**变压器和输电线路**构成的网络。
-- **动力系统**：电力系统加上发电厂动力部分（火电的锅炉、汽机、煤炭输送处理系统；水电的水轮机、水坝、水库等）。
-- 行业中最常用的是**电力网**和**电力系统**两个概念。
-## 电网分类
-- **地方电力网**：向固定地方供电，电压等级**110千伏及以下**（早期定义35千伏及以下），供电半径**20–50公里**，如**武汉电网**。
-- **区域电力网**：电压等级**110、220千伏**和少量**500千伏**，供电半径**超过50公里**，联系较多发电厂和负荷中心，如**华中电网**。
-- **超高压远距离输送网络**：电压等级**500千伏或1000千伏**（东北有**330千伏**），任务是把发电厂电能送到负荷中心，距离很远，构成跨省跨地区大型电力系统，如**晋东南至湖北荆门**特高压系统（跨三省，连接华北、华中电网）、**三峡至上海**输电线路。
-## 变电站分类
-- 按**最高电压等级**分类：如华工变电站为**10千伏**变电站（10千伏变380伏）；关山变电站为**220千伏**变电站；凤凰山变电站为**500千伏**变电站。
-- 按**主要功率流向**分类：大部分功率从高压侧流向低压侧为**降压变电站**；发电厂内大部分功率从低压侧升压到高压侧为**升压变电站**。
-# 课堂互动与答疑
-未提及
-# 课后任务与学习建议
-教师未布置具体作业，但强调课后应补充前修课程中变压器和同步电机的相关知识；要求课后仔细体会第1章的学习方法（注意概念内涵外延、从基本原理推导、寻找额定电压规律、比较不同接地方式特点）；作为电气专业学生应了解电力发展基本史，推荐阅读三本书（书名未明确）。</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="n">
-        <v>80.7</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>11163/4503</t>
-        </is>
-      </c>
+      <c r="C13" s="4" t="n"/>
     </row>
     <row r="14" ht="13.5" customHeight="1" s="9">
       <c r="A14" s="6" t="inlineStr">
@@ -4364,51 +4099,7 @@
           <t>知识笔记</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t># 知识主题与概述
-本视频围绕Stack Exchange上关于调和级数发散性的证明展开评论。皮卡首先介绍了级数收敛与发散的定义：正向级数若存在固定上界则收敛，若其下界无界则发散。随后评论了第一个网友的分组求和证明，指出其与柯西凝聚判别法的证明过程本质相同，都是通过分组估计部分和，并提及高斯求和也体现了类似的分组思想。第二个证明通过证明hn &gt; log(n+1)来论证发散，皮卡认为该证明技巧性强，但属于先知道结果再凑证明，不自然，并指出其与对数差分求和本质相同。第三种流派证明hn与log n同增长级别，皮卡同样认为不自然，属于先射箭后画靶。整体逻辑框架围绕调和级数发散性的多种证明方法展开，核心在于揭示不同证明背后的共同本质。
-# 核心概念
-## 级数收敛与发散
-- 正向级数收敛：对于任意n，部分和sn都小于某个固定实数a（上界），则收敛。
-- 正向级数发散：若能证明sn大于某个单向递增且无界的bn，则发散。
-## 分组求和证明
-- 第一个网友的证明：将调和级数分组，每组和均大于1/2，因此整体无上界，发散。
-- 皮卡指出该证明与**柯西凝聚判别法**的证明过程本质相同，都是通过分组估计部分和。
-- 高斯求和（1+2+...+100）也体现了类似的分组思想。
-## 柯西凝聚判别法
-- 对非负不增序列，其收敛发散性等价于加速后的序列。
-- 应用于调和级数时，等价于判断Σ1（无穷个1相加），显然发散。
-## hn &gt; log(n+1)证明
-- 第二个证明通过证明hn &gt; log(n+1)来论证发散，因为log(n+1)无上界。
-- 皮卡认为该证明技巧性强，但属于先知道结果再凑证明，不自然。
-- 该证明与对数差分求和本质相同：两边取对数后，利用e^(1/k) &gt; 1+1/k，连乘积可相消得n+1。
-## hn与log n同增长级别
-- 第三种流派证明hn与log n同增长级别，从而发散。
-- 皮卡认为该证明不自然，属于先射箭后画靶，因为事先知道hn满足的不等式。
-- 使用**Stolz定理**（中文称斯托尔兹定理）比较差分，分子差分得1/(n+1)，分母差分得log(1+1/n)，极限为1。
-# 核心结论
-## 核心结论
-- 调和级数发散，这是微积分中的经典结论。
-- 分组求和证明与柯西凝聚判别法本质相同，都是通过分组估计部分和。
-- 第二个证明（hn &gt; log(n+1)）与对数差分求和本质相同，但属于先知道结果再凑证明，不自然。
-## 易混淆点
-- **收敛与发散的定义**：收敛需存在固定上界，发散需证明下界无界，两者判断标准不同。
-- **柯西凝聚判别法**与分组求和证明的等价性，容易误认为是不同方法。
-- **hn与log n同增长级别**的证明，容易误认为是独立方法，实际依赖于事先知道的不等式。
-## 待澄清问题
-- 皮卡提到柯西凝聚判别法背后还有**dialectic分解**思路，但视频中未展开。
-- 皮卡提到证明调和级数发散还有积分估计、差分等其他流派，但未详细展开。</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>7465/1267</t>
-        </is>
-      </c>
+      <c r="C14" s="4" t="n"/>
     </row>
     <row r="15" ht="13.5" customHeight="1" s="9">
       <c r="A15" s="6" t="inlineStr">
@@ -4466,60 +4157,7 @@
           <t>知识笔记</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t># 知识主题与概述
-本次分享会由老李主讲，围绕GitHub的实用热门项目推荐、访问加速、页面汉化、搜索优化及项目页面解读展开，旨在帮助成员高效利用GitHub资源。老李推荐了多个实用项目，包括评估工作性价比的“B班值不值得上”、表情包博物馆、健康指南、一键证件照、自重健身动画、国内教材PDF合集、全自动视频生成项目Morning Printer Turbo、声音克隆模型ChatBox TTS、AI学习资源库（含500多页PDF教程）以及Awesome AI Apps（收录医学影像分析、AI投资、竞争对手情报分析等Agent应用）。针对国内访问GitHub卡顿问题，老李分享了三种方法：使用Watt Toolkit加速软件、使用GitHub镜像站（如gh-proxy）、以及使用魔法（科学上网），并个人最推荐第三种方法。针对GitHub全英文页面，推荐安装浏览器翻译插件（如谷歌翻译、沉浸式翻译）或汉化插件；针对原生搜索精准匹配对国人不好用的问题，推荐使用AI工具（如ChatGPT）用中文描述需求进行搜索。老李还讲解了GitHub项目页面的基本概念：项目本质是文件夹，watch关注、fork复制、star收藏点赞，about为简介，release为安装包，readme为说明书（默认在项目最下面展开），文件最近commit日期可判断项目是否维护，explore的trending可查看热门项目，也可用ChatGPT获取GitHub daily最新项目。
-# 核心概念
-## B班值不值得上
-- 评估工作性价比的项目，输入**年薪**、**工作地区**、**年假**、**通勤时长**、**学历**、**工作年限**、**领导同事们是否SB**等因素，综合给出**工作性价比分数和评级**。
-- 示例：老李测试程序员工作，评估结果为“性价比还不错，优质牛马”。
-## 表情包博物馆
-- 收录国内过去这些年**全网爆火的表情包大合集**，包括甄嬛传、罗翔老师、特朗普、马保国等表情包。
-## 健康指南（活到150岁）
-- 分享经过**科学研究证实**的健康知识，如**间歇性进食**促进胆汁代谢、炎症自愈，**天然发酵类食品**改善肠道菌群生态。
-## 一键证件照
-- 上传一张大头照，可**一键抠图换背景**，生成不同标准的证件照和**各种规格的打印模板**。
-## 自重健身教练
-- 选择要练习的肌肉群（如腹肌），提供**身体自重练习的参考动画**，适合请不起真人教练的用户。
-## 教材PDF合集
-- 收集国内所有**小学、初中、高中及部分大学**的PDF教材，**全部免费**使用。
-## Morning Printer Turbo
-- 最近超火的**全自动视频生成项目**。
-## ChatBox TTS
-- **零样本语音克隆**模型，**情感控制非常到位**，克隆的声音像真人说话；上传音频可合成英文台词。
-## AI学习资源库
-- 涵盖**大语言模型、RAG、AI Agents、MSI**等最新AI技术，作者整理成**500多页的PDF文档**，含大量示意图。
-## Awesome AI Apps
-- 收录大模型最新的**Agent应用**，如**医学影像数据分析Agent**、**AI投资Agent**、**竞争对手情报分析Agent**等，可跟进AI应用落地案例或找创业点子。
-## Watt Toolkit
-- **GitHub加速软件**：进入网站选择适合电脑的版本下载安装，打开后找到**网络加速**，勾选**GitHub加速**即可流畅访问。
-## GitHub镜像站（gh-proxy）
-- 浏览器直接访问即可上GitHub，默认是镜像的项目地址，也可搜索其他项目；**速度和稳定性较差**。
-## 魔法（科学上网）
-- 老李个人最推荐的方法；需注册GitHub账号，用**国内QQ邮箱**即可注册。
-## 浏览器翻译插件
-- 谷歌浏览器推荐**谷歌翻译**或**沉浸式翻译**，安装后可将网页翻译成中文；也可安装**汉化插件**。
-## GitHub原生搜索
-- 按**关键词精准匹配**排序，默认按匹配度，常用按**star数**排序；对国人不好用，如搜`screen record`和`screen recording`结果不同。
-## AI搜索（ChatGPT）
-- 用中文描述需求（如“在GitHub上帮我找好用的录屏软件”），AI可总结热门项目并整理成表格。
-## GitHub项目页面
-- 项目本质是**文件夹**；`watch`关注、`fork`复制、`star`收藏点赞；`about`是简介；`release`是安装包；`readme`是说明书，默认在项目最下面展开；每个文件有**最近commit日期**，可判断是否维护。
-## Explore Trending
-- 左侧`explore`的`trending`可看**当天、本周、本月**最热门项目；也可用ChatGPT找**GitHub daily**获取最新热门项目。
-# 核心结论
-核心结论：GitHub是巨大的宝藏资源库，包含教程、工具、开源大模型、面试题等资源；国内访问可用Watt Toolkit、镜像站或魔法加速，老李最推荐魔法；页面汉化用翻译插件或汉化插件；搜索推荐用AI工具（如ChatGPT）而非原生搜索。易混淆点：`watch`是关注、`fork`是复制、`star`是收藏点赞，三者功能不同；`release`是安装包，`readme`是说明书；文件最近`commit`日期可判断项目是否维护，更新日期久远则可能是僵尸项目。待澄清问题：魔法（科学上网）的具体操作未详细说明；镜像站地址整理在文档中，但未在原文列出具体网址。</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>4014/2399</t>
-        </is>
-      </c>
+      <c r="C15" s="4" t="n"/>
     </row>
     <row r="16" ht="13.5" customHeight="1" s="9">
       <c r="A16" s="6" t="inlineStr">

--- a/test_sample.xlsx
+++ b/test_sample.xlsx
@@ -568,48 +568,57 @@
       <c r="C2" s="4" t="inlineStr">
         <is>
           <t># 发布会概况
-王毅在慕尼黑安全会议上发表演讲并回答提问，主题为世界走向多极化，中国主张推动平等有序的世界多极化，这是习近平主席提出的重大主张。王毅表示中国必将是多极体系中的确定性因素，坚定做变革世界中的建设性力量，并提出4点看法：倡导平等相待、尊重国际法治、践行多边主义、坚持开放共赢。演讲后王毅就国际秩序、乌克兰危机、中美关系等问题回应提问，强调中国维护以联合国为核心的国际体系，坚持劝和促谈，对美政策保持连续性和稳定性。整体基调坚定务实，既宣示中国立场，也回应国际关切。
+王毅在慕尼黑安全会议上发表演讲并回答提问，阐述中国推动平等有序世界多极化的主张。他指出世界正走向多极化，80年前联合国成立时只有51个会员国，今天是193个国家，中国主张推动平等有序的世界多极化，这是习近平主席提出的重大主张。王毅提出四点看法：倡导平等相待、尊重国际法治、践行多边主义、坚持开放共赢。中国加入了几乎所有普遍性的政府间国际组织和600多项国际公约，承担超过20%的联合国会费，建成世界上最大的清洁发电体系。去年中国GDP增长5%，对世界经济增长贡献率接近30%。在问答环节，王毅回应了关于国际秩序、乌克兰危机和中美关系等提问，强调中国坚持维护联合国权威和国际法治，在乌克兰问题上坚持劝和促谈，对美政策保持连续性和稳定性。
 # 核心信息
-- 世界正走向多极化：**80年前**联合国成立时仅**51个**会员国，今天已有**193个**国家；中国主张推动平等有序的世界多极化，这是习近平主席提出的重大主张。
-- 中国是现行国际秩序的受益者，加入几乎所有普遍性政府间国际组织和**600多项**国际公约，从不搞例外主义，也不搞合则用、不合则弃。
-- 中国坚定维护联合国权威和地位，承担超过**20%**的联合国会费；切实履行`巴黎协定`，建成世界上最大的清洁发电体系。
-- 去年中国GDP增长**5%**，对世界经济增长贡献率接近**30%**，担当全球经济增长的重要引擎，向世界释放超大规模市场红利。
-- 中国愿推动高质量共建`一带一路`，与欧盟`全球门户`战略相互对接，赋能彼此也赋能世界。
+- 世界正走向多极化：80年前联合国成立时只有**51个**会员国，今天是**193个**国家，共乘一艘大船。
+- 中国主张推动**平等有序的世界多极化**，这是习近平主席提出的重大主张，中国必将是多极体系中的确定性因素。
+- 中国加入了几乎所有普遍性的政府间国际组织和**600多项**国际公约，从不搞例外主义，更不搞合则用、不合则弃。
+- 中国承担超过**20%**的联合国会费，切实履行`巴黎协定`，建成了世界上最大的清洁发电体系。
+- 去年中国GDP增长**5%**，对世界经济增长的贡献率接近**30%**，担当起全球经济增长的重要引擎。
+- 中国愿推动高质量共建`一带一路`，同欧盟的`全球门户`战略相互对接，赋能彼此也赋能世界。
 - 中国提出并落实`全球发展倡议`、`全球安全倡议`、`全球文明倡议`，为完善全球治理提供公共产品。
-- 关于乌克兰危机，**2022年2月25日**中方即提出对话协商解决；习近平主席提出4点主张：各国主权领土完整应得到尊重、联合国宪章应得到遵守、各国合理安全关切应得到重视、一切致力于和平的努力都应得到支持。
+- 今年是中欧建交**50周年**，中方愿意同欧方用好这一契机，深化战略沟通和互利合作。
 # 官方表态
-**多极化主张**
-- 王毅表示，多极化的世界既是历史的必然，也正在成为现实；中国给出的答案是我们应当推动平等有序的世界多极化，这是习近平主席提出的又一个重大主张，也是我们对多极世界真诚的期许。
+**关于多极化世界**
+- 王毅表示，多极化的世界既是历史的必然，也正在成为现实，中国给出的答案是我们应当推动平等有序的世界多极化。
 &gt; 中国必将是多极体系中的确定性因素。将坚定做变革世界中的建设性力量。
-- 王毅提出4点看法：一是应当倡导平等相待，坚持权利平等、机会平等、规则平等，应当成为建设多极世界的基本原则；二是应当尊重国际法治，联合国宪章宗旨和原则是国际关系的根本遵循，也是建设多极世界的重要基石；三是要践行多边主义，联合国是践行多边主义、推进全球治理的核心平台，对于这座大厦我们应该固本强基，而不是拆梁毁柱；四是要坚持开放共赢，发展是破解各种难题的钥匙，多极世界应该是各国共同发展的世界。
-**国际秩序与规则**
-- 王毅表示，中国是在现行国际秩序中发展起来的，是这个秩序的受益者；我们要做的就是按照大多数国家的愿望，推动这个秩序朝着更加公正合理的方向去发展。
-&gt; 我们需要共同来维护以联合国为核心的国际体系。共同遵守以联合国宪章宗旨和原则为基础的国际关系的基本准则。我想这应该是我们的最大的公约数。
-- 王毅强调，在遵守国际法上不能搞双重标准，要尊重各国的主权和领土完整，就应该支持中国实现完全统一。
-**乌克兰危机**
-- 王毅表示，中国同俄罗斯是两大邻国，建立结盟不对抗、不针对第三方的睦邻友好关系，进而增进战略互信，建立全面战略伙伴关系。
-- 王毅指出，中国历来主张一切争端和冲突都应该通过对话寻求政治解决，因为武力和制裁不可能真正和彻底的解决问题，乌克兰问题上同样如此。
-&gt; 任何冲突的终点都是谈判桌，历史最终一定是公正的。中方乐见一切致力于和平的努力。
-- 王毅表示，中国派出的特使去各国斡旋，同巴西等南方国家发起了和平之友；所有当事方包括利益攸关方，都应该适时的参与到这个和谈的进程当中。
-**中美关系**
-- 王毅表示，中国的对美政策保持着连续性和稳定性，我们不会轻易的翻烙饼；对美政策就是习近平主席提出的三原则：相互尊重、和平共处、合作共赢。
-&gt; 中方已经准备好了，我们愿意按照三原则同美方构建稳定健康可持续的双边关系，找到两个大国在这个星球上的正确相处之道。
-- 王毅强调，如果美方仍然还要对中国打压和遏制，那我们也别无选择，我们必将奉陪到底；必将坚定的维护中国的主权、国家的尊严和我们的正当发展权利，必将坚决的回击美方的单边和霸凌的行径。
+- 倡导平等相待：坚持权利平等、机会平等、规则平等，应当成为建设多极世界的基本原则；中国主张大小国家一律平等，呼吁提升发展中国家在国际体系中的代表性和发言权。
+- 尊重国际法治：联合国宪章宗旨和原则是处理国际关系的根本遵循，也是建设多极世界的重要基石；国家不论大小强弱，都是国际法治的利益攸关方。
+&gt; 如果没有了规矩，昨天在餐桌上明天就可能在菜单里。
+- 践行多边主义：联合国是践行多边主义、推进全球治理的核心平台，已经为各国遮风挡雨80年；对于这座大厦，我们应该固本强基，而不是拆梁毁柱。
+- 坚持开放共赢：发展是破解各种难题的钥匙，多极世界应该是各国共同发展的世界。
+&gt; 保护主义不是出路，滥加关税没有赢家。脱钩断链断的是机遇，小院高墙封的是自己。
+**关于国际秩序与规则**
+- 王毅表示，中国是现行国际秩序的受益者，要推动这个秩序朝着更加公正合理的方向去发展。
+&gt; 我们需要共同来维护以联合国为核心的国际体系。共同遵守以联合国宪章宗旨和原则为基础的国际关系的基本准则。
+- 强调在遵守国际法上不能搞双重标准，要尊重各国的主权和领土完整，就应该支持中国实现完全统一。
+**关于乌克兰危机**
+- 王毅表示，中国同俄罗斯是两大邻国，建立了结盟不对抗、不针对第三方的睦邻友好关系，中国同俄罗斯之间的交往是正常的国与国之间的交往。
+&gt; 我们历来主张一切争端和冲突都应该通过对话寻求政治解决。因为武力和制裁不可能真正和彻底的解决问题。
+- 中方从2022年2月25日（危机爆发第2天）就提出对话协商解决，习近平主席提出的4点主张是中国立场的最权威的阐释。
+&gt; 各国的主权领土完整应该得到尊重，联合国的宪章应该得到遵守。各国的合理安全关切应该得到重视。一切致力于和平的努力都应该得到支持。
+- 中方派出的特使去各国斡旋，同巴西等南方国家发起了`和平之友`。
+&gt; 任何冲突的终点都是谈判桌，历史最终一定是公正的。
+**关于中美关系**
+- 王毅表示，中国的对美政策保持着连续性和稳定性，不会轻易翻烙饼，这体现了作为大国的战略定力和国际信誉。
+&gt; 我们的对美政策就是习近平主席提出的三原则，相互尊重，和平共处。合作共赢。
+- 中方已准备好按照三原则同美方构建稳定健康可持续的双边关系，找到两个大国在这个星球上的正确相处之道。
+&gt; 如果美方不愿意，如果美方仍然还要对中国打压和遏制，那我们也别无选择，我们必将奉陪到底。
 # Q&amp;A环节
-**问**：周琦提问，当前国际秩序受到质疑，包括俄罗斯入侵乌克兰、美国总统威胁使用武力等；王毅即将前往纽约参加安理会会议，是否仍相信联合国和联合国宪章？是否将推动联合国改革？
-**答**：王毅表示，真正要挑战秩序、毁约退群的国家出现了，而中国是在现行国际秩序中发展起来的，是受益者，要推动秩序朝更加公正合理方向发展。谈到规则，应共同维护以联合国为核心的国际体系，遵守以联合国宪章宗旨和原则为基础的国际关系基本准则，这是最大的公约数；只要认同这一点，双重标准就不会出现。习近平主席提出全球发展倡议、全球安全倡议、全球文明倡议，希望国际社会携手解决发展赤字、安全赤字、治理赤字，共同构建人类命运共同体。
-**问**：周琦提问，自2022年以来慕安会持续关注俄罗斯入侵乌克兰；王毅此前曾确认乌克兰的主权、独立和领土完整应受尊重，如今俄罗斯已成为中国加油站（带军队的加油站），中国对乌克兰有很大影响力；在当前压力下，中国能否从自身角度切断俄罗斯向中国供应天然气的可能、降低价格或停止输送军民两用物资，以加大对俄施压、促其结束战争？
-**答**：王毅表示，中国同俄罗斯是两大邻国，建立结盟不对抗、不针对第三方的睦邻友好关系，交往是正常的国与国之间的交往；如果中国不从俄罗斯买油气，没有哪个国家能提供如此巨量的油气来满足中国民众的需求，那是不可能的，也是不保险的，因为常有国家把经贸问题政治化，当做打压中国的工具。中国在对待地区热点问题上有自己的立场，历来主张一切争端和冲突都应通过对话寻求政治解决，武力和制裁不可能真正彻底解决问题；从2022年2月25日起中方就提出对话协商解决，习近平主席提出的4点主张是中国立场的最权威阐释。中国以此推进劝和促谈，派特使斡旋，同巴西等南方国家发起和平之友；中方乐见一切致力于和平的努力，包括美国同俄罗斯达成的共识，同时认为所有当事方包括利益攸关方都应适时参与和谈进程，欧洲更有必要为此发挥重要作用，共同探讨欧洲的长治久安。
-**问**：周琦提问，能否预告中美关系将如何发展？
-**答**：王毅表示，中国的对美政策保持连续性和稳定性，不会轻易翻烙饼，这体现大国的战略定力和国际信誉；对美政策是习近平主席提出的三原则：相互尊重、和平共处、合作共赢。中美制度不同是各自人民做出的选择，想改造或颠覆对方不切实际；中方已准备好按三原则同美方构建稳定健康可持续的双边关系，希望美方相向而行；但如果美方仍对中国打压遏制，中国别无选择，必将奉陪到底，坚决回击美方单边霸凌行径，这也是为了维护国际公平正义和国际关系基本准则。</t>
+**问**：主持人提问，中国是否继续相信联合国和联合国宪章，是否推动联合国改革？
+**答**：王毅表示，中国是现行国际秩序的受益者，要推动这个秩序朝着更加公正合理的方向去发展。我们需要共同维护以联合国为核心的国际体系，共同遵守以联合国宪章宗旨和原则为基础的国际关系基本准则，这是最大的公约数。只要大家都认同这一点，有些人所说的双重标准就不会出现。习近平主席提出了一系列重大倡议和主张，包括全球发展倡议、全球安全倡议、全球文明倡议，希望国际社会携手解决发展赤字、安全赤字和治理赤字。习主席还提出了构建人类命运共同体的重大理念，希望各国超越历史文化社会制度意识形态的不同，共同建设好命运与共的地球村。
+**问**：主持人引用王毅此前关于尊重乌克兰主权和领土完整的言论，称俄罗斯已成为中国的加油站，提问中国是否可减少购买俄罗斯油气或停止双用途物资以施压俄罗斯。
+**答**：王毅表示，中国同俄罗斯是两大邻国，建立了结盟不对抗、不针对第三方的睦邻友好关系，中国同俄罗斯之间的交往是正常的国与国之间的交往。他反问，如果中国不从俄罗斯买油气，哪个国家能够提供如此巨量的油气来满足中国民众的需求？那是不可能的，也是不保险的，因为常常有的国家把经贸问题政治化，当做打压中国的工具。但中国在对待地区热点问题上有自己的立场，历来主张一切争端和冲突都应该通过对话寻求政治解决。从2022年2月25日（危机爆发第2天）开始，中方就提出对话协商解决，习近平主席提出的4点主张是中国立场的最权威的阐释。中方派特使去各国斡旋，同巴西等南方国家发起了和平之友。中方乐见一切致力于和平的努力，包括美国同俄罗斯达成的共识，同时认为所有当事方包括利益攸关方都应该适时参与到和谈进程当中。这场战事发生在欧洲大地上，欧洲更有必要为此发挥重要的作用，共同探讨欧洲的长治久安，找到均衡有效可持续的欧洲安全框架。
+**问**：主持人请王毅预告中美关系将如何发展。
+**答**：王毅表示，中国的对美政策保持着连续性和稳定性，不会轻易翻烙饼，这体现了作为大国的战略定力和国际信誉。对美政策就是习近平主席提出的三原则：相互尊重、和平共处、合作共赢。中美两国制度不一样，是各自人民做出的选择，如果想改造或颠覆对方是不切实际的。正确的态度就是相互尊重，这是中美交往的前提；和平共处更是理所当然，中美两个大国总不能冲突起来，因为那将殃及整个世界；合作共赢是因为国际社会期待中美开展合作，全球性挑战也需要中美携手应对。中方已经准备好了，愿意按照三原则同美方构建稳定健康可持续的双边关系。如果美方不愿意，仍然还要对中国打压和遏制，那我们也别无选择，必将奉陪到底，坚决维护中国的主权、国家的尊严和正当发展权利，坚决回击美方的单边霸凌行径。</t>
         </is>
       </c>
       <c r="D2" s="10" t="n">
-        <v>61.4</v>
+        <v>57.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>7004/2837</t>
+          <t>7004/3015</t>
         </is>
       </c>
     </row>
@@ -776,56 +785,29 @@
       <c r="C3" s="4" t="inlineStr">
         <is>
           <t># 沟通背景与目的
-电子科技大学电子科学与工程学院举办招生宣讲会，面向考生和家长介绍学院整体情况、学科方向、师资科研与人才培养。段院介绍学院源于1956年建校时的无线电系、电真空器件系、无线电零件系，经四次院系调整成立，一级学科电子科学与技术为国家重点一级学科，下设5个二级学科方向；现有本科生1545人、研究生1975人，教师302人，近5年科研到账经费稳定在3-4亿元/年。柳教授介绍电子信息材料与元器件方向，指出2021年中国集成电路电子产品进口额达2.8万亿元，属卡脖子问题之一。张教授介绍电磁场与微波技术、电路与系统方向，学科始于1956年，拥有6个团队及先进微波暗室群体。李天明教授介绍物理电子学方向，每年到校科研经费接近2亿元，为学院最多。在读博士田雨桐分享选择电子学院的8个理由，包括成都产业环境、学科A+评级、团队100%就业率等。会议达成共识：学院计划今年举办夏令营，时间待定，相关信息通过QQ群（978499108）发布。
+电子科技大学电子科学与工程学院举办招生宣讲会，面向考生和家长介绍学院整体情况、学科方向、师资科研与人才培养。段院介绍学院历史沿革、学科设置、师资规模与科研平台；柳教授介绍电子信息材料与元器件方向；张教授介绍电磁场与微波技术和电路与系统方向；李天明教授介绍物理电子学方向；在读博士田雨桐分享选择电子学院的8个理由。宣讲会达成吸引优秀生源的目的，并明确今年计划举办夏令营、时间待定，相关信息将通过QQ群（978499108）发布。
 # 信息同步
-**段院（学院整体情况）**
-- 学院历史：1956年建校时成立无线电系、电真空器件系、无线电零件系，经1979、1992、2001、2018年四次院系调整成立电子科学与工程学院，2023年成立电子科学与工程学院与集成电路学院。
-- 学科设置：一级学科电子科学与技术为国家重点一级学科，下设电磁场与微波技术、电路与系统、微电子学与固体电子学、物理电子学、电磁信息功能材料与机构5个二级学科方向，另有3个国防特色学科。
-- 人才培养：本科生1545人，招生专业为工科试验班（电子工程类），含电子科学与技术（国家特色专业、国家级一流本科专业建设点）和电磁场与无线技术两个专业方向；研究生1975人，学硕/博士专业为电子科学与技术、材料科学与工程，专硕/博士为电子信息、材料工程。
-- 师资队伍：教师302人（教研系列139人、科研系列95人、教学系列14人、实验系列21人、机关33人），两院院士2人、领军人才19人、青年人才28人、其他类型人才12人、博士后61人。
-- 科研实力：近5年科研到账经费稳定在3-4亿元/年，以纵向项目为主；牵头获国家科技奖励11项，近5年发表高水平论文2000余篇，专利申请1600余件、授权1300余件；20个科研团队中年度经费过千万元的15个、过亿元1个。
-- 平台与交流：拥有国家电磁辐射控制材料工程技术研究中心、微波电子器件国家级重点实验室2个国家级平台，4个国际合作平台、7个省部级科研平台；共建国际姊妹院系2个（香港大学电机工程电子系、香港城市大学电子工程系），主办高水平国际会议13场，学生长短期交流项目20多个。
-**柳教授（电子信息材料与元器件方向）**
-- 方向内涵：以电子在物质中的输运特性（电磁声光热力、化学生物）为基础，设计、研究和生产电子器件，以材料为基础、器件为核心、应用为目标导向。
-- 产业背景：2021年中国集成电路电子产品进口额达2.8万亿元，约为原油进口量的1.7倍，先进电子材料元器件电路系统是卡脖子问题之一；应用覆盖6G通讯、量子技术、智慧城市、光电技术、新能源、智能电子等领域，市场规模达万亿美元量级。
-- 发展趋势：元器件向微型化、片式化、集成化、薄膜化、智能化发展，强调材料和器件一体化，结合摩尔定律与超摩尔定律。
-- 研究队伍：国家级人才10余人；邓龙江院士电磁辐射控制材料与技术团队19人（正高13人、副高15人），近年发表包括Nature在内的论文300余篇，承担课题130余项，年均到账经费3000多万元，授权发明专利100余项，获国家科技进步奖或技术发明奖二等奖共3项；张怀武教授磁电薄膜与微型器件团队17人（正高15人、副高2人），开展LTCC材料及集成技术、微波毫米波晶圆及器件、自旋电子与磁量子器件、传感器芯片等研究，承担项目100余项，获科技进步二等奖3项，发表SCI论文400余篇，年均到账经费2000余万元。
-- 平台与条件：依托国家电磁辐射控制材料工程技术研究中心（可追溯至1990年校级中心，经2008、2013年两次升级）和电磁薄膜与集成器件全国重点实验室（2006年筹建，三个重点方向为电子聚合物与阵列传感器、功率半导体与集成技术）；科研面积2万余平米（超精尖3000平），建设两条国家重大任务试验生产线，大型设备/系统500余台套。
-- 成果与去向：获国家技术发明奖等共7项，每年在Nature及子刊发表多篇重要文章；毕业生去向包括英特尔、中芯国际、华为、德州仪器等企业及高校科研院所。
-- 学生案例：杨伟豪以第一作者在Nature Electronics、Nature Communications各发表一篇论文；5G滤波器芯片学生团队获挑战杯创新创业大赛四川省金奖；黄飞（2018年四川省优秀毕业生）获斯坦福大学博士全额奖学金；李凤霞读博期间发表论文16篇（一作6篇）；严巍获华为光产线优秀合作项目奖、王大珩光学奖，博士毕业后以优秀青年学者身份加入苏州大学；万位现任河北美泰电子科技公司副总，带领团队采用MEMS工艺研制出SIW环形器隔离器，突破卡脖子器件核心技术。
-**张教授（电磁场与微波技术、电路与系统方向）**
-- 方向构成：电磁场与微波技术含微波毫米波电路、电波传播与电磁兼容、计算电磁学与工程电子学、天线理论与技术4个细分方向；电路与系统含非线性电路与复杂电子系统、射频微波电路与系统、集成电路与系统3个方向。
-- 学科沿革：电磁场与微波技术学科始于1956年建校时期，由林为干先生和谢处方先生创建，形成电磁场与无线技术国家特色专业和电波传播与天线国防紧缺特色专业，所属一级学科电子科学与技术入选双一流A类。
-- 团队与平台：电磁场与微波技术有6个团队（电磁辐射与散射、毫米波技术与系统应用、微波毫米波集成电路与系统、电磁兼容、微波测试与成像、无线技术与集成系统）；拥有国家自然基金委创新群体、国家高等学校学科创新引智基地、国家工程技术研究中心、国家级重点实验室，以及中国高校最先进的微波暗室群体和微波毫米波太赫兹仿真测试平台。
-- 代表性成果：杨世文教授团队四维天线阵列技术、强耦合超宽带相控阵（应用于中电14所某大型机载相控阵雷达）、电磁测井仪器（获国家科技进步二等奖，在中海油推广应用）、计算电磁学（算法被评为20世纪十大算法之一）；樊勇教授团队太赫兹雷达成像（0.22THz、0.34THz、0.42THz系统，分辨率小于1厘米）、太赫兹通信（2023年成都大运会田径项目示范应用）；李恩教授团队微波毫米波测量技术（60多年积累）、生物医学电磁学及成像（20余项国家发明专利）；延波教授团队微波毫米波太赫兹芯片（应用于新一代高速通信系统）、三毫米导引头前端、毫米波引信前端、8毫米宽带收发前端。
-- 电路与系统学科：1981年开始招收研究生，1988年成立首批博士后流动站，含教育部国际合作联合实验室、国家高等学校学科创新引智基地，国家级人才4人、新世纪人才2人、教授10人、副教授22人；樊勇教授和李廷军教授团队研制高速磁浮交通38GHz车地通信系统，樊勇教授和张静团队研究毫米波通信雷达CMOS芯片，康凯教授团队研制超宽带模块级芯片及5G通信和雷达系统。
-- 人才培养：连续三年获全国大学生集成电路创新创业大赛奖项，获华为优秀合作项目奖、研究生优秀导学团队提名奖，学生获互联网+、国际HPV等奖项；就业覆盖华为、中兴等领军企业、研究所、高校，海外留学有突破。
-**李天明教授（物理电子学方向）**
-- 学科定义：物理电子学是物理学与电子科学与技术的交叉学科，将物理学最新研究成果应用于电子学产生新电子器件，如微波电子学（微波电真空器件）、光电子学（光电器件）；特点为基础性与前沿性，支撑现代信息技术。
-- 历史沿革：起源于1956年建校时在苏联专家帮助下成立的电子器件专业，归属电子器件系；1979年在刘盛纲院士带领下成立高能电子学研究所；2001年物理系、应用所、高能所成立物理电子学；2018年成立电子科学与工程学院。
-- 发展现状：发展近70年，纵向扩展至上游仿真设计、下游系统应用，拥有自主知识产权商用软件MMST和切皮克，并引入人工智能到器件设计；系统应用包括毫米波雷达（回旋行波管）、无线输能系统（行波管）、微波能干燥系统（磁控管）；横向拓展至毫米波、太赫兹频段，太赫兹成像用于医学诊断，太赫兹通信用于保密通信、高速通信。
-- 科研与地位：每年到校科研经费接近2亿元，为学院最多；是国际上最大的真空器件研究中心，2023年成功举办行业顶级会议；方向共9个团队。
-- 学生出口：团队学生约1/3硕博连读、1/3去企业、1/3去研究所或其他（公务员等）；个人每年约2个硕士毕业、1个博士毕业。
-**田雨桐（在读博士，学生视角）**
-- 城市因素：成都是四川省会、国家中心城市、新一线城市、国家历史文化名城、古蜀文明发祥地、中国十大古都之一，宣传标语“成都都成”指梦想都成；电子信息产业发达，英特尔、华为、京东方等巨头汇聚，提供实践平台和就业资源。
-- 学校与专业：电子科技大学是我国电子信息人才培育的代名词，有电子信息博物馆记录我国第一台晶体管收音机的诞生，构建了最完整的电子信息学科群；电子科学与技术学科在第4轮学科评估中获A+、稳居全国第一，拥有五大国防特色学科。
-- 团队与个人研究：所在毫米波技术与系统应用团队在樊勇老师带领下，围绕微波毫米波理论与技术、天线理论与技术、元器件与电路、通信技术与系统、雷达成像技术与系统五大方向开展研究；本人从事毫米波雷达通信信号处理研究，可做雷达或无线通信系统，团队硕博毕业生实现100%就业率。
-- 校园生活与奖助：东湖钢琴小屋、2021年跨年300架无人机灯光秀拼出UESTC字样；奖助体系全覆盖、高额度、长周期，含国家奖学金、学业奖学金、专项奖学金、新生奖学金、校园地国家助学贷款、生源地助学贷款等。
-- 择校建议：先选研究团队再选导师，可从学院网站按兴趣选择团队，再进入团队网页找导师；导师信息不完整时可用IEEE Xplore和中国知网检索导师论文和指导研究生情况。
+**段院（学院整体情况）**：学院源于1956年建校时成立的无线电系、电真空器件系、无线电零件系，经1979、1992、2001、2018年四次院系调整成立，2023年成立电子科学与工程学院与集成电路学院；一级学科电子科学与技术为国家重点一级学科，下设电磁场与微波技术、电路与系统、微电子学与固体电子学、物理电子学、电磁信息功能材料与机构5个二级学科方向，另有3个国防特色学科。现有本科生1545人（招生专业为工科试验班电子工程类，含电子科学与技术、电磁场与无线技术两个专业方向）、研究生1975人；教师302人（教研系列139人、科研系列95人、教学系列14人、实验系列21人、机关33人），高层次人才含两院院士2人、领军人才19人、青年人才28人；近5年科研经费到账稳定在3-4亿元，牵头获国家科技奖励11项，发表高水平论文2000余篇，拥有2个国家级平台、4个国际合作平台、7个省部级科研平台。
+**柳教授（电子信息材料与元器件方向）**：方向以电子在物质中的输运特性为基础，以材料为基础、器件为核心、应用为目标导向；2021年中国集成电路电子产品进口额度达2.8万亿元，约为原油进口量的1.7倍，先进电子材料、元器件、电路系统是我国最紧迫的卡脖子问题之一。方向拥有国家级人才10余人，两大团队为邓龙江院士的电磁辐射控制材料与技术团队（研究人员19人，年均到账经费3000多万元，获国家科技进步/技术发明二等奖共3项）和张怀武教授的磁电薄膜与微型器件团队（研究人员17人，年均到账经费2000余万元，获科技进步二等奖3项）；依托国家电磁辐射控制材料工程技术研究中心和电磁薄膜与集成器件全国重点实验室，科研面积2万余平米（超净间3000平），建设两条国家重大任务试验生产线，大型设备/系统500余台套；毕业生去向包括英特尔、中芯国际、华为、德州仪器等企业及高校科研院所。
+**张教授（电磁场与微波技术、电路与系统方向）**：电磁场与微波技术含微波毫米波电路、电波传播与电磁兼容、计算电磁学与工程电子学、天线理论与技术4个细分方向，电路与系统含非线性电路与复杂电子系统、射频微波电路与系统、集成电路与系统3个方向；学科始于1956年建校时期，由林为干先生和谢处方先生创建，所属一级学科电子科学与技术入选双一流A类学科。电磁场与微波技术有6个团队，硬件平台含中国高校最先进的微波暗室群体；代表性成果包括杨世文教授团队四维天线阵列技术应用于中电14所某大型机载相控阵雷达、樊勇教授团队研制0.22THz/0.34THz/0.42THz雷达成像系统（分辨率小于1厘米）、太赫兹通信成果在2023年成都大运会田径项目示范应用等；电路与系统学科1981年开始招收研究生，1988年成立首批博士后流动站，拥有国家级人才4人、教授10人、副教授22人，研究方向含高速磁浮交通38GHz车地通信系统、毫米波通信雷达CMOS芯片等；人才培养连续三年获全国大学生集成电路创新创业大赛奖项，就业面向华为、中兴等领军企业、研究所、高校。
+**李天明教授（物理电子学方向）**：物理电子学是物理学与电子科学与技术的交叉学科，将物理学最新研究成果应用于电子学产生新电子器件；学校物理电子学起源于1956年建校时在前苏联专家帮助下成立的电真空器件专业，1979年刘盛纲院士带领成立高能电子学研究所，2018年成立电子科学与工程学院。方向纵向发展（上游仿真设计、数字模拟材料，下游系统应用，拥有自主知识产权商用软件MMST和切皮克，引入人工智能到器件设计和电子学应用），横向发展（频段从微波上移到毫米波、太赫兹，与医学交叉利用太赫兹成像提高诊断准确性）；每年到校科研经费接近2亿元，在学院中最多，是国际上最大的真空器件研究中心，2023年成功举办行业顶级会议，物理电子学方向共9个团队；团队学生约1/3硕博连读、1/3去企业、1/3去研究所或其他。
+**田雨桐（在读博士，学生视角）**：成都是四川省会、国家中心城市、新一线城市，电子信息产业发达，英特尔、华为、京东方等巨头汇聚；电子科技大学是我国电子信息人才培育的代名词，构建了最完整的电子信息学科群；电子科学与技术学科在第4轮学科评估中获A+，稳居全国第一；其所在毫米波技术与系统应用团队在樊勇老师带领下围绕五大方向开展研究，团队硕博毕业生实现100%就业率；学院构建全覆盖、高额度、长周期的奖助体系；建议先选择研究团队再选择导师，可通过学院网站、文献检索网站（如IEEE、中国知网）了解导师论文和指导研究生情况。
 # 达成共识
-**段院承诺**：电子学院计划今年举办夏令营活动，时间待定，感兴趣的同学可加入QQ群，相关信息会及时发布。
-&gt; 段院原话：“我们电子学院呢要计划就是今年会计划这个夏令营活动时间还待定，希望呢同学们感兴趣的话呢加入我们这个QQ群相关的信息呢，我们会到时会及时的发布。”
-**主持人补充**：QQ群号为978499108，同学们可添加学院QQ群进行详细咨询和了解。
+**电子学院计划今年举办夏令营活动，时间待定**，相关信息将通过QQ群（978499108）及时发布。段院原话："我们电子学院呢要计划就是今年会计划这个夏令营活动时间还待定，希望呢同学们感兴趣的话呢加入我们这个QQ群相关的信息呢，我们会到时会及时的发布。"
 # 待协调事项
-**夏令营活动组织**：电子学院计划今年举办夏令营，具体时间和形式尚未确定，需学院后续确定并发布。对接人：段院；负责人：段院；预计完成时间：未明确；后续沟通计划：相关信息将通过QQ群（978499108）发布。</t>
+**事项1：夏令营活动组织**
+- 事项描述：电子学院计划今年举办夏令营活动，具体时间和形式尚未确定。
+- 对接人：段院
+- 负责人：段院
+- 预计完成时间或后续沟通计划：时间待定，相关信息将通过QQ群（978499108）发布。</t>
         </is>
       </c>
       <c r="D3" s="10" t="n">
-        <v>98.7</v>
+        <v>84.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>13887/4473</t>
+          <t>13887/2367</t>
         </is>
       </c>
     </row>
@@ -1362,35 +1344,34 @@
       <c r="C4" s="4" t="inlineStr">
         <is>
           <t># 复盘目标与结果概况
-本次年会复盘2023年公司经营状况与员工表现。预期目标为总结全年发展、公布数据并发放年终奖与奖项。实际结果：年终奖总额226,000元，全年实打实支出390万元，利润率约24%或27%，成本控制差是最大问题；公司总量提升，但结余到账往下跑，还有百来万未收回，老板比去年少拿约10万元并承担亏损100万元。会上按短视频、执行、商务三部门逐一评价，肯定员工克服困难与整体表现，颁发最佳新人、最佳进步、后期独当一面、最佳员工、特别贡献奖共6人5项奖，并抽奖15个奖品。成本控制问题留待明年再议。
+本次年会复盘2023年公司经营与团队表现。预期目标为总结发展状况、公布数据、评价员工并发放年终奖与奖项。实际结果：年终奖转账总额226,000元，全年支出390万元，利润率约24%或27%，成本控制差；最高工资（含年终奖）两三人到手20万元，平均工资1万多元；年终奖总额比去年多1312万余元，干满一年人数从四五人增至12人；公司总量提升但结余到账下滑，还有百来万未收回，老板承担亏损100万元。会上公布年终奖标准，逐人评价，颁发最佳新人、最佳进步、后期独当一面、最佳员工、特别贡献五项奖，并抽奖。
 # 亮点事项
-- 短视频账号实现显著涨粉：视频号粉丝从719人增至8万，小红书从2000+增至6.4万，抖音从2000+增至5.7万，B站从3.1万增至7.6万，关键转折点是6月20日第一条外出拍摄视频，源于郭东辉在潘老师多次劝退下坚持并**破釜沉舟说服潘老师外出拍摄**。
-- 账号变现课程自评达到7.5分（满分10），直播在视频号开展4-5场，平均在线人数5000人以上，为后续变现打下基础。
-- 商务部门实打实项目约300万元左右，基本达到预期，可能更多。
-- 员工评价中，刘腾宇获评职业性、专业性、纪律性最佳，客户反馈好，效率高；红叶子获政委高度评价，**既懂技术又懂英语且有把事情做好的精神**；张扬作为邀请人才，基本达到期待并带来改变。
-- 最具复用价值的经验：郭东辉坚持不放弃、以数据支撑决策（每晚8-9点刷直播间研究同行），以及说服自己比说服他人更难、**找准一个点破壳**的成长方法。
+- 短视频账号运营取得显著增长：视频号粉丝从2023年3月1日70019人增至8万，小红书从2000+增至6.4万，抖音从2000+增至5.7万，B站从3.1万增至7.6万，涨粉自6月20日第一条外出拍摄视频起有起色。成功原因：郭东辉在潘老师多次提醒放弃的情况下坚持，并破釜沉舟说服外出拍摄，加上forty加入，最终突破。
+- 账号变现课程拍摄达十分满分7.5分，直播每场平均在线5000人以上，虽重点项目未完成，但为软实力提升提供帮助。
+- 后期团队整体技术提升：林海腾指出今年后期人员分级模糊、效率接近，整体技术有进步，硬着头皮安排没做过的人也能完成好。
+- 张扬作为公司邀请人才，职业态度与工作能力基本达到期待，老板称2023年最有价值的事就是把他招进来。
+- 刘腾宇获最高评价，职业性、专业性、纪律性最好，迟到几乎没有，请假严格按规定，工作安排提前告知，成为团队标杆。
 # 不足事项
-- 成本控制非常差，是最大问题：全年实打实支出390万元（人员工资、外援配音字幕租机器），利润率仅24%或27%，非常不可观；根因是老板对成本关心或关注不够、不够雷厉风行，出现问题未及时解决。
-- 公司结余到账往下跑，还有百来万未收回，老板比去年少拿约10万元并承担亏损100万元。
-- 后期加班多，人不够是最大因素，根因是老板判断失误，未及时招合适人数的人员；外援成本高，部分因技术水平达不到。
-- 账号变现重点项目未完成，直播虽有人气但暂无课程可售，变现能力受限。
-- 拍摄人员安排困难，内部凑不出人按机位，需请外援且价格差很多；部分员工以没空、很忙、不想去为由推脱。
+- 成本控制非常差：全年实打实支出390万元（含人员工资、外援配音字幕、租机器），利润率仅约24%或27%，非常不可观。根因：老板对成本关心或关注不够、不够雷厉风行，问题未及时解决。
+- 公司结余到账往下跑，还有百来万未收回，老板每人比去年少拿约10万元，承担亏损100万元。
+- 账号变现重点项目未完成，直播暂无课程可变现。
+- 后期人员劳累程度高，今年尤其是后半年基本都在加班，很少正常休息。根因：老板未及时招合适人数，判断失误，人不够是最大因素。
+- 外援成本高：钱德峰指出请外援价格与内部拍摄差很多，但公司凑不出人按机位、让机器不关机，内部人员多以没空、很忙、不想去推脱。
 # 改进计划
-- 成本控制问题明年开会再议，责任人无，时间无。
-- 短视频部门期待明年开始变现，老板将投入更大精力并给予足够重视。
-- 执行部门期待老板更多进行组织协调，提高效率、减少休息时间侵占。
-- 老板自评今年给予支持、管理、关心不够，明年反思。
-- 鼓励全员参与拍摄，提升个人市场价值，明年向此方向靠拢。
-- 商务部门将获得老板更多支持与帮助，协助项目洽谈与打理。
-- 年终奖与奖项侧重后期，是唯一愿意解释的原因；加班补贴考虑一两千元。</t>
+- 成本控制问题明年开会再议，具体改进措施未明确，责任人无，时间无。
+- 短视频部门：期待明年账号能开始变现，老板将投入更大精力并给予足够重视，责任人无，时间无。
+- 执行部门：期待老板明年更多进行组织协调，提高效率，减少侵占休息时间，责任人无，时间无。
+- 商务部门：老板承认今年给予的支持、管理或关心不够，明年会反思，并考虑给张启更多支持和帮助，责任人无，时间无。
+- 拍摄参与：老板期待大家都能参与拍摄，明年往这个方向靠，提升个人市场价值，责任人无，时间无。
+- 加班补贴：年终奖中考虑加班因素，补贴一两千元，已实施。</t>
         </is>
       </c>
       <c r="D4" s="10" t="n">
-        <v>70</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>24562/1178</t>
+          <t>24562/1228</t>
         </is>
       </c>
     </row>
@@ -1933,30 +1914,28 @@
       <c r="C5" s="4" t="inlineStr">
         <is>
           <t># 全文摘要
-本次专项讨论会由办事处组织，召集小区业委会（刘主任、邱主任等）与物业公司（吴经理等）就业主大会召开、物业去留及11项服务问题展开协调。业委会称业主自发接龙约200来户要求召开业主大会，建议尽快召开业主大会表决物业去留；物业方称事先未接到任何沟通，已与集团法务沟通，本月将正式起诉业委会，并称起诉期间业委会无表决权。业委会认为业委会成立之日即自动解除物业合同，坚持推进业主大会；物业方要求先结清欠费，业委会表示可起诉。双方未达成一致，业委会决定正常推进业主大会，物业方将依法起诉。业委会列举11项服务问题，物业方逐项回应，双方在服务责任、欠费及经营亏损等问题上分歧明显。
+本次专项讨论会由办事处组织，旨在协调小区业委会与物业公司之间的矛盾，讨论业主大会召开及物业整改问题。业委会成员刘主任、邱主任及业主代表，物业方吴经理等参会。业委会提出，小区业主自发接龙约200来户，主要诉求是召开业主大会，由全体业主表决是否更换物业；物业方则表示事先未接到任何沟通，认为接龙有组织、议题不明。业委会列举了小区11项服务问题，物业方逐项回应称多属地产配套或费用问题。物业方称物业费欠账170多万，回款40万，账上一分钱没有，人工成本一年100多万，每年亏损。物业方宣布本月将正式起诉业委会，业委会表示将反诉并正常推进业主大会。双方就物业费欠费与整改先后顺序、业主大会召开与物业起诉的法律关系等未达成一致，矛盾激化。
 # 要点梳理
-## 业主大会召开与物业去留
-- 业主自发接龙约**200来户**要求召开业主大会，业委会建议尽快召开业主大会表决物业去留。
-- 物业方称事先未接到任何沟通，已与集团法务沟通，**本月将正式起诉业委会**，并称起诉期间业委会无表决权。
-- 业委会认为业委会成立之日即自动解除物业合同，坚持推进业主大会；物业方要求先结清欠费，业委会表示可起诉。
-- 双方未达成一致，业委会决定正常推进业主大会，物业方将依法起诉。
-## 小区11项服务问题
-- 业委会列举11项问题：入户门柱灯从未开启；内部水系、迎宾水系从未开启；监控几乎全部损坏，上月进贼无监控数据；监控室24小时值班服务荒废；绿化维护缺失，去年死树多棵；北边围墙用烂铁皮遮挡且有缺口，存在安全隐患；民生配套（快递柜、直饮水、宽带、暖气开户）无进展；雨水倒灌严重，2019年起多次反映无果；物业人员配备不足，办公室从10人减至4人，维修从5人减至2人。
-- 物业方逐项回应：门柱灯因能耗成本高未开，承诺收上费用后修复；水系为地产质量问题，非物业责任；监控损坏因无费用，物业费欠费**170多万**、回款**40万**；绿化死亡因冬季无法更换；北边围墙属红线外且涉违建，物业无责；民生配套属地产前期配套；雨水倒灌为地产设计问题；人员配备不足因地产补亏款未结。
-## 物业费欠费与经营亏损
-- 物业方称业主欠费**170多万**、回款**40万**，账上一分钱没有，每年亏损，人工成本**100多万**、保护收入**100来万**。
-- 业委会认为物业服务无滞后性，不能先收钱再服务。
-- 物业方称业委会在业主群煽动不缴费、阻碍经营，将起诉。
-## 物业经理言语冲突
-- 业委会成员称物业经理曾对业主说“不交物业费就上你家吃饭”，物业经理否认并要求拿出录音。</t>
+## 业主大会召开与表决
+- 业主自发接龙约**200来户**业主，主要议题是召开业主大会，业委会建议尽快召开，由全体业主表决是否更换物业。
+- 物业方表示事先未接到任何沟通，认为接龙有组织、议题不明，并称欠费人员不能成为业主代表，将依法追究责任。
+- 业委会成员表示，业委会成立之日即自动解除与物业的合同关系，将正常推进业主大会；物业方称案件存续期间无法更换物业公司。
+## 物业11项服务问题
+- 业委会列举11项问题：入户门柱灯从未开启；内部水系与迎宾水系从未开启；监控几乎全部损坏，上月进贼无监控数据；监控室24小时值班服务荒废；绿化维护缺失，去年死了很多树；北边围墙用烂铁皮遮挡且有缺口，存在安全隐患；快递柜、直饮水机、宽带、暖气开户等民生附属问题无进展；雨水倒灌问题严重，2019年起有财产损失；物业人员配备不足，办公室从10人减至4人，维修从5人减至2人。
+- 物业方逐项回应：门柱灯因能耗成本高未开，曾与业委会沟通；水系存在质量问题，属地产配套未完成；监控损坏因无费用，物业亏损；绿化死亡因冬季无法更换；北边围墙属红线以外且涉及违建官司，物业有权不处理；民生问题属地产前期配套；雨水倒灌属地产设计问题；人员配备不足因地产补亏款未结。
+- 物业方称物业费欠账**170多万**，回款**40万**，账上一分钱没有；人工成本一年**100多万**，保护收入100来万，每年亏损。
+- 业委会成员质疑物业服务滞后性，要求先服务后收费；物业方称需先解决费用问题。
+## 物业起诉与法律程序
+- 物业方称已与集团法务沟通，本月将正式起诉业委会，并称已与高级人民法院、滨城区人民法院沟通，掌握业主群内证据，将起诉业委会及保洁业主代表。
+- 业委会成员表示将反诉并拿出证据；物业方称起诉可能影响个人经营。</t>
         </is>
       </c>
       <c r="D5" s="10" t="n">
-        <v>40.5</v>
+        <v>46.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21511/1055</t>
+          <t>21511/1085</t>
         </is>
       </c>
     </row>
@@ -2205,73 +2184,28 @@
       <c r="C6" s="4" t="inlineStr">
         <is>
           <t># 研讨背景与议题
-本次圆桌论坛由发言者2主持，邀请多位学者与业界嘉宾围绕具身智能展开讨论，核心议题包括具身智能的形态与硬件期待、世界模型的定义与构建、强化学习与模仿学习的路线之争、数据采集与仿真等。发言者3（机械领域）提出具身智能形态是像人形还是像科幻片中的变形机器人，并提及机械智能概念；发言者4（薛寒博士）期待硬件寿命和可靠性高，因训练VLA时大规模真机评估机器人易碰撞损坏，现有工业机械臂并非为此设计，需要柔顺硬件结构；发言者2提到软硬件协同优化，松灵产品第二代比第一代在遥操和策略部署上更好，夹爪加凝胶可反馈触觉、更稳、摩擦力更好；发言者5（王岳老师）认为若大模型直通底层会消除硬件迭代可能性，模型至少应分上下层，大脑不变、小脑适应肢体；发言者6（赵昊老师）认为从第一性原理出发，人形机器人与特种机器人都会存在，如车厂、微电子制造厂已有97%以上自动化。关于世界模型，发言者8（志龙）从强化学习角度回溯到1990-91年Sutton的Dyna-Q，定义为黑盒输出下一时刻观测，可交互是首要要素，并提到18年Schmidhuber或LeCun定义的世界模型有表征和转移两个组件；发言者7（赵昊老师）认为CV界追求重建物理世界，可作为RL中world models的工具，但三维计算机视觉技术栈长，RL博士生难以完全学习，导致RL领域不关注三维表征，并讨论inductive bias，认为数据多时需要的inductive bias少、数据少时需要的多，梦想写一篇paper叫data bias trade off；发言者5（王岳老师）举例刺客信条游戏与真实世界跳楼，认为一个世界模型无法同时建模两个dynamics，因为输入相同输出不同是歧义问题，policy可能可以，world model做不到；发言者9（薛寒博士）认为CV的world model带3D inductive bias，强化学习的world model不带，但强化学习的world model是任务导向的，不一定需要CV那样的模型；发言者9与发言者5讨论不同物理结构是否能有统一表征，发言者5认为M个独立模型比一个高维可控模型更简单。关于强化学习与模仿学习路线，发言者2提到强化学习曾达顶峰但sim-to-real落地有困难，模仿学习如ALOHA收集海量数据展现可落地性质，但派零团队收集近万小时数据后仍看到模仿学习瓶颈；发言者10（业界嘉宾）表示公司采用模型强化加机理融合方式，监督学习动作空间大、数据分布不足，强化学习依赖仿真环境，纯强化学习不能很好sim-to-real迁移，需要限制决策空间和任务设定，上层用强化学习决策，底层用MPC或DWA等传统方法；发言者9（薛寒博士）同意混合方式，认为复杂任务应先模仿后强化，单独模仿不行除非任务简单，单独强化也不行除非任务足够简单；发言者5（王岳老师）认为PID有反馈，可拿反馈作为reward，强化必然走得成；发言者11（静波）认为IL和RL没有本质冲突，只是想要运动先验，有数据用模仿学习，没数据用强化学习生成。关于数据采集与仿真，发言者11（杨立新）分享数据质量经验，Open X等数据集相机视角不固定影响policy表现，采集时控制视角和标定，手眼标定仍是问题，Open X缺少物体运动信息，Oakink采集时记录物体运动但设备有限只能采集刚体和关节体；发言者4（薛寒博士）all in reward采集路线，柔性体操作如叠衣服难以仿真，需要IPC等先进图形学技术，算力要求高、全世界能做的人少如UCLA蒋正凡老师，进展慢，reward采集是低成本方案，现实生活是最好的仿真器，终极形态是脑机接口或机电方式无感采集，现阶段可穿戴设备，互联网视频数据与机器人所需数据不同如叠衣服视频是平铺状态而机器人需要从混乱状态展平；发言者2提到ego4d数据集洗了三个月，互联网数据质量低、数据金字塔最底层，仿真数据分传统仿真和强化生成，SIM数据加少量真机数据可显著提升成功率如300条SIM数据加20条真机数据；发言者7（赵昊老师）认为用真实数据还是仿真数据看成本，自动驾驶中真机数据收集困难，提出加入无标注真实数据，2025年主题是推广大规模利用无标注数据如segment anything和depth anything；发言者7提到国产仿真系统，宋应公司赌卡脖子做国产替代，但工作人员不会直接touch这个生意。
+本次圆桌论坛围绕具身智能领域的关键技术问题展开，参与人员包括多模态大模型与具身智能融合方向的代表、强化学习方向的博士生、柔性物体操作与数据采集方向的专家、计算机视觉与仿真方向的学者，以及产业界嘉宾。核心探讨的技术痛点包括：具身智能大模型形态与硬件期待、世界模型的定义与实现路径、强化学习与模仿学习的路线之争，以及数据采集与仿真数据之争。各方观点充分碰撞，但未形成统一结论。
 # 核心观点
-### 具身智能的形态与硬件期待
-- 发言者3（机械领域）提出具身智能形态问题：是像人形机器人，还是像科幻片中可变形的大方块（如《星际穿越》），并提及机械领域中的机械智能概念，如软手通过摩擦和顺应性实现误差较大时仍能抓牢。
-- 发言者4（薛寒博士）期待硬件寿命和可靠性高，因训练VLA时大规模真机评估，机器人易因碰撞损坏，难以可靠scale up，现有工业机械臂并非为此设计，需要柔顺硬件结构。
-- 发言者2提到软硬件协同优化，松灵产品第二代比第一代在遥操和策略部署上更好，夹爪加凝胶可反馈触觉、更稳、摩擦力更好。
-- 发言者5（王岳老师）认为若大模型直通底层会消除硬件迭代可能性，新硬件出现可能需要完全重新训练，模型至少应分上下层，大脑不变、小脑适应肢体。
-- 发言者6（赵昊老师）认为从第一性原理出发，人形机器人会存在（如双足或轮式加灵巧手），特种机器人也大量存在，如车厂、微电子制造厂已有97%以上自动化。
-### 世界模型的定义与构建
-- 发言者2提到赵昊老师有经典图从各维度评价世界模型，CV角度讨论是否需要重构pixel、3D，ACL上已有4D world model投稿。
-- 发言者8（志龙）从强化学习角度，世界模型概念可回溯到1990-91年Sutton的Dyna-Q，定义为黑盒输出下一时刻观测，可交互是首要要素，并提到18年Schmidhuber或LeCun定义的世界模型有表征和转移两个组件。
-- 发言者7（赵昊老师）认为CV界追求重建物理世界，可作为RL中world models的工具，但三维计算机视觉技术栈长，RL博士生难以完全学习，导致RL领域不关注三维表征。
-- 发言者7讨论inductive bias，认为数据多时需要的inductive bias少、数据少时需要的多，梦想写一篇paper叫data bias trade off。
-- 发言者5（王岳老师）举例刺客信条游戏与真实世界跳楼，认为一个世界模型无法同时建模两个dynamics，因为输入相同输出不同是歧义问题，policy可能可以，world model做不到。
-- 发言者9（薛寒博士）认为CV的world model带3D inductive bias，强化学习的world model不带，但强化学习的world model是任务导向的，不一定需要CV那样的模型。
-- 发言者9与发言者5讨论不同物理结构是否能有统一表征，发言者5认为M个独立模型比一个高维可控模型更简单。
-### 强化学习与模仿学习的路线之争
-- 发言者2提到强化学习曾达顶峰但sim-to-real落地有困难，模仿学习如ALOHA收集海量数据展现可落地性质，但派零团队收集近万小时数据后仍看到模仿学习瓶颈。
-- 发言者10（业界嘉宾）表示公司采用模型强化加机理融合方式，监督学习动作空间大、数据分布不足，强化学习依赖仿真环境，纯强化学习不能很好sim-to-real迁移，需要限制决策空间和任务设定，上层用强化学习决策，底层用MPC或DWA等传统方法。
-- 发言者9（薛寒博士）同意混合方式，认为复杂任务应先模仿后强化，单独模仿不行除非任务简单，单独强化也不行除非任务足够简单。
-- 发言者5（王岳老师）认为PID有反馈，可拿反馈作为reward，强化必然走得成。
-- 发言者11（静波）认为IL和RL没有本质冲突，只是想要运动先验，有数据用模仿学习，没数据用强化学习生成。
-### 数据采集与仿真
-- 发言者11（杨立新）分享数据质量经验，Open X等数据集相机视角不固定影响policy表现，采集时控制视角和标定，手眼标定仍是问题，Open X缺少物体运动信息，Oakink采集时记录物体运动但设备有限只能采集刚体和关节体。
-- 发言者4（薛寒博士）all in reward采集路线，柔性体操作如叠衣服难以仿真，需要IPC等先进图形学技术，算力要求高、全世界能做的人少如UCLA蒋正凡老师，进展慢，reward采集是低成本方案，现实生活是最好的仿真器，终极形态是脑机接口或机电方式无感采集，现阶段可穿戴设备，互联网视频数据与机器人所需数据不同如叠衣服视频是平铺状态而机器人需要从混乱状态展平。
-- 发言者2提到ego4d数据集洗了三个月，互联网数据质量低、数据金字塔最底层，仿真数据分传统仿真和强化生成，SIM数据加少量真机数据可显著提升成功率如300条SIM数据加20条真机数据。
-- 发言者7（赵昊老师）认为用真实数据还是仿真数据看成本，自动驾驶中真机数据收集困难，提出加入无标注真实数据，2025年主题是推广大规模利用无标注数据如segment anything和depth anything。
-- 发言者7提到国产仿真系统，宋应公司赌卡脖子做国产替代，但工作人员不会直接touch这个生意。
+**具身智能大模型形态与硬件期待**：发言者2提出具身智能分为大脑大模型、小脑大模型和端到端模型，派灵收集6000多小时数据训练出端到端模型；发言者3从机械角度提问具身智能形态收敛方向，提及人形机器人与非人形（如星际穿越中的方块机器人），并介绍机械智能、软手等硬件方案；发言者4（薛寒）强调硬件需高寿命、高可靠性，现有工业机械臂不适合大规模真机评估，需要柔顺硬件结构以支持scale up；发言者2提到松灵产品两代迭代，第二代在遥操和策略部署上更好，夹爪加凝胶可反馈触觉、更稳、摩擦力更好；发言者5认为大模型直通底层会消除硬件迭代可能性，新硬件出现需重新训练，应至少分两层，大脑不变、小脑自适应肢体；发言者6认为大模型不是终极方案，世界模型可能更接近人类水平，但也不是最终形态，人形机器人和特种机器人都会存在，特斯拉花一半精力做22自由度灵巧手，车厂等已实现97%以上自动化。
+**世界模型的定义与实现路径**：发言者2提到赵老师有经典图评价世界模型，从CV角度讨论是否需要重构pixel、3D，以及4D world model；发言者8（志龙）从强化学习角度指出世界模型概念可追溯至1990-91年Sutton的dyna Q，定义为黑盒输出下一时刻观测，18年Schmidhuber和LeCun定义世界模型含表征和转移两个组件，强化学习领域世界模型第一要义是可交互，当前在物理规律方面欠缺明显，希望引入3D、触觉等模态完善；发言者7认为CV界追求重建物理世界，可作为RL世界模型的工具，但三维视觉技术栈深，RL博士生难以完全学习，导致RL领域不关注三维表征，并讨论inductive bias，认为数据多时需要的inductive bias少，数据少时需要的多，整体由数据决定；发言者5以刺客信条游戏与真实世界跳楼为例，认为一个世界模型无法同时建模两个dynamics，因为输入相同输出不同是歧义问题，policy可能统一而世界模型做不到；发言者9提出反对意见，认为CV世界模型带3D inductive bias，强化世界模型是任务导向的，不一定需要CV式世界模型，并讨论不同物理结构是否能有统一表征，发言者5认为M个独立模型比一个高维可控模型更简单。
+**强化学习与模仿学习的路线之争**：发言者2提到强化学习曾达顶峰但sim-to-real有落地问题，模仿学习如aloha收集海量数据展现可落地性，但派零团队收集近万小时数据后仍看到模仿学习瓶颈，语言模型最后有RLHF环节，o1引入思维链和MCTS；发言者10（业界嘉宾）介绍公司采用模型强化加机理融合方式，监督学习动作空间大、数据分布不足，强化学习依赖仿真环境、sim-to-real迁移难，实物强化学习需限制决策规模和任务设定，其强化pc工作采用任务分层，上层强化学习决策，底层用MPC、DWA等传统方法；发言者9同意混合方式，认为复杂问题都是先模仿后强化，如AlphaStar和GPT，单独模仿达不到专家水平，除非任务简单，单独强化样本复杂度不可接受；发言者5认为PID系统必有反馈，可拿反馈作为reward，强化必然走得成；发言者11（静波）认为IL和RL没有本质冲突，运动先验可从模仿学习或强化学习获取，然后通过RL找到对应latent完成任务。
+**数据采集与仿真数据之争**：发言者11（杨立新）分享数据质量经验，指出open X等数据集相机视角不固定、视角影响policy表现，标定重要且手眼标定至今解决不好，open X等数据集缺少物体运动信息，orkin从采集角度记录物体运动但当时设备有限只能采集刚体和关节体；发言者4（薛寒）all in reward采集路线，认为柔性体操作（叠衣服、系鞋带）仿真需要IPC等先进图形学技术、算力要求高、能做的人少（如UCLA蒋正凡夫）、进展慢，reward采集是低成本方案、真实世界是最好的仿真器，终极形态是脑机接口或机电方式无感采集多模态数据，现阶段可穿戴式设备可扩展，并指出互联网视频数据与机器人所需数据不同（如叠衣服视频是平铺状态，机器人需要从混乱状态展平的数据）；发言者2提到自己受ego4d数据集毒害、洗数据洗了三个月，数据金字塔中互联网数据在最底层、质量低，仿真数据分传统仿真和强化收集数据、sim-to-real gap大，仿真数据加少量真机数据可显著提升成功率（如300条sim数据加20条真机数据），可穿戴设备精度相比遥操数据有gap；发言者7认为用真实数据还是仿真数据看成本、case by case，自动驾驶中真机数据收集困难且危险，提出加入第三个domain——无标注真实数据（如segment anything和depth anything），认为2025年应推广大规模利用无标注数据；发言者2提问中国是否强依赖英伟达生态、能否有国产仿真产品，发言者7提到宋应等在做国产替代、赌卡脖子，但工作人员不会直接touch这个生意。
 # 达成共识与解决方案
-### 具身智能的形态与硬件
-- **具身智能是软硬件协同优化的范式**，发言者2以松灵产品两代迭代和夹爪加凝胶为例，说明硬件改进能提升算法部署效果。
-- 发言者5（王岳老师）提出模型应分上下层，**大脑不变、小脑适应肢体**，避免新硬件出现时完全重新训练。
-- 发言者6（赵昊老师）认为**人形机器人与特种机器人将并存**，人形因现实环境为人设计而存在，特种机器人已在车厂、微电子制造厂实现97%以上自动化。
-### 世界模型
-- 发言者8（志龙）从强化学习角度，世界模型首要要素是**可交互**，最终目标是学策略。
-- 发言者7（赵昊老师）认为CV界追求重建物理世界，可作为RL中world models的工具，但三维表征技术栈长，RL领域难以完全学习。
-- 发言者7提出**数据量决定inductive bias需求**：数据多时需要的inductive bias少，数据少时需要的多。
-- 发言者5（王岳老师）认为**world model难以统一，policy可能统一**，因输入相同输出不同是歧义问题。
-### 强化学习与模仿学习
-- 发言者10（业界嘉宾）提出**模型强化加机理融合**方式，上层用强化学习决策，底层用MPC或DWA等传统方法。
-- 发言者9（薛寒博士）认为**复杂任务应先模仿后强化**，单独模仿或单独强化均不可行，除非任务足够简单。
-- 发言者5（王岳老师）认为**PID有反馈，可拿反馈作为reward**，强化必然走得成。
-- 发言者11（静波）认为**IL和RL没有本质冲突**，只是想要运动先验，有数据用模仿学习，没数据用强化学习生成。
-### 数据采集与仿真
-- 发言者11（杨立新）强调**数据质量关键在于视角控制和标定**，并记录物体运动信息。
-- 发言者4（薛寒博士）认为**reward采集是低成本方案**，现实生活是最好的仿真器，终极形态是脑机接口或机电方式无感采集。
-- 发言者2提出**仿真数据加少量真机数据可显著提升成功率**，如300条SIM数据加20条真机数据。
-- 发言者7（赵昊老师）提出**2025年应推广大规模利用无标注真实数据**，如segment anything和depth anything。
+**具身智能大模型形态**：发言者5提出大模型不应直通底层，应至少分两层，大脑不变、小脑自适应肢体；发言者6认为人形机器人和特种机器人都会存在，特斯拉花一半精力做22自由度灵巧手，车厂等已实现97%以上自动化。
+**世界模型**：发言者8（志龙）从强化学习角度指出世界模型第一要义是可交互，当前在物理规律方面欠缺明显；发言者7认为CV界追求重建物理世界，可作为RL世界模型的工具，inductive bias由数据量决定；发言者5认为一个世界模型无法同时建模多个dynamics，policy可能统一而世界模型做不到；发言者9认为强化世界模型是任务导向的，不一定需要CV式世界模型。
+**强化学习与模仿学习**：发言者10（业界嘉宾）介绍公司采用模型强化加机理融合方式，监督学习动作空间大、数据分布不足，强化学习依赖仿真环境、sim-to-real迁移难，实物强化学习需限制决策规模和任务设定，其强化pc工作采用任务分层，上层强化学习决策，底层用MPC、DWA等传统方法；发言者9同意混合方式，认为复杂问题都是先模仿后强化，如AlphaStar和GPT，单独模仿达不到专家水平，除非任务简单，单独强化样本复杂度不可接受；发言者5认为PID系统必有反馈，可拿反馈作为reward，强化必然走得成；发言者11（静波）认为IL和RL没有本质冲突，运动先验可从模仿学习或强化学习获取，然后通过RL找到对应latent完成任务。
+**数据采集与仿真数据**：发言者11（杨立新）分享数据质量经验，指出open X等数据集相机视角不固定、视角影响policy表现，标定重要且手眼标定至今解决不好，open X等数据集缺少物体运动信息，orkin从采集角度记录物体运动但当时设备有限只能采集刚体和关节体；发言者4（薛寒）all in reward采集路线，认为柔性体操作仿真需要IPC等先进图形学技术、算力要求高、能做的人少（如UCLA蒋正凡夫）、进展慢，reward采集是低成本方案、真实世界是最好的仿真器，终极形态是脑机接口或机电方式无感采集多模态数据，现阶段可穿戴式设备可扩展，并指出互联网视频数据与机器人所需数据不同（如叠衣服视频是平铺状态，机器人需要从混乱状态展平的数据）；发言者2提到自己受ego4d数据集毒害、洗数据洗了三个月，数据金字塔中互联网数据在最底层、质量低，仿真数据分传统仿真和强化收集数据、sim-to-real gap大，仿真数据加少量真机数据可显著提升成功率（如300条sim数据加20条真机数据），可穿戴设备精度相比遥操数据有gap；发言者7认为用真实数据还是仿真数据看成本、case by case，自动驾驶中真机数据收集困难且危险，提出加入第三个domain——无标注真实数据（如segment anything和depth anything），认为2025年应推广大规模利用无标注数据；发言者2提问中国是否强依赖英伟达生态、能否有国产仿真产品，发言者7提到宋应等在做国产替代、赌卡脖子，但工作人员不会直接touch这个生意。
 # 未决分歧与后续探索
-### 未决分歧
-- 具身智能的形态最终会收敛成什么样子？发言者3（机械领域）提出，未达成共识。
-- 世界模型是否需要3D inductive bias？发言者7（赵昊老师）认为数据决定，发言者9（薛寒博士）认为强化学习的世界模型是任务导向的，不一定需要CV那样的模型，未达成共识。
-- 强化学习和模仿学习最终路线如何？发言者10（业界嘉宾）主张混合方式，发言者9（薛寒博士）认为应先模仿后强化，发言者5（王岳老师）认为强化必然走得成，未达成共识。
-- 如何保证数据采集的高质量？发言者11（杨立新）强调视角控制和标定，发言者4（薛寒博士）主张reward采集，未达成共识。
-- 未来是否强依赖英伟达生态，还是可以有国产仿真产品？发言者7（赵昊老师）提到宋应公司赌卡脖子做国产替代，但工作人员不会直接touch这个生意，未明确。
-### 后续探索
-- 发言者7（赵昊老师）梦想写一篇paper叫data bias trade off，探讨数据量与inductive bias的关系，跟进人未明确。
-- 发言者4（薛寒博士）认为需要更多人投入真正准确的物理仿真技术（如IPC），以解决柔性体问题，跟进人未明确。
-- 发言者4（薛寒博士）提出终极数据采集形态是脑机接口或机电方式无感采集，现阶段可穿戴设备，跟进人未明确。</t>
+**未决分歧**：具身智能的形态最终会收敛成人形机器人还是非人形（如科幻片中的变形机器人）；世界模型是否需要3D inductive bias；一个世界模型能否同时建模多个dynamics（如游戏与真实世界）；不同物理结构是否能有统一的表征，从而构成统一模型；强化学习与模仿学习最终路线是混合还是单一；真机复杂任务的reward如何获取；中国仿真系统是否强依赖英伟达生态，能否有国产替代；如何保证数据采集的高质量（如视角、标定、物体运动记录）。
+**后续探索**：发言者7提出2025年应推广大规模利用无标注数据（如segment anything和depth anything）；发言者4（薛寒）提出终极形态是脑机接口或机电方式无感采集多模态数据，现阶段可穿戴式设备可扩展；发言者2提出仿真数据加少量真机数据可显著提升成功率（如300条sim数据加20条真机数据）。跟进人未明确。</t>
         </is>
       </c>
       <c r="D6" s="10" t="n">
-        <v>90.3</v>
+        <v>89.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>21458/5350</t>
+          <t>21458/3938</t>
         </is>
       </c>
     </row>
@@ -2770,46 +2704,42 @@
       <c r="C7" s="4" t="inlineStr">
         <is>
           <t># 庭审概况
-本案系上诉人国家开发银行不服云南省高级人民法院（2018）云民初88号民事判决，向最高人民法院提起上诉的金融借款合同纠纷二审案件，被上诉人为云南东源电力股份有限公司、云南东源曲靖电力有限公司及招银金融租赁有限公司。合议庭由审判长李少平与审判员魏文超、黄年、王海峰、葛洪涛组成，法官助理张瑞。庭审核对各方出庭人员身份后，围绕三个争议焦点展开法庭调查与辩论：国开行对案涉设备是否享有抵押权（善意取得）、一审判决对案涉借款罚息复息的计算及起算日期是否认定错误、东源煤电及东源煤业是否应连带给付违约金。合议庭多次到案发地调查走访并召开庭前会议，休庭评议后提出调解方案，各方均无异议，诉讼代理人依次在调解协议正式文本上签字，合议庭予以确认，庭后出具调解书。
+本案系上诉人国家开发银行与被上诉人云南东源电力股份有限公司、云南东源曲靖电力有限公司、招银金融租赁有限公司金融借款合同纠纷二审案件，国开行不服云南省高级人民法院2018云民初88号民事判决提起上诉。本案由审判员李少平担任审判长，与审判员魏文超、黄年、王海峰、葛洪涛组成合议庭，法官助理张瑞，依法公开开庭审理。庭审中，各方当事人核对身份无异议，东源煤电、东源煤业、曲靖电力合并发表意见。法庭围绕三个争议焦点展开调查与辩论：国开行对案涉设备是否享有抵押权（善意取得）、一审判决对借款罚息复息的计算及起算日期是否认定错误、东源煤电及东源煤业是否应连带给付违约金。合议庭休庭评议后提出调解方案，各方均无异议，合议庭予以确认，庭后出具调解书。
 # 原告诉称与被告辩称
-上诉人国家开发银行上诉请求：撤销一审判决相关判项，改判其对案涉设备享有抵押权，并支持其利息、罚息、复利及违约金主张。事实与理由：国开行已按央行规定对抵押人曲靖电力公司进行融资租赁登记查询且无记录，设备为无唯一标识码的通用设备，核查义务仅限于抵押人，已尽审慎义务构成善意取得；东源煤电利息支付截止2017年12月20日，2018年6月13日发函要求当日归还，罚息应自该日起算，复利按合同第6条约定计算；依借款合同第24条第3项，东源煤电未配合办理账户管理及柜台前移手续构成违约，应支付千分之一违约金。被上诉人东源煤电、东源煤业、曲靖电力共同答辩：2015年12月2日邮件中两家公司抵押设备名称完全相同且以红色标注，国开行应尽注意义务；合同约定限期偿还而非立即偿还，且复利不应以罚息为基数；国开行未举证证明违约事实，且依约应先限期纠正。被上诉人招银租赁答辩：国开行未在抵押时点（2015年12月）查询人行征信中心，且东源煤电系借款人及抵押人全资控股母公司，国开行对其有审查义务，不构成善意。
+上诉人国开行上诉请求：撤销一审判决相关判项，改判确认其对案涉设备享有抵押权，并支持其利息、罚息、复利及违约金主张。事实与理由：国开行已按央行规定查询融资租赁登记系统，未显示曲靖电力公司设备有融资租赁登记；设备为通用设备无唯一标识码，无法按设备查询；抵押人仅为曲靖电力公司，审查义务仅限于抵押人，已履行审慎义务，构成善意取得。被上诉人东源煤电、东源煤业、曲靖电力答辩称：国开行未举证证明东源煤电违反柜台前移和账户管理约定，且按合同约定应先限期纠正，国开行从未发出书面纠正函；罚息不应作为复利计算基数，复利再计算复利无合同依据。被上诉人招银租赁答辩称：国开行未在抵押时点（2015年12月）查询融资租赁登记系统，仅提供2018年9月查询证书，不符合规定；审查义务应扩大到东源煤电（借款人与抵押人全资控股关系）；东源煤电出资行为系无权处分，招银租赁2012年已取得设备所有权。
 | 方 | 诉讼请求/答辩意见 | 事实与理由 |
 | --- | --- | --- |
-| 上诉人（原审原告） | 请求撤销一审判决相关判项，改判其对案涉设备享有抵押权，并支持其利息、罚息、复利及违约金主张 | 已按央行规定对抵押人曲靖电力公司进行融资租赁登记查询且无记录，设备为无唯一标识码的通用设备，核查义务仅限于抵押人，已尽审慎义务构成善意取得；东源煤电利息支付截止2017年12月20日，2018年6月13日发函要求当日归还，罚息应自该日起算，复利按合同第6条约定计算；依借款合同第24条第3项，东源煤电未配合办理账户管理及柜台前移手续构成违约，应支付千分之一违约金 |
-| 被上诉人（原审被告）东源煤电、东源煤业、曲靖电力 | 请求驳回上诉，维持原判 | 2015年12月2日邮件中两家公司抵押设备名称完全相同且以红色标注，国开行应尽注意义务；合同约定限期偿还而非立即偿还，且复利不应以罚息为基数；国开行未举证证明违约事实，且依约应先限期纠正 |
-| 被上诉人（原审被告）招银租赁 | 请求驳回上诉，维持原判 | 国开行未在抵押时点（2015年12月）查询人行征信中心，且东源煤电系借款人及抵押人全资控股母公司，国开行对其有审查义务，不构成善意 |
+| 上诉人（国开行） | 撤销一审判决相关判项，改判确认其对案涉设备享有抵押权，并支持利息、罚息、复利及违约金主张 | 已按央行规定查询融资租赁登记系统，未显示曲靖电力公司设备有融资租赁登记；设备为通用设备无唯一标识码，无法按设备查询；抵押人仅为曲靖电力公司，审查义务仅限于抵押人，已履行审慎义务，构成善意取得 |
+| 被上诉人（东源煤电、东源煤业、曲靖电力） | 驳回上诉，维持原判；罚息不应作为复利计算基数，复利再计算复利无合同依据；国开行未举证证明违约，且未先限期纠正 | 2015年12月2日邮件已告知融资租赁情况，设备名称相同且用红色标注，国开行应尽注意义务；国开行当天发函要求当天偿还未给合理期限；国开行从未发出书面纠正函 |
+| 被上诉人（招银租赁） | 驳回上诉，维持原判；国开行不构成善意取得 | 国开行未在抵押时点（2015年12月）查询融资租赁登记系统，仅提供2018年9月查询证书，不符合规定；审查义务应扩大到东源煤电（借款人与抵押人全资控股关系）；东源煤电出资行为系无权处分，招银租赁2012年已取得设备所有权 |
 # 举证与法庭调查
 **证据与质证意见**
-- 国开行提交2015年12月2日东源煤电发送的邮件及《东源公司融资情况统计表》，主张表中招银租赁抵押物为恩洪电厂设备资产且已登记，国开行抵押物为恩洪电厂设备在建工程正在办理，两者设备完全不同，不能得出已告知的结论；东源方反驳称该邮件系抵押合同签订（2015年12月22日）前发出，两家公司抵押设备名称完全相同且以红色标注，国开行应尽注意义务。
-- 国开行提交证据54页、58页权属证明及股东会决议，主张显示所有权属曲靖电力公司，已尽审慎义务；招银租赁主张东源煤电出资行为系无权处分，招银租赁2012年已取得设备所有权。
-- 招银租赁提交证据第7页回租设备清单，主张载明设备名称、生产厂家；国开行反驳称清单无型号，出厂日期2012年3月1日，而现场调查铭牌生产日期均在2013年以后，看不出同一设备。
-- 招银租赁提交证据82页、95页审计报告，主张载明曲靖电力公司注册资本4个亿且实缴；国开行据此主张招银租赁应知道设备出资情况。
-- 国开行提交2018年9月融资租赁查询证书，主张已尽查询义务；招银租赁反驳称该证书不符合2014年93号文规定，国开行应提供2015年12月抵押时点的查询结果。
-- 东源方提交融资情况统计表及邮件截屏，主张两家公司抵押设备名称完全相同且用红色标注；国开行反驳称统计表中招银租赁抵押类型为不动产抵押，与融资租赁是两个法律概念。
+- 国开行提交2018年9月对曲靖电力公司的融资租赁查询证书，招银租赁质证认为不符合要求，依据2014年93号中国人民银行规定，国开行应在抵押时点（2015年12月）查询人行征信中心。
+- 招银租赁提交回租设备清单（证据第7页），仅载明设备名称和生产厂家，未载明型号；国开行质证称清单记载出厂日期为2012年3月1日，而现场调查核实抵押设备铭牌生产日期均在2013年以后，看不出是同一设备。
+- 国开行提交证据第54页、58页，显示东源煤电公司、曲靖电力公司对设备权属的证明材料及股东会决议，证明设备所有权属曲靖电力公司。
+- 国开行提交融资租赁登记信息核查表（证据第108页），显示曲靖电力公司名下无融资租赁登记，招银租赁质证称该核查表系2018年9月查询，非抵押时点查询。
+- 招银租赁提交2013年和2015年审计报告（证据第82页、95页），载明曲靖电力公司注册资本4亿元且已实缴，国开行据此主张招银租赁知道或应当知道设备出资情况。
 **法官询问要点**
-- 合议庭询问各方如何理解人行征信中心融资租赁登记的性质及法律后果：国开行认为系行业内强制性规范，目的是防范金融风险；东源方认为系行业指导性规范，非强制性，不当然产生物权后果；招银租赁认为系权利公示，可能产生对抗效力，但不影响所有权设立转移等法定效果。
-- 合议庭询问央行融资租赁登记系统的查询方式：国开行称目前只能使用一种查询方式（查询单位）；招银租赁称可通过公司名称或设备查询，设备查询涉及种类物区分问题。
-- 合议庭询问案涉5套设备登记时识别码是否登记清楚：东源方称设备交付时系种类物，无唯一识别码，未登记。
-- 合议庭询问国开行贷款前审查内部是否有规定必须查询融资租赁系统、未查到也要保留记录：国开行称按央行规定必须查询，但未查到记录，未保留筛查记录，内部无此规定。
-- 合议庭询问融资租赁登记系统设备唯一标识码是否必填项：招银租赁称不是必填项，案涉设备无唯一识别码，无法填写；发电机铭牌只有型号和参数，15万伏发电机只要是上海电气出厂，铭牌都一样。
-- 合议庭询问违反查询规范多大程度导致司法解释第9条第2款法律后果、是基本查询义务还是全面审慎义务：国开行认为是基本查询义务，针对抵押人，审慎调查义务已完成；招银租赁认为是严格义务，银行未查询即不构成善意，本案中恩洪矿区发电厂只有两台设备，综合信息能确定5台设备唯一性，已足够引起国开行注意。
-- 合议庭询问若银行通过其他途径了解到动产属融资租赁物，是否相当于已掌握风控情况：国开行称基本义务必须做，查询动作完成即可得出结论；东源方称金融机构接受抵押物前需确权查询，若通过其他渠道知道可能存在租赁，仍应查询；招银租赁称通过其他方式获知后仍应通过央行系统查询，因为其他方式无法证明，只有确定标准才能衡量善意。
-- 合议庭询问融资租赁司法解释第9条第2款举证责任如何分担：国开行称按谁主张谁举证原则，争议焦点是查询范围和主体；招银租赁称第9条列举1、2、4项由出租人举证，第3项由第三人（国开行）证明办理抵押时查询了央行系统，国开行应扩展调查东源煤电，查询购买合同购买发票。
-- 合议庭询问不同登记机构产生的登记信息冲突有何意见和建议：国开行称人行融资租赁系统和工商动产抵押登记信息不统一导致矛盾，是系统问题，建议系统整合；东源方称系统整合或衔接有必要，但提不出成熟建议；招银租赁建议从立法层面统一要求、发挥行业协会作用形成行业惯例、从操作和技术层面实现信息互通，企业主体也应主动登记。
+- 合议庭询问各方对中国人民银行征信中心融资租赁登记性质及法律后果的理解：国开行认为系行业强制性规范，用于防范金融风险；东源方认为系行业指导性规范，不产生物权后果；招银租赁认为系行业性强制性规范，不构成法律效力约束。
+- 合议庭询问融资租赁登记系统查询方式：国开行称仅能按单位查询；招银租赁称可按公司名称或设备查询，但设备查询需特定化。
+- 合议庭询问案涉5套设备是否登记唯一识别码：招银租赁称设备无唯一识别码，非必填项，未登记。
+- 合议庭询问国开行内部是否有规定要求保留未查询到结果的记录：国开行称无此规定，因未查询到结果故未保留记录。
+- 合议庭询问查询义务程度：国开行认为系基本义务，仅需查询抵押人名下登记；招银租赁认为系严格义务，未查询即不构成善意。
+- 合议庭询问融资租赁司法解释第9条第2款举证责任分担：国开行主张谁主张谁举证；招银租赁主张第1、2、4项由出租人举证，第3项由第三人（国开行）举证。
 **双方辩论的争议焦点**
-- 争议焦点一：国开行对案涉设备是否享有抵押权（善意取得）。国开行主张已按央行规定对抵押人曲靖电力公司进行融资租赁登记查询且无记录，设备为无唯一标识码的通用设备，核查义务仅限于抵押人，已尽审慎义务构成善意取得；东源方反驳称2015年12月2日邮件中两家公司抵押设备名称完全相同且以红色标注，国开行应尽注意义务；招银租赁主张国开行未在抵押时点（2015年12月）查询人行征信中心，且东源煤电系借款人及抵押人全资控股母公司，国开行对其有审查义务，不构成善意。
-- 争议焦点二：一审判决对案涉借款罚息复息的计算及起算日期是否认定错误。国开行主张利息自2017年12月21日计算至2018年6月12日合计21,795,727.68元，罚息自2018年6月13日计算至2019年2月19日（破产受理日）合计41,050,579.57元，复利自2018年3月21日计算至2019年2月19日合计1,918,206.23元；东源方反驳称合同约定限期偿还而非立即偿还，且复利不应以罚息为基数，合同第6条第4款仅表述为利息未提罚息，并援引最高法2015年、2016年判例。
-- 争议焦点三：东源煤电、东源煤业是否应连带给付违约金。国开行主张依借款合同第24条第3项，东源煤电未配合办理账户管理及柜台前移手续构成违约，应支付千分之一违约金；东源方反驳称国开行未举证证明违约事实，且依约应先限期纠正，国开行从未发出书面函件。
+- 争议焦点一：国开行对案涉设备是否享有抵押权（善意取得）。国开行主张已履行审慎义务构成善意取得；东源方主张2015年12月2日邮件已告知融资租赁情况，设备名称相同且用红色标注，国开行应尽注意义务；招银租赁主张国开行未在抵押时点查询系统，审查义务应扩大到东源煤电，东源煤电出资行为系无权处分。
+- 争议焦点二：一审判决对案涉借款罚息复息的计算及起算日期是否认定错误。国开行主张利息自2017年12月21日计算至2018年6月12日合计21,795,727.68元，罚息自2018年6月13日计算至2019年2月19日合计41,050,579.57元，复利自2018年3月21日计算至2019年2月19日合计1,918,206.23元；东源方主张国开行当天发函要求当天偿还未给合理期限，罚息不应作为复利计算基数，复利再计算复利无合同依据。
+- 争议焦点三：东源煤电、东源煤业是否应当连带给付违约金。国开行主张借款合同第24条第3项约定违约金为千分之一，东源煤电未配合办理账户管理及柜台前移手续构成违约；东源方主张国开行未举证证明违约，且按合同约定应先限期纠正，国开行从未发出书面纠正函。
 # 庭审结果
-本案争议焦点为：一、国开行对案涉设备是否享有抵押权（善意取得）；二、一审判决对案涉借款罚息复息的计算及起算日期是否认定错误；三、东源煤电、东源煤业是否应连带给付违约金。合议庭休庭评议后提出调解方案，各方均无异议，自愿达成调解协议，合议庭予以确认，庭后出具调解书。调解方案主要内容：国开行对东源煤电债权扣除破产已清偿本金外，利息、罚息、复利三项共计6474.4513万元；确定招银租赁对涉案6项设备享有所有权（对应债权1377.4137万元）、国开行对93项设备有抵押权，双方对案涉全部发电设备整体盘活处置，调解书生效后20日内由国开行向一审法院提出执行申请启动司法处置，变现价款双方各得50%、费用各担50%；未实现债权待执行法院出具体本裁定后按破产重整计划预留方案实现，若破产管理人不予纳入预留方案由东源煤电按有担保清偿方案清偿，若司法变现不能双方放弃权益由东源曲靖电力自主生产经营；案涉设备管理费用由东源曲靖电力承担并无条件配合司法处置；各方对一审判决第2项、第4项无争议按判项确认；一审诉讼费用中国开行诉请部分按一审判决执行、招银租赁诉请部分由国开行承担，二审诉讼费用由国开行和东源煤电各承担50%；协议签订后各方就本案问题不再存在任何争议。</t>
+本案三个争议焦点：一是国开行对案涉设备是否享有抵押权（善意取得）；二是一审判决对案涉借款罚息复息的计算及起算日期是否认定错误；三是东源煤电、东源煤业是否应当连带给付违约金。合议庭休庭评议后提出调解方案，各方当事人均无异议，合议庭予以确认，庭后出具调解书。调解方案主要内容：国开行对东源煤电的债权扣除破产中已清偿本金外，利息、罚息、复利合计6474.4513万元；招银租赁对涉案6项设备享有所有权，对应债权数额1377.4137万元，国开行对93项设备有抵押权；案涉全部发电设备整体盘活处置，变现价款双方各得50%，实现费用双方各担50%；调解书生效后20日内由国开行向一审法院提出执行申请；未实现债权按破产重整计划预留方案实现，若司法变现不能，双方放弃设备权益，由东源曲靖电力自主生产经营。各方对一审判决第2项、第4项无争议，按判项内容在调解书中确认。</t>
         </is>
       </c>
       <c r="D7" s="10" t="n">
-        <v>128</v>
+        <v>79</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>28485/4107</t>
+          <t>28485/2996</t>
         </is>
       </c>
     </row>
@@ -2966,36 +2896,40 @@
       <c r="C8" s="4" t="inlineStr">
         <is>
           <t># 项目概况
-本次会议为原占比二玉米面加工厂项目中期验收会，验收组于18号、19号提前介入项目前期摸排，20号召开首次会议，工作分内业检查和外业检查，专业方向涵盖建筑工程、安装工程和设备机电设备。截至会议当天，卢萨卡点除带料加工调试外的所有验收工作已完成，蒙泽点验收工作全部完成，并利用带料调试厂家人员在场顺带完成全流程试生产及外方操作手培训；某皮卡点现场验收尚未开展，内业资料已提前送至卢萨卡点。内业检查基本满足规范标准，但分类整理和签字规范性需完善；外业检查中建筑、钢结构、设备安装均满足要求，工艺设备投料试运行正常、产能符合设计指标。财务检查符合规范，无挪用资金情况。会议提出人员履约、内业资料、现场整改等多项整改要求，合作局领导强调混凝土路面开裂成因分析及整改闭环，公司领导要求注意交通安全。
+本次会议为原占比二玉米面加工厂项目中期验收会议，验收组汇报了卢萨卡、蒙泽两点的内业与外业检查情况。截止目前，卢萨卡点除带料加工调试外已完成全部验收工作，蒙泽点因带料调试厂家人员在场顺带完成全流程试生产，某皮卡点现场验收尚未开展，内业资料已提前拿到卢萨卡点。验收组于18、19号提前介入项目摸排，20号召开首次会议，检查分内业与外业，专业方向涵盖建筑工程、安装工程和设备机电设备。内业检查方面，管理组和技术组基本能按合同组建项目执行团队，主要人员基本保证在前方岗位，编制了施工组织计划、管理计划、实施细则及专项预案，内业资料基本满足项目有关标准和规范要求。外业检查方面，建筑部分整体品质良好，主要建材除国内采购出口外，预制构件、广场地砖等从卢萨卡200多公里外集中采购；安装部分钢结构材料从国内定制发货，施工工艺和外观质量满足规范标准；设备部分与中粮西安设计院及厂家签订专项供货合同，参照中国标准定制三套成套设备，蒙泽点工艺设备运行正常，产能符合设计指标，机电设备安装符合国家质量检验标准。财务方面，账户设置、资金往来、银行开户等完全符合财务处理规范和标准，中基公司在此为第一个也是唯一项目，没有挪用资金情况。验收组提出多项整改要求，管理组田组长表示会后与技术组一起细化问题，技术组龚总汇报已开展护照证书收集、资料汇总及现场整改工作。合作局领导强调蒙泽厂区混凝土路面开裂问题需管理组和总包单位共同研究制定科学合理的整改方案，最迟在出报告前完成整改形成闭环，验收组需复核；公司林总指示按照商务部经参局指示完成验收任务，注意新冠防疫和交通安全。
 # 进度追踪
 | 模块 | 进展 | 状态 |
 | --- | --- | --- |
-| 卢萨卡点验收 | 除带料加工调试外的所有验收工作已完成，内业资料已提前集中至卢萨卡点 | ✅已完成 |
-| 蒙泽点验收 | 全部验收工作完成，利用带料调试厂家人员在场顺带完成全流程试生产及外方操作手培训，工艺设备投料试运行正常、产能符合设计指标 | ✅已完成 |
-| 某皮卡点验收 | 现场验收尚未开展，内业资料已提前拿到卢萨卡点 | 🔄进行中 |
-| 内业资料 | 程序性文件、过程检查文件及整改文件基本齐全，基本达到组卷成册要求，但分类整理和签字规范性需完善，资料分散需汇总至卢萨卡 | 🔄进行中 |
-| 人员履约 | 主要人员基本保证在前方岗位，但个别人员进出场时间、护照及特种人员证件有效期需完善，人员统计需计入厂家服务人员 | 🔄进行中 |
-| 现场整改 | 建筑局部损伤、装饰装修、排水、混凝土路面开裂、监控管线接头脱落、雨水倒灌、廊桥竖条加密等问题待整改 | 🔄进行中 |
-| 财务检查 | 账户设置、资金往来、银行开户等完全符合财务处理规范和标准，无挪用资金情况 | ✅已完成 |
+| 卢萨卡点验收 | 除带料加工调试外，已完成全部验收工作，包括内业资料检查、外业现场抽检及机电设备投料试运行 | ✅已完成 |
+| 蒙泽点验收 | 已完成全部验收工作，因带料调试厂家工作人员在场，顺带完成全流程试生产，工艺设备运行正常，产能符合设计指标 | ✅已完成 |
+| 某皮卡点验收 | 现场验收尚未开展，内业资料已提前拿到卢萨卡点，待后续安排现场验收 | 🔄进行中 |
+| 内业资料检查 | 管理组和技术组基本能按合同组建项目执行团队，编制施工组织计划、管理计划、实施细则及专项预案，内业资料基本满足项目有关标准和规范要求，但分类整理及签字规范性需进一步规范完善 | 🔄进行中 |
+| 外业建筑检查 | 卢萨卡和蒙泽厂区建筑部分整体品质良好，主要建材除国内采购出口外，预制构件、广场地砖等从卢萨卡200多公里外集中采购，现场抽检满足规范标准 | ✅已完成 |
+| 外业安装检查 | 钢结构材料从国内定制发货，施工工艺和外观质量满足规范标准，但监控管线接头处有脱落需全面检查 | 🔄进行中 |
+| 设备机电检查 | 与中粮西安设计院及厂家签订专项供货合同，参照中国标准定制三套成套设备，蒙泽点工艺设备运行正常，机电设备安装符合国家质量检验标准 | ✅已完成 |
+| 财务检查 | 财务验收专家查阅本项目财务资料，账户设置、资金往来、银行开户等完全符合财务处理规范和标准，中基公司在此为第一个也是唯一项目，没有挪用资金情况 | ✅已完成 |
 # 风险预警
 | 风险/瓶颈 | 等级 | 影响 | 责任人 | 应对计划 |
 | --- | --- | --- | --- | --- |
-| 混凝土路面开裂 | 中 | 某厂区非主要通道混凝土路面少量开裂，若处理不当可能影响移交后使用和对外形象，且存在其他部位未显现的隐患 | 管理组、总包单位（未明确具体个人） | 共同分析成因（气候、施工工艺、材料），制定科学合理整改方案，最迟出报告前完成整改并形成闭环，验收组复核 |
-| 人员履约资料不完善 | 中 | 个别人员进出场时间、护照及特种人员证件有效期问题，可能影响验收报告闭合 | 施工部、管理组 | 完善资料，与国内人力资源对接确认证件延期或更新，验收报告前达到闭合条件 |
-| 内业资料分散 | 中 | 资料分散在多个点，分类整理和签字规范性不足，可能影响竣工文件组卷 | 执行单位（技术组） | 按标准和规范及时汇总至卢萨卡，分类成册，按竣工文件归档要求组卷 |
-| 卢萨卡点雨水倒灌 | 中 | 提升桶往上位置雨水可能倒灌，影响设备运行 | 施工组（未明确具体个人） | 检查并考虑增加覆盖面积或采取技术措施解决 |
-| 监控管线接头脱落 | 低 | 设备启动震动导致管线接头脱落，可能引起机械故障 | 施工组（未明确具体个人） | 全面检查，保证有效性和安全性 |
-| 成品保护疏忽 | 中 | 工程实体完工时间较长，带料调试无法进行导致验收推后，成品保护有疏忽，可能有破损 | 参建单位（未明确具体个人） | 移交外方前继续做好成品保护，及时修补破损 |
-| 姆皮卡路途交通安全 | 中 | 姆皮卡路途遥远、路况不好，且赞比亚雨季来临，存在交通安全风险 | 验收组（未明确具体个人） | 注意交通安全和疫情防控，安全完成验收任务 |
+| 人员履约及护照问题 | 中 | 受疫情影响及EPC项目特点，个别同志进出场时间及护照需完善，个别特种人员证件有效期可能过期或未及时更新 | 施工部、管理组 | 会后完善相关资料，与国内人力资源对接确认证件延期或更新情况 |
+| 人员统计数量不完整 | 低 | 技术组未将厂家服务人员等计入人员统计数量，影响合同履约数据准确性 | 技术组 | 完善人员统计，将厂家服务人员计入团队人员 |
+| 内业资料分类及签字不规范 | 中 | 质检资料、程序性文件等分类整理及签字规范性需进一步规范完善，影响竣工文件组卷 | 执行单位 | 按照项目执行标准和规范，及时将资料汇总到卢萨卡分类成册，按竣工文件归档要求组卷 |
+| 混凝土路面开裂 | 中 | 某厂区非主要通道混凝土路面有少量开裂现象，当地工人处理效果不好，可能受水侵蚀，若移交外方后出现大面积开裂对外影响不好 | 管理组、总包单位 | 共同研究制定科学合理的整改方案，分析成因（气候、施工工艺、材料），重新清理并用防水材料封管，最迟在出报告前完成整改，验收组复核 |
+| 监控管线接头脱落 | 低 | 设备启动时震动导致监控管线接头处脱落，可能引起机械故障 | 施工组 | 全面检查管线接头，保证有效性和安全性 |
+| 卢萨卡点雨水倒灌风险 | 中 | 提升桶位置雨水可能倒灌，存在安全隐患 | 施工组 | 检查原设计施工是否足以解决水的问题，考虑增加覆盖面积或采取技术措施解决 |
+| 卢萨卡点廊桥竖条不足 | 低 | 廊桥横向只有三个竖条，可能影响巡检维护人员安全 | 施工组 | 建议中间再加两个竖条，增强安全感 |
+| 成品保护疏忽 | 中 | 工程实体完工时间较长，成品保护有疏忽，可能存在破损，移交外方前需修补 | 施工组 | 移交前继续做好成品保护，有破损或问题的地方及时修补 |
+| 姆皮卡点交通安全 | 高 | 姆皮卡点路途遥远，路况不好，存在交通安全风险 | 验收组 | 注意交通安全，做好新冠疫情防控 |
+| 不可预见费使用证据不足 | 中 | 本项目有动用不可预见费的情况，有关依据证据和数据需进一步完善和收集整理 | 验收组、施工单位 | 后续继续跟踪完善，末次汇报时再进行沟通 |
 # 后续计划</t>
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>90.90000000000001</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11110/1611</t>
+          <t>11110/2360</t>
         </is>
       </c>
     </row>
@@ -3203,7 +3137,55 @@
           <t>新闻发布</t>
         </is>
       </c>
-      <c r="C9" s="4" t="n"/>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t># 发布会概况
+本次中金宏观策略争论周会由策略组刘刚凯文主持，围绕大美丽法案、关税、港股流动性三大宏观议题展开，并邀请公用事业首席分析师刘佳妮、机械军工分析师郭文秀、传媒首席分析师张雪琴分别解读光伏反内卷、人形机器人、游戏板块的投资机会。整体基调为：对美股美债不悲观，波动提供再配置机会；关税大概率是谈判技巧，市场逐渐脱敏；港股流动性三季度边际收紧但基本面可盖过；光伏反内卷政策力度升级、行业底部夯实；人形机器人三季度围绕华为链、本土企业技术闭环、特斯拉硬件替代三条主线；游戏板块在消费、政策和新品周期三重利好下有望戴维斯双击。
+# 核心信息
+- 大美丽法案三大块：提高债务上限约**5万亿美元**，延长2017年减税法案（新增支出**3.4万亿**、每年**3400亿**，减新能源补贴**1.4万亿**），取消`899条款`。
+- 信用周期框架：政府、AI产业投资、传统私人部门需求三部分；美国如篝火自然修复，中国如煮水需持续添柴；上半年美国遭遇`DeepSeek`、财政收缩、`4月2日对等关税`三盆冷水，纳斯达克从底部反弹**35%**。
+- 7-9月美债供给约**1万亿美元**，参考2023年三季度推高美债利率从3.8%到5%、美股小幅下跌4-5%；当前期限溢价已是**2013年以来高点**，预计利率抬升幅度可能不及2023年；四季度美元可能小幅走强，美股可能反弹跑赢。
+- 关税四点信息：一定要做以支撑收入；需维持一定税率（当前豁免**10%**水平）以收**3000-4000亿**；不能太高以免通胀；市场逐渐脱敏。新变化：时间拖后（原`7月9日`），大部分税率相比`4月2日对等关税`回落，除巴西；加拿大、墨西哥、欧盟单拎出因贸易占比高。有效税率当前**10-12%**，若`8月1日`全回去可能10-15%，最极端**18%**；通胀压力缓慢抬升，年底约**3.3-3.4%**。对中国关税约**40-50%**，越南转口限制**40%**，需关注`8月12日`中美谈判及转口限制。
+- 港股流动性：`7-9月`美债利率走高、美元流动性供给压力，四季度美元可能小幅走强，边际上对港股略偏负面；港股5月后微观流动性释放，`HIBOR`大幅下降，金管局投放大量资金，港币触及**7.85**，金管局会收流动性但可小幅收（如收90亿放1000多亿），流动性边际变紧，`IPO`融资较多形成约束。指数在**23000-24000**区间震荡，类似3月底；风格上长期两头分红，银行股溢价低于**20%**短期透支，**125%**是隐形底；成长端新消费拥挤，创新药稍降，科技硬件AI应用降幅大，可提前埋伏。
+- 光伏反内卷：需求端全球新增装机从2020年**130GW**增至2024年**530GW**（CAGR **42%**），2025-26年增速回落至**10%**左右；供给端2023年产能从**600GW**增至**1000GW**，电池产能是需求**1.5倍**、硅片组件**2倍**、硅料**2.5倍**；2022年以来产业链价格下跌**70%-90%**，硅片电池2023Q4亏损，硅料组件2024Q2亏损。反内卷政策力度升级（`2024年5月17日`光伏行业高质量发展座谈会、`2025年2月`国常会、`6月29日`人民日报发声、`7月1日`中财委第6次会议、`7月3日`工信部座谈会），价格恶性竞争有望告一段落，行业底部夯实。硅料环节最易整合（集中度高、成本曲线陡峭、供需比超**200%**），电池环节供需最好（`PERC`退出、`TOPCon`占**90%**、`BC`渗透率**5-6%**）；光伏玻璃`2024年9月`第一轮产能出清降幅**6%**，第二轮计划7月降产**30%**，需出清约**2万吨**，龙头企业成本**1元/平米**。市场反馈：多晶硅期货价格触及**40元/公斤**，现货从35元上涨，硅片涨**10%**，电池涨**2分**，硅料和玻璃股价涨**20-30%**，组件涨**10%**。穿越周期企业：头部一体化组件企业议价能力强，低杠杆强现金企业财务健康，技术创新（颗粒硅使用比例从10-20%提升到**50%**，铜替代银2025-26年导入）。
+- 人形机器人：二季度A股机器人板块按流通市值加权跌约**9%**，跑输机械设备约**12个百分点**，特斯拉核心供应商股价从3月高点回调**30%-40%**，回调原因系特斯拉4月后量产时间线延后叠加中美关税。三季度三条主线：华为云生态开放（6月底发布`盘古世界模型`和`CloudRobot平台`，具备多模态生成、规划大模型、执行大模型毫米级精度，华为明确不造机器人，以`RTC`方式开放，探索`AI agent`或`license`收费）、本土人形机器人企业技术闭环（智元机器人拟收购材料厂商在A股上市，宇树科技年收入突破**10亿**、下半年加速上市，两家同时中标中国移动近**1.2亿**人形机器人采购订单）、特斯拉延期带来的硬件替代窗口（`Optimus`存在电机过热、灵巧手负载不足、续航问题，正在变更方案和筛选供应商）。物流端是投资回报率明确的场景，2025年降低单件运输成本是刚需；国内至少**100家以上**人形机器人本体厂商；港股机器人板块二季度估值溢价明显，下半年有确定性扩容。关注三类信号：华为云生态接入厂商新增、头部企业出货量跨越年化**500台**或**1000台**、电机硬件优化窗口。
+- 游戏板块：上涨接近两三个月，上周初开始调整，观点仍看好。政策端今年1月和3月国务院层面发布游戏行业支持政策，广东、浙江、北京、上海等地有专门政策支持包；版号发放今年6月单月发放**158个**（国产**147个**，进口**11个**），**2018年以来单月最高**；市场数据2024年8月以来单月持续正增长，今年1-5月游戏市场规模同比增长**17%**（**1400多亿**），手游同比增长**20%**。新品周期：市场预期今年缺乏大作，但中型厂商新品成为核心催化，如吉比特`《仗剑传说》`首月流水**2亿多**，巨人网络`《超自然行动组》`6月流水过亿，年化乐观**20亿**，利润提升**50%以上**。估值：`TTM PE`约**30倍**（2023年AI行情到过**45倍**），2025年静态`PE`约**20倍**。游戏板块逆周期性，政策友好，新品周期延续，但利润有滞后性，今年新品利润明年兑现；建议关注新品市场表现、用户获取下载榜排名等领先指标。
+# 官方表态
+- 关于去美元化：刘刚凯文表示，我们并不是完全认同去美元化这个观点，这个现在成了一个高度趋同的共识，而且都是基于宏大叙事，5~10年之后的事即便认可这个逻辑的人也没法拍胸脯说一定兑现。
+- 关于市场误区：刘刚凯文指出，现在市场两个最大的误区，一个是把美元弱当成去美元化，另一个是把美元弱和美股弱直接划等号；美元弱在大部分时间，只要不是抛售美国资产的弱，实际是对美股有利的。
+- 关于美股美债：刘刚凯文重申，我们对美股也不悲观，波动提供再配置的机会，背后的原因是信用周期的再度转好，只不过三季度有一个流动性的波折。
+- 关于关税：刘刚凯文判断，关税大概率要做，需要维持一定税率才能收上钱，也不能太高以免通胀受不了，所以市场逐渐脱敏，静观其变。
+- 关于港股流动性：刘刚凯文强调，美元美债利率并不是绝对主导港股市场的唯一变量，很多时候自己的基本面强完全可以盖过它的影响。
+- 关于光伏反内卷：刘佳妮表示，随着反内卷力度不断强化升级，价格恶性竞争有望告一段落，至少对行业来讲夯实了它的底部。
+- 关于人形机器人：郭文秀认为，三季度将是从二季度的迷茫期到商业兑现过渡的小阶段，建议关注华为云生态接入、头部企业出货量跨越年化500台或1000台、电机硬件优化三类信号。
+- 关于游戏板块：张雪琴重申，在消费、政策和新品周期三重利好下，游戏行业有望在调整后再次实现戴维斯双击。
+# Q&amp;A环节
+**问**：大美丽法案对美股、美债、美元流动性有什么影响？
+**答**：刘刚凯文表示，大美丽法案三大块（提高债务上限约5万亿美元、延长2017年减税法案、取消899条款）对信用周期中长期有利，但短期7-9月有流动性抽水效应，美债供给约1万亿美元，参考2023年三季度推高美债利率从3.8%到5%、美股小幅下跌4-5%；当前期限溢价已是2013年以来高点，预计利率抬升幅度可能不及2023年，波动提供再配置机会，对美股美债不悲观。
+**问**：关税是否在升级？对通胀和美联储降息有什么影响？
+**答**：刘刚凯文表示，关税大概率要做以支撑收入，需维持一定税率（当前豁免10%水平）以收3000-4000亿，不能太高以免通胀；新变化是时间拖后（原7月9日），大部分税率相比4月2日对等关税回落，除巴西；有效税率当前10-12%，若8月1日全回去可能10-15%，最极端18%；通胀压力缓慢抬升，年底约3.3-3.4%，不大幅改变通胀路径，美联储7-9月仍可降息。
+**问**：对中国关税和转口限制有什么影响？
+**答**：刘刚凯文提示，对中国关税约40-50%，越南转口限制40%，我们比这个税率还要低，需关注8月12日中美谈判进展及转口限制。
+**问**：港股流动性三季度会怎样？
+**答**：刘刚凯文表示，7-9月美债利率走高、美元流动性供给压力，四季度美元可能小幅走强，边际上对港股略偏负面；港股5月后微观流动性释放，HIBOR大幅下降，金管局投放大量资金，港币触及7.85，金管局会收流动性但可小幅收（如收90亿放1000多亿），流动性边际变紧，IPO融资较多形成约束；指数在23000-24000区间震荡，类似3月底。
+**问**：光伏反内卷政策对行业有什么影响？哪些环节最受益？
+**答**：刘佳妮表示，反内卷政策力度升级（2024年5月17日光伏行业高质量发展座谈会、2025年2月国常会、6月29日人民日报发声、7月1日中财委第6次会议、7月3日工信部座谈会），价格恶性竞争有望告一段落，行业底部夯实；硅料环节最易整合（集中度高、成本曲线陡峭、供需比超200%），电池环节供需最好（PERC退出、TOPCon占90%、BC渗透率5-6%）；光伏玻璃第二轮产能出清计划7月降产30%，需出清约2万吨。
+**问**：光伏产业链价格和股价有什么反应？
+**答**：刘佳妮表示，多晶硅期货价格触及40元/公斤，现货从35元上涨，硅片涨10%，电池涨2分，硅料和玻璃股价涨20-30%，组件涨10%；组件价格能否跟涨取决于下游电站能否接受产业链价格上涨传导，需观望招标情况。
+**问**：人形机器人三季度有哪些催化剂和投资主线？
+**答**：郭文秀表示，三季度围绕三条主线：华为云生态开放（6月底发布盘古世界模型和CloudRobot平台，华为明确不造机器人，以RTC方式开放）、本土人形机器人企业技术闭环（智元机器人拟收购材料厂商在A股上市，宇树科技年收入突破10亿、下半年加速上市，两家同时中标中国移动近1.2亿人形机器人采购订单）、特斯拉延期带来的硬件替代窗口（Optimus存在电机过热、灵巧手负载不足、续航问题，正在变更方案和筛选供应商）；建议关注三类信号：华为云生态接入厂商新增、头部企业出货量跨越年化500台或1000台、电机硬件优化窗口。
+**问**：游戏板块上涨后调整，是结束还是回调后更健康？
+**答**：张雪琴表示，观点旗帜鲜明是后者；估值上TTM PE约30倍（2023年AI行情到过45倍），2025年静态PE约20倍，游戏板块逆周期性，政策友好，新品周期延续，但利润有滞后性，今年新品利润明年兑现；在消费、政策和新品周期三重利好下，游戏行业有望在调整后再次实现戴维斯双击。</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>121.9</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>22868/4863</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="13.5" customHeight="1" s="9">
       <c r="A10" s="6" t="inlineStr">
@@ -3513,7 +3495,45 @@
           <t>课堂记录</t>
         </is>
       </c>
-      <c r="C10" s="4" t="n"/>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t># 课程概况
+本次课程为“梦想”主题班会，围绕认识梦想、思考实现梦想的条件展开。老师先询问学生们的梦想，学生回答有当保安、当喜剧人、当太空人、当世界冠军、当歌手等；老师分享自己的梦想是成为受学生喜爱的有名望的优秀人民教师，并讲述个人经历：曾梦想考中国美术学院，单考过了但未去，因离家远和没钱，后选择定向生，去广东技术师范大学（原民族学院），定向回龙川县教书；定向生免学费，但定向不能考研，只能在职考研，边工作边读研，学费自己交。老师还分享大学梦想：加入学生会、参加比赛、保持专业排名第一（专业41人，大学4年保持第一）、考教师资格证；并提到高中时在国旗下讲话立志考中国美术学院，被嘲笑，但坚持梦想。课上播放视频：航模爱好者何宗发（中国唯一去法国巴黎比赛的）和想当歌手的普通人，讨论实现梦想的条件；讨论得出实现梦想需要坚持努力、勇敢、机会、兴趣、能力、学习等条件；提到马云中考考两次、高考考三次，最终成为中国首富，强调坚持的重要性。最后老师让学生写下自己的梦想清单，并分享部分学生的梦想；总结实现梦想需要坚持、行动、机会、能力、学习等条件，梦想可以分阶段调整，鼓励学生写下梦想清单并努力实现。
+# 核心知识点梳理
+## 梦想的定义与价值
+- 梦想是个人追求的目标，每一个梦想都值得尊重，**不被嘲笑的梦想不是梦想**。
+- 梦想可以分阶段调整：先定小目标，再定大目标，如考不进年级前50可先调整为前百，再逐步前进。
+## 实现梦想的条件
+- **坚持努力**：如老师大学4年保持专业排名第一（专业41人），需每天5点起床，体现自律与坚持。
+- **勇敢行动**：如班上同学虽被起哄仍勇敢站上讲台唱歌。
+- **机会**：机会留给有准备的人。
+- **兴趣、能力与学习**：如唱歌走调可通过后天学习调整。
+- 天赋只是1%，**努力更重要**。
+## 梦想的案例
+- 航模爱好者**何宗发**：中国唯一去法国巴黎比赛的航模选手，通过一步步努力走上更大舞台，让世界冠军关注其成长，梦想从国内走向世界。
+- 想当歌手的普通人：虽唱歌走调，但通过后天学习和努力可以调整，最终可能成为歌手。
+- **马云**：中考考两次、高考考三次，最终成为中国首富，说明起点高低不重要，关键在坚持。
+## 梦想清单的制定
+- 梦想可以列清单，实现后打勾，并思考实现所需时间与收获。
+- 梦想可大可小，如考试不犯糊涂、考上重本、成为人民教师等。
+# 课堂互动与答疑
+**问**：如果缺少一个条件，梦想还会实现吗？
+**答**：可能因为缺少某一个条件，梦想仍有可能实现；但如果具备所有条件，梦想会更快实现。
+延伸思考：老师强调学习、坚持、行动是梦想条件中必不可少的三个。
+&gt; 不被嘲笑的梦想不是梦想。
+&gt; 机会都是留给有准备的人。
+# 课后任务与学习建议
+老师布置任务：请同学们拿出纸写下自己的梦想清单，可像老师一样列清单，写清第1个、第2个、第3个梦想，实现后打勾，并思考实现梦想所需时间及实现后的收获。写完后每个小组第1个同学收齐交给老师。老师强调写梦想要实在、诚恳，并鼓励相信每一个同学的梦想。</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>9362/1292</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="13.5" customHeight="1" s="9">
       <c r="A11" s="6" t="inlineStr">
@@ -3683,7 +3703,63 @@
           <t>通用纪要</t>
         </is>
       </c>
-      <c r="C11" s="4" t="n"/>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t># 全文摘要
+本段文本为《新闻联播》2024年7月14日内容汇总，围绕文化自信与中华民族现代文明建设、赵乐际访俄、夏粮产量创新高、铁路货运增长、快递业提速、油气管网建设、多地降雨应对及国内外新闻等多项议题展开。核心结论包括：习近平总书记强调文化自信，提出‘两个结合’特别是‘第二个结合’的重大意义，2023年10月首次提出习近平文化思想；赵乐际访俄期间双方同意加强立法机构合作；我国夏粮产量达2996亿斤创历史新高；6月国家铁路货运多项指标创历史同期新高；上半年快递业务量超800亿件；油气管网建设提速，‘全国一张网’不断完善。整体呈现我国在文化、经济、基础设施等领域的发展成就，以及国内外重要事件进展。
+# 要点梳理
+## 文化自信与中华民族现代文明建设
+- 习近平总书记强调文化自信，提出‘两个结合’特别是‘第二个结合’的重大意义，指出把中华优秀传统文化精华与马克思主义立场、观点、方法结合起来是中国特色社会主义。
+- 2023年6月，习近平总书记主持召开文化传承发展座谈会，系统论述中华文明五个突出特性；2023年10月，全国宣传思想文化工作会议首次提出习近平文化思想。
+- 《深化文化体制改革实施方案》是中央深改领导小组审议通过的第一个专项小组改革方案；《关于实施中华优秀传统文化传承发展工程的意见》首次以中央文件形式部署文化传承发展。
+- 文化领域供给侧结构性改革推进，文化旅游融合、非遗保护、公共文化服务体系等取得进展，我国成为图书、电视剧、动漫等领域生产大国，数字文化产业成为消费新引擎，电影市场规模屡创新高。
+## 赵乐际对俄罗斯进行正式友好访问
+- 全国人大常委会委员长赵乐际于7月9日至13日对俄罗斯进行正式友好访问，在圣彼得堡会见普京，在莫斯科与马特维延科、沃洛金会谈，并出席中俄议会合作委员会第九次会议。
+- 今年是中俄建交75周年，双方强调加强立法机构合作，落实两国元首共识，深化多层级、多领域交流；普京表示俄中立法机构合作有助于推进双边合作优先议题。
+- 马特维延科表示发展对华关系得到俄社会广泛认同；沃洛金表示俄坚定恪守一个中国原则，反对任何外部势力干涉中国内政。
+- 赵乐际在致辞中提出密切战略协作、交流治国理政经验等五点建议，访问期间向俄无名烈士墓敬献花圈。
+## 我国夏粮产量创历史新高
+- 今年我国夏粮产量达2996亿斤，比2023年增加72.5亿斤，再创历史新高；夏粮单产每亩375.2公斤，小麦单产399.1公斤，比2023年增加10公斤。
+- 中央推进‘藏粮于地、藏粮于技’战略，全国已建成高标准农田10亿多亩，农业农村部启动小麦单产提升三年行动，中央财政首次提前下拨16亿元小麦‘一喷三防’资金。
+- 小麦质量为近年来最好水平，主产区一、二等小麦占比普遍较高，夏粮首战告捷为全年粮食丰收奠定坚实基础。
+## 6月份国家铁路货运多项指标稳定增长
+- 6月份国家铁路发送货物3.32亿吨，完成货运周转量2665亿吨公里，同比分别增长6.1%、5.3%，创历史同期新高；我国铁路货运量、货运周转量等指标稳居世界首位。
+- 化肥农药运量增幅最大，同比增长26.2%；煤炭日均装车量、集装箱、商品汽车、冷链货物发送量均创历史同期新高。
+- 多式联运快车已覆盖各省会城市，铁海快线班列已覆盖全国主要港口；6月中欧班列开行1719列，发送货物18万标箱，同比分别增长15%、11%。
+## 上半年我国快递业发展提速
+- 今年上半年我国快递业务量超800亿件，截至6月30日已达800亿件；快递企业已运行国际航线40余条，面向东南亚开通陆运专线，运行美西海运航线。
+- 每天超1亿多件快递包裹在农村地区流动，5—6月快递日均业务量近5亿件；快递业与制造业融合发展，服务场景不断丰富。
+## 我国油气管网建设提速
+- 预计全年新增管道里程超4000公里；西气东输四线已完成吐鲁番至中卫段主体管道工程建设，投产后年输气能力将提升150亿立方米。
+- 我国主干油气管网约10万公里，输气能力从2020年2230亿立方米增加到3290亿立方米，增幅达48%，天然气‘全国一张网’日供气能力超10亿立方米。
+- 到2025年将初步形成东北、西北、西南及海上四大油气战略通道，建成‘五纵五横’天然气干线管网。
+## 渝川皖等地积极应对降雨天气
+- 重庆28个区县出现暴雨，其中13个区县大暴雨，当地组织工作人员连夜抢险排涝；四川内江出现内涝、滑坡等险情，消防救援人员转移被困群众。
+- 安徽多条河流水位上涨，滁州市全椒县加强巡堤，及时处置堤防渗漏和管涌；水利部针对‘七下八上’防汛关键期逐流域安排防御。
+- 长江1号、2号洪水正在演进，三峡水库15日将迎来洪峰流量45000立方米每秒量级的洪水过程，水利部联合调度嘉陵江亭子口水库等上游干支流水库群，减小三峡水库入库洪峰流量。
+## 国内联播快讯
+- 北京上半年320个市区重大项目全部开工，总投资超过4000亿元，包括丽泽数字金融科技示范园、温榆河生态治理工程等。
+- 燕矶长江大桥北岸主塔封顶，主跨1860米，上层高速公路、下层城市快速路，连接湖北鄂州和黄冈，建成后将成为鄂东空铁、空陆联运立体交通运输体系的重要过江通道。
+- 第二十三届环青海湖国际公路自行车赛收官，22支车队154名运动员参赛，决出个人总成绩、爬山积分、团体总积分等5个奖项冠军。
+- 内蒙古第34届草原那达慕开幕，主题‘相约草原遇见那达慕’，持续到8月底，开展体育赛事、文艺表演、美食品鉴、非遗展示等活动。
+- ‘中非儿童手拉手’活动在京启动，来自纳米比亚、南非、中非、索马里、乌干达五国儿童代表将在北京、河南参观访问。
+## 国际新闻
+- 多国人士高度评价中国全面深化改革扩大开放成就，关注即将召开的二十届三中全会，认为中国为世界提供更广阔的市场和发展机遇。
+- 美联邦调查局称前总统特朗普在竞选集会遭未遂刺杀，特朗普右耳中枪受伤，一名观众死亡、两名重伤，枪手为20岁左右男性，来自宾夕法尼亚州，作案动机待查明。
+- 以军空袭加沙地带马瓦西地区致90人死亡、约300人受伤，巴勒斯坦谴责以军违反国际法，约旦、卡塔尔、埃及等发表声明谴责。
+- 以军袭击黎巴嫩多个边境村镇，黎真主党武装打击以军集结地和情报设施；叙利亚首都大马士革遭空袭，1名政府军士兵死亡、3人受伤。
+- 俄称使用‘伊斯坎德尔-M’导弹打击哈尔科夫方向乌军军用火车停车点，摧毁20件装备；乌称在波克罗夫斯克方向击退俄军17次进攻。
+- 加拿大东北部林火蔓延，过火面积100平方公里，9600人被疏散，消防人员无法继续使用灭火飞机；加拿大正应对500多起活跃林火，超400起失控。</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>7755/2745</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="13.5" customHeight="1" s="9">
       <c r="A12" s="6" t="inlineStr">
@@ -3917,7 +3993,63 @@
           <t>课堂记录</t>
         </is>
       </c>
-      <c r="C12" s="4" t="n"/>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t># 课程概况
+本节课为初中光学复习课，共三讲中的第一讲，主题涵盖光的直线传播、光的反射定律、镜面反射与漫反射、平面镜成像及球面镜应用，并讲解相关习题。光在均匀介质中沿直线传播，实例包括三点一线、激光准直、小孔成像、日食月食、影子的形成；小孔成像成倒立、实像，放大缩小不一定，与孔形状无关。光速在真空中为3×10^8米/秒，空气中约2.99×10^8米/秒，水中约为真空中的3/4，玻璃中约为2/3；一束激光从地球射到月球表面时间1.25秒，距离为3.75×10^8米。光的反射定律：反射光线、入射光线和法线在同一平面内，反射光线和入射光线分居法线两侧，反射角等于入射角；法线是垂直于镜面的辅助线，是虚线，不存在。光垂直射到镜面上，入射角和反射角都是0度；反射光线与平面镜夹角40度时，入射角为50度。作图步骤为先画法线，再根据反射角等于入射角画入射或反射光线。镜面反射是一束平行光射到光滑表面，反射光线平行，人眼在特定位置才能看到；漫反射是表面凹凸不平，反射光线射向各个方向，人眼在任何位置都能看到。生活中大多数反射是漫反射，如黑板、电影银幕；黑板反光看不清粉笔字是镜面反射。雨后夜晚，迎着月光走，发亮处是水潭；背着月光走，发暗处是水潭。平面镜成像原理是光的反射定律，成像是虚像，特点为正立、等大、虚像，像与物连线垂直镜面，像到镜面距离等于物到镜面距离。实验用玻璃板代替平面镜便于确定像的位置，用刻度尺比较像与物到镜面的距离，用两段相同蜡烛比较像与物大小；光屏不能接收到虚像。玻璃板与水平面不垂直会导致像距测量不准确，玻璃板有厚度，两个面反射会形成两个像。视力表距镜子3.5米，人距镜子1.5米时，看虚像距离为5米；人站在平面镜前1米，人与像距离2米。凸面镜对光线起发散作用，成像是正立、缩小的虚像，应用于汽车后视镜、丁字路口拐弯处；凹面镜对光线起会聚作用，应用于手电筒、汽车前大灯、探照灯、耳鼻喉科检查、太阳灶。阿基米德利用凹面镜汇聚光线烧毁敌人帆船；玻璃幕墙形成凹面会汇聚光线，可能烧死树木、引燃电线，造成光污染。
+# 核心知识点梳理
+## 光的直线传播
+- **光源**：自身能够发光的物体，分为自然光源（如太阳、萤火虫）和人造光源（如火把、蜡烛、煤油灯、电灯）。
+- **光线**：用一条带有箭头的直线代表，是物理模型，不是真实存在的。
+- **光在均匀介质中沿直线传播**：实例包括三点一线、激光准直、小孔成像、日食月食、影子的形成。
+- **小孔成像**：成倒立、实像，放大缩小不一定，与孔形状无关；生活中如树荫下的光斑。
+- **日食与月食**：日食时太阳、月球、地球在同一直线上，月球在中间；月食时地球在中间。
+- **光速**：真空中为3×10^8米/秒，空气中约2.99×10^8米/秒，水中约为真空中的3/4，玻璃中约为2/3。
+- **计算**：一束激光从地球射到月球表面时间1.25秒，距离为3.75×10^8米。
+- **雷电现象**：先看到闪电后听到雷声，因为光速比声速快。
+## 光的反射定律
+- **内容**：反射光线、入射光线和法线在同一平面内；反射光线和入射光线分居法线两侧；反射角等于入射角。
+- **法线**：垂直于镜面的辅助线，是虚线，不存在。
+- **垂直入射**：光垂直射到镜面上，入射角和反射角都是0度。
+- **角度计算**：反射光线与平面镜夹角40度时，入射角为50度。
+- **作图步骤**：先画法线，再根据反射角等于入射角画入射或反射光线。
+## 镜面反射与漫反射
+- **镜面反射**：一束平行光射到光滑表面，反射光线平行，人眼在特定位置才能看到。
+- **漫反射**：表面凹凸不平，反射光线射向各个方向，人眼在任何位置都能看到。
+- **应用**：生活中大多数反射是漫反射，如黑板、电影银幕；黑板反光看不清粉笔字是镜面反射。
+- **雨后夜晚**：迎着月光走，发亮处是水潭；背着月光走，发暗处是水潭。
+## 平面镜成像
+- **原理**：光的反射定律，成像是虚像。
+- **特点**：正立、等大、虚像，像与物连线垂直镜面，像到镜面距离等于物到镜面距离。
+- **实验**：用玻璃板代替平面镜便于确定像的位置；用刻度尺比较像与物到镜面的距离；用两段相同蜡烛比较像与物大小。
+- **光屏**：不能接收到虚像。
+- **误差原因**：玻璃板与水平面不垂直会导致像距测量不准确；玻璃板有厚度，两个面反射会形成两个像。
+- **应用**：视力表距镜子3.5米，人距镜子1.5米时，看虚像距离为5米；人站在平面镜前1米，人与像距离2米。
+## 球面镜及其应用
+- **凸面镜**：对光线起发散作用，成像是正立、缩小的虚像，应用于汽车后视镜、丁字路口拐弯处。
+- **凹面镜**：对光线起会聚作用，应用于手电筒、汽车前大灯、探照灯、耳鼻喉科检查、太阳灶。
+- **历史案例**：阿基米德利用凹面镜汇聚光线烧毁敌人帆船。
+- **光污染**：玻璃幕墙形成凹面会汇聚光线，可能烧死树木、引燃电线。
+# 课堂互动与答疑
+**问**：光垂直射到镜面上，入射角是多少度？
+**答**：入射角是0度，因为入射角是入射光线与法线的夹角，垂直入射时夹角为0度。
+**问**：为什么用玻璃板代替平面镜做实验？
+**答**：因为玻璃板既能反射成像，又能透过光线，便于移动后面的蜡烛来确定像的位置。
+**问**：为什么玻璃板会看到两个像？
+**答**：因为玻璃板有厚度，两个面都能发生反射，形成两个像。
+&gt; 教师提醒："光线是物理模型，不是真实存在的。"
+# 课后任务与学习建议
+教师布置了练习第1~5题、第10~11题、第13~17题、第19~24题等作为课堂练习，并讲解了答案。未提及课后作业的具体提交要求。复习重点包括：光在均匀介质中沿直线传播及其实例、光的反射定律、镜面反射与漫反射的区别、平面镜成像特点及实验、球面镜的应用。学习建议：可在家用激光笔、纸杯、蜡烛等材料做小孔成像和平面镜成像实验，加深理解。</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>25691/2481</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="13.5" customHeight="1" s="9">
       <c r="A13" s="6" t="inlineStr">
@@ -4023,7 +4155,63 @@
           <t>课堂记录</t>
         </is>
       </c>
-      <c r="C13" s="4" t="n"/>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t># 课程概况
+本次课程为《电气工程基础》导论，是电气工程专业入门课。课程教学目的有二：一是掌握电力系统发电、输电、配电、用电四个典型环节的构成、工作原理及与系统整体的关系，建立电力系统整体概念；二是掌握电力系统分析、设计、运行、管理方面的基础理论、技术与计算方法。前修课程要求电路理论与电机学知识，特别是变压器和同步电机，有欠缺的同学需自行补充；后续重要课程为电力系统分析、电力系统机电保护、电力系统自动化、高电压技术。第一章是概念最多、最重要的章节，要求掌握电力系统、电力网、动力系统、变电站等基本概念，理解电力系统特点及要求，掌握电能质量指标及国家标准规定范围，了解常用接地方式特别是中性点接地方式。课程还梳理了交直流输电发展史，讲解了三相交流输电优势、电力系统形成过程，以及电力系统、电力网、动力系统的定义与电网分类。
+# 核心知识点梳理
+## 课程定位与教学目标
+- 电气工程基础是专业课入门课，教学目的解决两个问题：掌握电力系统**发电、输电、配电、用电**四个典型环节的构成、工作原理及与系统整体关系；掌握电力系统分析、设计、运行、管理方面的基础理论、技术与计算方法。
+- 前修课程要求：电路理论、电机学知识，特别是**变压器和同步电机**相关知识要求较高，有欠缺的同学需自行补充。
+- 后续重要课程：电力系统分析、电力系统机电保护、电力系统自动化、高电压技术。
+## 第一章学习内容与难点
+- 第一章是概念最多、最重要的章节，要求掌握：电力系统若干基本概念（电力系统、电力网、动力系统、变电站）；理解电力系统特点及由此引起的设计运行基础理论；理解对电力系统的要求；掌握电能质量指标及国家标准规定范围；了解常用接地方式，特别是中性点接地方式的不同特点。
+- 三个学习难点：电力系统特点引出的基本原理（如电能不能大量储存决定有功无功动态平衡）⭐；额定电压规定繁杂需搞清楚 ⭐；各种中性点接地方式影响后续章节且学习困难 ⭐。
+- 学习方法建议：注意概念内涵外延并适当实际；从特点要求出发、从基础原理推导，不记结论；寻找额定电压规定间基本规律；比较不同中性点接地方式特点。
+## 电力发展简史（直流与交流输电）
+- 直流输电发展：福泰勒用2000米导线连接瓦斯发电机拖动直流发电机和电动机，证明直流输电可行；1874年俄国工程师在彼得堡建成4.5公里直流输电线路，传输功率4.5千瓦；1882年法国德普勒架设首条57公里直流试验线路，采用电报线，首端电压343伏、末端850伏，输送功率200瓦，损耗78%；1883年德普勒从法国南部进行14公里输电试验，输送功率1.1千瓦，从瓦利尔书店到巴黎56公里损耗55%；1882年10月英国科学家发明直流三线制系统，外线与中线间电压110伏，两外线间220伏，后扩展到5根线形成直流无限制系统。
+- 直流输电限制：电压等级低时损耗大、电压降落快，提高电压困难，制造大容量高压直流发电机困难，限制远距离大容量输电。
+- 19世纪末法国方剑将多台直流发电机串联提高电压，将75千瓦电力送75千米；20世纪初瑞典科学家装短路器使任意发电机投切不停电，此后20多年建15条直流输电线路，最大规模1906年法国慕尼黑水电厂到里昂180公里、57千伏、4700千瓦；1927年改建成260公里、125千伏、19000千瓦，接入两座水电站。
+- 直流输电制约因素多：设备复杂、运行方式复杂、造价高、可靠性差。
+- 交流输电发展：英国法拉第电磁感应原理；美国亨利用多线圈做原边、少线圈做副边实现高电压感应低电压，是变压器前身；1876年俄国科学家发明单相变压器用于照明；法国和英国科学家联合将多台变压器串联到输电线路，负荷变化时输电电压受干扰；1883年美国特斯拉制造感应电机；1885年匈牙利科学家设计多台变压器并联运行方式。
+- 威斯汀豪斯与爱迪生交直流电力战争：爱迪生和凯尔文主张直流电，理由为效率高、交流电有危险性（购买威斯汀豪斯交流发电机卖给监狱给死刑犯执行死刑证明危险性）；威斯汀豪斯和特斯拉主张交流电，因易用变压器升压降压减少电能损失。
+- 1886年威斯汀豪斯在美国麻省进行1000米1.2千米30千伏交流输电示范，又在意大利建成17英里、2千伏高压输电线路；1886年俄国科学家发明三相交流电、三相交流输电和三相异步电动机。
+- 交直流电力战争标志：法国到德国交流输电线路，从水电厂安装三相发电机和两台升压变压器，升压后送到德国，在法兰克福建两座降压变，一座供展览会照明，另一座供100马力三相异步电动机用于人工瀑布离心泵。
+- 交流输电进展：1898年发明真实绝缘子，美国加利福尼亚输电电压等级提高到33千伏；1906年发明悬式绝缘子，建成110千伏高压输电；1912年发现电晕临界电压与导线直径成比例增加，铝线和刚性铝绞线开始应用，美国建成154千伏线路；1923年均压阀技术应用，建成220千伏线路；1936年美国287千伏线路投运；1952年瑞典建成380千伏线路，第一次采用分裂导线；1956年苏联400千伏双回线路投入运行；1965年加拿大建成735千伏输电系统；1969年美国765千伏线路并入电网；1985年苏联特高压线路1150千伏投运，后降压到500千伏运行。
+- 国内投运：224千伏1941年投运，330千伏1972年投运，500千伏1981年投运，2009年1000千伏投运（交流特高压第一次）。
+- 直流输电复兴：交流大电网稳定问题突出，直流在联网中优势显露，用于电网间连接。1954年瑞典本土与哥特兰岛建成世界第一个工业采用海底电缆，电压等级100千伏、96公里，采用汞弧阀；1970年扩建50千伏、1万千瓦晶闸管换流阀试验工程；1972年世界第一个晶闸管换流阀背靠背直流工程在加拿大投运。
+- 中国直流输电：第一个直流输电工程连接舟山群岛与浙江定海电网；第二个是1989年葛上直流（葛洲坝电厂到上海），±500千伏；今年6月投运云广直流±800特高压直流工程。
+## 三相交流输电优势与电力系统形成
+- 交流指ABC三相对称系统，具有三个优点：易于产生旋转磁场，三相电动机容易做驱动；瞬时功率恒定不随时间变化；输电线路导线量（金属消耗量）最少。
+- 除室内配电等小功率供电采用单相交流外，其它场合基本采用三相交流；国内电力系统大多数高压、超高压、特高压输电采用三相交流，联网才用直流。
+- 三相三线制传输效率最高，金属消耗量在同等功率和功率因数下最小。
+- 电力系统形成过程：最早单台发电机向附近负荷供电，可靠性差；后把多台发电机连接起来提高可靠性，但导线有电阻和电抗，产生电压损耗和功率损耗，输电线路不能太长；解决办法是提高电压，电流减小，损耗和电压降落减小，距离变长；交流升压用变压器，一侧升压另一侧降压。
+- 电力系统形成后好处：多台发电机供电，一台停机不影响；能装大机组，供电范围大，带来经济效益。
+- 输电距离很长时（如湖北送电华东、云贵送电两广），中间装变电站降压供电，并可引接部分负荷；输电距离长出现稳定问题，可装变电站采取设备调整。
+- 现代电力系统特征：发电机发电，经升压变压器升压，通过输电线路传输到负荷中心，再降压给用电设备。
+## 电力系统、电力网、动力系统定义与电网分类
+- 电力系统定义：由发电机、变压器、输电线路和用电设备构成的整体，完成电能生产、输送、分配、消耗四个职能，有发电、输电、配电、用电四个环节。
+- 电力网定义：电力系统中去除发电机和用电设备的部分，即变压器和输电线路构成的网络。
+- 动力系统定义：电力系统基础上加上发电厂动力部分（火电厂的锅炉、汽机、煤炭输送处理系统；水电厂的水轮机、水坝、水库等）。
+- 行业常用概念：电力网和电力系统，动力系统很少说。
+- 电网分类：地方电力网（电压等级110千伏及以下，早期定义35千伏及以下，供电半径20~50公里）；区域电力网（电压等级110、220千伏和少量500千伏，供电半径超过50公里，联系较多发电厂和负荷中心）；超高压远距离输送网络（电压等级500千伏或1000千伏，东北有330千伏，任务是把发电厂电能送到负荷中心，距离很远，构成跨省跨地区大型电力系统）。
+- 实例：武汉电网属于地方电力网，主要供电电压110千伏和35千伏，少数220千伏，供电半径50公里以内；华中网是典型区域网；葛上直流、三峡到上海输电线路是连接华中与华东的超高压远距离输电网络；特高压系统从山西晋东南到湖北荆门，跨三个省，连接华北电网和华中电网，属于超高压远距离输送网络。
+- 电压等级随电网发展提高，各级电网电压等级会变化，一般提高。
+- 变电站分类方法：按最高电压等级分类（如华工变电站10千伏变380伏，是10千伏变电站；关山变电站最高电压220千伏，是220千伏变电站；凤凰山变电站最高电压500千伏，是500千伏变电站）；按主要功率流通方向分类（大部分功率从高压侧流向低压侧为降压变电站，发电厂中大部分功率从低压侧升压到高压侧为升压变电站）。
+# 课堂互动与答疑
+未提及
+# 课后任务与学习建议
+教师未布置具体作业，但强调第一章是重点内容，要求掌握电力系统、电力网、动力系统、变电站等基本概念，理解电力系统特点及要求，掌握电能质量指标及国家标准规定范围，了解常用接地方式特别是中性点接地方式。三个学习难点需重点攻克：电力系统特点引出的基本原理（如电能不能大量储存决定有功无功动态平衡）、额定电压规定、各种中性点接地方式。学习方法建议：注意概念内涵外延并适当实际；从特点要求出发、从基础原理推导，不记结论；寻找额定电压规定间基本规律；比较不同中性点接地方式特点。教师推荐三本书供学生进一步阅读，并建议学生了解电力发展的基本发展史。</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>11163/4006</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="13.5" customHeight="1" s="9">
       <c r="A14" s="6" t="inlineStr">
@@ -4099,7 +4287,37 @@
           <t>知识笔记</t>
         </is>
       </c>
-      <c r="C14" s="4" t="n"/>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t># 知识主题与概述
+本视频围绕Stack Exchange上关于调和级数∑1/n收敛性的经典问题展开，皮卡以评论者身份逐一点评网友的证明方法。他首先从高中数学的前n项和定义出发，解释级数收敛与发散的标准：若所有部分和Sn小于某个固定上界a则收敛，若部分和能超过任意给定的数则发散。随后他介绍了两种主要证明流派：第一种通过分组估计，每组和大于1/2，从而证明部分和无上界；第二种通过证明H_n &gt; log(n+1)来证明发散，因为log无上界。皮卡还补充了柯西凝聚判别法、积分估计和Stolz定理等工具，并批评某些证明是事后凑出来的、故弄玄虚，妨碍理解。整体逻辑框架是从基础定义出发，逐步剖析不同证明思路的优劣，最终强调自然、可理解的证明方法。
+# 核心概念
+## 调和级数
+- 调和级数指∑1/n = 1 + 1/2 + 1/3 + …，其部分和记为H_n（英文为harmonic，调和之意），是微积分中的经典问题，属于清朝初年（康熙治鳌拜时期）提出的微积分范畴。
+- 收敛与发散的定义：对正向级数，若所有部分和Sn都小于某个固定实数a（如100或1000万），则收敛；若部分和能超过任意给定的数，则发散。
+## 分组估计证明
+- 第一个网友的证明：将项分组，如1单独一组，1/2+1/3一组，1/4+1/5+1/6+1/7一组，每组和都大于1/2，因此任意多组相加无上界，故发散。
+- 皮卡指出，这种分组求和思路与高斯小时候计算1+2+3+…+100的方法类似，都是发现具有良好性质的组（如和恒定或满足估计），从而简化求和问题。
+## 柯西凝聚判别法
+- 柯西凝聚判别法的证明过程与分组估计完全一样，适用于非负不增序列，通过分组取上界或下界来估计部分和。
+- 应用该方法，∑1/n的收敛发散性等价于∑2^k·(1/2^k) = ∑1，即无穷个1相加，显然发散，从而简化了对增长缓慢序列的判断。
+## 积分估计流派
+- 该流派用积分曲线面积近似H_n：因为H_n的每一项高为1/n、底为1，矩形面积始终大于下方曲边梯形面积，故H_n &gt; ∫₁ⁿ⁺¹ (1/x)dx = log(n+1)，而log无上界，所以发散。
+## 差分流派（Stolz定理）
+- 该流派试图证明H_n与log n同增长级别，通过Stolz定理（中文称Stolz定理，数学竞赛和考研常用）求差分极限：分子差分H_{n+1}-H_n = 1/(n+1)，分母差分log(n+1)-log n = log(1+1/n)，两者极限均为1，故H_n/log n → 1。
+- 皮卡认为此方法不自然，因为需要事先知道H_n与log n同阶，属于先射箭后画靶。
+# 核心结论
+核心结论：调和级数∑1/n是发散的，这是微积分中的经典结论，可通过分组估计、柯西凝聚判别法、积分估计或Stolz定理等多种方法证明。易混淆点：收敛与发散的定义需明确上界a是固定的，且对所有n成立；部分和H_n与log n的关系是H_n &gt; log(n+1)，但H_n本身无上界。待澄清问题：皮卡批评某些证明（如差分流派）是事后凑出来的，不自然，认为它们故弄玄虚、妨碍理解，但未给出更自然的替代证明。易错点：**不要误以为调和级数收敛**，因为虽然项趋于0，但部分和无上界；**不要混淆log与ln**，皮卡指出log是美国的写法，ln是欧洲传苏联再传中国的写法，两者本质相同。</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>7465/1412</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="13.5" customHeight="1" s="9">
       <c r="A15" s="6" t="inlineStr">
@@ -4157,7 +4375,68 @@
           <t>知识笔记</t>
         </is>
       </c>
-      <c r="C15" s="4" t="n"/>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t># 知识主题与概述
+本期视频由工作室老李主讲，围绕GitHub这一资源库展开，核心议题包括实用热门项目介绍与使用技巧。整体逻辑框架为：先展示一批实用项目（如工作性价比评估、表情包合集、健康指南、证件照生成、健身指导、教材下载、AI视频生成、声音克隆、AI学习资源等），再针对国内用户访问GitHub的常见问题（网络不通、页面全英文、原生搜索不好用）逐一给出解决方案，包括使用加速软件、镜像站、魔法上网、翻译插件、AI搜索等。老李强调GitHub是巨大的宝藏资源库，几乎能找到所需资源、教程与工具，并推荐用AI工具（如ChatGPT）辅助搜索与追踪热门项目。
+# 核心概念
+## GitHub
+- **GitHub** 被形容为“巨大的宝藏资源库”，几乎能找到想要的资源、教程、工具，包括名校公开课、大厂面试题、开源大模型、AI学习资料等。
+## b班值不值得上
+- 输入**年薪、工作地区、年假、通勤时长、学历、工作年限**等，综合评估工作性价比，给出分数和评级；示例中程序员工作被评为“性价比还不错，优质牛马”。
+## 表情包博物馆
+- 收录国内过去几年全网爆火的表情包合集，包括甄嬛传、罗翔、特朗普、马保国等，用于斗图。
+## 活到150岁指南
+- 分享经科学验证的健康知识，如**间歇性进食**促进胆汁代谢、炎症自愈，吃天然发酵食品改善肠道菌群生态。
+## 一键做证件照
+- 上传大头照即可一键抠图换背景，生成不同标准的证件照和打印模板。
+## 健身项目
+- 可选择自重、哑铃、弹力带、长凳等器材，选择肌肉群后提供参考动画，如练习腹肌的自重动作。
+## 教材项目
+- 收集国内小学、初中、高中及部分大学PDF教材，全部免费。
+## 全自动视频生成项目
+- 名为 `morning printer Turbo`，近期超火。
+## 声音克隆模型 chat box TTS
+- **零样本语音克隆**，情感控制到位，克隆声音像真人；上传音频可合成英文台词。
+## AI学习资源库
+- 涵盖大语言模型、RAG、AI Agents等最新AI技术，作者整理成**500多页PDF文档**，含大量示意图。
+## awesome am. Ap ps
+- 收录大模型最新agent应用，如医学影像数据分析、AI投资、竞争对手情报分析等，适合跟进AI应用落地案例或找创业点子。
+## 访问加速方法
+- 方法一：使用 `watch tool Kit` 加速软件，下载安装后勾选GitHub加速。
+- 方法二：使用镜像站如 `gh proxy`，浏览器直接访问。
+- 方法三：使用魔法（科学上网），需注册GitHub，可用国内QQ邮箱。
+## 页面汉化
+- 给浏览器装翻译插件，如谷歌浏览器推荐 `谷歌translate` 或 `沉浸式翻译`；动手能力强的可装汉化插件。
+## 搜索技巧
+- GitHub原生搜索按精准匹配排序，对国人不好用；推荐用AI搜索（如ChatGPT）用中文描述需求。
+## 项目主页元素
+- 项目本质是文件夹；`watch` 关注、`fork` 复制、`star` 收藏点赞；`about` 是简介；`release` 是安装包；`read me` 是说明书。
+## 判断项目维护状态
+- 查看文件最近 `commit` 日期，若更新日期久远，大概率是僵尸项目。
+## 追踪热门项目
+- 通过 `explore` 的 `trending` 查看当天、本周、本月最热门项目；也可用ChatGPT找 `GitHub daily`。
+# 核心结论
+**核心结论**：
+- GitHub是资源宝库，但国内访问存在卡顿、全英文、搜索不好用等问题，可通过加速软件、镜像站、魔法、翻译插件、AI搜索等方法解决。
+- 推荐使用 `watch tool Kit` 加速软件或魔法访问GitHub，镜像站速度和稳定性较差。
+- 推荐用AI搜索（如ChatGPT）替代原生搜索，用中文描述需求可得到更全面准确的结果。
+**易混淆点**：
+- GitHub原生搜索按精准匹配排序，搜 `screen record` 和 `screen recording` 结果不同，导致搜不全。
+- `star` 是收藏点赞，`watch` 是关注，`fork` 是复制项目，三者功能不同。
+- `commit` 日期是最近更新时间，更新久远可能是僵尸项目。
+**待澄清问题**：
+- 未提及。</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>4014/1852</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="13.5" customHeight="1" s="9">
       <c r="A16" s="6" t="inlineStr">
@@ -4523,7 +4802,57 @@
           <t>采访记录</t>
         </is>
       </c>
-      <c r="C16" s="4" t="n"/>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t># 访谈概述
+本期《锵锵三人行》邀请《明朝那些事儿》作者当年明月与嘉宾马先生，围绕日本历史剧《大奥》与明朝历史展开对谈。节目先讨论《大奥》所体现的日本文化中的极端精神、忠诚文化与终身雇佣制，并与中国的融合、中庸文化对比；随后转向明朝历史，探讨明史资料丰富但说法纷杂、明朝兴亡的跌宕过程、朱元璋从乞丐到皇帝的传奇、明末江南的富足生活，以及明武宗、天启帝等皇帝的个性与明式家具的审美地位。受访者当年明月以写史者身份分享研究明史的缘由与对历史认知的思考，马先生则以文化观察者视角对比中日民族精神差异。
+# 访谈详细记录
+## 《大奥》与日本文化
+- 当年明月认为《大奥》是继《大长今》之后最有影响的外国电视剧，三部曲中前两部对应中国晚明到清初，第三部在明治维新之前，是一部有跨越性的历史剧。
+- 当年明月表示，吸引他的是剧中体现的严谨精神，并对比说回头看《三国演义》会看到群众演员笑场，而日本历史剧看不到笑，每个人都特别认真、有专业精神。
+- 马先生介绍，大奥即后宫，日语中「奥」指屋子最深处，规矩严谨，后宫不许进人；幕府将军与约1000名女人生活在大奥中，全是伺候他一人。
+- 当年明月指出，日本天皇一直是摆设，实际权力掌握在幕府将军手中，德川家康开创德川幕府后权力集中；天皇曾因想办活动没钱向将军要钱被拒，最后以退位抗议。
+- 马先生认为，日本战后用30年时间成为世界第二经济强国（绝对量），是唯一没有资源的国家，这与其全民族的极端精神有关，是必然而非偶然。
+- 当年明月对比中日文化精神，认为中国文化精神是中庸，讲究融合、走最适合的路；日本精神则坚持一个原则、做事做到尽头，如炮手开炮时忘记一切只记得把炮开出去即达最高境界。
+- 马先生提到日本跳槽率最低，实行终身雇佣制，西方经济学家认为缺乏竞争会导致效率低下，但日本终身雇佣下积极性仍高，是经济学上的奇迹。
+- 马先生举例日本豆腐厂当天做当天卖，夜里11:45所有人坐好看表，12点整准时开工，4点多干完上市，无人闲聊，体现一丝不苟。
+- 当年明月认为日本作为岛国，没有资源、常火山地震，人本身有极强求生欲望，对世界悲观，必须融入团体按固定规则做事才能生存。
+- 马先生认为日本投机取巧者没有生存环境，社会文化鄙视使其无法生存；举例做绳子的人几年不赚钱铺市场，最后通过两边各加2%获利4%。
+- 当年明月表示不愿做日本人，因其常盲从且有寻死的潜在欲望，如看樱花只看落的那天，对死亡不惧怕甚至有点向往；马先生则认为日本民族不是藐视生命而是重视死亡，经济危机时身家万贯者剖腹自杀。
+## 明朝历史与《明朝那些事儿》
+- 马先生称赞《明朝那些事儿》写得好、写得放松，发行量在文学类排行榜第一；当年明月回应说主要原因是他不知道什么叫拘着，只能这么写。
+- 当年明月解释自己写明史是因为明史资料最多，但同一事件可能有7种不同说法，如罗生门；先秦因史料少难研究，明清因说法太多也难说清。
+- 马先生认为明朝260多年过程本身跌宕起伏，土木堡之变、夺门之变等怪事特别多，皇上被瓦剌军抓了又扶弟弟上位，构成现代版电视剧情节。
+- 当年明月推崇朱元璋，认为他从乞丐到皇帝独此一份，定下明朝规章制度且基本无大改动，是了不起的人才；马先生补充说朱元璋因要过饭、知道每层猫腻而疑心重。
+- 当年明月认为朱元璋参加起义军是逼上梁山，因信差送信被听到告发，没办法才去；他强调历史最重要的是弄明白这事是真的，旁观者觉得好玩，但当事人要掉脑袋，是很有风险的事。
+- 当年明月指出明末很多真相被掩盖，当时市民生活轻松舒服，江浙一带工商业兴起，给人当雇工活得很滋润，三言二拍这类娱乐产品出现说明有养活自己的资本。
+- 当年明月认为李自成起义是因为陕西一带发生大规模灾荒；马先生补充说明末江南富足，工艺精细，文征明、唐寅、董其昌都是那个时期的人，生活不好画不出小桥流水。
+- 当年明月引用名言「我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训」，认为历史事件发生时有背景，不能套用经验，否则一定要倒霉。
+- 当年明月说明朝皇帝有趣，宦官专政（魏忠贤、刘瑾）、文官专政（张居正）、皇帝专政（朱元璋、朱棣）都有，什么都能发生，皇帝出去了还能回来做皇帝。
+- 当年明月提到1644年明朝灭亡时北京闹瘟疫（疙瘩瘟，可能天花），李自成军打到京城无人抵抗；他曾与老师王佩奇交流，认为明朝亡得蹊跷，坏事衰事都赶上了。
+- 马先生认为中国王朝300年大限，宋朝因退让大半个国土延续319年，汉朝中间隔断14年，唐朝、明朝、清朝都没跨过界限；当年明月比喻说明朝像公司，摊子几千万人，能撑276年已不易。
+- 马先生对比宋明汉人文人政权与满族异族政权的审美差异，认为汉人审美素雅、非表象，满族审美表象，晚清民国初年收藏中素雅之物才值钱。
+- 当年明月说明武宗正德皇帝被写坏，因接班的嘉靖是其堂兄弟而非亲生，明武宗实录由嘉靖指派杨廷和等人编纂，有偏颇；正德皇帝从江南回来在通州停半天先派人打探京城情况，很有城府。
+- 马先生提到天启皇帝爱当木匠，做完家具差大臣去卖，还打听卖得怎么样，成就感特大；他认为这反映当时社会时尚，明式家具国际地位高绝非偶然。
+- 当年明月认为明神宗几十年不上朝但不出去；马先生补充说明武宗对宫廷内女人没兴趣，因禁忌太多，对宫廷外女人有兴趣，但史料无法证实其出宫行为。
+# 关键引语与金句
+&gt; 慢慢来才是最快的方法。
+&gt; 所有人按照自己的角色去做自己的事情，最节省成本了，就不会有互相的作用力互相抵消，大家都会有一个共同的目标往前走。
+&gt; 我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训。
+&gt; 历史它那个事儿发生的时候是有背景的，就是当你要明白你不比前人聪明，你甚至可能比前人笨，就是当那种情况出现的时候，你也得那么办。
+&gt; 史书上记载下来是什么？照片。我们实际的生活，古人的生活都是录像，在史书上下来的只是一个照片，咔嚓。但你不知道为那一幕之前跟之后是什么。
+&gt; 日本的文化跟中国的文化存在一个极大的不同。中国的文化精神是什么？是中庸。日本的精神就恰相反，他坚持一个原则，你看鞠一刀就知道。
+&gt; 日本民族它不是藐视生命，它是重视死亡，它是翻着的。</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>14719/2548</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="13.5" customHeight="1" s="9">
       <c r="A17" s="6" t="inlineStr">
@@ -4855,7 +5184,32 @@
           <t>就医咨询</t>
         </is>
       </c>
-      <c r="C17" s="4" t="n"/>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t># 就诊概况
+患者张学恒，男，48岁，因上腹反复疼痛4年、近3个月加重，于消化专科门诊就诊。疼痛位于心窝处，呈烧灼感，与进食冷、硬、辛辣食物及工作紧张劳累相关，白天发作，夜间无痛醒。近4年出现两次黑便，近两个月呕吐数次。初步判断需排除消化道出血及恶性病变可能，已安排大便潜血及胃镜检查。
+# 诊断与检查结果
+本次门诊未进行胃镜及大便潜血检查，医生根据病史初步判断需排除消化道出血及恶性病变可能。患者近4年出现两次黑便，均查大便示出血，**一年前**一次持续约一个月并住院10天，**三个月前**一次住院两三天。近三个月无黑便，大便黄色正常，小便正常。既往16岁患甲肝，在三医院住院一个月，出院及后续体检肝功能均正常；对磺胺药过敏（左手起红疹，持续约半个月）。
+# 治疗方案与医嘱
+治疗计划：待大便潜血及胃镜检查结果明确后，再判断是否需要手术；若药物可控制病情则无需手术。生活注意事项：医生建议患者尽量少抽或不抽烟、少喝酒，因吸烟饮酒对胃部疾病不利；注意避免工作紧张、劳累及加班熬夜，因可能加重病情。用药说明：患者近期服用达喜、奥美拉唑、阿莫西林及胃炎合剂，均停药后复发，具体用药方案见下表。
+| 药品名称 | 剂量 | 频次 | 用法 | 注意事项 |
+| --- | --- | --- | --- | --- |
+| 达喜 | 未明确 | 初始一天两次，每次一颗；后增至每天四五次 | 口服 | 初始有效，后效果不佳，停药后复发 |
+| 奥美拉唑（国产，武汉药厂） | 未明确 | 未明确 | 口服 | 停药后复发 |
+| 阿莫西林 | 未明确 | 未明确 | 口服 | 停药后复发 |
+| 胃炎合剂（医务室配制） | 未明确 | 未明确 | 口服 | 停药后复发 |
+# 复诊与预警信号
+复诊时间：胃镜预约在后天进行，胃镜活检后由张大夫查房，医生将总结病情向上一级张医生汇报后再与患者商量下一步处理意见。⚠️ 预警症状：若再次出现黑便、呕血、剧烈腹痛或体重明显下降，需立即就医。</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>8519/846</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="13.5" customHeight="1" s="9">
       <c r="A18" s="6" t="inlineStr">
@@ -5805,7 +6159,44 @@
           <t>庭审记录</t>
         </is>
       </c>
-      <c r="C18" s="4" t="n"/>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t># 庭审概况
+本案系上诉人国家开发银行与被上诉人云南东源电力股份有限公司、云南东源曲靖电力有限公司、招银金融租赁有限公司金融借款合同纠纷一案，因不服云南省高级人民法院云民初88号民事判决提起上诉。本院依法组成合议庭，依据《中华人民共和国民事诉讼法》第134条第一款、第169条的规定公开开庭审理。庭审围绕三个争议焦点展开：抵押权与融资租赁所有权冲突、罚息复利计算、违约金连带给付。各方对央行融资租赁登记性质存在分歧，国开行主张系行业强制性规范，招银租赁主张系行业指导性规范，东源公司认为不产生物权后果。合议庭询问查询方式，国开行称仅能按单位查询，招银租赁称可登记唯一识别码但非必填项。经合议庭评议，各方当事人自愿达成调解协议，法院予以确认，庭后出具调解书。
+# 原告诉称与被告辩称
+上诉人国家开发银行请求确认对案涉设备享有抵押权，主张已尽审查义务，构成善意取得；被上诉人东源公司、曲靖电力公司、招银租赁对抵押权效力提出异议。
+| 方 | 诉讼请求/答辩意见 | 事实与理由 |
+| --- | --- | --- |
+| 上诉人（原审原告） | 确认对案涉设备享有抵押权，主张已尽审查义务，构成善意取得 | 抵押设备为通用设备无唯一标识，查询无登记；已按人民银行规定完成贷款抵押的刑事审查、资料审查、法律审查 |
+| 被上诉人（原审被告） | 主张国开行未尽审查义务，不构成善意取得 | 东源公司主张2015年12月2日邮件已告知抵押设备与招银租赁设备名称一致；招银租赁主张国开行未按央行规定查询融资租赁登记，东源煤电出资行为系无权处分 |
+# 举证与法庭调查
+**证据与质证意见**
+- 国开行提交2018年9月融资租赁查询证书，招银租赁质证认为不符合201493号文要求，查询时点与操作抵押时点不符。
+- 国开行提交工商出资证明、权属证明等材料，主张已尽审慎义务；招银租赁认为东源煤电出资行为系无权处分，工商登记公示的是出资行为而非动产公示。
+- 东源公司提交2015年12月2日邮件及融资情况统计表，主张已告知抵押设备与招银租赁设备名称一致，并用红色标注；国开行认为统计表仅显示并列关系，无法得出告知结论。
+- 招银租赁提交回租设备清单（证据7页），载明设备名称、生产厂家，但无型号；国开行认为无法据此识别设备唯一性。
+- 招银租赁提交2013年、2015年审计报告（证据82页、95页），载明曲靖电力公司注册资本4亿元已实缴；国开行据此主张招银租赁知道或应当知道设备出资情况。
+**法官询问要点**
+- 合议庭询问各方对央行征信中心融资租赁登记性质及法律后果的理解。
+- 询问国开行贷款前审查是否有内部规定必须查询融资租赁登记，未查到结果是否需保留单证作为风控材料；国开行称无此规定，未保留查询记录。
+- 询问招银租赁融资租赁登记系统中设备唯一标识码是否必填项；招银租赁称非必填项，本案设备无唯一识别码故未登记。
+- 询问国开行和招银租赁关于查询通知的规范性质及违反后果。
+**双方辩论的争议焦点**
+- 国开行主张抵押设备为通用设备无唯一标识，查询无登记，构成善意取得；招银租赁主张国开行未按央行规定查询融资租赁登记，不构成善意。
+- 东源公司主张2015年12月2日邮件已告知抵押设备与招银租赁设备名称一致，国开行未尽注意义务。
+- 各方对央行融资租赁登记性质存在分歧：国开行认为系行业强制性规范，招银租赁认为系行业指导性规范，东源公司认为不产生物权后果。
+# 庭审结果
+本案争议焦点为：一、抵押权与融资租赁所有权冲突；二、罚息、复利计算；三、违约金连带给付。经合议庭评议，各方当事人自愿达成调解协议：确定国开行对东源公司债权扣除破产清偿本金后，利息、罚息、复利合计6474.4513万元；招银租赁对六项设备享有所有权，对应债权1377.4137万元；国开行对93项设备有抵押权。双方对案涉全部发电设备整体盘活处置，变现款各50%，费用各担50%；变现不足清偿时，招银租赁未实现债权按破产重整计划预留方案清偿。各方对调解方案均无异议，签字确认，法院予以确认，庭后出具调解书。</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>30731/1699</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="13.5" customHeight="1" s="9">
       <c r="A19" s="6" t="inlineStr">
@@ -5907,7 +6298,21 @@
           <t>面试报告</t>
         </is>
       </c>
-      <c r="C19" s="4" t="n"/>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t># 公务员面试：四题综合考察公共服务能力
+公务员面试：四题综合考察公共服务能力
+会议要点：本次面试共20分钟，考生需回答4个问题，分别考察对公务员工作的理解、问题解决能力和公共服务意识。第一题中，考生将绳子比喻为鞭策、平衡和动力，分别对应骏马、风筝和陀螺：对骏马而言，绳子意味着自我反省，引用曾子“吾日三省吾身”，强调反思工作中的失误和拖延，并指出单位应形成紧张、活泼、团结、有趣的风气，同事之间比较能力和效率而非票子、车子、房子；对风筝而言，绳子意味着平衡，需建立权利清单、责任清单；对陀螺而言，绳子意味着动力，源于责任感和成就感，如撰写材料加班加点。；第二题中，考生作为小王提出AI企业调研方案：先完善统筹准备，利用课余时间补课，学习兄弟城市经验，查阅国务院和省厅关于人工智能的指导意见；制定包含客观（企业发展现状）和主观（政府服务需求）两方面的工作方案；调研分三部分：市场状况、服务需求、管理措施；具体实施包括与企业对接阅读发展报告、制定调查问卷并请专家修改、召开座谈会听取企业意见，询问人才引进、政策倾斜、用地审批、人才吸引和培养机制；管理措施通过问卷调查了解AI发展不完善之处，以便政策规范。；第三题中，考生模拟小王答复记者：承认管道问题，解释管道是90年代修建，老城区改造难度大，夏天用水高峰问题集中；已联系维修师傅准备现场维修，并将硬件问题汇报上级，计划通过城市综合保障工程改善；承认工作失职，请求媒体和居民给予改进机会，并希望媒体解释政府难处。；第四题中，考生分析存在主要矛盾（时间上的需求不满足）和次要矛盾（噪音、出行、舆论）；坚持推进城市建设，同时处理次要矛盾：督促施工方加快进度减少扰民，使用防噪墙、洒水降尘减少噪音灰尘，建议使用替代道路、通过交通广播推荐路线、鼓励公交出行并增加公交班次；通过公告形式在网络上发布信息，公开透明表达政府举措，获得市民理解。</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>5808/789</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="13.5" customHeight="1" s="9">
       <c r="A20" s="6" t="inlineStr">
@@ -5971,7 +6376,50 @@
           <t>参观游览</t>
         </is>
       </c>
-      <c r="C20" s="4" t="n"/>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t># 参观概况
+本次参观为故宫中轴线及东西六宫、珍宝馆等区域的游览讲解，全程约12分钟，覆盖午门、太和门、太和殿、中和殿、保和殿、乾清门、乾清宫、交泰殿、坤宁宫、储秀宫、慈宁宫、断虹桥、武英殿、文华殿、箭亭、钟表馆、珍宝馆、御花园、神武门等景点。讲解重点包括午门明三暗五门洞及通行规则、太和殿为举行盛大典礼之地而非上朝处、乾清宫正大光明牌匾后藏立储诏书、珍宝馆即乾隆养老院宁寿全宫等历史典故，并介绍了七个免费盖章点及三条游览路线。整体过程按中轴线由南向北推进，穿插东西六宫与珍宝馆等支线，最后从神武门结束。
+# 核心看点与讲解
+- 午门：有三个门洞，进门后变五个，即明三暗五；中间正门仅供皇帝、皇后大婚、殿试前三名（状元、榜眼、探花）通行，旁门走皇亲国戚和文武百官。
+- 太和门广场：有五座金水桥，中间桥供皇帝，挨着中间的两座桥供黄金国器，最边上的桥供文武百官。
+- 太和门：明朝皇帝在此御门听政，即上朝的地方；门口铜狮子是故宫六对铜狮中最大的一对，脚踩寰宇象征权力，建议单独拍照，不要站在狮子底下。
+- 太和殿：即金銮殿，是举行盛大典礼的地方（皇帝登基、皇后册封），不是上朝处；文武百官在太和殿广场站列，文东武西。
+- 中和殿：举行盛大典礼时皇帝的休息室，文武百官站好后皇帝再过去。
+- 保和殿：从乾隆五十四年开始是殿试考场；东北角有汉字馆，内有4枚免费印章，可购买紫禁城100现场盖章。
+- 乾清门：后宫入口，东边九卿直房，西边军机处；门口狮子耳朵耷拉、眉毛遮眼，警示后宫不该看的不看、不该听的不听。
+- 乾清宫：皇帝睡觉的地方，有27张龙床防刺客；牌匾“正大光明”后藏立储诏书，皇帝写两份，驾崩后对比。
+- 交泰殿：放25块传国玉玺。
+- 坤宁宫：住皇后，明朝所有皇后都住这；东北角文创店有5枚免费印章。
+- 储秀宫：慈禧住了20多年，现为慈禧五十大寿原状陈列，其子在此出生；旁边文创店有3枚免费印章。
+- 翊坤宫、永寿宫：永寿宫西边是太极殿，是东西六宫唯一被称为殿的。
+- 慈宁宫：康熙给奶奶孝庄皇太后修建的养老院，旁边是寿康宫（甄嬛居住）。
+- 断虹桥：网红打卡地，有形态各异的石狮子，最有名的是武当狮。
+- 武英殿（西）：后改陶瓷馆，目前关闭状态；文华殿（东）：据说现在有展览。
+- 箭亭：清朝皇帝及子孙练习骑马射箭的地方，旁边商店可买文创雪糕。
+- 钟表馆：展示各种造型的钟表。
+- 珍宝馆：门口有我国现存三座古代九龙壁之一，左边数第三条白龙下有一块木头，因当年烧制琉璃砖瓦弄坏一块，工匠用木头刷白漆以假乱真；珍宝馆不是单独展厅，院子周围屋子都是展品；即宁寿全宫，为乾隆给自己修建的养老院，乾隆退休后未放权，每天照常上朝办公；皇极殿据说是1:1复刻乾清宫，宁寿宫对标坤宁宫；乐寿堂为故宫唯一能进去参观的皇家寝室，有二龙仙楼设计；珍妃井为当年慈禧把珍妃丢进去的地方，现上头是井口石，珍妃不是从那个小眼进去的。
+- 延禧宫：网红打卡地，旁边景仁宫是甄嬛被封熹妃时所住，珍妃也住过。
+- 御花园：有钦安殿供奉真武大帝；紫禁城靠山景山从天上看酷似闭目盘坐的人像，有人说就是真武大帝。
+- 神武门：故宫北门，出门左手边有角楼咖啡（2枚免费印章）和故宫文创（2枚免费印章）两个盖章点。
+# 互动与体验
+- 盖章互动：共标注七个免费盖章位置，包括保和殿东北角汉字馆4枚、坤宁宫东北角文创店5枚、储秀宫边文创店3枚、冰窖书吧3枚、珍宝馆出口右手边商店3枚、神武门出门左手边角楼咖啡2枚、故宫文创2枚；汉字馆可购买紫禁城100现场盖章，每家店印章不同，买了不能去其他店铺盖章，汉字馆印章数量最多，可邮寄到家或背着走。
+- 文创雪糕：箭亭旁边商店可购买文创雪糕，讲解者提问雪糕造型是谁，欢迎评论区分享。
+- 个人感受：在冰窖书吧盖章时有批折子的感觉；钟表馆的钟表造型令人开眼；珍宝馆的宝贝每一样都能让人说出感叹词，但游客太多，尤其看凤冠的挤不进去；东筒子夹道拍照非常出片。
+# 收获与建议
+- 建议早起排队，一进门沿中轴线往后走，可错开大批旅游团人群，在人少时逛完最重要景点。
+- 三条游览路线：第一条走完视频内所有景点，适合待一整天的朋友，一天走3万步，需适当休息和补充水分；第二条看完坤宁宫去看景仁宫和延禧宫，接着逛钟表馆和珍宝馆，出来直奔御花园，从神武门出，大概半天时间；第三条看完坤宁宫去储秀宫，出来去御花园，从神武门出，最省力，预计2小时左右。
+- 盖章建议：喜欢盖章的朋友可截图保存七个免费盖章位置；买了紫禁城100后不能去其他店铺盖章，需有所取舍。</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>4497/1880</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="13.5" customHeight="1" s="9">
       <c r="A21" s="6" t="inlineStr">
@@ -6111,7 +6559,57 @@
           <t>调研访谈</t>
         </is>
       </c>
-      <c r="C21" s="4" t="n"/>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t># 访谈概况
+本次访谈以留守老人养老问题为核心议题，受访对象包括农村留守老人、村政府和民政局干部、城市社区社工等多元群体。访谈目的为梳理留守老人养老现状、政策落实困境及社区实践路径。据2021社区居家养老现状与未来趋势报告，65.5%的老人子女长期不在身边而独居，仅26.8%与子女同住；独居老人存在无人照料、无人慰藉、就医困难等问题，并列举了黑龙江绥滨独居老人因寂寞报警、上海与杭州各一名67岁独居老人去世多日后才被发现等案例。农村留守老人群体庞大，原因包括子女外出打工、经济压力大、老人适应能力降低及城市对农村老人的歧视等。整体反馈基调为：农村养老面临经济困难、子女不在身边、娱乐方式少等现实困境，政策覆盖有限且运营经费不足；城市社区通过志愿者制度、养老服务中心等实践取得一定成效，但社工行业面临供给不足、资金短缺、专业欠缺等困境。
+# 核心反馈
+## 农村留守老人
+- 黑龙江绥滨一位独居老奶奶因独自在家太寂寞，报警称有人敲门，民警上门后老奶奶承认是想找人聊天才报警，反映独居老人无人慰藉的普遍困境。
+- 上海一名67岁独居老人去世多日后，家中溢出刺鼻气味才被邻居发现；杭州一名67岁独居老人同样在去世数天后才被发现，凸显独居老人无人照料的致命风险。
+- 农村留守老人群体庞大，原因包括子女外出打工、经济压力大、老人适应能力降低以及城市对农村老人的无形歧视，多重因素叠加导致留守老人愈发增多。
+- 有老人反映子女外出后无人照料，日常只能自己操持农活、喂猪养鱼，生病时也缺乏陪伴，生活孤独且辛苦。
+## 村政府和民政局干部
+- 农村养老面临三大问题：经济困难（地方经济不发达）、子女不在身边（生病住院麻烦）、娱乐方式少（只能坐在一起聊天打牌）。
+- 此前探索在农村建养老公共设施，提供日托、休闲娱乐、沟通交友平台，但地方财政困难，运营经费后续无支持，设施难以持续发挥作用。
+- 五保户（三无人员）分集中供养和分散供养：集中供养将生活护理补贴直接发给敬老院护理人员，生活费直接发给敬老院；分散供养每月发475元生活费，另有护理补贴。
+- 残疾人一级二级纳入最低生活保障，有160、270、380三个标准，按家庭状况制定，最起码保证最低生活保障。
+- 农村老年人每月养老金118元，可能还要提高；但农村养老金与工人养老金待遇完全一样，对老年人不公平。
+- 村支两委和志愿者通过敲门串门、宣传政策、搞卫生等方式服务老人，每月开党员组织会，上午开会下午搞活动，到孤寡老人、留守老人家里走一圈。
+## 城市社区社工
+- 城市小区留守老人与外界社交机会更少，更容易产生孤独、抑郁等情绪，社区建立志愿者制度以就近帮扶方式传递善意。
+- 志愿者一对一帮扶，如发现老人住在楼下，上下楼时天天去看望，老人身体不好时天天送菜；通过定期表彰、志愿者积分兑换（年底可在雷锋超市兑换礼品）激励志愿者长期坚持。
+- 发掘中年志愿者，开展小手拉大手活动，从儿童青少年入手拉动家长参与；这周四准备开展送春联活动，邀请书法老师写对联，孩子们上门送对联。
+- 去年中秋节开展做月饼活动，还做过百家宴，让老人感觉社区就是大家庭；2023年目标是家长自己组织活动，社区作为协助者。
+- 每个社区成立养老服务中心，提供理疗、按摩、老年大学、心理咨询等服务。
+- 社工曾帮助一位有心理问题的老人：老人与邻里关系不和谐、半夜摔门，抗拒上门帮助，觉得周围人陌生、没有关心他的人；通过社工日复一日的关心和照料，老人心理问题逐渐好转，现在与邻里关系还算好，能接受一些意见。
+- 社工制度困境：社会需求量大而供给不足，政府和社区资金有限，难以承担长期专业社工服务费用；大量社工迫于生计转行，阻碍行业长期发展。
+- 每个街道和乡镇派两名社工驻点，围绕老人小孩服务，但很难坚持下来；社工工资低，影响就业率，很多同学做不超过一年就离开。
+- 长沙社工机构领域多，但专注力不集中，需花钱购买服务，项目不一定每年都有；一年服务成效不明显，资金拨不下来，项目结束，服务成效不一定达到。
+- 湖南省街道社工花费十来万，省里拨了钱，但很多社工不专业，专业上欠缺。
+# 关键洞察与建议
+## 洞察
+- 独居老人无人照料、无人慰藉、就医困难等问题普遍存在，且可能独自在家发生意外（如上海、杭州67岁独居老人去世多日后才被发现），说明独居老人安全与情感需求均未得到有效保障。
+- 农村留守老人群体庞大，原因包括子女外出打工、经济压力大、老人适应能力降低及城市对农村老人的歧视，说明养老问题与人口流动、城乡差距密切相关。
+- 农村养老公共设施因地方财政困难、运营经费无后续支持而难以持续，说明一次性投入不足以解决养老问题，需考虑长期运营经费。
+- 城市社区志愿者制度（一对一帮扶、积分兑换、小手拉大手）和养老服务中心（理疗、按摩、老年大学、心理咨询）取得一定成效，说明社区参与和多元服务模式有助于缓解养老困境。
+- 社工行业面临供给不足、资金短缺、专业欠缺、人员流失快（很多同学做不超过一年）等困境，说明社工制度需解决资金可持续性和专业人才培养问题。
+## 建议
+- 请专业施工人进行陪伴，为老人提供日常照料与陪伴。
+- 倡导在外务工的子女多与老人联系，缓解老人孤独感。
+- 丰富老人文化生活，增加娱乐方式。
+- 希望老年协会专项执行，专门建养老设施，有固定场地，定期开展宣传和健康知识讲座，并考虑持续运营经费。
+- 社区志愿者制度应长期坚持，通过表彰、积分兑换等激励志愿者，并发掘中年志愿者、开展小手拉大手活动，让家长自己组织活动，社区作为协助者。</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>5309/2292</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="13.5" customHeight="1" s="9">
       <c r="A22" s="6" t="inlineStr">

--- a/test_sample.xlsx
+++ b/test_sample.xlsx
@@ -568,57 +568,47 @@
       <c r="C2" s="4" t="inlineStr">
         <is>
           <t># 发布会概况
-王毅在慕尼黑安全会议上发表演讲并回答提问，阐述中国推动平等有序世界多极化的主张。他指出世界正走向多极化，80年前联合国成立时只有51个会员国，今天是193个国家，中国主张推动平等有序的世界多极化，这是习近平主席提出的重大主张。王毅提出四点看法：倡导平等相待、尊重国际法治、践行多边主义、坚持开放共赢。中国加入了几乎所有普遍性的政府间国际组织和600多项国际公约，承担超过20%的联合国会费，建成世界上最大的清洁发电体系。去年中国GDP增长5%，对世界经济增长贡献率接近30%。在问答环节，王毅回应了关于国际秩序、乌克兰危机和中美关系等提问，强调中国坚持维护联合国权威和国际法治，在乌克兰问题上坚持劝和促谈，对美政策保持连续性和稳定性。
+王毅在慕尼黑安全会议上发表演讲并回答提问，阐述中国推动平等有序世界多极化的主张。他指出世界正走向多极化，联合国会员国从51个增至193个，中国将坚定做变革世界中的建设性力量。王毅提出四点看法：倡导平等相待、尊重国际法治、践行多边主义、坚持开放共赢。他回应了关于国际秩序、乌克兰危机和中美关系的提问，强调中国维护以联合国为核心的国际体系，坚持劝和促谈，愿按相互尊重、和平共处、合作共赢三原则同美方构建稳定健康可持续的双边关系。整体基调坚定务实，展现中国作为负责任大国的确定性。
 # 核心信息
-- 世界正走向多极化：80年前联合国成立时只有**51个**会员国，今天是**193个**国家，共乘一艘大船。
-- 中国主张推动**平等有序的世界多极化**，这是习近平主席提出的重大主张，中国必将是多极体系中的确定性因素。
-- 中国加入了几乎所有普遍性的政府间国际组织和**600多项**国际公约，从不搞例外主义，更不搞合则用、不合则弃。
-- 中国承担超过**20%**的联合国会费，切实履行`巴黎协定`，建成了世界上最大的清洁发电体系。
-- 去年中国GDP增长**5%**，对世界经济增长的贡献率接近**30%**，担当起全球经济增长的重要引擎。
-- 中国愿推动高质量共建`一带一路`，同欧盟的`全球门户`战略相互对接，赋能彼此也赋能世界。
-- 中国提出并落实`全球发展倡议`、`全球安全倡议`、`全球文明倡议`，为完善全球治理提供公共产品。
-- 今年是中欧建交**50周年**，中方愿意同欧方用好这一契机，深化战略沟通和互利合作。
+**世界多极化趋势**：联合国成立时仅**51个**会员国，现为**193个**，多极化是历史必然。
+**中国主张**：推动**平等有序的世界多极化**，系习近平主席提出的重大主张。
+**四点看法**：
+  - 倡导平等相待，坚持权利平等、机会平等、规则平等，提升发展中国家代表性和发言权。
+  - 尊重国际法治，维护联合国宪章宗旨和原则，反对双重标准。
+  - 践行多边主义，坚持共商共建共享的全球治理观。
+  - 坚持开放共赢，以普惠包容的经济全球化支撑多极化。
+**中国贡献**：加入几乎所有普遍性政府间国际组织和**600多项**国际公约；承担超过**20%**的联合国会费；建成世界上最大的清洁发电体系；落实全球发展倡议、全球安全倡议、全球文明倡议。
+**经济数据**：去年中国GDP增长**5%**，对世界经济增长贡献率接近**30%**。
+**合作举措**：愿推动高质量共建`一带一路`，与欧盟`全球门户`战略对接。
 # 官方表态
-**关于多极化世界**
-- 王毅表示，多极化的世界既是历史的必然，也正在成为现实，中国给出的答案是我们应当推动平等有序的世界多极化。
+**多极化主张**：
+&gt; 我们应当推动平等有序的世界多极化。这是习近平主席提出的又一个重大主张，也是我们对多极世界真诚的期许。
 &gt; 中国必将是多极体系中的确定性因素。将坚定做变革世界中的建设性力量。
-- 倡导平等相待：坚持权利平等、机会平等、规则平等，应当成为建设多极世界的基本原则；中国主张大小国家一律平等，呼吁提升发展中国家在国际体系中的代表性和发言权。
-- 尊重国际法治：联合国宪章宗旨和原则是处理国际关系的根本遵循，也是建设多极世界的重要基石；国家不论大小强弱，都是国际法治的利益攸关方。
-&gt; 如果没有了规矩，昨天在餐桌上明天就可能在菜单里。
-- 践行多边主义：联合国是践行多边主义、推进全球治理的核心平台，已经为各国遮风挡雨80年；对于这座大厦，我们应该固本强基，而不是拆梁毁柱。
-- 坚持开放共赢：发展是破解各种难题的钥匙，多极世界应该是各国共同发展的世界。
+**国际法治**：
+&gt; 国家不论大小强弱，都是国际法治的利益攸关法。多极格局不能是无序的状态。
+&gt; 我们从不搞例外主义，更不搞合则用，不合则弃。
+**多边主义**：
+&gt; 联合国是践行多边主义，推进全球治理的核心平台。已经为各国遮风挡雨80年。
+&gt; 对于这座大厦，我们应该固本强基，而不是拆梁毁柱。
+**开放共赢**：
 &gt; 保护主义不是出路，滥加关税没有赢家。脱钩断链断的是机遇，小院高墙封的是自己。
-**关于国际秩序与规则**
-- 王毅表示，中国是现行国际秩序的受益者，要推动这个秩序朝着更加公正合理的方向去发展。
-&gt; 我们需要共同来维护以联合国为核心的国际体系。共同遵守以联合国宪章宗旨和原则为基础的国际关系的基本准则。
-- 强调在遵守国际法上不能搞双重标准，要尊重各国的主权和领土完整，就应该支持中国实现完全统一。
-**关于乌克兰危机**
-- 王毅表示，中国同俄罗斯是两大邻国，建立了结盟不对抗、不针对第三方的睦邻友好关系，中国同俄罗斯之间的交往是正常的国与国之间的交往。
-&gt; 我们历来主张一切争端和冲突都应该通过对话寻求政治解决。因为武力和制裁不可能真正和彻底的解决问题。
-- 中方从2022年2月25日（危机爆发第2天）就提出对话协商解决，习近平主席提出的4点主张是中国立场的最权威的阐释。
-&gt; 各国的主权领土完整应该得到尊重，联合国的宪章应该得到遵守。各国的合理安全关切应该得到重视。一切致力于和平的努力都应该得到支持。
-- 中方派出的特使去各国斡旋，同巴西等南方国家发起了`和平之友`。
-&gt; 任何冲突的终点都是谈判桌，历史最终一定是公正的。
-**关于中美关系**
-- 王毅表示，中国的对美政策保持着连续性和稳定性，不会轻易翻烙饼，这体现了作为大国的战略定力和国际信誉。
-&gt; 我们的对美政策就是习近平主席提出的三原则，相互尊重，和平共处。合作共赢。
-- 中方已准备好按照三原则同美方构建稳定健康可持续的双边关系，找到两个大国在这个星球上的正确相处之道。
-&gt; 如果美方不愿意，如果美方仍然还要对中国打压和遏制，那我们也别无选择，我们必将奉陪到底。
+**中欧关系**：
+&gt; 中方始终认为欧洲是多极世界的重要一极。中欧双方是伙伴而不是对手。
 # Q&amp;A环节
-**问**：主持人提问，中国是否继续相信联合国和联合国宪章，是否推动联合国改革？
-**答**：王毅表示，中国是现行国际秩序的受益者，要推动这个秩序朝着更加公正合理的方向去发展。我们需要共同维护以联合国为核心的国际体系，共同遵守以联合国宪章宗旨和原则为基础的国际关系基本准则，这是最大的公约数。只要大家都认同这一点，有些人所说的双重标准就不会出现。习近平主席提出了一系列重大倡议和主张，包括全球发展倡议、全球安全倡议、全球文明倡议，希望国际社会携手解决发展赤字、安全赤字和治理赤字。习主席还提出了构建人类命运共同体的重大理念，希望各国超越历史文化社会制度意识形态的不同，共同建设好命运与共的地球村。
-**问**：主持人引用王毅此前关于尊重乌克兰主权和领土完整的言论，称俄罗斯已成为中国的加油站，提问中国是否可减少购买俄罗斯油气或停止双用途物资以施压俄罗斯。
-**答**：王毅表示，中国同俄罗斯是两大邻国，建立了结盟不对抗、不针对第三方的睦邻友好关系，中国同俄罗斯之间的交往是正常的国与国之间的交往。他反问，如果中国不从俄罗斯买油气，哪个国家能够提供如此巨量的油气来满足中国民众的需求？那是不可能的，也是不保险的，因为常常有的国家把经贸问题政治化，当做打压中国的工具。但中国在对待地区热点问题上有自己的立场，历来主张一切争端和冲突都应该通过对话寻求政治解决。从2022年2月25日（危机爆发第2天）开始，中方就提出对话协商解决，习近平主席提出的4点主张是中国立场的最权威的阐释。中方派特使去各国斡旋，同巴西等南方国家发起了和平之友。中方乐见一切致力于和平的努力，包括美国同俄罗斯达成的共识，同时认为所有当事方包括利益攸关方都应该适时参与到和谈进程当中。这场战事发生在欧洲大地上，欧洲更有必要为此发挥重要的作用，共同探讨欧洲的长治久安，找到均衡有效可持续的欧洲安全框架。
-**问**：主持人请王毅预告中美关系将如何发展。
-**答**：王毅表示，中国的对美政策保持着连续性和稳定性，不会轻易翻烙饼，这体现了作为大国的战略定力和国际信誉。对美政策就是习近平主席提出的三原则：相互尊重、和平共处、合作共赢。中美两国制度不一样，是各自人民做出的选择，如果想改造或颠覆对方是不切实际的。正确的态度就是相互尊重，这是中美交往的前提；和平共处更是理所当然，中美两个大国总不能冲突起来，因为那将殃及整个世界；合作共赢是因为国际社会期待中美开展合作，全球性挑战也需要中美携手应对。中方已经准备好了，愿意按照三原则同美方构建稳定健康可持续的双边关系。如果美方不愿意，仍然还要对中国打压和遏制，那我们也别无选择，必将奉陪到底，坚决维护中国的主权、国家的尊严和正当发展权利，坚决回击美方的单边霸凌行径。</t>
+**问**：您提到国际秩序，现在很多人质疑联合国宪章，包括俄罗斯入侵乌克兰、美国总统威胁使用武力等，您是否仍相信联合国和联合国宪章？会否推动联合国改革？
+**答**：中国是现行国际秩序的受益者，真正挑战秩序的是毁约退群的国家。我们应共同维护以联合国为核心的国际体系，遵守以联合国宪章宗旨和原则为基础的国际关系基本准则，这是最大公约数。中国愿推动秩序朝更加公正合理方向发展，提供更多公共产品。
+**问**：您曾表示乌克兰的主权、独立和领土完整应得到尊重，现在俄罗斯已成为中国有军队的加油站，您能否减少从俄罗斯购买油气或停止双用途货物，以施压俄罗斯结束战争？
+**答**：中国同俄罗斯是两大邻国，建立了不结盟、不对抗、不针对第三方的睦邻友好关系。如果中国不从俄罗斯买油气，哪个国家能提供如此巨量油气？那是不可能的，也是不保险的。中国主张一切争端和冲突应通过对话寻求政治解决，武力和制裁不能真正解决问题。从2022年2月25日危机爆发第二天起，中方就提出对话协商解决。习近平主席提出四点主张：各国主权领土完整应得到尊重、联合国宪章应得到遵守、各国合理安全关切应得到重视、一切致力于和平的努力都应得到支持。中国派特使斡旋，同巴西等南方国家发起`和平之友`。中方乐见美国同俄罗斯达成的共识，所有当事方和利益攸关方应适时参与和谈，欧洲应发挥重要作用。
+**问**：您能否预告中美关系将如何发展？
+**答**：中国对美政策保持连续性和稳定性，不会轻易翻烙饼。对美政策就是习近平主席提出的三原则：相互尊重、和平共处、合作共赢。中方已准备好按三原则同美方构建稳定健康可持续的双边关系。如果美方打压遏制中国，我们别无选择，必将奉陪到底，坚决维护中国的主权、国家的尊严和正当发展权利。</t>
         </is>
       </c>
       <c r="D2" s="10" t="n">
-        <v>57.7</v>
+        <v>46.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>7004/3015</t>
+          <t>7004/1765</t>
         </is>
       </c>
     </row>
@@ -787,27 +777,50 @@
           <t># 沟通背景与目的
 电子科技大学电子科学与工程学院举办招生宣讲会，面向考生和家长介绍学院整体情况、学科方向、师资科研与人才培养。段院介绍学院历史沿革、学科设置、师资规模与科研平台；柳教授介绍电子信息材料与元器件方向；张教授介绍电磁场与微波技术和电路与系统方向；李天明教授介绍物理电子学方向；在读博士田雨桐分享选择电子学院的8个理由。宣讲会达成吸引优秀生源的目的，并明确今年计划举办夏令营、时间待定，相关信息将通过QQ群（978499108）发布。
 # 信息同步
-**段院（学院整体情况）**：学院源于1956年建校时成立的无线电系、电真空器件系、无线电零件系，经1979、1992、2001、2018年四次院系调整成立，2023年成立电子科学与工程学院与集成电路学院；一级学科电子科学与技术为国家重点一级学科，下设电磁场与微波技术、电路与系统、微电子学与固体电子学、物理电子学、电磁信息功能材料与机构5个二级学科方向，另有3个国防特色学科。现有本科生1545人（招生专业为工科试验班电子工程类，含电子科学与技术、电磁场与无线技术两个专业方向）、研究生1975人；教师302人（教研系列139人、科研系列95人、教学系列14人、实验系列21人、机关33人），高层次人才含两院院士2人、领军人才19人、青年人才28人；近5年科研经费到账稳定在3-4亿元，牵头获国家科技奖励11项，发表高水平论文2000余篇，拥有2个国家级平台、4个国际合作平台、7个省部级科研平台。
-**柳教授（电子信息材料与元器件方向）**：方向以电子在物质中的输运特性为基础，以材料为基础、器件为核心、应用为目标导向；2021年中国集成电路电子产品进口额度达2.8万亿元，约为原油进口量的1.7倍，先进电子材料、元器件、电路系统是我国最紧迫的卡脖子问题之一。方向拥有国家级人才10余人，两大团队为邓龙江院士的电磁辐射控制材料与技术团队（研究人员19人，年均到账经费3000多万元，获国家科技进步/技术发明二等奖共3项）和张怀武教授的磁电薄膜与微型器件团队（研究人员17人，年均到账经费2000余万元，获科技进步二等奖3项）；依托国家电磁辐射控制材料工程技术研究中心和电磁薄膜与集成器件全国重点实验室，科研面积2万余平米（超净间3000平），建设两条国家重大任务试验生产线，大型设备/系统500余台套；毕业生去向包括英特尔、中芯国际、华为、德州仪器等企业及高校科研院所。
-**张教授（电磁场与微波技术、电路与系统方向）**：电磁场与微波技术含微波毫米波电路、电波传播与电磁兼容、计算电磁学与工程电子学、天线理论与技术4个细分方向，电路与系统含非线性电路与复杂电子系统、射频微波电路与系统、集成电路与系统3个方向；学科始于1956年建校时期，由林为干先生和谢处方先生创建，所属一级学科电子科学与技术入选双一流A类学科。电磁场与微波技术有6个团队，硬件平台含中国高校最先进的微波暗室群体；代表性成果包括杨世文教授团队四维天线阵列技术应用于中电14所某大型机载相控阵雷达、樊勇教授团队研制0.22THz/0.34THz/0.42THz雷达成像系统（分辨率小于1厘米）、太赫兹通信成果在2023年成都大运会田径项目示范应用等；电路与系统学科1981年开始招收研究生，1988年成立首批博士后流动站，拥有国家级人才4人、教授10人、副教授22人，研究方向含高速磁浮交通38GHz车地通信系统、毫米波通信雷达CMOS芯片等；人才培养连续三年获全国大学生集成电路创新创业大赛奖项，就业面向华为、中兴等领军企业、研究所、高校。
-**李天明教授（物理电子学方向）**：物理电子学是物理学与电子科学与技术的交叉学科，将物理学最新研究成果应用于电子学产生新电子器件；学校物理电子学起源于1956年建校时在前苏联专家帮助下成立的电真空器件专业，1979年刘盛纲院士带领成立高能电子学研究所，2018年成立电子科学与工程学院。方向纵向发展（上游仿真设计、数字模拟材料，下游系统应用，拥有自主知识产权商用软件MMST和切皮克，引入人工智能到器件设计和电子学应用），横向发展（频段从微波上移到毫米波、太赫兹，与医学交叉利用太赫兹成像提高诊断准确性）；每年到校科研经费接近2亿元，在学院中最多，是国际上最大的真空器件研究中心，2023年成功举办行业顶级会议，物理电子学方向共9个团队；团队学生约1/3硕博连读、1/3去企业、1/3去研究所或其他。
-**田雨桐（在读博士，学生视角）**：成都是四川省会、国家中心城市、新一线城市，电子信息产业发达，英特尔、华为、京东方等巨头汇聚；电子科技大学是我国电子信息人才培育的代名词，构建了最完整的电子信息学科群；电子科学与技术学科在第4轮学科评估中获A+，稳居全国第一；其所在毫米波技术与系统应用团队在樊勇老师带领下围绕五大方向开展研究，团队硕博毕业生实现100%就业率；学院构建全覆盖、高额度、长周期的奖助体系；建议先选择研究团队再选择导师，可通过学院网站、文献检索网站（如IEEE、中国知网）了解导师论文和指导研究生情况。
+**段院（学院整体情况）**：
+- **历史沿革**：学院源于1956年建校时的无线电系、电真空器件系、无线电零件系，经1979、1992、2001、2018年四次院系调整成立，2023年成立电子科学与工程学院与集成电路学院。
+- **学科设置**：一级学科电子科学与技术为国家重点一级学科，下设电磁场与微波技术、电路与系统、微电子学与固体电子学、物理电子学、电磁信息功能材料与机构5个二级学科方向，另有3个国防特色学科。
+- **人才培养**：本科生1545人，招生专业为工科试验班（电子工程类），含电子科学与技术（国家特色专业、国家级一流本科专业建设点）和电磁场与无线技术两个专业方向；研究生1975人，学硕/博士专业为电子科学与技术、材料科学与工程，专硕/博士为电子信息、材料工程。
+- **师资科研**：教师302人（教研系列139人、科研系列95人、教学系列14人、实验系列21人、机关33人），两院院士2人、领军人才19人、青年人才28人；近5年科研经费到账稳定在3-4亿元，牵头获国家科技奖励11项，发表高水平论文2000余篇，专利申请1600余件、授权1300余件。
+- **平台交流**：拥有2个国家级平台（国家电磁辐射控制材料工程技术研究中心、微波电子器件国家级重点实验室）、4个国际合作平台、7个省部级科研平台；共建国际姊妹院系2个（香港大学电机工程电子系、香港城市大学电子工程系），主办高水平国际会议13场，学生长短期交流项目20多个。
+**柳教授（电子信息材料与元器件方向）**：
+- **方向定位**：以材料为基础、器件为核心、应用为目标导向，涉及电子材料与电子器件的设计、研制、生产和应用。
+- **行业背景**：2021年中国集成电路电子产品进口额度达2.8万亿元，约为原油进口量的1.7倍，先进电子材料、元器件、电路系统等属最紧迫的卡脖子问题之一。
+- **研究团队**：国家级人才10余人；邓龙江院士电磁辐射控制材料与技术团队19人（正高13、副高15），年均到账经费3000多万元，授权发明专利100余项，获国家科技进步/技术发明二等奖共3项；张怀武教授磁电薄膜与微型器件团队17人（正高15、副高2），年均到账经费2000余万元，获科技进步二等奖3项，发表SCI论文400余篇。
+- **平台条件**：依托国家电磁辐射控制材料工程技术研究中心（可追溯至1990年校级中心，经2008、2013年两次升级）和电磁薄膜与集成器件全国重点实验室（2006年筹建）；科研面积2万余平米（超净间3000平），建设两条国家重大任务试验生产线，大型设备/系统500余台套。
+- **成果与去向**：获国家技术发明等奖项共7项，高水平论文每年多篇发表于Nature及子刊；毕业生去向包括英特尔、中芯国际、华为、德州仪器等企业及高校科研院所。
+**张教授（电磁场与微波技术、电路与系统方向）**：
+- **学科构成**：电磁场与微波技术含微波毫米波电路、电波传播与电磁兼容、计算电磁学与工程电子学、天线理论与技术4个细分方向；电路与系统含非线性电路与复杂电子系统、射频微波电路与系统、集成电路与系统3个方向。
+- **历史与平台**：学科始于1956年由林为干先生和谢处方先生创建，所属一级学科入选双一流A类；硬件平台含中国高校最先进的微波暗室群体、先进的微波毫米波太赫兹仿真测试平台。
+- **代表性成果**：杨世文教授团队四维天线阵列技术应用于中电14所某大型机载相控阵雷达，电磁测井仪器获国家科技进步二等奖并在中海油推广应用；樊勇教授团队研制0.22THz、0.34THz、0.42THz雷达成像系统（分辨率小于1厘米），太赫兹通信成果在2023年成都大运会示范应用；延波教授团队引领微波毫米波太赫兹芯片研究，获国家科技重大专项及军科委支持。
+- **人才培养**：连续三年获全国大学生集成电路创新创业大赛奖项，获华为优秀合作项目奖、研究生优秀导学团队提名奖；就业单位含华为、中兴等领军企业、研究所、高校。
+**李天明教授（物理电子学方向）**：
+- **学科定位**：物理电子学是物理学与电子科学与技术的交叉学科，将物理学最新研究成果应用于电子学，产生新电子器件，如微波电子学（微波电真空器件）、光电子学（光电器件）。
+- **发展历程**：起源于1956年建校时成立的电真空器件专业，1979年刘盛纲院士带领成立高能电子学研究所，2001年成立物理电子学，2018年并入电子科学与工程学院。
+- **研究方向**：纵向发展含自主知识产权商用软件MMST和切皮克、引入人工智能到器件设计，系统应用含毫米波雷达（回旋行波管）、无线输能系统（行波管）、微波能干燥系统（磁控管）；横向发展频段从微波上移到毫米波、太赫兹，并与医学交叉利用太赫兹成像提高诊断准确性。
+- **科研实力**：每年到校科研经费接近2亿元（学院中最多），为世界上最大的真空器件研究中心，2023年成功举办行业顶级会议，方向共9个团队；团队学生约1/3硕博连读、1/3去企业、1/3去研究所或其他。
+**田雨桐（在读博士，学生视角）**：
+- **城市与产业**：成都是四川省会、国家中心城市、新一线城市，电子信息产业发达，英特尔、华为、京东方等巨头汇聚，提供实践平台和就业资源。
+- **学校与专业**：电子科技大学是我国电子信息人才培育的代名词，拥有电子信息博物馆和最完整的电子信息学科群；电子科学与技术学科在第4轮学科评估中获A+稳居全国第一。
+- **团队与培养**：其所在毫米波技术与系统应用团队在樊勇老师带领下围绕五大方向开展研究，团队硕博毕业生实现100%就业率，就业单位含民营企业、大型央国企和头部科研院所。
+- **奖助与建议**：学院构建全覆盖、高额度、长周期的奖助体系，含国家奖学金、学业奖学金、专项奖学金、新生奖学金及助学贷款；择校建议为先选择研究团队再选择导师，可通过学院网站和文献检索网站（如IEEE、中国知网）了解导师情况。
 # 达成共识
-**电子学院计划今年举办夏令营活动，时间待定**，相关信息将通过QQ群（978499108）及时发布。段院原话："我们电子学院呢要计划就是今年会计划这个夏令营活动时间还待定，希望呢同学们感兴趣的话呢加入我们这个QQ群相关的信息呢，我们会到时会及时的发布。"
+**夏令营安排**：电子学院计划今年举办夏令营活动，时间待定，相关信息将通过QQ群（978499108）发布。段院原话："我们电子学院呢要计划就是今年会计划这个夏令营活动时间还待定，希望呢同学们感兴趣的话呢加入我们这个QQ群相关的信息呢，我们会到时会及时的发布。"
+**招生承诺**：学院欢迎考生和家长加入QQ群咨询，并期待在夏令营或研究生入学时与大家面对面沟通交流。
 # 待协调事项
-**事项1：夏令营活动组织**
-- 事项描述：电子学院计划今年举办夏令营活动，具体时间和形式尚未确定。
-- 对接人：段院
-- 负责人：段院
-- 预计完成时间或后续沟通计划：时间待定，相关信息将通过QQ群（978499108）发布。</t>
+**夏令营时间与形式确定**：
+- 事项描述：电子学院计划今年举办夏令营，但具体时间和形式尚未确定。
+- 对接人：段院。
+- 负责人：段院。
+- 预计完成时间或后续沟通计划：时间待定，相关信息将通过QQ群（978499108）及时发布。</t>
         </is>
       </c>
       <c r="D3" s="10" t="n">
-        <v>84.5</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>13887/2367</t>
+          <t>13887/3032</t>
         </is>
       </c>
     </row>
@@ -1344,34 +1357,34 @@
       <c r="C4" s="4" t="inlineStr">
         <is>
           <t># 复盘目标与结果概况
-本次年会复盘2023年公司经营与团队表现。预期目标为总结发展状况、公布数据、评价员工并发放年终奖与奖项。实际结果：年终奖转账总额226,000元，全年支出390万元，利润率约24%或27%，成本控制差；最高工资（含年终奖）两三人到手20万元，平均工资1万多元；年终奖总额比去年多1312万余元，干满一年人数从四五人增至12人；公司总量提升但结余到账下滑，还有百来万未收回，老板承担亏损100万元。会上公布年终奖标准，逐人评价，颁发最佳新人、最佳进步、后期独当一面、最佳员工、特别贡献五项奖，并抽奖。
+本次年会复盘2023年公司经营与团队表现。预期目标为总结发展状况、公布数据、评价员工并发放年终奖。实际结果：年终奖转账总额**226,000元**，全年实际支出（含人员工资、外援配音字幕、租机器）**390万元**，利润率约**24%或27%**，成本控制较差；最高工资（含年终奖）两三人到手达**20万元**，平均工资到手**1万多元**；年终奖总额比去年多**13万多元**，去年干满一年仅四五人，今年达**12人**；公司总量提升但结余到账往下跑，还有**百来万**未收回；老板每人比去年少拿约**10万元**，承担风险亏损**100万元**。会议对全员逐一进行肯定性评价，颁发**最佳新人奖**（红叶子、张扬）、**最佳进步奖**（欧阳小元）、**后期独当一面奖**（刘腾宇）、**最佳员工奖**（游腾宇）、**特别贡献奖**（李海腾），并抽奖。
 # 亮点事项
-- 短视频账号运营取得显著增长：视频号粉丝从2023年3月1日70019人增至8万，小红书从2000+增至6.4万，抖音从2000+增至5.7万，B站从3.1万增至7.6万，涨粉自6月20日第一条外出拍摄视频起有起色。成功原因：郭东辉在潘老师多次提醒放弃的情况下坚持，并破釜沉舟说服外出拍摄，加上forty加入，最终突破。
-- 账号变现课程拍摄达十分满分7.5分，直播每场平均在线5000人以上，虽重点项目未完成，但为软实力提升提供帮助。
-- 后期团队整体技术提升：林海腾指出今年后期人员分级模糊、效率接近，整体技术有进步，硬着头皮安排没做过的人也能完成好。
-- 张扬作为公司邀请人才，职业态度与工作能力基本达到期待，老板称2023年最有价值的事就是把他招进来。
-- 刘腾宇获最高评价，职业性、专业性、纪律性最好，迟到几乎没有，请假严格按规定，工作安排提前告知，成为团队标杆。
+- **账号增长**：郭东辉负责的短视频账号从**6月20日**第一条外出拍摄视频起色，视频号粉丝从**7万**涨至**8万**，小红书从**2000+**涨至**6.4万**，抖音从**2000+**涨至**5.7万**，B站从**3.1万**涨至**7.6万**；变现课程达**7.5分**（满分10分），直播**4-5场**平均在线**5000+**。成功原因：**坚持**（潘老师多次提醒放弃仍坚持）、**破釜沉舟说服外出拍摄**、**数据支撑决策**（每晚8-9点刷竞品直播间）。
+- **人才引进**：张扬为公司邀请人才，职业态度和工作能力有目共睹，老板称**2023年最有价值的事就是把他招进来**。
+- **员工表现**：刘腾宇获**评价最高**，职业性、专业性、纪律性最好，能完美胜任后期各种类型；红叶子获政委**非常高的评价**，既懂技术又懂英语；张文倩综合能力强，宁波项目完成超预期；宋俊逸编导效率高，首次安排活即获认可。
+- **复用经验**：**坚持与破局**（郭东辉在项目低谷时坚持并说服外出拍摄）、**数据驱动**（所有内容决策有数据支撑）、**仪式感建设**（认真准备证书、奖项，增强团队凝聚力）。
 # 不足事项
-- 成本控制非常差：全年实打实支出390万元（含人员工资、外援配音字幕、租机器），利润率仅约24%或27%，非常不可观。根因：老板对成本关心或关注不够、不够雷厉风行，问题未及时解决。
-- 公司结余到账往下跑，还有百来万未收回，老板每人比去年少拿约10万元，承担亏损100万元。
-- 账号变现重点项目未完成，直播暂无课程可变现。
-- 后期人员劳累程度高，今年尤其是后半年基本都在加班，很少正常休息。根因：老板未及时招合适人数，判断失误，人不够是最大因素。
-- 外援成本高：钱德峰指出请外援价格与内部拍摄差很多，但公司凑不出人按机位、让机器不关机，内部人员多以没空、很忙、不想去推脱。
+- **成本控制差**：全年实际支出**390万元**，利润率仅**24%或27%**，非常不可观；老板自评**最大问题是老板对关心或关注不够、不够雷厉风行、问题未及时解决**。
+- **结余缩水**：公司总量提升但结余到账往下跑，还有**百来万**未收回；老板每人比去年少拿约**10万元**，承担风险亏损**100万元**。
+- **账号变现未完成**：重点项目**账号变现**未完成，直播无课程无法变现；郭东辉称重点项目**没有完成**。
+- **后期加班多**：后期人员劳累程度高，后半年基本都在加班，晚上、周末均被侵占；老板承认**人不够是最大因素**，是**判断失误**。
+- **拍摄参与不足**：钱德峰提出请外援成本高，公司内部凑不出人按机位，很多人以没空、很忙、不想去推脱。
+- **商务支持少**：张启表现高于预期，但老板给的支持比较少，几乎没什么项目，靠老板帮忙聊或打理。
 # 改进计划
-- 成本控制问题明年开会再议，具体改进措施未明确，责任人无，时间无。
-- 短视频部门：期待明年账号能开始变现，老板将投入更大精力并给予足够重视，责任人无，时间无。
-- 执行部门：期待老板明年更多进行组织协调，提高效率，减少侵占休息时间，责任人无，时间无。
-- 商务部门：老板承认今年给予的支持、管理或关心不够，明年会反思，并考虑给张启更多支持和帮助，责任人无，时间无。
-- 拍摄参与：老板期待大家都能参与拍摄，明年往这个方向靠，提升个人市场价值，责任人无，时间无。
-- 加班补贴：年终奖中考虑加班因素，补贴一两千元，已实施。</t>
+- **成本控制**：明年开会再讨论具体措施，责任人无，时间无。
+- **账号变现**：期待明年账号能开始变现，老板将投入更大精力并给予足够重视，责任人无，时间无。
+- **组织协调**：老板明年更多进行组织协调，减少侵占员工休息时间，责任人无，时间无。
+- **拍摄参与**：明年希望每个人都能参与拍摄，提升市场价值，责任人无，时间无。
+- **商务支持**：老板考虑给商务部门更多支持和帮助，责任人无，时间无。
+- **老板反思**：老板自评今年给予支持、管理或关心不够，明年会反思，责任人无，时间无。</t>
         </is>
       </c>
       <c r="D4" s="10" t="n">
-        <v>95.40000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>24562/1228</t>
+          <t>24562/1581</t>
         </is>
       </c>
     </row>
@@ -1914,28 +1927,43 @@
       <c r="C5" s="4" t="inlineStr">
         <is>
           <t># 全文摘要
-本次专项讨论会由办事处组织，旨在协调小区业委会与物业公司之间的矛盾，讨论业主大会召开及物业整改问题。业委会成员刘主任、邱主任及业主代表，物业方吴经理等参会。业委会提出，小区业主自发接龙约200来户，主要诉求是召开业主大会，由全体业主表决是否更换物业；物业方则表示事先未接到任何沟通，认为接龙有组织、议题不明。业委会列举了小区11项服务问题，物业方逐项回应称多属地产配套或费用问题。物业方称物业费欠账170多万，回款40万，账上一分钱没有，人工成本一年100多万，每年亏损。物业方宣布本月将正式起诉业委会，业委会表示将反诉并正常推进业主大会。双方就物业费欠费与整改先后顺序、业主大会召开与物业起诉的法律关系等未达成一致，矛盾激化。
+本次专项讨论会由办事处牵头，召集小区业委会（刘主任、邱主任等）与物业方（吴经理等），就业主大会召开、物业11项服务问题、物业费欠费与经营亏损、法律诉讼等议题进行协调。业主自发接龙约200来户业主，主要诉求是召开业主大会表决是否更换物业；业委会建议尽快召开业主大会，由全体业主表决，并基本确定将表决换物业。物业方表示未接到任何沟通，质疑接龙有组织，称存在违法情况，已沟通集团法务，本月将正式起诉业委会，并称诉讼期间业主大会可能无法召开；业委会认为若无法律禁止则应照常召开。双方未达成一致，矛盾激化。
 # 要点梳理
 ## 业主大会召开与表决
-- 业主自发接龙约**200来户**业主，主要议题是召开业主大会，业委会建议尽快召开，由全体业主表决是否更换物业。
-- 物业方表示事先未接到任何沟通，认为接龙有组织、议题不明，并称欠费人员不能成为业主代表，将依法追究责任。
-- 业委会成员表示，业委会成立之日即自动解除与物业的合同关系，将正常推进业主大会；物业方称案件存续期间无法更换物业公司。
+- **业主诉求**：业主自发接龙约**200来户**业主，主要议题是召开业主大会，表决是否更换物业。
+- **业委会建议**：尽快召开业主大会，由全体业主表决；业委会成员表示基本确定召开业主大会并表决换物业。
+- **物业质疑**：物业方称未接到任何沟通，质疑接龙有组织，且称存在违法情况，已沟通集团法务，本月将起诉。
+- **法律争议**：物业方称诉讼期间业主大会可能无法召开；业委会认为若无法律禁止则应照常召开。
+- **最终分歧**：业委会表示将正常推进业主大会；物业方同意更换物业，但前提是结清费用。
 ## 物业11项服务问题
-- 业委会列举11项问题：入户门柱灯从未开启；内部水系与迎宾水系从未开启；监控几乎全部损坏，上月进贼无监控数据；监控室24小时值班服务荒废；绿化维护缺失，去年死了很多树；北边围墙用烂铁皮遮挡且有缺口，存在安全隐患；快递柜、直饮水机、宽带、暖气开户等民生附属问题无进展；雨水倒灌问题严重，2019年起有财产损失；物业人员配备不足，办公室从10人减至4人，维修从5人减至2人。
-- 物业方逐项回应：门柱灯因能耗成本高未开，曾与业委会沟通；水系存在质量问题，属地产配套未完成；监控损坏因无费用，物业亏损；绿化死亡因冬季无法更换；北边围墙属红线以外且涉及违建官司，物业有权不处理；民生问题属地产前期配套；雨水倒灌属地产设计问题；人员配备不足因地产补亏款未结。
-- 物业方称物业费欠账**170多万**，回款**40万**，账上一分钱没有；人工成本一年**100多万**，保护收入100来万，每年亏损。
-- 业委会成员质疑物业服务滞后性，要求先服务后收费；物业方称需先解决费用问题。
-## 物业起诉与法律程序
-- 物业方称已与集团法务沟通，本月将正式起诉业委会，并称已与高级人民法院、滨城区人民法院沟通，掌握业主群内证据，将起诉业委会及保洁业主代表。
-- 业委会成员表示将反诉并拿出证据；物业方称起诉可能影响个人经营。</t>
+- **门柱灯**：业委会称入户庭院门柱灯从未开启；物业回应因能耗成本高无法运营。
+- **水系**：内部水系、迎宾水系从未开启；物业称存在严重质量问题，属地产配套未完成。
+- **监控**：几乎全部损坏，上月进贼无监控数据；物业称因无费用，物业费欠款**170多万**、回款**40万**。
+- **监控室服务**：24小时值班及一键直达功能荒废；物业未正面回应。
+- **绿化**：去年死了很多树，小区门口死了**三棵**；物业称冬季无法更换。
+- **北边围墙**：用烂铁皮挡着、有缺口外人可随意进出，物业拆除后未装新围挡；物业称属红线以外且涉及违建，有权不处理。
+- **民生附属**：快递柜、直饮水机、宽带、暖气开户无进展；物业称属地产前期配套。
+- **雨水倒灌**：从**2019年**至今未解决，明年大雨可能再淹；物业称是地产设计问题。
+- **人员配备**：办公室从近**10人**减至**4人**，维修从**5人**减至**2人**；物业称因地产补亏款未结。
+## 物业费欠费与经营亏损
+- **欠费规模**：物业方称业主欠物业费**170多万**，回款**40万**，账上一分钱没有。
+- **经营亏损**：园区保护收入**100来万**，光人工成本就**100多万**，每年亏损，今年亏损额度拉大。
+- **维修支出**：物业方称维修费今年花了几十万。
+- **服务争议**：业委会称物业服务没有滞后性，不能先收钱再服务。
+- **煽动指控**：物业方称业委会在业主群煽动不缴费、阻碍经营，将起诉。
+## 法律诉讼与维权
+- **起诉决定**：物业方宣布本月正式起诉业委会，理由是选举违法、煽动业主、阻碍经营等。
+- **沟通记录**：物业方称上午**9:52**与高级人民法院通话，也与滨城区人民法院沟通。
+- **证据掌握**：物业方称已掌握业主群截图等证据。
+- **业委会回应**：业委会成员表示支持起诉，将反诉并拿出证据。</t>
         </is>
       </c>
       <c r="D5" s="10" t="n">
-        <v>46.5</v>
+        <v>53.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21511/1085</t>
+          <t>21511/1377</t>
         </is>
       </c>
     </row>
@@ -2184,28 +2212,61 @@
       <c r="C6" s="4" t="inlineStr">
         <is>
           <t># 研讨背景与议题
-本次圆桌论坛围绕具身智能领域的关键技术问题展开，参与人员包括多模态大模型与具身智能融合方向的代表、强化学习方向的博士生、柔性物体操作与数据采集方向的专家、计算机视觉与仿真方向的学者，以及产业界嘉宾。核心探讨的技术痛点包括：具身智能大模型形态与硬件期待、世界模型的定义与实现路径、强化学习与模仿学习的路线之争，以及数据采集与仿真数据之争。各方观点充分碰撞，但未形成统一结论。
+本次圆桌论坛围绕具身智能领域的关键技术问题与发展趋势展开，旨在促进学术与产业交流。与会者包括来自学术界与产业界的多位老师及博士生，如发言者2（主持人）、发言者3（机械领域）、发言者4（薛寒）、发言者5（王老师）、发言者6、发言者7（赵老师）、发言者8（志龙）、发言者9、发言者10（业界嘉宾）、发言者11（杨立新/静波）等。核心探讨的技术痛点包括：具身智能大模型的形态与硬件期待、世界模型的定义与实现路径、强化学习与模仿学习的路线之争、数据采集与仿真数据之争。各方观点碰撞激烈，未形成统一结论。
 # 核心观点
-**具身智能大模型形态与硬件期待**：发言者2提出具身智能分为大脑大模型、小脑大模型和端到端模型，派灵收集6000多小时数据训练出端到端模型；发言者3从机械角度提问具身智能形态收敛方向，提及人形机器人与非人形（如星际穿越中的方块机器人），并介绍机械智能、软手等硬件方案；发言者4（薛寒）强调硬件需高寿命、高可靠性，现有工业机械臂不适合大规模真机评估，需要柔顺硬件结构以支持scale up；发言者2提到松灵产品两代迭代，第二代在遥操和策略部署上更好，夹爪加凝胶可反馈触觉、更稳、摩擦力更好；发言者5认为大模型直通底层会消除硬件迭代可能性，新硬件出现需重新训练，应至少分两层，大脑不变、小脑自适应肢体；发言者6认为大模型不是终极方案，世界模型可能更接近人类水平，但也不是最终形态，人形机器人和特种机器人都会存在，特斯拉花一半精力做22自由度灵巧手，车厂等已实现97%以上自动化。
-**世界模型的定义与实现路径**：发言者2提到赵老师有经典图评价世界模型，从CV角度讨论是否需要重构pixel、3D，以及4D world model；发言者8（志龙）从强化学习角度指出世界模型概念可追溯至1990-91年Sutton的dyna Q，定义为黑盒输出下一时刻观测，18年Schmidhuber和LeCun定义世界模型含表征和转移两个组件，强化学习领域世界模型第一要义是可交互，当前在物理规律方面欠缺明显，希望引入3D、触觉等模态完善；发言者7认为CV界追求重建物理世界，可作为RL世界模型的工具，但三维视觉技术栈深，RL博士生难以完全学习，导致RL领域不关注三维表征，并讨论inductive bias，认为数据多时需要的inductive bias少，数据少时需要的多，整体由数据决定；发言者5以刺客信条游戏与真实世界跳楼为例，认为一个世界模型无法同时建模两个dynamics，因为输入相同输出不同是歧义问题，policy可能统一而世界模型做不到；发言者9提出反对意见，认为CV世界模型带3D inductive bias，强化世界模型是任务导向的，不一定需要CV式世界模型，并讨论不同物理结构是否能有统一表征，发言者5认为M个独立模型比一个高维可控模型更简单。
-**强化学习与模仿学习的路线之争**：发言者2提到强化学习曾达顶峰但sim-to-real有落地问题，模仿学习如aloha收集海量数据展现可落地性，但派零团队收集近万小时数据后仍看到模仿学习瓶颈，语言模型最后有RLHF环节，o1引入思维链和MCTS；发言者10（业界嘉宾）介绍公司采用模型强化加机理融合方式，监督学习动作空间大、数据分布不足，强化学习依赖仿真环境、sim-to-real迁移难，实物强化学习需限制决策规模和任务设定，其强化pc工作采用任务分层，上层强化学习决策，底层用MPC、DWA等传统方法；发言者9同意混合方式，认为复杂问题都是先模仿后强化，如AlphaStar和GPT，单独模仿达不到专家水平，除非任务简单，单独强化样本复杂度不可接受；发言者5认为PID系统必有反馈，可拿反馈作为reward，强化必然走得成；发言者11（静波）认为IL和RL没有本质冲突，运动先验可从模仿学习或强化学习获取，然后通过RL找到对应latent完成任务。
-**数据采集与仿真数据之争**：发言者11（杨立新）分享数据质量经验，指出open X等数据集相机视角不固定、视角影响policy表现，标定重要且手眼标定至今解决不好，open X等数据集缺少物体运动信息，orkin从采集角度记录物体运动但当时设备有限只能采集刚体和关节体；发言者4（薛寒）all in reward采集路线，认为柔性体操作（叠衣服、系鞋带）仿真需要IPC等先进图形学技术、算力要求高、能做的人少（如UCLA蒋正凡夫）、进展慢，reward采集是低成本方案、真实世界是最好的仿真器，终极形态是脑机接口或机电方式无感采集多模态数据，现阶段可穿戴式设备可扩展，并指出互联网视频数据与机器人所需数据不同（如叠衣服视频是平铺状态，机器人需要从混乱状态展平的数据）；发言者2提到自己受ego4d数据集毒害、洗数据洗了三个月，数据金字塔中互联网数据在最底层、质量低，仿真数据分传统仿真和强化收集数据、sim-to-real gap大，仿真数据加少量真机数据可显著提升成功率（如300条sim数据加20条真机数据），可穿戴设备精度相比遥操数据有gap；发言者7认为用真实数据还是仿真数据看成本、case by case，自动驾驶中真机数据收集困难且危险，提出加入第三个domain——无标注真实数据（如segment anything和depth anything），认为2025年应推广大规模利用无标注数据；发言者2提问中国是否强依赖英伟达生态、能否有国产仿真产品，发言者7提到宋应等在做国产替代、赌卡脖子，但工作人员不会直接touch这个生意。
+**具身智能大模型形态**：
+- **发言者2**：具身智能分为大脑大模型、小脑大模型和端到端模型，派灵收集**6000多小时**数据训练出端到端模型。
+- **发言者3**：从机械角度提问形态收敛方向，提及人形与非人形（如星际穿越中的方块机器人），介绍机械智能、软手等硬件方案。
+- **发言者4（薛寒）**：硬件需高寿命、高可靠性，现有工业机械臂不适合大规模真机评估，需柔顺硬件结构以支持scale up。
+- **发言者5**：大模型直通底层会消除硬件迭代可能性，新硬件出现需重新训练，应至少分两层，大脑不变，小脑自适应肢体。
+- **发言者6**：大模型不是终极方案，世界模型可能更接近人类水平，但也不是最终形态；人形机器人和特种机器人都会存在，特斯拉花一半精力做**22自由度**灵巧手，车厂等已实现**97%以上**自动化。
+**世界模型定义与路径**：
+- **发言者8（志龙）**：世界模型概念可追溯至**1990-91年**Sutton的dyna Q，定义为黑盒输出下一时刻观测；18年Schmidhuber和LeCun定义含表征和转移两个组件；强化学习领域第一要义是可交互，当前世界模型在物理规律方面欠缺明显，希望引入3D、触觉等模态完善。
+- **发言者7**：CV界追求重建物理世界可作为RL世界模型的工具，但三维视觉技术栈深，RL博士生难以完全学习；讨论inductive bias，认为数据多时需要的inductive bias少，数据少时需要的多，整体由数据决定。
+- **发言者5**：举例刺客信条游戏与真实世界跳楼，认为一个世界模型无法同时建模两个dynamics，因为输入相同输出不同是歧义问题；policy可能统一，世界模型可能做不到。
+- **发言者9**：提出反对意见，认为CV世界模型带3D inductive bias，强化世界模型是任务导向的，不一定需要CV式世界模型；讨论不同物理结构是否能有统一表征，发言者5认为M个独立模型比一个高维可控模型更简单。
+**强化学习与模仿学习**：
+- **发言者2**：强化学习曾达顶峰但sim-to-real有落地问题，模仿学习如aloha收集海量数据展现可落地性，但派零团队收集近万小时数据后仍看到模仿学习瓶颈；语言模型最后有RLHF环节，o1引入思维链和MCTS。
+- **发言者10（业界嘉宾）**：公司采用模型强化加机理融合方式，监督学习动作空间大、数据分布不足，强化学习依赖仿真环境、sim-to-real迁移难；实物强化学习需限制决策规模和任务设定；其强化pc工作采用任务分层，上层强化学习决策，底层用MPC、DWA等传统方法。
+- **发言者9**：同意混合方式，认为复杂问题都是先模仿后强化，如AlphaStar和GPT；单独模仿达不到专家水平，除非任务简单；单独强化也不行，样本复杂度不可接受。
+- **发言者5**：PID系统必有反馈，可拿反馈作为reward，强化必然走得成。
+- **发言者11（静波）**：IL和RL没有本质冲突，运动先验可从模仿学习或强化学习获取，然后通过RL找到对应latent完成任务。
+**数据采集与仿真**：
+- **发言者11（杨立新）**：open X等数据集相机视角不固定，视角影响policy表现；标定重要，手眼标定至今解决不好；open X等数据集缺少物体运动信息，orkin从采集角度记录物体运动，当时设备有限只能采集刚体和关节体。
+- **发言者4（薛寒）**：all in reward采集路线，柔性体操作（叠衣服、系鞋带）仿真需要IPC等先进图形学技术，算力要求高，能做的人少（如UCLA蒋正凡夫），进展慢；reward采集是低成本方案，真实世界是最好的仿真器；终极形态是脑机接口或机电方式无感采集多模态数据，现阶段可穿戴式设备可扩展；互联网视频数据与机器人所需数据不同，如叠衣服视频是平铺状态，机器人需要从混乱状态展平的数据。
+- **发言者2**：受ego4d数据集毒害，洗数据洗了三个月；数据金字塔中互联网数据在最底层，质量低；仿真数据分传统仿真和强化收集数据，sim-to-real gap大；仿真数据加少量真机数据可显著提升成功率，如**300条sim数据加20条真机数据**；可穿戴设备精度相比遥操数据有gap。
+- **发言者7**：用真实数据还是仿真数据看成本，case by case；自动驾驶中真机数据收集困难且危险；提出加入第三个domain——无标注真实数据，如segment anything和depth anything，认为**2025年**应推广大规模利用无标注数据。
 # 达成共识与解决方案
-**具身智能大模型形态**：发言者5提出大模型不应直通底层，应至少分两层，大脑不变、小脑自适应肢体；发言者6认为人形机器人和特种机器人都会存在，特斯拉花一半精力做22自由度灵巧手，车厂等已实现97%以上自动化。
-**世界模型**：发言者8（志龙）从强化学习角度指出世界模型第一要义是可交互，当前在物理规律方面欠缺明显；发言者7认为CV界追求重建物理世界，可作为RL世界模型的工具，inductive bias由数据量决定；发言者5认为一个世界模型无法同时建模多个dynamics，policy可能统一而世界模型做不到；发言者9认为强化世界模型是任务导向的，不一定需要CV式世界模型。
-**强化学习与模仿学习**：发言者10（业界嘉宾）介绍公司采用模型强化加机理融合方式，监督学习动作空间大、数据分布不足，强化学习依赖仿真环境、sim-to-real迁移难，实物强化学习需限制决策规模和任务设定，其强化pc工作采用任务分层，上层强化学习决策，底层用MPC、DWA等传统方法；发言者9同意混合方式，认为复杂问题都是先模仿后强化，如AlphaStar和GPT，单独模仿达不到专家水平，除非任务简单，单独强化样本复杂度不可接受；发言者5认为PID系统必有反馈，可拿反馈作为reward，强化必然走得成；发言者11（静波）认为IL和RL没有本质冲突，运动先验可从模仿学习或强化学习获取，然后通过RL找到对应latent完成任务。
-**数据采集与仿真数据**：发言者11（杨立新）分享数据质量经验，指出open X等数据集相机视角不固定、视角影响policy表现，标定重要且手眼标定至今解决不好，open X等数据集缺少物体运动信息，orkin从采集角度记录物体运动但当时设备有限只能采集刚体和关节体；发言者4（薛寒）all in reward采集路线，认为柔性体操作仿真需要IPC等先进图形学技术、算力要求高、能做的人少（如UCLA蒋正凡夫）、进展慢，reward采集是低成本方案、真实世界是最好的仿真器，终极形态是脑机接口或机电方式无感采集多模态数据，现阶段可穿戴式设备可扩展，并指出互联网视频数据与机器人所需数据不同（如叠衣服视频是平铺状态，机器人需要从混乱状态展平的数据）；发言者2提到自己受ego4d数据集毒害、洗数据洗了三个月，数据金字塔中互联网数据在最底层、质量低，仿真数据分传统仿真和强化收集数据、sim-to-real gap大，仿真数据加少量真机数据可显著提升成功率（如300条sim数据加20条真机数据），可穿戴设备精度相比遥操数据有gap；发言者7认为用真实数据还是仿真数据看成本、case by case，自动驾驶中真机数据收集困难且危险，提出加入第三个domain——无标注真实数据（如segment anything和depth anything），认为2025年应推广大规模利用无标注数据；发言者2提问中国是否强依赖英伟达生态、能否有国产仿真产品，发言者7提到宋应等在做国产替代、赌卡脖子，但工作人员不会直接touch这个生意。
+**统一认知**：
+- **软硬件协同优化**：发言者2认为具身智能是软硬件协同优化的范式，松灵产品两代迭代，第二代在遥操和策略部署上更好，夹爪加凝胶可反馈触觉、更稳、摩擦力更好。
+- **混合策略学习路线**：发言者9和发言者10均认为复杂任务应先模仿后强化，单独模仿或单独强化均不可行；发言者11认为IL和RL没有本质冲突，运动先验可从模仿学习或强化学习获取。
+- **仿真与真机数据互补**：发言者2指出仿真数据加少量真机数据可显著提升成功率，如**300条sim数据加20条真机数据**；发言者7提出加入无标注真实数据作为第三个domain。
+- **数据质量关键**：发言者11强调视角和标定对policy表现影响大，需记录物体运动信息。
+**可落地思路**：
+- **任务分层**：发言者10提出上层强化学习决策，底层用MPC、DWA等传统方法，可提升整体性能。
+- **可穿戴式采集**：发言者4提出现阶段通过可穿戴式设备在人们做事情过程中采集数据，是能scale的方案。
+- **国产仿真替代**：发言者7提到宋应等在做国产替代，赌卡脖子，但工作人员不会直接touch这个生意。
 # 未决分歧与后续探索
-**未决分歧**：具身智能的形态最终会收敛成人形机器人还是非人形（如科幻片中的变形机器人）；世界模型是否需要3D inductive bias；一个世界模型能否同时建模多个dynamics（如游戏与真实世界）；不同物理结构是否能有统一的表征，从而构成统一模型；强化学习与模仿学习最终路线是混合还是单一；真机复杂任务的reward如何获取；中国仿真系统是否强依赖英伟达生态，能否有国产替代；如何保证数据采集的高质量（如视角、标定、物体运动记录）。
-**后续探索**：发言者7提出2025年应推广大规模利用无标注数据（如segment anything和depth anything）；发言者4（薛寒）提出终极形态是脑机接口或机电方式无感采集多模态数据，现阶段可穿戴式设备可扩展；发言者2提出仿真数据加少量真机数据可显著提升成功率（如300条sim数据加20条真机数据）。跟进人未明确。</t>
+**未决分歧**：
+- **具身智能形态**：最终会收敛成人形机器人还是非人形（如科幻片中的变形机器人），未达成一致。
+- **世界模型是否需要3D inductive bias**：发言者7认为由数据决定，发言者9认为强化世界模型是任务导向的，不一定需要CV式世界模型。
+- **一个世界模型能否同时建模多个dynamics**：发言者5认为输入相同输出不同是歧义问题，世界模型可能做不到，policy可能统一；发言者9提出不同物理结构可能有统一表征。
+- **强化学习与模仿学习最终路线**：是混合还是单一，未形成统一结论。
+- **真机复杂任务的reward如何获取**：发言者5认为PID系统必有反馈，可拿反馈作为reward，但未完全解决。
+- **中国仿真系统是否强依赖英伟达生态**：能否有国产替代，未明确。
+- **如何保证数据采集的高质量**：如视角、标定、物体运动记录，未完全解决。
+**后续探索方向**：
+- **无标注数据利用**：发言者7提出2025年应推广大规模利用无标注真实数据，如segment anything和depth anything。
+- **柔性体仿真**：发言者4呼吁更多人在真正准的物理仿真上投入资源，如UCLA蒋正凡夫的工作。
+- **国产仿真系统**：发言者2提问中国是否强依赖英伟达生态，发言者7提到宋应等在做国产替代，但未明确跟进人。</t>
         </is>
       </c>
       <c r="D6" s="10" t="n">
-        <v>89.3</v>
+        <v>86.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>21458/3938</t>
+          <t>21458/3320</t>
         </is>
       </c>
     </row>
@@ -2704,42 +2765,39 @@
       <c r="C7" s="4" t="inlineStr">
         <is>
           <t># 庭审概况
-本案系上诉人国家开发银行与被上诉人云南东源电力股份有限公司、云南东源曲靖电力有限公司、招银金融租赁有限公司金融借款合同纠纷二审案件，国开行不服云南省高级人民法院2018云民初88号民事判决提起上诉。本案由审判员李少平担任审判长，与审判员魏文超、黄年、王海峰、葛洪涛组成合议庭，法官助理张瑞，依法公开开庭审理。庭审中，各方当事人核对身份无异议，东源煤电、东源煤业、曲靖电力合并发表意见。法庭围绕三个争议焦点展开调查与辩论：国开行对案涉设备是否享有抵押权（善意取得）、一审判决对借款罚息复息的计算及起算日期是否认定错误、东源煤电及东源煤业是否应连带给付违约金。合议庭休庭评议后提出调解方案，各方均无异议，合议庭予以确认，庭后出具调解书。
+本案系上诉人国家开发银行与被上诉人云南东源电力股份有限公司（东源煤电）、云南东源曲靖电力有限公司、招银金融租赁有限公司金融借款合同纠纷二审案件，由最高人民法院审判员李少平担任审判长，与审判员魏文超、黄年、王海峰、葛洪涛组成合议庭，法官助理张瑞，于二审公开开庭审理。庭审程序包括宣布法庭纪律、核对当事人身份、确认诉讼权利义务、法庭调查、法庭辩论及调解。各方对出庭人员身份均无异议，东源煤电、东源煤业、曲靖电力三方同意合并发表意见。合议庭归纳三个争议焦点：国开行是否尽到审查义务并构成善意取得、一审判决对罚息复息计算及起算日期是否认定错误、东源煤电与东源煤业是否应连带给付违约金。经法庭调查与辩论，合议庭休庭评议后提出调解方案，各方均无异议，合议庭予以确认，将出具调解书。
 # 原告诉称与被告辩称
-上诉人国开行上诉请求：撤销一审判决相关判项，改判确认其对案涉设备享有抵押权，并支持其利息、罚息、复利及违约金主张。事实与理由：国开行已按央行规定查询融资租赁登记系统，未显示曲靖电力公司设备有融资租赁登记；设备为通用设备无唯一标识码，无法按设备查询；抵押人仅为曲靖电力公司，审查义务仅限于抵押人，已履行审慎义务，构成善意取得。被上诉人东源煤电、东源煤业、曲靖电力答辩称：国开行未举证证明东源煤电违反柜台前移和账户管理约定，且按合同约定应先限期纠正，国开行从未发出书面纠正函；罚息不应作为复利计算基数，复利再计算复利无合同依据。被上诉人招银租赁答辩称：国开行未在抵押时点（2015年12月）查询融资租赁登记系统，仅提供2018年9月查询证书，不符合规定；审查义务应扩大到东源煤电（借款人与抵押人全资控股关系）；东源煤电出资行为系无权处分，招银租赁2012年已取得设备所有权。
+未提及
 | 方 | 诉讼请求/答辩意见 | 事实与理由 |
 | --- | --- | --- |
-| 上诉人（国开行） | 撤销一审判决相关判项，改判确认其对案涉设备享有抵押权，并支持利息、罚息、复利及违约金主张 | 已按央行规定查询融资租赁登记系统，未显示曲靖电力公司设备有融资租赁登记；设备为通用设备无唯一标识码，无法按设备查询；抵押人仅为曲靖电力公司，审查义务仅限于抵押人，已履行审慎义务，构成善意取得 |
-| 被上诉人（东源煤电、东源煤业、曲靖电力） | 驳回上诉，维持原判；罚息不应作为复利计算基数，复利再计算复利无合同依据；国开行未举证证明违约，且未先限期纠正 | 2015年12月2日邮件已告知融资租赁情况，设备名称相同且用红色标注，国开行应尽注意义务；国开行当天发函要求当天偿还未给合理期限；国开行从未发出书面纠正函 |
-| 被上诉人（招银租赁） | 驳回上诉，维持原判；国开行不构成善意取得 | 国开行未在抵押时点（2015年12月）查询融资租赁登记系统，仅提供2018年9月查询证书，不符合规定；审查义务应扩大到东源煤电（借款人与抵押人全资控股关系）；东源煤电出资行为系无权处分，招银租赁2012年已取得设备所有权 |
+| 上诉人（原审原告） | 请求确认对案涉设备享有抵押权，主张利息、罚息、复利合计6474.4513万元，并主张东源煤电、东源煤业连带给付违约金 | 已按央行规定查询融资租赁登记系统但未保留查询记录，审查义务仅限于抵押人曲靖电力公司；设备系通用设备无唯一标识码，已尽审慎义务，构成善意取得 |
+| 被上诉人（原审被告） | 主张国开行未在抵押时点查询融资租赁登记系统，不构成善意取得；罚息不应作为复利计算基数；违约金请求无依据 | 2015年12月2日邮件已用红色标注告知设备存在融资租赁；国开行宣布贷款提前到期未给合理期限；未举证证明违约行为 |
 # 举证与法庭调查
-**证据与质证意见**
-- 国开行提交2018年9月对曲靖电力公司的融资租赁查询证书，招银租赁质证认为不符合要求，依据2014年93号中国人民银行规定，国开行应在抵押时点（2015年12月）查询人行征信中心。
-- 招银租赁提交回租设备清单（证据第7页），仅载明设备名称和生产厂家，未载明型号；国开行质证称清单记载出厂日期为2012年3月1日，而现场调查核实抵押设备铭牌生产日期均在2013年以后，看不出是同一设备。
-- 国开行提交证据第54页、58页，显示东源煤电公司、曲靖电力公司对设备权属的证明材料及股东会决议，证明设备所有权属曲靖电力公司。
-- 国开行提交融资租赁登记信息核查表（证据第108页），显示曲靖电力公司名下无融资租赁登记，招银租赁质证称该核查表系2018年9月查询，非抵押时点查询。
-- 招银租赁提交2013年和2015年审计报告（证据第82页、95页），载明曲靖电力公司注册资本4亿元且已实缴，国开行据此主张招银租赁知道或应当知道设备出资情况。
-**法官询问要点**
-- 合议庭询问各方对中国人民银行征信中心融资租赁登记性质及法律后果的理解：国开行认为系行业强制性规范，用于防范金融风险；东源方认为系行业指导性规范，不产生物权后果；招银租赁认为系行业性强制性规范，不构成法律效力约束。
-- 合议庭询问融资租赁登记系统查询方式：国开行称仅能按单位查询；招银租赁称可按公司名称或设备查询，但设备查询需特定化。
-- 合议庭询问案涉5套设备是否登记唯一识别码：招银租赁称设备无唯一识别码，非必填项，未登记。
-- 合议庭询问国开行内部是否有规定要求保留未查询到结果的记录：国开行称无此规定，因未查询到结果故未保留记录。
-- 合议庭询问查询义务程度：国开行认为系基本义务，仅需查询抵押人名下登记；招银租赁认为系严格义务，未查询即不构成善意。
-- 合议庭询问融资租赁司法解释第9条第2款举证责任分担：国开行主张谁主张谁举证；招银租赁主张第1、2、4项由出租人举证，第3项由第三人（国开行）举证。
-**双方辩论的争议焦点**
-- 争议焦点一：国开行对案涉设备是否享有抵押权（善意取得）。国开行主张已履行审慎义务构成善意取得；东源方主张2015年12月2日邮件已告知融资租赁情况，设备名称相同且用红色标注，国开行应尽注意义务；招银租赁主张国开行未在抵押时点查询系统，审查义务应扩大到东源煤电，东源煤电出资行为系无权处分。
-- 争议焦点二：一审判决对案涉借款罚息复息的计算及起算日期是否认定错误。国开行主张利息自2017年12月21日计算至2018年6月12日合计21,795,727.68元，罚息自2018年6月13日计算至2019年2月19日合计41,050,579.57元，复利自2018年3月21日计算至2019年2月19日合计1,918,206.23元；东源方主张国开行当天发函要求当天偿还未给合理期限，罚息不应作为复利计算基数，复利再计算复利无合同依据。
-- 争议焦点三：东源煤电、东源煤业是否应当连带给付违约金。国开行主张借款合同第24条第3项约定违约金为千分之一，东源煤电未配合办理账户管理及柜台前移手续构成违约；东源方主张国开行未举证证明违约，且按合同约定应先限期纠正，国开行从未发出书面纠正函。
+**证据与质证**：
+- **融资情况统计表**：东源方主张2015年12月2日邮件所附《东源公司融资情况统计表》已告知设备存在融资租赁，且抵押设备部分用红色标注；国开行反驳称邮件正文及附表均无文字载明告知融资租赁情形，且招银租赁栏记载的抵押类型为不动产抵押，与本案融资租赁系不同法律概念。
+- **回租设备清单**：国开行指出招银租赁一审提交的证据第7页回租设备清单仅载明设备名称和生产厂家，未载明型号，出厂日期为2012年3月1日，而国开行现场调查核实抵押设备铭牌生产日期均在2013年以后，无法认定同一设备。
+- **权属证明材料**：国开行提交证据第54页、58页显示东源煤电公司、曲靖电力公司对抵押设备的权属证明及股东会决议，证明设备所有权属曲靖电力公司，国开行已尽审慎义务。
+- **融资租赁查询证书**：招银租赁主张国开行提供的2018年9月查询证书不符合要求，依据2014年93号文，国开行应在抵押时点（2015年12月）查询人行征信中心融资租赁登记系统。
+- **审计报告**：招银租赁一审提交2013年、2015年审计报告（证据第82页、95页）载明曲靖电力公司注册资本4亿元且已实缴，国开行据此主张招银租赁应当知道设备出资情况。
+**法官询问要点**：
+- **融资租赁登记性质**：合议庭询问各方对央行征信中心融资租赁登记性质及法律后果的理解，国开行认为是行业强制性规范，东源方认为是行业指导性规范，招银租赁认为是行业性强制性规范但不影响物权效力。
+- **查询方式**：法官询问融资租赁登记系统查询方式，国开行称仅能按单位查询，招银租赁称可按公司名称或设备查询，但案涉5套设备因无唯一识别码未登记。
+- **查询义务程度**：法官询问违反查询规范导致的法律后果，国开行主张为基本查询义务，招银租赁主张为严格义务，未查询即不构成善意。
+- **举证责任**：法官询问融资租赁司法解释第9条第2款举证责任分担，国开行主张按谁主张谁举证原则，招银租赁主张第1、2、4项由出租人举证，第3项由第三人（国开行）举证。
+**争议焦点辩论**：
+- **审查义务范围**：国开行主张审查义务仅限于抵押人曲靖电力公司，不能扩大到关联企业；招银租赁主张因东源煤电系借款人且为曲靖电力全资控股母公司，国开行应扩展调查东源煤电。
+- **善意取得**：国开行主张已按央行规定查询系统且无登记记录，构成善意取得；招银租赁主张国开行未在抵押时点查询，不构成善意。
+- **设备所有权**：招银租赁主张2012年设备交付时即取得所有权，东源煤电出资行为系无权处分；国开行主张设备系通用设备无唯一标识码，已对抵押人尽审查义务。
 # 庭审结果
-本案三个争议焦点：一是国开行对案涉设备是否享有抵押权（善意取得）；二是一审判决对案涉借款罚息复息的计算及起算日期是否认定错误；三是东源煤电、东源煤业是否应当连带给付违约金。合议庭休庭评议后提出调解方案，各方当事人均无异议，合议庭予以确认，庭后出具调解书。调解方案主要内容：国开行对东源煤电的债权扣除破产中已清偿本金外，利息、罚息、复利合计6474.4513万元；招银租赁对涉案6项设备享有所有权，对应债权数额1377.4137万元，国开行对93项设备有抵押权；案涉全部发电设备整体盘活处置，变现价款双方各得50%，实现费用双方各担50%；调解书生效后20日内由国开行向一审法院提出执行申请；未实现债权按破产重整计划预留方案实现，若司法变现不能，双方放弃设备权益，由东源曲靖电力自主生产经营。各方对一审判决第2项、第4项无争议，按判项内容在调解书中确认。</t>
+本案争议焦点为：一、国开行是否尽到审查义务、是否构成善意取得；二、一审判决对案涉借款罚息复息的计算及起算日期是否认定错误；三、东源煤电、东源煤业是否应当连带给付违约金。经合议庭评议，各方当事人对调解方案均无异议，合议庭予以确认，将出具调解书。调解方案主要内容：国开行对东源煤电的债权扣除破产清偿本金外，利息、罚息、复利合计6474.4513万元；招银租赁对6项设备享有所有权，对应债权1377.4137万元，国开行对93项设备有抵押权；案涉全部发电设备整体盘活处置，变现价款双方各得50%，费用各担50%；调解书生效后20日内，国开行向一审法院提出执行申请；若司法变现不能，双方放弃设备权益，由东源曲靖电力自主生产经营。</t>
         </is>
       </c>
       <c r="D7" s="10" t="n">
-        <v>79</v>
+        <v>58.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>28485/2996</t>
+          <t>28485/2124</t>
         </is>
       </c>
     </row>
@@ -2896,40 +2954,41 @@
       <c r="C8" s="4" t="inlineStr">
         <is>
           <t># 项目概况
-本次会议为原占比二玉米面加工厂项目中期验收会议，验收组汇报了卢萨卡、蒙泽两点的内业与外业检查情况。截止目前，卢萨卡点除带料加工调试外已完成全部验收工作，蒙泽点因带料调试厂家人员在场顺带完成全流程试生产，某皮卡点现场验收尚未开展，内业资料已提前拿到卢萨卡点。验收组于18、19号提前介入项目摸排，20号召开首次会议，检查分内业与外业，专业方向涵盖建筑工程、安装工程和设备机电设备。内业检查方面，管理组和技术组基本能按合同组建项目执行团队，主要人员基本保证在前方岗位，编制了施工组织计划、管理计划、实施细则及专项预案，内业资料基本满足项目有关标准和规范要求。外业检查方面，建筑部分整体品质良好，主要建材除国内采购出口外，预制构件、广场地砖等从卢萨卡200多公里外集中采购；安装部分钢结构材料从国内定制发货，施工工艺和外观质量满足规范标准；设备部分与中粮西安设计院及厂家签订专项供货合同，参照中国标准定制三套成套设备，蒙泽点工艺设备运行正常，产能符合设计指标，机电设备安装符合国家质量检验标准。财务方面，账户设置、资金往来、银行开户等完全符合财务处理规范和标准，中基公司在此为第一个也是唯一项目，没有挪用资金情况。验收组提出多项整改要求，管理组田组长表示会后与技术组一起细化问题，技术组龚总汇报已开展护照证书收集、资料汇总及现场整改工作。合作局领导强调蒙泽厂区混凝土路面开裂问题需管理组和总包单位共同研究制定科学合理的整改方案，最迟在出报告前完成整改形成闭环，验收组需复核；公司林总指示按照商务部经参局指示完成验收任务，注意新冠防疫和交通安全。
+本次会议为原占比二玉米面加工厂项目中期验收会议。验收组于18、19号提前介入项目前期摸排，20号召开首次会议，分内业检查和外业检查（建筑工程、安装工程、设备机电设备三个专业方向）对卢萨卡、蒙泽两个点开展验收。截止目前，已完成了卢萨卡点除带料加工调试以外的所有验收工作；蒙泽点已完成了全部验收工作，并利用带料调试厂家工作人员在现场的时机，顺带完成了全流程试生产；某皮卡点的现场验收工作尚未开展，内业资料已提前拿到卢萨卡点。内业资料基本满足项目有关标准和规范要求；外业方面，工艺设备运行正常，产能符合设计指标，整个项目内在品质和外在表观达到很好标准，但最终结论待资料整理结果出来后确定。财务方面，账户设置、资金往来、银行开户等完全符合财务处理规范和标准。验收组提出人员履约、内业资料、现场整改等整改项要求，管理组和技术组已汇报整改安排。合作局领导强调蒙泽厂区混凝土路面开裂问题需分析成因并限期整改闭环，公司林总要求注意交通安全。
 # 进度追踪
 | 模块 | 进展 | 状态 |
 | --- | --- | --- |
-| 卢萨卡点验收 | 除带料加工调试外，已完成全部验收工作，包括内业资料检查、外业现场抽检及机电设备投料试运行 | ✅已完成 |
-| 蒙泽点验收 | 已完成全部验收工作，因带料调试厂家工作人员在场，顺带完成全流程试生产，工艺设备运行正常，产能符合设计指标 | ✅已完成 |
-| 某皮卡点验收 | 现场验收尚未开展，内业资料已提前拿到卢萨卡点，待后续安排现场验收 | 🔄进行中 |
-| 内业资料检查 | 管理组和技术组基本能按合同组建项目执行团队，编制施工组织计划、管理计划、实施细则及专项预案，内业资料基本满足项目有关标准和规范要求，但分类整理及签字规范性需进一步规范完善 | 🔄进行中 |
-| 外业建筑检查 | 卢萨卡和蒙泽厂区建筑部分整体品质良好，主要建材除国内采购出口外，预制构件、广场地砖等从卢萨卡200多公里外集中采购，现场抽检满足规范标准 | ✅已完成 |
-| 外业安装检查 | 钢结构材料从国内定制发货，施工工艺和外观质量满足规范标准，但监控管线接头处有脱落需全面检查 | 🔄进行中 |
-| 设备机电检查 | 与中粮西安设计院及厂家签订专项供货合同，参照中国标准定制三套成套设备，蒙泽点工艺设备运行正常，机电设备安装符合国家质量检验标准 | ✅已完成 |
-| 财务检查 | 财务验收专家查阅本项目财务资料，账户设置、资金往来、银行开户等完全符合财务处理规范和标准，中基公司在此为第一个也是唯一项目，没有挪用资金情况 | ✅已完成 |
+| 卢萨卡点验收 | 已完成除带料加工调试以外的所有验收工作，内业资料已提前拿到卢萨卡点 | ✅已完成 |
+| 蒙泽点验收 | 已完成全部验收工作，利用带料调试厂家工作人员在现场的时机，顺带完成全流程试生产，工艺设备运行正常，产能符合设计指标 | ✅已完成 |
+| 某皮卡点验收 | 现场验收工作尚未开展，内业资料已提前拿到卢萨卡点 | 🔄进行中 |
+| 内业检查 | 管理组和技术组基本能按合同组建执行团队，编制施工组织计划、管理计划、实施细则及专项预案，内业资料基本满足项目有关标准和规范要求 | ✅已完成 |
+| 外业检查-建筑部分 | 卢萨卡和蒙泽厂区建筑部分，过程性隐蔽工程只能查阅文件，现场抽检和量测了可操作范围；预制构件、广场地砖等从卢萨卡大规模采购，供货单位是合作平台内单位，从200多公里外拉运 | ✅已完成 |
+| 外业检查-安装部分 | 以钢结构为主，材料从国内定制发货，施工工艺和外观质量满足规范标准 | ✅已完成 |
+| 外业检查-设备部分 | 执行单位与中粮西安设计院及厂家签订专项供货合同，设备参照中国标准，按三类产品定制三套成套设备，安装高峰期厂家派十几名工作人员到现场指导，验收组对工艺设备逐台复核并进行了投料试运行 | ✅已完成 |
+| 蒙泽点全流程生产调试 | 相关管理人员和技术人员已到达现场，继续对蒙泽点进行全流程生产调试 | 🔄进行中 |
+| 财务检查 | 财务验收专家查阅了本项目财务资料，账户设置、资金往来、银行开户等完全符合财务处理规范和标准，中基公司在此是第一个项目也是唯一项目，没有挪用资金的情况 | ✅已完成 |
 # 风险预警
 | 风险/瓶颈 | 等级 | 影响 | 责任人 | 应对计划 |
 | --- | --- | --- | --- | --- |
-| 人员履约及护照问题 | 中 | 受疫情影响及EPC项目特点，个别同志进出场时间及护照需完善，个别特种人员证件有效期可能过期或未及时更新 | 施工部、管理组 | 会后完善相关资料，与国内人力资源对接确认证件延期或更新情况 |
-| 人员统计数量不完整 | 低 | 技术组未将厂家服务人员等计入人员统计数量，影响合同履约数据准确性 | 技术组 | 完善人员统计，将厂家服务人员计入团队人员 |
-| 内业资料分类及签字不规范 | 中 | 质检资料、程序性文件等分类整理及签字规范性需进一步规范完善，影响竣工文件组卷 | 执行单位 | 按照项目执行标准和规范，及时将资料汇总到卢萨卡分类成册，按竣工文件归档要求组卷 |
-| 混凝土路面开裂 | 中 | 某厂区非主要通道混凝土路面有少量开裂现象，当地工人处理效果不好，可能受水侵蚀，若移交外方后出现大面积开裂对外影响不好 | 管理组、总包单位 | 共同研究制定科学合理的整改方案，分析成因（气候、施工工艺、材料），重新清理并用防水材料封管，最迟在出报告前完成整改，验收组复核 |
-| 监控管线接头脱落 | 低 | 设备启动时震动导致监控管线接头处脱落，可能引起机械故障 | 施工组 | 全面检查管线接头，保证有效性和安全性 |
-| 卢萨卡点雨水倒灌风险 | 中 | 提升桶位置雨水可能倒灌，存在安全隐患 | 施工组 | 检查原设计施工是否足以解决水的问题，考虑增加覆盖面积或采取技术措施解决 |
-| 卢萨卡点廊桥竖条不足 | 低 | 廊桥横向只有三个竖条，可能影响巡检维护人员安全 | 施工组 | 建议中间再加两个竖条，增强安全感 |
-| 成品保护疏忽 | 中 | 工程实体完工时间较长，成品保护有疏忽，可能存在破损，移交外方前需修补 | 施工组 | 移交前继续做好成品保护，有破损或问题的地方及时修补 |
-| 姆皮卡点交通安全 | 高 | 姆皮卡点路途遥远，路况不好，存在交通安全风险 | 验收组 | 注意交通安全，做好新冠疫情防控 |
-| 不可预见费使用证据不足 | 中 | 本项目有动用不可预见费的情况，有关依据证据和数据需进一步完善和收集整理 | 验收组、施工单位 | 后续继续跟踪完善，末次汇报时再进行沟通 |
+| 人员履约和合同履约问题 | 中 | 受疫情影响及EPC项目特点，个别同志进出场时间及护照需完善，个别岗位人员更换流程需完善，技术组对厂家服务人员等未计算进人员统计数量 | 技术组 | 正在收集所有参与项目现场人员的护照证书，与国内人力资源对接完善证件 |
+| 个别特种人员证件有效期问题 | 中 | 个别特种人员证件有效期可能过期或未及时更新 | 技术组 | 与国内人力资源对接确认是否延期或更新 |
+| 内业资料分类整理及签字规范性 | 中 | 分类整理及少量质检和管理机构验收签字规范性需完善，资料分散需汇总 | 技术组 | 在验收完成第一时间将三个厂区资料全部汇总于卢萨卡，包括竣工图分类汇总、分类组卷及编码 |
+| 蒙泽厂区混凝土路面开裂 | 高 | 非主要通道范围内混凝土路面有少量开裂现象，当地工人处理效果不好，可能受水侵蚀，移交外方后可能大面积开裂 | 管理组和总包单位 | 分析成因，结合赞比亚气候特点制定切实可行整改方案，最迟在出报告前完成整改，形成闭环，验收组还要复核 |
+| 监控管线接头脱落 | 中 | 设备启动时震动导致监控管线接头处有脱落，可能引起机械故障 | 施工组 | 全面检查，保证有效性和安全性 |
+| 卢萨卡点提升桶位置雨水倒灌 | 中 | 赞比亚雨量大且风大，雨水可能倒灌 | 施工组 | 检查并考虑增加覆盖面积或采取技术措施解决 |
+| 卢萨卡点廊墙端头竖条少 | 低 | 横向只有三个竖条，可能影响巡检维护人员安全 | 施工组 | 建议中间再加两个竖条，增强安全感 |
+| 成品保护疏忽 | 中 | 工程实体完工时间较长，成品保护有疏忽，可能有破损 | 施工组 | 交给外方前继续做好成品保护，有破损及时修补 |
+| 姆皮卡点交通安全 | 高 | 姆皮卡点路途遥远，交通不好，存在交通安全风险 | 验收组 | 注意交通安全及疫情防控，安全完成验收任务 |
+| 赞比亚雨季排水 | 中 | 雨季来临，需检查厂区排水，防止阻塞 | 施工组 | 检查厂区及办公区排水，清理屋面排水和室外通道 |
 # 后续计划</t>
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>91.90000000000001</v>
+        <v>100.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11110/2360</t>
+          <t>11110/2101</t>
         </is>
       </c>
     </row>
@@ -3140,50 +3199,50 @@
       <c r="C9" s="4" t="inlineStr">
         <is>
           <t># 发布会概况
-本次中金宏观策略争论周会由策略组刘刚凯文主持，围绕大美丽法案、关税、港股流动性三大宏观议题展开，并邀请公用事业首席分析师刘佳妮、机械军工分析师郭文秀、传媒首席分析师张雪琴分别解读光伏反内卷、人形机器人、游戏板块的投资机会。整体基调为：对美股美债不悲观，波动提供再配置机会；关税大概率是谈判技巧，市场逐渐脱敏；港股流动性三季度边际收紧但基本面可盖过；光伏反内卷政策力度升级、行业底部夯实；人形机器人三季度围绕华为链、本土企业技术闭环、特斯拉硬件替代三条主线；游戏板块在消费、政策和新品周期三重利好下有望戴维斯双击。
+本次研讨会由中金公司策略组刘刚凯文主持，围绕大美丽法案、关税更新、港股流动性三大宏观热点展开解读，并邀请公用事业首席分析师刘佳妮、机械军工分析师郭文秀、传媒首席分析师张雪琴分别就光伏反内卷、人形机器人、游戏板块进行行业更新。整体基调偏积极：大美丽法案对信用周期中长期有利，关税大概率维持且市场逐渐脱敏，港股流动性边际收紧但基本面强可盖过影响；行业层面光伏反内卷政策升级夯实底部，人形机器人三季度迎催化窗口，游戏板块有望在调整后实现戴维斯双击。
 # 核心信息
-- 大美丽法案三大块：提高债务上限约**5万亿美元**，延长2017年减税法案（新增支出**3.4万亿**、每年**3400亿**，减新能源补贴**1.4万亿**），取消`899条款`。
-- 信用周期框架：政府、AI产业投资、传统私人部门需求三部分；美国如篝火自然修复，中国如煮水需持续添柴；上半年美国遭遇`DeepSeek`、财政收缩、`4月2日对等关税`三盆冷水，纳斯达克从底部反弹**35%**。
-- 7-9月美债供给约**1万亿美元**，参考2023年三季度推高美债利率从3.8%到5%、美股小幅下跌4-5%；当前期限溢价已是**2013年以来高点**，预计利率抬升幅度可能不及2023年；四季度美元可能小幅走强，美股可能反弹跑赢。
-- 关税四点信息：一定要做以支撑收入；需维持一定税率（当前豁免**10%**水平）以收**3000-4000亿**；不能太高以免通胀；市场逐渐脱敏。新变化：时间拖后（原`7月9日`），大部分税率相比`4月2日对等关税`回落，除巴西；加拿大、墨西哥、欧盟单拎出因贸易占比高。有效税率当前**10-12%**，若`8月1日`全回去可能10-15%，最极端**18%**；通胀压力缓慢抬升，年底约**3.3-3.4%**。对中国关税约**40-50%**，越南转口限制**40%**，需关注`8月12日`中美谈判及转口限制。
-- 港股流动性：`7-9月`美债利率走高、美元流动性供给压力，四季度美元可能小幅走强，边际上对港股略偏负面；港股5月后微观流动性释放，`HIBOR`大幅下降，金管局投放大量资金，港币触及**7.85**，金管局会收流动性但可小幅收（如收90亿放1000多亿），流动性边际变紧，`IPO`融资较多形成约束。指数在**23000-24000**区间震荡，类似3月底；风格上长期两头分红，银行股溢价低于**20%**短期透支，**125%**是隐形底；成长端新消费拥挤，创新药稍降，科技硬件AI应用降幅大，可提前埋伏。
-- 光伏反内卷：需求端全球新增装机从2020年**130GW**增至2024年**530GW**（CAGR **42%**），2025-26年增速回落至**10%**左右；供给端2023年产能从**600GW**增至**1000GW**，电池产能是需求**1.5倍**、硅片组件**2倍**、硅料**2.5倍**；2022年以来产业链价格下跌**70%-90%**，硅片电池2023Q4亏损，硅料组件2024Q2亏损。反内卷政策力度升级（`2024年5月17日`光伏行业高质量发展座谈会、`2025年2月`国常会、`6月29日`人民日报发声、`7月1日`中财委第6次会议、`7月3日`工信部座谈会），价格恶性竞争有望告一段落，行业底部夯实。硅料环节最易整合（集中度高、成本曲线陡峭、供需比超**200%**），电池环节供需最好（`PERC`退出、`TOPCon`占**90%**、`BC`渗透率**5-6%**）；光伏玻璃`2024年9月`第一轮产能出清降幅**6%**，第二轮计划7月降产**30%**，需出清约**2万吨**，龙头企业成本**1元/平米**。市场反馈：多晶硅期货价格触及**40元/公斤**，现货从35元上涨，硅片涨**10%**，电池涨**2分**，硅料和玻璃股价涨**20-30%**，组件涨**10%**。穿越周期企业：头部一体化组件企业议价能力强，低杠杆强现金企业财务健康，技术创新（颗粒硅使用比例从10-20%提升到**50%**，铜替代银2025-26年导入）。
-- 人形机器人：二季度A股机器人板块按流通市值加权跌约**9%**，跑输机械设备约**12个百分点**，特斯拉核心供应商股价从3月高点回调**30%-40%**，回调原因系特斯拉4月后量产时间线延后叠加中美关税。三季度三条主线：华为云生态开放（6月底发布`盘古世界模型`和`CloudRobot平台`，具备多模态生成、规划大模型、执行大模型毫米级精度，华为明确不造机器人，以`RTC`方式开放，探索`AI agent`或`license`收费）、本土人形机器人企业技术闭环（智元机器人拟收购材料厂商在A股上市，宇树科技年收入突破**10亿**、下半年加速上市，两家同时中标中国移动近**1.2亿**人形机器人采购订单）、特斯拉延期带来的硬件替代窗口（`Optimus`存在电机过热、灵巧手负载不足、续航问题，正在变更方案和筛选供应商）。物流端是投资回报率明确的场景，2025年降低单件运输成本是刚需；国内至少**100家以上**人形机器人本体厂商；港股机器人板块二季度估值溢价明显，下半年有确定性扩容。关注三类信号：华为云生态接入厂商新增、头部企业出货量跨越年化**500台**或**1000台**、电机硬件优化窗口。
-- 游戏板块：上涨接近两三个月，上周初开始调整，观点仍看好。政策端今年1月和3月国务院层面发布游戏行业支持政策，广东、浙江、北京、上海等地有专门政策支持包；版号发放今年6月单月发放**158个**（国产**147个**，进口**11个**），**2018年以来单月最高**；市场数据2024年8月以来单月持续正增长，今年1-5月游戏市场规模同比增长**17%**（**1400多亿**），手游同比增长**20%**。新品周期：市场预期今年缺乏大作，但中型厂商新品成为核心催化，如吉比特`《仗剑传说》`首月流水**2亿多**，巨人网络`《超自然行动组》`6月流水过亿，年化乐观**20亿**，利润提升**50%以上**。估值：`TTM PE`约**30倍**（2023年AI行情到过**45倍**），2025年静态`PE`约**20倍**。游戏板块逆周期性，政策友好，新品周期延续，但利润有滞后性，今年新品利润明年兑现；建议关注新品市场表现、用户获取下载榜排名等领先指标。
+**大美丽法案**：提高债务上限约**5万亿美元**，延长2017年减税法案（新增支出**3.4万亿**，每年**3400亿**，减新能源补贴**1.4万亿**），取消`899条款`；财政赤字率预计维持**5-6%**，关税收入**3000-4000亿**可覆盖新增支出；7-9月美债供给压力约**1万亿美元**，参考2023年三季度推高美债利率从**3.8%**到**5%**，美股小幅下跌**4-5%**；当前期限溢价已处于**2013年以来**高位，预计美债利率抬升幅度可能不及2023年。
+**关税**：四点信息——一定要做以支撑收入；需维持一定税率（当前豁免**10%**水平）以收**3000-4000亿**；不能太高以免通胀；市场逐渐脱敏。新变化：时间拖后（原**7月9日**），大部分国家税率相比**4月2日**回落，除巴西大幅增加；加拿大、墨西哥、欧盟贸易占比高需谈妥，其他占比小，日本最高**4.5%**。有效税率当前**10-12%**，若8月1日全回去可能**10-15%**，最极端**18%**；通胀压力缓慢抬升，年底约**3.3-3.4%**。关注**8月12日**中美谈判进展，越南转口限制**40%**，英国协议有转口限制。
+**港股流动性**：5月后微观流动性释放，HIBOR大幅下降，金管局投放大量资金，港币触及**7.85**；金管局会收流动性，但可小幅收（如收**90亿**，放**1000多亿**），延缓利率收紧；三季度流动性供给不如二季度，IPO融资多形成约束；指数在**23000-24000**区间震荡。
+**光伏**：全球新增装机从2020年**130GW**增至2024年**530GW**（CAGR **42%**），预计2025-26年增速回落至**10%**左右；2023年产能从**600GW**增至**1000GW**，电池产能为需求**1.5倍**，硅片组件**2倍**，硅料**2.5倍**；2022年以来产业链价格下跌**70-90%**，硅片电池**2023Q4**亏损，硅料组件**2024Q2**亏损。反内卷政策：`2024年5月17日光伏行业高质量发展座谈会`、`2025年2月国常会`、`6月29日人民日报发声`、`7月1日中财委第6次会议`、`7月3日工信部座谈会`。硅料环节最易整合（集中度高、成本曲线陡峭、供需比超**200%**），电池环节供需最好（PERC退出，TOPCon占**90%**，BC渗透率**5-6%**）；光伏玻璃第二波降产**30%**，需出清约**2万吨**，价格创历史新低。市场反馈：多晶硅期货价格反弹至**40元/公斤**，现货从**35元**上涨；硅片报价涨**10%**，电池涨**2分**；硅料和玻璃股价涨**20-30%**，组件涨**10%**。
+**人形机器人**：二季度A股板块按流通市值加权跌约**9%**，跑输机械设备约**12个百分点**，特斯拉核心供应商股价从3月高点回调**30-40%**；三季度三条主线——华为云生态开放（6月底发布`盘古世界模型`和`Cloud Robot平台`，三大能力：多模态生成、规划大模型、执行大模型毫米级精度；华为明确不造机器人，以RTC方式开放，探索AI agent或license收费）、本土企业技术闭环（智元机器人拟收购材料厂商在A股上市，宇树科技年收入突破**10亿**，两家同时中标中国移动近**1.2亿**人形机器人采购订单）、特斯拉延期带来的硬件替代窗口（Optimus存在电机过热、灵巧手负载不足、续航问题，轻量化以塑代钢是方向）。港股机器人板块二季度估值溢价明显，下半年确定扩容，关注A+H动向。
+**游戏板块**：上涨接近两三个月，上周初开始调整，观点仍看好。政策端：去年`黑神话悟空`后政策支持空前，今年1月和3月国务院发布支持政策，广东、浙江、北京、上海等地有专门政策包。版号发放：今年每月国产和进口版号都发，6月单月创新高（国产**147个**，进口**11个**，共**158个**），**2018年以来**单月最高。市场数据：2024年8月以来单月持续正增长；今年1-5月游戏市场规模同比增长**17%**（**1400多亿**），手游同比增长**20%**。新品周期：中型厂商新品亮眼，如吉比特`《仗剑传说》`首月流水**2亿多**，巨人网络`《超自然行动组》`6月流水过亿，年化乐观**20亿**，利润提升**50%以上**。估值：TTM PE约**30倍**（2023年AI行情**45倍**），2025年静态PE约**20倍**；新品利润有滞后性，明年兑现。
 # 官方表态
-- 关于去美元化：刘刚凯文表示，我们并不是完全认同去美元化这个观点，这个现在成了一个高度趋同的共识，而且都是基于宏大叙事，5~10年之后的事即便认可这个逻辑的人也没法拍胸脯说一定兑现。
-- 关于市场误区：刘刚凯文指出，现在市场两个最大的误区，一个是把美元弱当成去美元化，另一个是把美元弱和美股弱直接划等号；美元弱在大部分时间，只要不是抛售美国资产的弱，实际是对美股有利的。
-- 关于美股美债：刘刚凯文重申，我们对美股也不悲观，波动提供再配置的机会，背后的原因是信用周期的再度转好，只不过三季度有一个流动性的波折。
-- 关于关税：刘刚凯文判断，关税大概率要做，需要维持一定税率才能收上钱，也不能太高以免通胀受不了，所以市场逐渐脱敏，静观其变。
-- 关于港股流动性：刘刚凯文强调，美元美债利率并不是绝对主导港股市场的唯一变量，很多时候自己的基本面强完全可以盖过它的影响。
-- 关于光伏反内卷：刘佳妮表示，随着反内卷力度不断强化升级，价格恶性竞争有望告一段落，至少对行业来讲夯实了它的底部。
-- 关于人形机器人：郭文秀认为，三季度将是从二季度的迷茫期到商业兑现过渡的小阶段，建议关注华为云生态接入、头部企业出货量跨越年化500台或1000台、电机硬件优化三类信号。
-- 关于游戏板块：张雪琴重申，在消费、政策和新品周期三重利好下，游戏行业有望在调整后再次实现戴维斯双击。
+**大美丽法案与美股美债**：
+&gt; 我们重申我们这个观点并不悲观。背后的原因呢就是因为信用周期的再度转好，只不过三季度呢有一个流动性的波折，它要过一些坎儿。
+&gt; 波动提供再配置的机会。
+**关税**：
+&gt; 他一定要做，哪怕遇到各种各样的对吧？这是第1点。大概率要做。
+&gt; 他现在威胁的那么高，有可能是一个谈判技巧。
+**港股流动性**：
+&gt; 美元美债利率它并不是绝对主导港股市场的唯一的变量，很多时候你自己的基本面强，完全可以盖过它的影响。
+**光伏反内卷**：
+&gt; 随着反内卷的力度不断的强化升级，我们相信就是价格的恶性竞争有望告一段落。那至少呢对于行业来讲，它的这个夯实了它的一个底部。
+**人形机器人**：
+&gt; 三季度将是一个二季度的迷茫期到商业兑现过度的这样的一个小阶段。
+**游戏板块**：
+&gt; 我们还是认为在消费政策和新品周期三重利好下面，游戏行业有望在调整后再次实现戴维斯双击。
 # Q&amp;A环节
 **问**：大美丽法案对美股、美债、美元流动性有什么影响？
-**答**：刘刚凯文表示，大美丽法案三大块（提高债务上限约5万亿美元、延长2017年减税法案、取消899条款）对信用周期中长期有利，但短期7-9月有流动性抽水效应，美债供给约1万亿美元，参考2023年三季度推高美债利率从3.8%到5%、美股小幅下跌4-5%；当前期限溢价已是2013年以来高点，预计利率抬升幅度可能不及2023年，波动提供再配置机会，对美股美债不悲观。
-**问**：关税是否在升级？对通胀和美联储降息有什么影响？
-**答**：刘刚凯文表示，关税大概率要做以支撑收入，需维持一定税率（当前豁免10%水平）以收3000-4000亿，不能太高以免通胀；新变化是时间拖后（原7月9日），大部分税率相比4月2日对等关税回落，除巴西；有效税率当前10-12%，若8月1日全回去可能10-15%，最极端18%；通胀压力缓慢抬升，年底约3.3-3.4%，不大幅改变通胀路径，美联储7-9月仍可降息。
-**问**：对中国关税和转口限制有什么影响？
-**答**：刘刚凯文提示，对中国关税约40-50%，越南转口限制40%，我们比这个税率还要低，需关注8月12日中美谈判进展及转口限制。
-**问**：港股流动性三季度会怎样？
-**答**：刘刚凯文表示，7-9月美债利率走高、美元流动性供给压力，四季度美元可能小幅走强，边际上对港股略偏负面；港股5月后微观流动性释放，HIBOR大幅下降，金管局投放大量资金，港币触及7.85，金管局会收流动性但可小幅收（如收90亿放1000多亿），流动性边际变紧，IPO融资较多形成约束；指数在23000-24000区间震荡，类似3月底。
+**答**：大美丽法案三大块——提高债务上限约5万亿美元、延长2017年减税法案（新增支出3.4万亿，每年3400亿，减新能源补贴1.4万亿）、取消899条款。信用周期框架下，美国如篝火自然修复，中国如煮水需持续添柴；上半年美国遭遇DeepSeek、财政收缩、4月2日对等关税三盆冷水，下半年环比改善。财政赤字率预计维持5-6%，关税收入3000-4000亿可覆盖新增支出。7-9月美债供给压力约1万亿美元，参考2023年三季度推高美债利率从3.8%到5%，美股小幅下跌4-5%；当前期限溢价已处于2013年以来高位，预计美债利率抬升幅度可能不及2023年。四季度美元可能小幅走强，美股可能反弹跑赢。
+**问**：关税是否只是谈判技巧？对通胀和美联储降息有什么影响？
+**答**：关税四点信息——一定要做以支撑收入；需维持一定税率（当前豁免10%水平）以收3000-4000亿；不能太高以免通胀；市场逐渐脱敏。新变化：时间拖后（原7月9日），大部分国家税率相比4月2日回落，除巴西大幅增加；加拿大、墨西哥、欧盟贸易占比高需谈妥，其他占比小，日本最高4.5%。有效税率当前10-12%，若8月1日全回去可能10-15%，最极端18%；通胀压力缓慢抬升，年底约3.3-3.4%，不大幅改变通胀路径。美联储7月降息勉强，9月后仍可降。关注8月12日中美谈判进展，越南转口限制40%，英国协议有转口限制。
+**问**：港股流动性三季度会怎样？对港股市场有什么影响？
+**答**：7-9月美债利率走高、美元流动性供给压力，四季度美元可能小幅走强，边际挤压港股。港股微观流动性5月后释放，HIBOR大幅下降，金管局投放大量资金，港币触及7.85；金管局会收流动性，但可小幅收（如收90亿，放1000多亿），延缓利率收紧。三季度流动性供给不如二季度，IPO融资多形成约束；指数在23000-24000区间震荡，类似3月底。但美元美债利率不是绝对主导变量，基本面强可盖过影响。风格建议：长期两头分红，短期银行溢价低于20%已透支；成长端新消费拥挤，创新药稍降，科技硬件AI应用降幅大，可提前埋伏。
 **问**：光伏反内卷政策对行业有什么影响？哪些环节最受益？
-**答**：刘佳妮表示，反内卷政策力度升级（2024年5月17日光伏行业高质量发展座谈会、2025年2月国常会、6月29日人民日报发声、7月1日中财委第6次会议、7月3日工信部座谈会），价格恶性竞争有望告一段落，行业底部夯实；硅料环节最易整合（集中度高、成本曲线陡峭、供需比超200%），电池环节供需最好（PERC退出、TOPCon占90%、BC渗透率5-6%）；光伏玻璃第二轮产能出清计划7月降产30%，需出清约2万吨。
-**问**：光伏产业链价格和股价有什么反应？
-**答**：刘佳妮表示，多晶硅期货价格触及40元/公斤，现货从35元上涨，硅片涨10%，电池涨2分，硅料和玻璃股价涨20-30%，组件涨10%；组件价格能否跟涨取决于下游电站能否接受产业链价格上涨传导，需观望招标情况。
-**问**：人形机器人三季度有哪些催化剂和投资主线？
-**答**：郭文秀表示，三季度围绕三条主线：华为云生态开放（6月底发布盘古世界模型和CloudRobot平台，华为明确不造机器人，以RTC方式开放）、本土人形机器人企业技术闭环（智元机器人拟收购材料厂商在A股上市，宇树科技年收入突破10亿、下半年加速上市，两家同时中标中国移动近1.2亿人形机器人采购订单）、特斯拉延期带来的硬件替代窗口（Optimus存在电机过热、灵巧手负载不足、续航问题，正在变更方案和筛选供应商）；建议关注三类信号：华为云生态接入厂商新增、头部企业出货量跨越年化500台或1000台、电机硬件优化窗口。
-**问**：游戏板块上涨后调整，是结束还是回调后更健康？
-**答**：张雪琴表示，观点旗帜鲜明是后者；估值上TTM PE约30倍（2023年AI行情到过45倍），2025年静态PE约20倍，游戏板块逆周期性，政策友好，新品周期延续，但利润有滞后性，今年新品利润明年兑现；在消费、政策和新品周期三重利好下，游戏行业有望在调整后再次实现戴维斯双击。</t>
+**答**：反内卷政策升级——2024年5月17日光伏行业高质量发展座谈会、2025年2月国常会、6月29日人民日报发声、7月1日中财委第6次会议、7月3日工信部座谈会。价格恶性竞争有望告一段落，行业底部夯实。硅料环节最易整合（集中度高、成本曲线陡峭、供需比超200%），电池环节供需最好（PERC退出，TOPCon占90%，BC渗透率5-6%）；光伏玻璃第二波降产30%，需出清约2万吨，价格创历史新低。市场反馈：多晶硅期货价格反弹至40元/公斤，现货从35元上涨；硅片报价涨10%，电池涨2分；硅料和玻璃股价涨20-30%，组件涨10%。组件价格能否跟涨需观望招标情况。
+**问**：人形机器人三季度有哪些催化剂？投资主线是什么？
+**答**：三季度三条主线——华为云生态开放（6月底发布盘古世界模型和Cloud Robot平台，三大能力：多模态生成、规划大模型、执行大模型毫米级精度；华为明确不造机器人，以RTC方式开放，探索AI agent或license收费）、本土企业技术闭环（智元机器人拟收购材料厂商在A股上市，宇树科技年收入突破10亿，两家同时中标中国移动近1.2亿人形机器人采购订单）、特斯拉延期带来的硬件替代窗口（Optimus存在电机过热、灵巧手负载不足、续航问题，轻量化以塑代钢是方向）。建议关注三类信号：华为云生态接入厂商新增、头部企业出货量跨越年化500台或1000台、电机硬件优化窗口。
+**问**：游戏板块调整是结束还是回调后更健康？估值和业绩怎么看？
+**答**：观点旗帜鲜明是后者。估值水平：TTM PE约30倍（2023年AI行情45倍），2025年静态PE约20倍；新品利润有滞后性，今年上新利润明年才兑现。政策端：今年1月和3月国务院发布支持政策，广东、浙江、北京、上海等地有专门政策包。版号发放：6月单月创新高（国产147个，进口11个，共158个），2018年以来单月最高。市场数据：今年1-5月游戏市场规模同比增长17%（1400多亿），手游同比增长20%。新品周期：中型厂商新品亮眼，如吉比特《仗剑传说》首月流水2亿多，巨人网络《超自然行动组》6月流水过亿，年化乐观20亿，利润提升50%以上。建议关注新品市场表现、用户获取下载榜排名等领先指标。</t>
         </is>
       </c>
       <c r="D9" s="10" t="n">
-        <v>121.9</v>
+        <v>107.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>22868/4863</t>
+          <t>22868/4501</t>
         </is>
       </c>
     </row>
@@ -3498,40 +3557,47 @@
       <c r="C10" s="4" t="inlineStr">
         <is>
           <t># 课程概况
-本次课程为“梦想”主题班会，围绕认识梦想、思考实现梦想的条件展开。老师先询问学生们的梦想，学生回答有当保安、当喜剧人、当太空人、当世界冠军、当歌手等；老师分享自己的梦想是成为受学生喜爱的有名望的优秀人民教师，并讲述个人经历：曾梦想考中国美术学院，单考过了但未去，因离家远和没钱，后选择定向生，去广东技术师范大学（原民族学院），定向回龙川县教书；定向生免学费，但定向不能考研，只能在职考研，边工作边读研，学费自己交。老师还分享大学梦想：加入学生会、参加比赛、保持专业排名第一（专业41人，大学4年保持第一）、考教师资格证；并提到高中时在国旗下讲话立志考中国美术学院，被嘲笑，但坚持梦想。课上播放视频：航模爱好者何宗发（中国唯一去法国巴黎比赛的）和想当歌手的普通人，讨论实现梦想的条件；讨论得出实现梦想需要坚持努力、勇敢、机会、兴趣、能力、学习等条件；提到马云中考考两次、高考考三次，最终成为中国首富，强调坚持的重要性。最后老师让学生写下自己的梦想清单，并分享部分学生的梦想；总结实现梦想需要坚持、行动、机会、能力、学习等条件，梦想可以分阶段调整，鼓励学生写下梦想清单并努力实现。
+本次班会课以“梦想”为主题，老师通过提问引导学生分享各自的梦想（如当保安、喜剧人、太空人、世界冠军、歌手等），并分享自己的梦想是成为受学生喜爱的有名望的优秀人民教师。老师结合个人经历讲述追梦过程：曾梦想考中国美术学院，单考通过但因离家远和没钱未就读，后选择定向生，就读广东技术师范大学（原民族学院），定向回龙川县教书；定向生免学费但不能考研，只能在职考研、边工作边读研且学费自理。老师大学期间保持专业排名第一（专业41人），每天5点起床坚持自律，并考取教师资格证。班会播放两个视频：航模爱好者何宗发（何聪发）通过努力走上更大舞台，受到世界冠军关注，梦想从中国走向世界；普通人想当歌手，即使唱歌走调，通过后天学习可以调整。师生共同讨论实现梦想的条件，包括坚持、努力、勇敢、机会、兴趣、能力、学习等。老师以马云为例（中考考两次、高考考多次，最终成为中国首富）说明起点不重要、坚持重要，并提到马云的新梦想：过去15年中国因他们改变，未来15年世界因他们改变。老师建议梦想可以分阶段调整，如先考进年级前百，再前50；并展示自己的梦想之路：考上大学（11年）、优秀班干部（2年）、国家励志奖学金（1年）、成为优秀人民教师（待定）。学生写下自己的梦想清单，老师展示部分学生的梦想，如考630分、健康身体、家人平安、世界和平等。
 # 核心知识点梳理
 ## 梦想的定义与价值
-- 梦想是个人追求的目标，每一个梦想都值得尊重，**不被嘲笑的梦想不是梦想**。
-- 梦想可以分阶段调整：先定小目标，再定大目标，如考不进年级前50可先调整为前百，再逐步前进。
+- **梦想**：每个人心中追求的目标，如学生分享的当保安、喜剧人、太空人、世界冠军、歌手等。
+- **梦想值得尊重**：老师强调“每一个梦想都是值得我们尊重的”，即使被嘲笑也要坚持。
+- **不被嘲笑的梦想**：老师引用“不被嘲笑的梦想不是梦想”，鼓励学生勇敢追梦。
 ## 实现梦想的条件
-- **坚持努力**：如老师大学4年保持专业排名第一（专业41人），需每天5点起床，体现自律与坚持。
-- **勇敢行动**：如班上同学虽被起哄仍勇敢站上讲台唱歌。
-- **机会**：机会留给有准备的人。
-- **兴趣、能力与学习**：如唱歌走调可通过后天学习调整。
-- 天赋只是1%，**努力更重要**。
+- **坚持与努力**：老师以自身为例，大学4年保持专业排名第一（专业41人），每天5点起床，坚持自律。
+- **勇敢与行动**：老师表扬勇敢上台唱歌的同学，强调“机会都是留给有准备的人”。
+- **兴趣与能力**：老师指出兴趣、能力、学习等也是实现梦想的必备条件。
+- **机会**：老师强调机会的重要性，但机会留给有准备的人。
+## 梦想的调整与分阶段
+- **分阶段目标**：老师建议梦想可以分阶段调整，如先考进年级前百，再前50。
+- **量力而行**：老师提醒“量力而行”，目标实现不了可以调整。
 ## 梦想的案例
-- 航模爱好者**何宗发**：中国唯一去法国巴黎比赛的航模选手，通过一步步努力走上更大舞台，让世界冠军关注其成长，梦想从国内走向世界。
-- 想当歌手的普通人：虽唱歌走调，但通过后天学习和努力可以调整，最终可能成为歌手。
-- **马云**：中考考两次、高考考三次，最终成为中国首富，说明起点高低不重要，关键在坚持。
-## 梦想清单的制定
-- 梦想可以列清单，实现后打勾，并思考实现所需时间与收获。
-- 梦想可大可小，如考试不犯糊涂、考上重本、成为人民教师等。
+- **航模爱好者何宗发**：通过努力走上更大舞台，受到世界冠军关注，梦想从中国走向世界。
+- **普通人想当歌手**：即使唱歌走调，通过后天学习可以调整，最终可能成为歌手。
+- **马云**：中考考两次、高考考多次，最终成为中国首富，说明起点不重要、坚持重要。
+## 梦想清单
+- **梦想清单**：老师建议学生列出梦想清单，实现后打勾，并思考实现梦想所需时间和收获。
+- **学生梦想示例**：如考630分、健康身体、家人平安、世界和平等。
 # 课堂互动与答疑
-**问**：如果缺少一个条件，梦想还会实现吗？
-**答**：可能因为缺少某一个条件，梦想仍有可能实现；但如果具备所有条件，梦想会更快实现。
-延伸思考：老师强调学习、坚持、行动是梦想条件中必不可少的三个。
+**问**：老师，你的梦想是什么？
+**答**：我的梦想是成为受学生喜爱的有名望的优秀人民教师，目前还在努力过程中。
+**问**：如果梦想实现不了怎么办？
+**答**：我们可以先把自己的梦想调整为考进年级的前百，考进前百之后再定考进前50，一步步往前面去。
 &gt; 不被嘲笑的梦想不是梦想。
 &gt; 机会都是留给有准备的人。
+&gt; 梦想还是要有的，万一实现了呢？
 # 课后任务与学习建议
-老师布置任务：请同学们拿出纸写下自己的梦想清单，可像老师一样列清单，写清第1个、第2个、第3个梦想，实现后打勾，并思考实现梦想所需时间及实现后的收获。写完后每个小组第1个同学收齐交给老师。老师强调写梦想要实在、诚恳，并鼓励相信每一个同学的梦想。</t>
+**作业**：学生写下自己的梦想清单，每个小组第1个同学负责收齐交给老师。
+**提交要求**：梦想清单需写实在、诚恳，可列多个梦想，实现后打勾。
+**学习建议**：老师强调实现梦想需要坚持、努力、勇敢、机会、兴趣、能力、学习等条件，建议学生分阶段调整目标，量力而行。</t>
         </is>
       </c>
       <c r="D10" s="10" t="n">
-        <v>31.7</v>
+        <v>38.5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>9362/1292</t>
+          <t>9362/1560</t>
         </is>
       </c>
     </row>
@@ -3706,58 +3772,62 @@
       <c r="C11" s="4" t="inlineStr">
         <is>
           <t># 全文摘要
-本段文本为《新闻联播》2024年7月14日内容汇总，围绕文化自信与中华民族现代文明建设、赵乐际访俄、夏粮产量创新高、铁路货运增长、快递业提速、油气管网建设、多地降雨应对及国内外新闻等多项议题展开。核心结论包括：习近平总书记强调文化自信，提出‘两个结合’特别是‘第二个结合’的重大意义，2023年10月首次提出习近平文化思想；赵乐际访俄期间双方同意加强立法机构合作；我国夏粮产量达2996亿斤创历史新高；6月国家铁路货运多项指标创历史同期新高；上半年快递业务量超800亿件；油气管网建设提速，‘全国一张网’不断完善。整体呈现我国在文化、经济、基础设施等领域的发展成就，以及国内外重要事件进展。
+本段文本为近期国内外重要新闻与政策进展的汇总播报，围绕文化自信与中华民族现代文明建设、赵乐际访俄、夏粮产量创新高、铁路货运增长、快递业提速、油气管网建设、防汛应对及国内外新闻等多项内容展开。核心结论为：以文化自信筑牢强国复兴精神之基，建设中华民族现代文明；中俄双方同意加强立法机构合作，落实两国元首共识；夏粮首战告捷，为全年粮食丰收奠定坚实基础；铁路货运、快递业、油气管网建设等多项指标创历史新高或显著提升。同时，国内多地积极应对强降雨，国际方面特朗普竞选集会遭未遂刺杀、以军空袭加沙致90人死亡等事件引发关注。
 # 要点梳理
 ## 文化自信与中华民族现代文明建设
-- 习近平总书记强调文化自信，提出‘两个结合’特别是‘第二个结合’的重大意义，指出把中华优秀传统文化精华与马克思主义立场、观点、方法结合起来是中国特色社会主义。
-- 2023年6月，习近平总书记主持召开文化传承发展座谈会，系统论述中华文明五个突出特性；2023年10月，全国宣传思想文化工作会议首次提出习近平文化思想。
-- 《深化文化体制改革实施方案》是中央深改领导小组审议通过的第一个专项小组改革方案；《关于实施中华优秀传统文化传承发展工程的意见》首次以中央文件形式部署文化传承发展。
-- 文化领域供给侧结构性改革推进，文化旅游融合、非遗保护、公共文化服务体系等取得进展，我国成为图书、电视剧、动漫等领域生产大国，数字文化产业成为消费新引擎，电影市场规模屡创新高。
-## 赵乐际对俄罗斯进行正式友好访问
-- 全国人大常委会委员长赵乐际于7月9日至13日对俄罗斯进行正式友好访问，在圣彼得堡会见普京，在莫斯科与马特维延科、沃洛金会谈，并出席中俄议会合作委员会第九次会议。
-- 今年是中俄建交75周年，双方强调加强立法机构合作，落实两国元首共识，深化多层级、多领域交流；普京表示俄中立法机构合作有助于推进双边合作优先议题。
-- 马特维延科表示发展对华关系得到俄社会广泛认同；沃洛金表示俄坚定恪守一个中国原则，反对任何外部势力干涉中国内政。
-- 赵乐际在致辞中提出密切战略协作、交流治国理政经验等五点建议，访问期间向俄无名烈士墓敬献花圈。
-## 我国夏粮产量创历史新高
-- 今年我国夏粮产量达2996亿斤，比2023年增加72.5亿斤，再创历史新高；夏粮单产每亩375.2公斤，小麦单产399.1公斤，比2023年增加10公斤。
-- 中央推进‘藏粮于地、藏粮于技’战略，全国已建成高标准农田10亿多亩，农业农村部启动小麦单产提升三年行动，中央财政首次提前下拨16亿元小麦‘一喷三防’资金。
-- 小麦质量为近年来最好水平，主产区一、二等小麦占比普遍较高，夏粮首战告捷为全年粮食丰收奠定坚实基础。
-## 6月份国家铁路货运多项指标稳定增长
-- 6月份国家铁路发送货物3.32亿吨，完成货运周转量2665亿吨公里，同比分别增长6.1%、5.3%，创历史同期新高；我国铁路货运量、货运周转量等指标稳居世界首位。
-- 化肥农药运量增幅最大，同比增长26.2%；煤炭日均装车量、集装箱、商品汽车、冷链货物发送量均创历史同期新高。
-- 多式联运快车已覆盖各省会城市，铁海快线班列已覆盖全国主要港口；6月中欧班列开行1719列，发送货物18万标箱，同比分别增长15%、11%。
-## 上半年我国快递业发展提速
-- 今年上半年我国快递业务量超800亿件，截至6月30日已达800亿件；快递企业已运行国际航线40余条，面向东南亚开通陆运专线，运行美西海运航线。
-- 每天超1亿多件快递包裹在农村地区流动，5—6月快递日均业务量近5亿件；快递业与制造业融合发展，服务场景不断丰富。
-## 我国油气管网建设提速
-- 预计全年新增管道里程超4000公里；西气东输四线已完成吐鲁番至中卫段主体管道工程建设，投产后年输气能力将提升150亿立方米。
-- 我国主干油气管网约10万公里，输气能力从2020年2230亿立方米增加到3290亿立方米，增幅达48%，天然气‘全国一张网’日供气能力超10亿立方米。
-- 到2025年将初步形成东北、西北、西南及海上四大油气战略通道，建成‘五纵五横’天然气干线管网。
-## 渝川皖等地积极应对降雨天气
-- 重庆28个区县出现暴雨，其中13个区县大暴雨，当地组织工作人员连夜抢险排涝；四川内江出现内涝、滑坡等险情，消防救援人员转移被困群众。
-- 安徽多条河流水位上涨，滁州市全椒县加强巡堤，及时处置堤防渗漏和管涌；水利部针对‘七下八上’防汛关键期逐流域安排防御。
-- 长江1号、2号洪水正在演进，三峡水库15日将迎来洪峰流量45000立方米每秒量级的洪水过程，水利部联合调度嘉陵江亭子口水库等上游干支流水库群，减小三峡水库入库洪峰流量。
+- **理论引领**：习近平总书记强调文化自信，提出“两个结合”特别是“第二个结合”的重大意义；2023年6月文化传承发展座谈会系统论述中华文明五个突出特性，2023年10月全国宣传思想文化工作会议首次提出习近平文化思想。
+- **体制改革**：《深化文化体制改革实施方案》是中央深改领导小组审议通过的第一个专项小组改革方案；《关于实施中华优秀传统文化传承发展工程的意见》首次以中央文件形式部署文化传承发展。
+- **实践成果**：文化领域供给侧结构性改革推进，文化旅游融合、非遗保护、公共文化服务体系健全；深入实施中华文明探源工程，推进国家文化公园建设，落成中国共产党历史展览馆、国家版本馆等；重大文化工程《复兴文库》、“中国历代绘画大系”出版。
+- **创作导向**：深化国有文艺院团改革，树立以人民为中心的创作导向；我国成为图书、电视剧、动漫等领域生产大国，数字文化产业成为消费“新引擎”，电影市场规模屡创新高。
+## 赵乐际访俄
+- **访问行程**：应俄罗斯联邦会议国家杜马主席沃洛金和联邦委员会主席马特维延科邀请，赵乐际于7月9日至13日访俄，在圣彼得堡会见总统普京，在莫斯科与马特维延科、沃洛金分别会谈，并出席中俄议会合作委员会第九次会议。
+- **高层表态**：今年是中俄建交75周年；赵乐际表示中国全国人大愿同俄罗斯联邦会议从立法机构层面落实两国元首重要共识；普京表示俄中立法机构高水平合作有助于推进双边合作优先议题；马特维延科表示发展对华关系得到俄社会广泛认同；沃洛金表示俄坚定恪守一个中国原则，反对任何外部势力干涉中国内政。
+- **会议致辞**：赵乐际出席中俄议会合作委员会第九次会议并致辞，提出密切战略协作、交流治国理政经验、发挥立法机构职能、传承友谊、加强多边协作等五点建议。
+- **其他活动**：访问期间，赵乐际在莫斯科向俄无名烈士墓敬献花圈。
+## 夏粮产量创新高
+- **产量数据**：今年我国夏粮产量达2996亿斤，比2023年增加72.5亿斤，再创历史新高；夏粮单产每亩达到375.2公斤，其中小麦单产达399.1公斤，比2023年增加10公斤。
+- **增产原因**：单产实现恢复性增长是夏粮产量增加的主要原因；全国已建成高标准农田10亿多亩；农业农村部启动小麦单产提升三年行动；中央财政首次提前下拨16亿元小麦“一喷三防”资金。
+- **质量亮点**：小麦质量为近年来最好水平，主产区一、二等小麦占比普遍较高。
+## 铁路货运增长
+- **总体指标**：6月份国家铁路发送货物3.32亿吨，完成货运周转量2665亿吨公里，同比分别增长6.1%、5.3%，创历史同期新高；我国铁路货运量、货运周转量等指标稳居世界首位。
+- **品类亮点**：化肥农药运量增幅最大，同比增长26.2%；煤炭日均装车量、集装箱、商品汽车、冷链货物发送量均创历史同期新高。
+- **网络完善**：多式联运快车已覆盖各省会城市，铁海快线班列已覆盖全国主要港口。
+- **国际联运**：6月份中欧班列累计开行1719列，发送货物18万标箱，同比分别增长15%、11%。
+## 快递业提速
+- **业务总量**：今年上半年我国快递业务量超800亿件，截至6月30日已达800亿件。
+- **国际能力**：快递企业已运行国际航线40余条，面向东南亚开通陆运专线，运行美西海运航线。
+- **农村网络**：每天超1亿多件快递包裹在农村地区流动；5—6月生鲜商品销售旺季，快递日均业务量近5亿件。
+- **融合发展**：快递业与制造业融合发展。
+## 油气管网建设
+- **建设进展**：预计全年新增管道里程超4000公里；西气东输四线已完成吐鲁番至中卫段主体管道工程建设，今年投产后年输气能力将提升150亿立方米；川气东送二线、虎林到长春天然气管道等工程加速推进。
+- **供应能力**：我国主干油气管网约10万公里；输气能力从2020年2230亿立方米增加到3290亿立方米，增幅达48%；天然气“全国一张网”日供气能力超10亿立方米。
+- **规划目标**：到2025年，将初步形成东北、西北、西南以及海上四大油气战略通道，建成“五纵五横”的天然气干线管网。
+## 防汛应对
+- **重庆**：九龙坡、江北等28个区县出现暴雨，其中沙坪坝、江津等13个区县大暴雨，当地组织工作人员连夜抢险排涝。
+- **四川**：暴雨造成内江部分地区出现内涝、滑坡等险情，消防救援人员紧急出动转移被困群众。
+- **安徽**：多条河流水位上涨，滁州市全椒县工作人员加强巡堤，处置堤防渗漏和管涌。
+- **水利部部署**：针对“七下八上”防汛关键期逐流域安排防御；长江1号、2号洪水正在演进，三峡水库15日将迎来洪峰流量45000立方米每秒量级的洪水过程；联合调度嘉陵江亭子口水库等上游干支流水库群，减小三峡水库入库洪峰流量。
 ## 国内联播快讯
-- 北京上半年320个市区重大项目全部开工，总投资超过4000亿元，包括丽泽数字金融科技示范园、温榆河生态治理工程等。
-- 燕矶长江大桥北岸主塔封顶，主跨1860米，上层高速公路、下层城市快速路，连接湖北鄂州和黄冈，建成后将成为鄂东空铁、空陆联运立体交通运输体系的重要过江通道。
-- 第二十三届环青海湖国际公路自行车赛收官，22支车队154名运动员参赛，决出个人总成绩、爬山积分、团体总积分等5个奖项冠军。
-- 内蒙古第34届草原那达慕开幕，主题‘相约草原遇见那达慕’，持续到8月底，开展体育赛事、文艺表演、美食品鉴、非遗展示等活动。
-- ‘中非儿童手拉手’活动在京启动，来自纳米比亚、南非、中非、索马里、乌干达五国儿童代表将在北京、河南参观访问。
+- **北京项目**：上半年320个市区重大项目全部开工，总投资超过4000亿元，包括丽泽数字金融科技示范园、温榆河生态治理工程等。
+- **燕矶长江大桥**：北岸主塔封顶，主跨1860米，上层高速公路，下层城市快速路，连接湖北鄂州和黄冈。
+- **环湖赛**：第二十三届环青海湖国际公路自行车赛收官，22支车队154名运动员参赛，决出5个奖项冠军。
+- **那达慕**：内蒙古第34届草原那达慕开幕，主题“相约草原遇见那达慕”，持续到8月底。
+- **中非儿童手拉手**：活动在京启动，来自纳米比亚、南非、中非、索马里、乌干达五国儿童代表将在北京、河南参观访问。
 ## 国际新闻
-- 多国人士高度评价中国全面深化改革扩大开放成就，关注即将召开的二十届三中全会，认为中国为世界提供更广阔的市场和发展机遇。
-- 美联邦调查局称前总统特朗普在竞选集会遭未遂刺杀，特朗普右耳中枪受伤，一名观众死亡、两名重伤，枪手为20岁左右男性，来自宾夕法尼亚州，作案动机待查明。
-- 以军空袭加沙地带马瓦西地区致90人死亡、约300人受伤，巴勒斯坦谴责以军违反国际法，约旦、卡塔尔、埃及等发表声明谴责。
-- 以军袭击黎巴嫩多个边境村镇，黎真主党武装打击以军集结地和情报设施；叙利亚首都大马士革遭空袭，1名政府军士兵死亡、3人受伤。
-- 俄称使用‘伊斯坎德尔-M’导弹打击哈尔科夫方向乌军军用火车停车点，摧毁20件装备；乌称在波克罗夫斯克方向击退俄军17次进攻。
-- 加拿大东北部林火蔓延，过火面积100平方公里，9600人被疏散，消防人员无法继续使用灭火飞机；加拿大正应对500多起活跃林火，超400起失控。</t>
+- **国际评价**：多国人士高度评价中国全面深化改革扩大开放成就。
+- **美国**：美联邦调查局称前总统特朗普在竞选集会遭未遂刺杀，枪手为20岁左右男性，来自宾夕法尼亚州，作案动机待查明。
+- **巴以冲突**：以军空袭加沙地带马瓦西地区致90人死亡，约300人受伤，巴勒斯坦谴责以军违反国际法；以军袭击黎巴嫩多个边境村镇，黎真主党武装打击以军集结地。
+- **叙利亚**：首都大马士革遭空袭，造成1名政府军士兵死亡、3人受伤。
+- **俄乌冲突**：俄称打击乌军列车点，乌称击退俄军进攻。
+- **加拿大林火**：东北部林火蔓延，过火面积100平方公里，拉布拉多城9600人被疏散，加拿大正应对500多起活跃林火，超400起失控。</t>
         </is>
       </c>
       <c r="D11" s="10" t="n">
-        <v>71.3</v>
+        <v>78.5</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>7755/2745</t>
+          <t>7755/2930</t>
         </is>
       </c>
     </row>
@@ -3996,58 +4066,59 @@
       <c r="C12" s="4" t="inlineStr">
         <is>
           <t># 课程概况
-本节课为初中光学复习课，共三讲中的第一讲，主题涵盖光的直线传播、光的反射定律、镜面反射与漫反射、平面镜成像及球面镜应用，并讲解相关习题。光在均匀介质中沿直线传播，实例包括三点一线、激光准直、小孔成像、日食月食、影子的形成；小孔成像成倒立、实像，放大缩小不一定，与孔形状无关。光速在真空中为3×10^8米/秒，空气中约2.99×10^8米/秒，水中约为真空中的3/4，玻璃中约为2/3；一束激光从地球射到月球表面时间1.25秒，距离为3.75×10^8米。光的反射定律：反射光线、入射光线和法线在同一平面内，反射光线和入射光线分居法线两侧，反射角等于入射角；法线是垂直于镜面的辅助线，是虚线，不存在。光垂直射到镜面上，入射角和反射角都是0度；反射光线与平面镜夹角40度时，入射角为50度。作图步骤为先画法线，再根据反射角等于入射角画入射或反射光线。镜面反射是一束平行光射到光滑表面，反射光线平行，人眼在特定位置才能看到；漫反射是表面凹凸不平，反射光线射向各个方向，人眼在任何位置都能看到。生活中大多数反射是漫反射，如黑板、电影银幕；黑板反光看不清粉笔字是镜面反射。雨后夜晚，迎着月光走，发亮处是水潭；背着月光走，发暗处是水潭。平面镜成像原理是光的反射定律，成像是虚像，特点为正立、等大、虚像，像与物连线垂直镜面，像到镜面距离等于物到镜面距离。实验用玻璃板代替平面镜便于确定像的位置，用刻度尺比较像与物到镜面的距离，用两段相同蜡烛比较像与物大小；光屏不能接收到虚像。玻璃板与水平面不垂直会导致像距测量不准确，玻璃板有厚度，两个面反射会形成两个像。视力表距镜子3.5米，人距镜子1.5米时，看虚像距离为5米；人站在平面镜前1米，人与像距离2米。凸面镜对光线起发散作用，成像是正立、缩小的虚像，应用于汽车后视镜、丁字路口拐弯处；凹面镜对光线起会聚作用，应用于手电筒、汽车前大灯、探照灯、耳鼻喉科检查、太阳灶。阿基米德利用凹面镜汇聚光线烧毁敌人帆船；玻璃幕墙形成凹面会汇聚光线，可能烧死树木、引燃电线，造成光污染。
+本节课为初中光学复习课，共三讲中的第一讲，系统复习光的直线传播、光的反射定律、镜面反射与漫反射、平面镜成像及球面镜应用。课程首先讲解光源定义（自然光源如太阳、萤火虫，人造光源如火把、蜡烛、煤油灯、电灯）与光线概念（带箭头的直线，是物理模型而非真实存在），并强调光在均匀介质中沿直线传播，实例包括三点一线、激光准直、小孔成像、日食月食、影子形成。小孔成像特点为倒立、实像，放大缩小不一定，与孔形状无关；日食时月球在中间，月食时地球在中间。光速在真空中为3×10^8米/秒，空气中略慢，水中约为真空中的3/4，玻璃中约为2/3。例题：激光从地球到月球1.25秒，距离为3.75×10^8米。光的反射定律内容为三线共面、分居两侧、反射角等于入射角；法线是辅助线，垂直于镜面，不存在，画虚线。镜面反射是平行光射到光滑表面，反射光平行；漫反射是平行光射到凹凸不平表面，反射光向各个方向，两者都遵守光的反射定律。平面镜成像原理是光的反射定律，成像是正立、等大的虚像，像与物连线垂直镜面，像距等于物距。球面镜分为凸面镜和凹面镜，凸面镜对光线起发散作用，成像是正立、缩小的虚像，应用于汽车后视镜、丁字路口拐弯镜；凹面镜对光线起会聚作用，应用于手电筒、汽车前大灯、探照灯、耳鼻喉科检查镜、太阳灶。
 # 核心知识点梳理
 ## 光的直线传播
 - **光源**：自身能够发光的物体，分为自然光源（如太阳、萤火虫）和人造光源（如火把、蜡烛、煤油灯、电灯）。
-- **光线**：用一条带有箭头的直线代表，是物理模型，不是真实存在的。
-- **光在均匀介质中沿直线传播**：实例包括三点一线、激光准直、小孔成像、日食月食、影子的形成。
-- **小孔成像**：成倒立、实像，放大缩小不一定，与孔形状无关；生活中如树荫下的光斑。
-- **日食与月食**：日食时太阳、月球、地球在同一直线上，月球在中间；月食时地球在中间。
-- **光速**：真空中为3×10^8米/秒，空气中约2.99×10^8米/秒，水中约为真空中的3/4，玻璃中约为2/3。
-- **计算**：一束激光从地球射到月球表面时间1.25秒，距离为3.75×10^8米。
-- **雷电现象**：先看到闪电后听到雷声，因为光速比声速快。
+- **光线**：用一条带有箭头的直线代表光线，是物理模型，不是真实存在。
+- **光在均匀介质中沿直线传播**：实例包括三点一线、激光准直、小孔成像、日食月食、影子形成。
+- **小孔成像**：成倒立、实像，放大缩小不一定，与孔形状无关；生活中大杨树底下的光斑就是太阳透过树叶缝隙形成的小孔成像。
+- **日食**：太阳、月球、地球在同一直线，月球在中间，分为日全食、日偏食、日环食。
+- **月食**：太阳、地球、月球在同一直线，地球在中间，月全食是月球完全在地球阴影中，月偏食是月球部分在阴影中。
+- **光速**：真空中为3×10^8米/秒，空气中略慢，水中约为真空中的3/4，玻璃中约为2/3。
+- **例题**：激光从地球到月球1.25秒，距离为3.75×10^8米。
 ## 光的反射定律
-- **内容**：反射光线、入射光线和法线在同一平面内；反射光线和入射光线分居法线两侧；反射角等于入射角。
-- **法线**：垂直于镜面的辅助线，是虚线，不存在。
-- **垂直入射**：光垂直射到镜面上，入射角和反射角都是0度。
-- **角度计算**：反射光线与平面镜夹角40度时，入射角为50度。
-- **作图步骤**：先画法线，再根据反射角等于入射角画入射或反射光线。
+- **反射定律内容**：反射光线、入射光线、法线在同一平面内（三线共面）；反射光线和入射光线分居法线两侧；反射角等于入射角。
+- **法线**：辅助线，垂直于镜面，不存在，画虚线。
+- **垂直入射**：入射角和反射角均为0度。
+- **作图步骤**：先画法线，再根据反射角等于入射角画反射或入射光线，保留作图痕迹。
+- **例题**：反射光线与平面镜夹角40度，入射角为50度。
 ## 镜面反射与漫反射
-- **镜面反射**：一束平行光射到光滑表面，反射光线平行，人眼在特定位置才能看到。
-- **漫反射**：表面凹凸不平，反射光线射向各个方向，人眼在任何位置都能看到。
-- **应用**：生活中大多数反射是漫反射，如黑板、电影银幕；黑板反光看不清粉笔字是镜面反射。
-- **雨后夜晚**：迎着月光走，发亮处是水潭；背着月光走，发暗处是水潭。
+- **镜面反射**：平行光射到光滑表面，反射光平行，人眼在特定位置才能看到。
+- **漫反射**：平行光射到凹凸不平表面，反射光向各个方向，人眼在任何位置都能看到。
+- **应用**：生活中大多数反射是漫反射，如黑板、电影银幕。
+- **共同点**：镜面反射和漫反射都遵守光的反射定律。
+- **例题**：雨后夜晚，迎着月光走，亮处是水潭；背着月光走，暗处是水潭。
 ## 平面镜成像
-- **原理**：光的反射定律，成像是虚像。
-- **特点**：正立、等大、虚像，像与物连线垂直镜面，像到镜面距离等于物到镜面距离。
-- **实验**：用玻璃板代替平面镜便于确定像的位置；用刻度尺比较像与物到镜面的距离；用两段相同蜡烛比较像与物大小。
+- **成像原理**：光的反射定律，成像是虚像。
+- **成像特点**：正立、等大、虚像，像与物连线垂直镜面，像距等于物距。
+- **实验器材**：用玻璃板代替平面镜，便于确定像的位置；用刻度尺比较像与物到镜面距离；用两段相同蜡烛比较像与物大小。
 - **光屏**：不能接收到虚像。
-- **误差原因**：玻璃板与水平面不垂直会导致像距测量不准确；玻璃板有厚度，两个面反射会形成两个像。
-- **应用**：视力表距镜子3.5米，人距镜子1.5米时，看虚像距离为5米；人站在平面镜前1米，人与像距离2米。
+- **实验误差原因**：玻璃板与水平面不垂直，或玻璃板有厚度导致两个像。
+- **例题**：视力表距镜子3.5米，人距镜子1.5米可看到5米处虚像；平面镜前一米处，人与像距离2米。
 ## 球面镜及其应用
-- **凸面镜**：对光线起发散作用，成像是正立、缩小的虚像，应用于汽车后视镜、丁字路口拐弯处。
-- **凹面镜**：对光线起会聚作用，应用于手电筒、汽车前大灯、探照灯、耳鼻喉科检查、太阳灶。
-- **历史案例**：阿基米德利用凹面镜汇聚光线烧毁敌人帆船。
-- **光污染**：玻璃幕墙形成凹面会汇聚光线，可能烧死树木、引燃电线。
+- **凸面镜**：对光线起发散作用，成像是正立、缩小的虚像，应用于汽车后视镜、丁字路口拐弯镜。
+- **凹面镜**：对光线起会聚作用，应用于手电筒、汽车前大灯、探照灯、耳鼻喉科检查镜、太阳灶。
+- **光污染**：凹面镜会聚光线可能引起光污染，如玻璃幕墙烧死树木、电线自燃。
 # 课堂互动与答疑
-**问**：光垂直射到镜面上，入射角是多少度？
-**答**：入射角是0度，因为入射角是入射光线与法线的夹角，垂直入射时夹角为0度。
-**问**：为什么用玻璃板代替平面镜做实验？
-**答**：因为玻璃板既能反射成像，又能透过光线，便于移动后面的蜡烛来确定像的位置。
-**问**：为什么玻璃板会看到两个像？
-**答**：因为玻璃板有厚度，两个面都能发生反射，形成两个像。
-&gt; 教师提醒："光线是物理模型，不是真实存在的。"
+**问**：为什么研究反射时要引进法线？
+**答**：法线是辅助线，垂直于镜面，不存在，画虚线。引进法线是为了后面研究折射做准备，如果只研究反射，用入射光线与镜面的夹角也可以，但折射时就不行了。
+**问**：小孔成像的像一定是倒立的吗？
+**答**：小孔成像一定成倒立的实像，但放大缩小不一定，与孔的形状无关。
+&gt; 光线是真实存在的吗？我画一个写上它实际上是一个物理模型，你不能说老师我一开灯我们家屋子一下亮了，我感觉好多处箭冲我飞过来了。
+&gt; 光在均匀介质中沿直线传播没有问题，但如果这个光是穿过整个大气层过来的，你就会发现哪俩字就不成立了。
+&gt; 咱们中国人以前的习惯，就是天一黑大家就睡觉了。
 # 课后任务与学习建议
-教师布置了练习第1~5题、第10~11题、第13~17题、第19~24题等作为课堂练习，并讲解了答案。未提及课后作业的具体提交要求。复习重点包括：光在均匀介质中沿直线传播及其实例、光的反射定律、镜面反射与漫反射的区别、平面镜成像特点及实验、球面镜的应用。学习建议：可在家用激光笔、纸杯、蜡烛等材料做小孔成像和平面镜成像实验，加深理解。</t>
+**复习重点**：光在均匀介质中沿直线传播的实例（三点一线、激光准直、小孔成像、日食月食、影子形成）；光的反射定律（三线共面、分居两侧、反射角等于入射角）；镜面反射与漫反射的区别及共同点；平面镜成像特点（正立、等大、虚像）及实验注意事项；凸面镜与凹面镜对光线的作用及应用。
+**学习建议**：建议同学们在家用激光笔、纸杯、蜡烛等器材动手做小孔成像和平面镜成像实验，加深理解；作图题注意先画法线，保留作图痕迹；注意区分易混点，如垂直入射时入射角为0度而非90度，平面镜成的是正立等大的虚像而小孔成的是倒立的实像。</t>
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>56.1</v>
+        <v>56.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>25691/2481</t>
+          <t>25691/2341</t>
         </is>
       </c>
     </row>
@@ -4158,58 +4229,72 @@
       <c r="C13" s="4" t="inlineStr">
         <is>
           <t># 课程概况
-本次课程为《电气工程基础》导论，是电气工程专业入门课。课程教学目的有二：一是掌握电力系统发电、输电、配电、用电四个典型环节的构成、工作原理及与系统整体的关系，建立电力系统整体概念；二是掌握电力系统分析、设计、运行、管理方面的基础理论、技术与计算方法。前修课程要求电路理论与电机学知识，特别是变压器和同步电机，有欠缺的同学需自行补充；后续重要课程为电力系统分析、电力系统机电保护、电力系统自动化、高电压技术。第一章是概念最多、最重要的章节，要求掌握电力系统、电力网、动力系统、变电站等基本概念，理解电力系统特点及要求，掌握电能质量指标及国家标准规定范围，了解常用接地方式特别是中性点接地方式。课程还梳理了交直流输电发展史，讲解了三相交流输电优势、电力系统形成过程，以及电力系统、电力网、动力系统的定义与电网分类。
+本次课程为《电气工程基础》导论，是电气专业入门课。课程教学目的有二：一是掌握电力系统发电、输电、配电、用电四个典型环节的构成、工作原理及与系统整体的关系，建立整体概念；二是掌握电力系统分析、设计、运行、管理的最基础理论、技术与计算方法。前修课程为电路理论、电机学，尤其对变压器和同步电机知识要求较高；后续课程包括电力系统分析、电力系统继电保护、电力系统自动化、高电压技术。第一章是概念最多、最重要的章节，涵盖电力系统、电力网、动力系统、变电站等基本概念，电力系统特点及要求、电能质量指标、中性点接地方式等内容，并梳理了交直流输电发展简史、三相交流输电优势、电力系统形成过程与定义、电网分类及变电站分类。
 # 核心知识点梳理
 ## 课程定位与教学目标
-- 电气工程基础是专业课入门课，教学目的解决两个问题：掌握电力系统**发电、输电、配电、用电**四个典型环节的构成、工作原理及与系统整体关系；掌握电力系统分析、设计、运行、管理方面的基础理论、技术与计算方法。
-- 前修课程要求：电路理论、电机学知识，特别是**变压器和同步电机**相关知识要求较高，有欠缺的同学需自行补充。
-- 后续重要课程：电力系统分析、电力系统机电保护、电力系统自动化、高电压技术。
+- **课程性质**：电气工程基础是进入专业课的第一门课，属专业入门课。
+- **教学目标一**：掌握电力系统**发电、输电、配电、用电**四个典型环节的构成、工作原理及与系统整体的关系，建立整体概念。
+- **教学目标二**：掌握电力系统分析、设计、运行、管理的最基础理论、技术与计算方法。
+- **前修课程**：电路理论、电机学，特别是**变压器和同步电机**知识要求较高，有欠缺的同学需自行补充。
+- **后续课程**：电力系统分析、电力系统继电保护、电力系统自动化、高电压技术。
 ## 第一章学习内容与难点
-- 第一章是概念最多、最重要的章节，要求掌握：电力系统若干基本概念（电力系统、电力网、动力系统、变电站）；理解电力系统特点及由此引起的设计运行基础理论；理解对电力系统的要求；掌握电能质量指标及国家标准规定范围；了解常用接地方式，特别是中性点接地方式的不同特点。
-- 三个学习难点：电力系统特点引出的基本原理（如电能不能大量储存决定有功无功动态平衡）⭐；额定电压规定繁杂需搞清楚 ⭐；各种中性点接地方式影响后续章节且学习困难 ⭐。
-- 学习方法建议：注意概念内涵外延并适当实际；从特点要求出发、从基础原理推导，不记结论；寻找额定电压规定间基本规律；比较不同中性点接地方式特点。
-## 电力发展简史（直流与交流输电）
-- 直流输电发展：福泰勒用2000米导线连接瓦斯发电机拖动直流发电机和电动机，证明直流输电可行；1874年俄国工程师在彼得堡建成4.5公里直流输电线路，传输功率4.5千瓦；1882年法国德普勒架设首条57公里直流试验线路，采用电报线，首端电压343伏、末端850伏，输送功率200瓦，损耗78%；1883年德普勒从法国南部进行14公里输电试验，输送功率1.1千瓦，从瓦利尔书店到巴黎56公里损耗55%；1882年10月英国科学家发明直流三线制系统，外线与中线间电压110伏，两外线间220伏，后扩展到5根线形成直流无限制系统。
-- 直流输电限制：电压等级低时损耗大、电压降落快，提高电压困难，制造大容量高压直流发电机困难，限制远距离大容量输电。
-- 19世纪末法国方剑将多台直流发电机串联提高电压，将75千瓦电力送75千米；20世纪初瑞典科学家装短路器使任意发电机投切不停电，此后20多年建15条直流输电线路，最大规模1906年法国慕尼黑水电厂到里昂180公里、57千伏、4700千瓦；1927年改建成260公里、125千伏、19000千瓦，接入两座水电站。
-- 直流输电制约因素多：设备复杂、运行方式复杂、造价高、可靠性差。
-- 交流输电发展：英国法拉第电磁感应原理；美国亨利用多线圈做原边、少线圈做副边实现高电压感应低电压，是变压器前身；1876年俄国科学家发明单相变压器用于照明；法国和英国科学家联合将多台变压器串联到输电线路，负荷变化时输电电压受干扰；1883年美国特斯拉制造感应电机；1885年匈牙利科学家设计多台变压器并联运行方式。
-- 威斯汀豪斯与爱迪生交直流电力战争：爱迪生和凯尔文主张直流电，理由为效率高、交流电有危险性（购买威斯汀豪斯交流发电机卖给监狱给死刑犯执行死刑证明危险性）；威斯汀豪斯和特斯拉主张交流电，因易用变压器升压降压减少电能损失。
-- 1886年威斯汀豪斯在美国麻省进行1000米1.2千米30千伏交流输电示范，又在意大利建成17英里、2千伏高压输电线路；1886年俄国科学家发明三相交流电、三相交流输电和三相异步电动机。
-- 交直流电力战争标志：法国到德国交流输电线路，从水电厂安装三相发电机和两台升压变压器，升压后送到德国，在法兰克福建两座降压变，一座供展览会照明，另一座供100马力三相异步电动机用于人工瀑布离心泵。
-- 交流输电进展：1898年发明真实绝缘子，美国加利福尼亚输电电压等级提高到33千伏；1906年发明悬式绝缘子，建成110千伏高压输电；1912年发现电晕临界电压与导线直径成比例增加，铝线和刚性铝绞线开始应用，美国建成154千伏线路；1923年均压阀技术应用，建成220千伏线路；1936年美国287千伏线路投运；1952年瑞典建成380千伏线路，第一次采用分裂导线；1956年苏联400千伏双回线路投入运行；1965年加拿大建成735千伏输电系统；1969年美国765千伏线路并入电网；1985年苏联特高压线路1150千伏投运，后降压到500千伏运行。
-- 国内投运：224千伏1941年投运，330千伏1972年投运，500千伏1981年投运，2009年1000千伏投运（交流特高压第一次）。
-- 直流输电复兴：交流大电网稳定问题突出，直流在联网中优势显露，用于电网间连接。1954年瑞典本土与哥特兰岛建成世界第一个工业采用海底电缆，电压等级100千伏、96公里，采用汞弧阀；1970年扩建50千伏、1万千瓦晶闸管换流阀试验工程；1972年世界第一个晶闸管换流阀背靠背直流工程在加拿大投运。
-- 中国直流输电：第一个直流输电工程连接舟山群岛与浙江定海电网；第二个是1989年葛上直流（葛洲坝电厂到上海），±500千伏；今年6月投运云广直流±800特高压直流工程。
-## 三相交流输电优势与电力系统形成
-- 交流指ABC三相对称系统，具有三个优点：易于产生旋转磁场，三相电动机容易做驱动；瞬时功率恒定不随时间变化；输电线路导线量（金属消耗量）最少。
-- 除室内配电等小功率供电采用单相交流外，其它场合基本采用三相交流；国内电力系统大多数高压、超高压、特高压输电采用三相交流，联网才用直流。
-- 三相三线制传输效率最高，金属消耗量在同等功率和功率因数下最小。
-- 电力系统形成过程：最早单台发电机向附近负荷供电，可靠性差；后把多台发电机连接起来提高可靠性，但导线有电阻和电抗，产生电压损耗和功率损耗，输电线路不能太长；解决办法是提高电压，电流减小，损耗和电压降落减小，距离变长；交流升压用变压器，一侧升压另一侧降压。
-- 电力系统形成后好处：多台发电机供电，一台停机不影响；能装大机组，供电范围大，带来经济效益。
-- 输电距离很长时（如湖北送电华东、云贵送电两广），中间装变电站降压供电，并可引接部分负荷；输电距离长出现稳定问题，可装变电站采取设备调整。
-- 现代电力系统特征：发电机发电，经升压变压器升压，通过输电线路传输到负荷中心，再降压给用电设备。
-## 电力系统、电力网、动力系统定义与电网分类
-- 电力系统定义：由发电机、变压器、输电线路和用电设备构成的整体，完成电能生产、输送、分配、消耗四个职能，有发电、输电、配电、用电四个环节。
-- 电力网定义：电力系统中去除发电机和用电设备的部分，即变压器和输电线路构成的网络。
-- 动力系统定义：电力系统基础上加上发电厂动力部分（火电厂的锅炉、汽机、煤炭输送处理系统；水电厂的水轮机、水坝、水库等）。
-- 行业常用概念：电力网和电力系统，动力系统很少说。
-- 电网分类：地方电力网（电压等级110千伏及以下，早期定义35千伏及以下，供电半径20~50公里）；区域电力网（电压等级110、220千伏和少量500千伏，供电半径超过50公里，联系较多发电厂和负荷中心）；超高压远距离输送网络（电压等级500千伏或1000千伏，东北有330千伏，任务是把发电厂电能送到负荷中心，距离很远，构成跨省跨地区大型电力系统）。
-- 实例：武汉电网属于地方电力网，主要供电电压110千伏和35千伏，少数220千伏，供电半径50公里以内；华中网是典型区域网；葛上直流、三峡到上海输电线路是连接华中与华东的超高压远距离输电网络；特高压系统从山西晋东南到湖北荆门，跨三个省，连接华北电网和华中电网，属于超高压远距离输送网络。
-- 电压等级随电网发展提高，各级电网电压等级会变化，一般提高。
-- 变电站分类方法：按最高电压等级分类（如华工变电站10千伏变380伏，是10千伏变电站；关山变电站最高电压220千伏，是220千伏变电站；凤凰山变电站最高电压500千伏，是500千伏变电站）；按主要功率流通方向分类（大部分功率从高压侧流向低压侧为降压变电站，发电厂中大部分功率从低压侧升压到高压侧为升压变电站）。
+- **学习内容**：电力系统、电力网、动力系统、变电站等基本概念；电力系统特点及引起的基础理论；对电力系统的要求；电能质量指标及国家标准规定范围；常用接地方式，特别是**中性点接地方式**。
+- **难点一** ⭐：电能不能大量储存，决定电力系统**有功功率和无功功率的动态平衡**问题。
+- **难点二** ⭐：电力系统**额定电压的规定**繁杂，需注意搞清。
+- **难点三** ⭐：各种**中性点接地方式**直接影响后续多个章节内容，学习较困难。
+- **学习方法**：注意概念的内涵和外延；从电力系统特点要求出发、从最基础原理推导，*不要只记结论*；寻找额定电压规定之间的基本规律；比较不同中性点接地方式的特点。
+## 电力发展简史
+- **直流输电起步**：福泰勒用**2000米**导线连接瓦斯发电机，拖动直流电动机和水泵，证明直流远距离输电可行。
+- **1874年**：俄国工程师在彼得堡建成**4.5公里**直流输电线路，传输功率**4.5千瓦**。
+- **1882年**：法国德普勒架设**57公里**直流试验线路，首端电压**343伏**、末端**850伏**，输送功率**200瓦**，损耗**78%**。
+- **1883年**：德普勒从法国南部进行**14公里**输电试验，输送功率**1.1千瓦**，从瓦利尔书店到巴黎**56公里**损耗**55%**。
+- **1882年10月**：英国科学家发明直流**三线制系统**，外线与中线电压**110伏**、外线间**220伏**，后扩展至5线。
+- **19世纪末**：法国方剑串联多台直流发电机，将**75千瓦**电力送**75千米**。
+- **20世纪初**：瑞典科学家装短路器，20多年建**15条**直流线路；最大为**1906年**法国慕尼黑水电厂到里昂**180公里**、**57千伏**、**4700千瓦**；**1927年**改建**260公里**、**125千伏**、**19000千瓦**。
+- **交流输电基础**：法拉第电磁感应原理；美国亨利用多线圈做变压器前身；**1876年**俄国科学家发明单相变压器；**1883年**特斯拉制造感应电机；**1885年**匈牙利科学家设计多台变压器并联运行。
+- **1886年**：威斯汀豪斯在美国麻省进行**1.2千米**、**30千伏**交流输电示范，又在意大利建成**17英里**、**2千伏**线路；同年俄国科学家发明三相交流电和三相异步电动机。
+- **交直流电力战争**：爱迪生与凯尔文主张直流电，称其效率高、交流电有危险性，曾购买威斯汀豪斯交流发电机卖给监狱执行死刑；威斯汀豪斯与特斯拉主张交流电，因易用变压器升压降压、减少电能损失。
+- **标志性线路**：从法国到德国的交流输电线路，水电厂装三相发电机和升压变压器，法兰克福建两座降压变，一座供展览照明，一座供**100马力**三相异步电动机带动离心泵做人工瀑布。
+- **高压输电发展**：**1898年**针式绝缘子，美国加利福尼亚**33千伏**；**1906年**悬式绝缘子，建成**110千伏**；**1912年**发现电晕临界电压与导线直径成比例，铝线和钢芯铝绞线应用，美国建成**154千伏**；**1923年**均压阀技术，建成**220千伏**；**1936年**美国**287千伏**投运；**1952年**瑞典**380千伏**首次采用分裂导线；**1956年**苏联**400千伏**双回线路；**1965年**加拿大**735千伏**；**1969年**美国**765千伏**；**1985年**苏联**1150千伏**特高压投运后降压至**500千伏**。
+- **国内发展**：**220千伏**1941年投运，**330千伏**1972年，**500千伏**1981年，**1000千伏**2009年投运（交流特高压标志性成果）。
+- **直流输电复兴**：**1954年**瑞典本土与哥特兰岛建成世界第一个工业海底电缆，**100千伏**、**96公里**，汞弧阀；**1970年**扩建**50千伏**、**1万千瓦**晶闸管换流阀试验工程；**1972年**世界第一个晶闸管换流阀背靠背直流工程在加拿大投运。
+- **中国直流工程**：第一个直流输电工程连接舟山群岛与浙江定海；**1989年**葛上直流（葛洲坝到上海）**±500千伏**；今年**6月**云广直流**±800**特高压直流投运。
+- **推荐阅读**：教师推荐三本书供学生进一步阅读，作为电气专业学生应了解电力发展基本史。
+## 三相交流输电优势
+- **三相优点一**：易于产生旋转磁场，三相电动机容易做驱动。
+- **三相优点二**：瞬时功率恒定，不随时间变化。
+- **三相优点三**：输电线路导线金属消耗量最少。
+- **应用现状**：除室内配电等小功率供电采用单相交流外，其他场合基本采用三相交流；国内大多数高压、超高压、特高压输电采用三相交流，联网才用直流。
+- **三相三线制**：传输效率最高，同等功率和功率因数下金属消耗量最小，目前仍采用这种输电方式。
+## 电力系统的形成与定义
+- **形成过程**：从单机向附近负荷供电，到多机并联提高可靠性，再到升压输电扩大距离。
+- **输电线路参数**：导线有电阻和电抗，传输功率时产生电压损耗和功率损耗，距离不能太长。
+- **升压原理**：传输有功功率一定时，电压升高则电流减小，线路有功损耗和电压降落减小，距离可变长；交流采用变压器升压。
+- **电力系统定义**：发电机、变压器、输电线路和用电设备构成的整体，完成电能**生产、输送、分配、消耗**四个职能。
+- **电力网定义**：电力系统中去除发电机和用电设备的部分，即变压器和输电线路构成的网络。
+- **动力系统定义**：电力系统加上发电厂动力部分（火电锅炉汽机煤炭系统，水电水轮机水坝水库）。
+- **行业常用**：电力网和电力系统两个概念，动力系统很少说。
+## 电网分类与变电站分类
+- **地方电力网**：向固定地方供电，电压等级**110千伏及以下**（早期定义35千伏及以下），供电半径**20-50公里**。
+- **区域电力网**：电压等级**110、220千伏**和少量**500千伏**，供电半径超过**50公里**，联系较多发电厂和负荷中心。
+- **超高压远距离输送网络**：电压等级**500千伏或1000千伏**（东北有330千伏），任务是把发电厂电能送到负荷中心，构成跨省跨地区大型电力系统。
+- **实例**：武汉电网属地方电力网，主要供电电压110和35千伏，少数220；华中网是典型区域网；葛上直流、三峡到上海输电线路属超高压远距离输送网络；特高压系统从山西晋东南到湖北荆门，跨三省，连接华北和华中电网。
+- **按电压等级分类**：华工变电站**10千伏**，关山变电站**220千伏**，凤凰山变电站**500千伏**。
+- **按功率流向分类**：大部分功率从高压侧流向低压侧为**降压变电站**；发电厂内从低压侧升压到高压侧为**升压变电站**。
 # 课堂互动与答疑
 未提及
 # 课后任务与学习建议
-教师未布置具体作业，但强调第一章是重点内容，要求掌握电力系统、电力网、动力系统、变电站等基本概念，理解电力系统特点及要求，掌握电能质量指标及国家标准规定范围，了解常用接地方式特别是中性点接地方式。三个学习难点需重点攻克：电力系统特点引出的基本原理（如电能不能大量储存决定有功无功动态平衡）、额定电压规定、各种中性点接地方式。学习方法建议：注意概念内涵外延并适当实际；从特点要求出发、从基础原理推导，不记结论；寻找额定电压规定间基本规律；比较不同中性点接地方式特点。教师推荐三本书供学生进一步阅读，并建议学生了解电力发展的基本发展史。</t>
+**课后任务**：教师布置学生课后阅读电力发展史相关内容，作为电气专业学生应了解电力发展的基本发展史，并推荐三本书供学生阅读。
+**复习重点**：第一章是概念最多、最重要的章节，需掌握电力系统、电力网、动力系统、变电站等基本概念，理解电力系统特点及引起的基础理论，掌握电能质量指标及国家标准规定范围，了解常用接地方式特别是中性点接地方式。
+**学习建议**：对基本概念注意内涵和外延并适当记忆；从电力系统特点要求出发、从最基础原理推导，*不要只记结论*；注意寻找额定电压规定之间的基本规律；比较不同中性点接地方式的特点。</t>
         </is>
       </c>
       <c r="D13" s="10" t="n">
-        <v>96.3</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11163/4006</t>
+          <t>11163/3859</t>
         </is>
       </c>
     </row>
@@ -4290,32 +4375,41 @@
       <c r="C14" s="4" t="inlineStr">
         <is>
           <t># 知识主题与概述
-本视频围绕Stack Exchange上关于调和级数∑1/n收敛性的经典问题展开，皮卡以评论者身份逐一点评网友的证明方法。他首先从高中数学的前n项和定义出发，解释级数收敛与发散的标准：若所有部分和Sn小于某个固定上界a则收敛，若部分和能超过任意给定的数则发散。随后他介绍了两种主要证明流派：第一种通过分组估计，每组和大于1/2，从而证明部分和无上界；第二种通过证明H_n &gt; log(n+1)来证明发散，因为log无上界。皮卡还补充了柯西凝聚判别法、积分估计和Stolz定理等工具，并批评某些证明是事后凑出来的、故弄玄虚，妨碍理解。整体逻辑框架是从基础定义出发，逐步剖析不同证明思路的优劣，最终强调自然、可理解的证明方法。
+本视频评论 Stack Exchange 上关于调和级数 ∑1/n 收敛性的帖子，核心议题是证明调和级数发散。皮卡先介绍第一个网友的分组估计证明，每组和大于 1/2，从而证明发散；再补充柯西凝聚判别法，其证明思路与分组估计相同，适用于非负不增序列。随后介绍第二个证明，通过证明 H_n &gt; log(n+1) 证明发散，因为 log 无上界；并提及积分估计流派用积分曲线面积近似 H_n 进行放缩，以及差分流派使用 Stolz 定理通过差分求极限。皮卡认为某些证明方法（如取对数、差分）是事后凑出来的，不自然，有故弄玄虚之嫌，并批评这些方法妨碍理解。
 # 核心概念
 ## 调和级数
-- 调和级数指∑1/n = 1 + 1/2 + 1/3 + …，其部分和记为H_n（英文为harmonic，调和之意），是微积分中的经典问题，属于清朝初年（康熙治鳌拜时期）提出的微积分范畴。
-- 收敛与发散的定义：对正向级数，若所有部分和Sn都小于某个固定实数a（如100或1000万），则收敛；若部分和能超过任意给定的数，则发散。
+- **调和级数** ∑1/n 是发散的，这是微积分中的经典问题，属于 `Calculus`（微积分）范畴。
+- 调和级数的部分和记为 `H_n`，即 `H_n = 1 + 1/2 + 1/3 + … + 1/n`，英文中调和为 `harmonic`。
+## 收敛与发散的定义
+- 对正向级数，若所有部分和 `S_n` 都小于某个固定实数 `a`（上界），则级数收敛；若部分和大于某个无界递增的 `b_n`，则级数发散。
 ## 分组估计证明
-- 第一个网友的证明：将项分组，如1单独一组，1/2+1/3一组，1/4+1/5+1/6+1/7一组，每组和都大于1/2，因此任意多组相加无上界，故发散。
-- 皮卡指出，这种分组求和思路与高斯小时候计算1+2+3+…+100的方法类似，都是发现具有良好性质的组（如和恒定或满足估计），从而简化求和问题。
+- 第一个网友的证明：将项分组，如 `1`、`1/2+1/3`、`1/4+1/5+1/6+1/7` 等，每组和都大于 `1/2`，因此部分和无上界，级数发散。
 ## 柯西凝聚判别法
-- 柯西凝聚判别法的证明过程与分组估计完全一样，适用于非负不增序列，通过分组取上界或下界来估计部分和。
-- 应用该方法，∑1/n的收敛发散性等价于∑2^k·(1/2^k) = ∑1，即无穷个1相加，显然发散，从而简化了对增长缓慢序列的判断。
+- **柯西凝聚判别法** 的证明思路与分组估计完全一样，适用于非负不增序列，通过分组取上界或下界估计部分和。
+- 对 ∑1/n，凝聚后等价于 ∑(2^k · 1/2^k) = ∑1，即无穷个 1 相加，显然发散。
 ## 积分估计流派
-- 该流派用积分曲线面积近似H_n：因为H_n的每一项高为1/n、底为1，矩形面积始终大于下方曲边梯形面积，故H_n &gt; ∫₁ⁿ⁺¹ (1/x)dx = log(n+1)，而log无上界，所以发散。
-## 差分流派（Stolz定理）
-- 该流派试图证明H_n与log n同增长级别，通过Stolz定理（中文称Stolz定理，数学竞赛和考研常用）求差分极限：分子差分H_{n+1}-H_n = 1/(n+1)，分母差分log(n+1)-log n = log(1+1/n)，两者极限均为1，故H_n/log n → 1。
-- 皮卡认为此方法不自然，因为需要事先知道H_n与log n同阶，属于先射箭后画靶。
+- 用积分曲线面积近似 `H_n`，因为 `H_n` 的几何意义是矩形面积，始终大于曲线 `f(x)=1/x` 下的面积，而 `∫1/x dx = log x`，故 `H_n &gt; log(n+1)`，而 `log` 无上界，所以发散。
+## 差分流派
+- 使用 **Stolz 定理**（中文常称 `Stolz` 定理），通过比较 `H_n` 与 `log n` 的差分极限：分子差分 `1/(n+1)`，分母差分 `log(1+1/n)`，两者比值极限为 1，从而证明 `H_n` 与 `log n` 同阶，`log n` 无上界，故发散。
+## 取对数证明
+- 另一证明通过 `e^{H_n}` 放缩，利用 `e^{1/k} &gt; 1+1/k`，连乘积 `∏(1+1/k)` 相邻项相消得 `n+1`，从而证明发散；皮卡认为这是事后凑出来的。
 # 核心结论
-核心结论：调和级数∑1/n是发散的，这是微积分中的经典结论，可通过分组估计、柯西凝聚判别法、积分估计或Stolz定理等多种方法证明。易混淆点：收敛与发散的定义需明确上界a是固定的，且对所有n成立；部分和H_n与log n的关系是H_n &gt; log(n+1)，但H_n本身无上界。待澄清问题：皮卡批评某些证明（如差分流派）是事后凑出来的，不自然，认为它们故弄玄虚、妨碍理解，但未给出更自然的替代证明。易错点：**不要误以为调和级数收敛**，因为虽然项趋于0，但部分和无上界；**不要混淆log与ln**，皮卡指出log是美国的写法，ln是欧洲传苏联再传中国的写法，两者本质相同。</t>
+**核心结论**：调和级数 ∑1/n 是发散的，这是微积分中的经典问题，可通过分组估计、柯西凝聚判别法、积分估计、差分等多种方法证明。
+**易混淆点**：
+- 收敛与发散的定义：收敛要求所有部分和小于某个固定上界，发散则部分和无上界。
+- 柯西凝聚判别法与分组估计的证明思路相同，但适用范围更广（非负不增序列）。
+- 积分估计中 `H_n` 的几何意义是矩形面积，始终大于曲线 `1/x` 下的面积，故 `H_n &gt; log(n+1)`。
+**待澄清问题**：
+- 皮卡认为取对数证明和差分流派是“先射箭后画靶”，即先知道结果再凑方法，不自然，有故弄玄虚之嫌。
+- 皮卡指出 `e^{1/k} &gt; 1+1/k` 本身需要微积分，而微积分建立在极限之上，但该不等式也可不用微积分证明。</t>
         </is>
       </c>
       <c r="D14" s="10" t="n">
-        <v>31.5</v>
+        <v>28.5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>7465/1412</t>
+          <t>7465/1461</t>
         </is>
       </c>
     </row>
@@ -4378,63 +4472,41 @@
       <c r="C15" s="4" t="inlineStr">
         <is>
           <t># 知识主题与概述
-本期视频由工作室老李主讲，围绕GitHub这一资源库展开，核心议题包括实用热门项目介绍与使用技巧。整体逻辑框架为：先展示一批实用项目（如工作性价比评估、表情包合集、健康指南、证件照生成、健身指导、教材下载、AI视频生成、声音克隆、AI学习资源等），再针对国内用户访问GitHub的常见问题（网络不通、页面全英文、原生搜索不好用）逐一给出解决方案，包括使用加速软件、镜像站、魔法上网、翻译插件、AI搜索等。老李强调GitHub是巨大的宝藏资源库，几乎能找到所需资源、教程与工具，并推荐用AI工具（如ChatGPT）辅助搜索与追踪热门项目。
+本期视频由工作室老李主讲，围绕GitHub上的实用热门项目及使用技巧展开，旨在帮助观众高效利用GitHub资源。老李首先介绍了多个实用项目，包括工作性价比评估工具“b班值不值得上”、表情包博物馆、健康指南“教你健康的活到150岁”、一键做证件照、健身项目、教材项目、全自动视频生成项目morning printer Turbo、声音克隆模型chat box TTS、AI学习资源库及awesome am. Ap ps等。随后针对GitHub访问与使用问题，分享了使用watch tool Kit加速软件、GitHub镜像站（如gh proxy）、魔法（科学上网）等解决方法，并讲解了页面汉化、搜索优化、项目主页功能及热门项目追踪技巧。整体逻辑框架为：先展示实用项目，再解决访问与使用痛点，最后提供高效使用GitHub的方法。
 # 核心概念
-## GitHub
-- **GitHub** 被形容为“巨大的宝藏资源库”，几乎能找到想要的资源、教程、工具，包括名校公开课、大厂面试题、开源大模型、AI学习资料等。
 ## b班值不值得上
-- 输入**年薪、工作地区、年假、通勤时长、学历、工作年限**等，综合评估工作性价比，给出分数和评级；示例中程序员工作被评为“性价比还不错，优质牛马”。
+- **b班值不值得上**：输入**年薪**、**工作地区**、**年假**、**通勤时长**、**学历**、**工作年限**等，综合评估工作性价比并给出**评级**。
+- 示例：老李测试程序员工作，评估结果为“性价比还不错，优质牛马”。
 ## 表情包博物馆
-- 收录国内过去几年全网爆火的表情包合集，包括甄嬛传、罗翔、特朗普、马保国等，用于斗图。
-## 活到150岁指南
-- 分享经科学验证的健康知识，如**间歇性进食**促进胆汁代谢、炎症自愈，吃天然发酵食品改善肠道菌群生态。
+- **表情包博物馆**：收录国内过去几年全网爆火的表情包合集，包括**甄嬛传**、**罗翔**、**特朗普**、**马保国**等。
+## 教你健康的活到150岁指南
+- **教你健康的活到150岁指南**：分享经科学验证的健康知识，如**间歇性进食**促进胆汁代谢、炎症自愈，吃**天然发酵食品**改善肠道菌群。
 ## 一键做证件照
-- 上传大头照即可一键抠图换背景，生成不同标准的证件照和打印模板。
+- **一键做证件照**：上传**大头照**，一键**抠图换背景**，生成不同标准证件照和**打印模板**。
 ## 健身项目
-- 可选择自重、哑铃、弹力带、长凳等器材，选择肌肉群后提供参考动画，如练习腹肌的自重动作。
+- **健身项目**：可选择**自重**、**哑铃**、**弹力带**、**长凳**等，选择肌肉群后提供**参考动画**。
 ## 教材项目
-- 收集国内小学、初中、高中及部分大学PDF教材，全部免费。
+- **教材项目**：收集国内**小学**、**初中**、**高中**及部分**大学**的PDF教材，全部**免费**。
 ## 全自动视频生成项目
-- 名为 `morning printer Turbo`，近期超火。
-## 声音克隆模型 chat box TTS
-- **零样本语音克隆**，情感控制到位，克隆声音像真人；上传音频可合成英文台词。
+- **morning printer Turbo**：最近超火的**全自动视频生成**项目。
+## 声音克隆模型
+- **chat box TTS**：**零样本语言克隆**，**情感控制**到位，克隆声音像真人说话。
 ## AI学习资源库
-- 涵盖大语言模型、RAG、AI Agents等最新AI技术，作者整理成**500多页PDF文档**，含大量示意图。
+- **AI学习资源库**：涵盖**大语言模型**、**RAG**、**AI Agents**等，整理成**500多页PDF**文档，含大量示意图。
 ## awesome am. Ap ps
-- 收录大模型最新agent应用，如医学影像数据分析、AI投资、竞争对手情报分析等，适合跟进AI应用落地案例或找创业点子。
-## 访问加速方法
-- 方法一：使用 `watch tool Kit` 加速软件，下载安装后勾选GitHub加速。
-- 方法二：使用镜像站如 `gh proxy`，浏览器直接访问。
-- 方法三：使用魔法（科学上网），需注册GitHub，可用国内QQ邮箱。
-## 页面汉化
-- 给浏览器装翻译插件，如谷歌浏览器推荐 `谷歌translate` 或 `沉浸式翻译`；动手能力强的可装汉化插件。
-## 搜索技巧
-- GitHub原生搜索按精准匹配排序，对国人不好用；推荐用AI搜索（如ChatGPT）用中文描述需求。
-## 项目主页元素
-- 项目本质是文件夹；`watch` 关注、`fork` 复制、`star` 收藏点赞；`about` 是简介；`release` 是安装包；`read me` 是说明书。
-## 判断项目维护状态
-- 查看文件最近 `commit` 日期，若更新日期久远，大概率是僵尸项目。
-## 追踪热门项目
-- 通过 `explore` 的 `trending` 查看当天、本周、本月最热门项目；也可用ChatGPT找 `GitHub daily`。
+- **awesome am. Ap ps**：收录大模型**agent应用**，如**医学影像数据分析**、**AI投资**、**竞争对手情报分析**等。
 # 核心结论
-**核心结论**：
-- GitHub是资源宝库，但国内访问存在卡顿、全英文、搜索不好用等问题，可通过加速软件、镜像站、魔法、翻译插件、AI搜索等方法解决。
-- 推荐使用 `watch tool Kit` 加速软件或魔法访问GitHub，镜像站速度和稳定性较差。
-- 推荐用AI搜索（如ChatGPT）替代原生搜索，用中文描述需求可得到更全面准确的结果。
-**易混淆点**：
-- GitHub原生搜索按精准匹配排序，搜 `screen record` 和 `screen recording` 结果不同，导致搜不全。
-- `star` 是收藏点赞，`watch` 是关注，`fork` 是复制项目，三者功能不同。
-- `commit` 日期是最近更新时间，更新久远可能是僵尸项目。
-**待澄清问题**：
-- 未提及。</t>
+**核心结论**：GitHub是巨大的资源库，包含教程、工具、开源模型等；访问问题可通过**watch tool Kit加速软件**、**镜像站**（如gh proxy）或**魔法**解决；页面汉化可用**翻译插件**（谷歌translate、沉浸式翻译）或**汉化插件**；搜索推荐用**AI搜索**（如ChatGPT）替代原生精准匹配。
+**易混淆点**：GitHub原生搜索按**匹配度**排序，但精准匹配导致不同关键词（如screen record与screen recording）结果不同；项目主页的**watch**（关注）、**fork**（复制）、**star**（收藏点赞）功能易混淆；**commit日期**用于判断项目活跃度，更新久远可能为僵尸项目。
+**待澄清问题**：原文未明确各项目的具体链接、适用平台及部分项目的详细功能（如morning printer Turbo的具体操作）。</t>
         </is>
       </c>
       <c r="D15" s="10" t="n">
-        <v>45.9</v>
+        <v>37.8</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>4014/1852</t>
+          <t>4014/1619</t>
         </is>
       </c>
     </row>
@@ -4805,52 +4877,50 @@
       <c r="C16" s="4" t="inlineStr">
         <is>
           <t># 访谈概述
-本期《锵锵三人行》邀请《明朝那些事儿》作者当年明月与嘉宾马先生，围绕日本历史剧《大奥》与明朝历史展开对谈。节目先讨论《大奥》所体现的日本文化中的极端精神、忠诚文化与终身雇佣制，并与中国的融合、中庸文化对比；随后转向明朝历史，探讨明史资料丰富但说法纷杂、明朝兴亡的跌宕过程、朱元璋从乞丐到皇帝的传奇、明末江南的富足生活，以及明武宗、天启帝等皇帝的个性与明式家具的审美地位。受访者当年明月以写史者身份分享研究明史的缘由与对历史认知的思考，马先生则以文化观察者视角对比中日民族精神差异。
+本次访谈由窦文涛主持，嘉宾为《明朝那些事》作者当年明月与收藏家马未都，围绕日剧《大奥》与明朝历史展开对话。访谈前半段讨论《大奥》所体现的日本文化精神，包括极端精神、忠诚文化与规则意识，并与中国的中庸文化作对比；后半段聚焦明朝历史的趣味性、史料复杂性及朱元璋、正德皇帝等人物评价。受访者认为日本文化强调极致与忠诚，战后用30年成为世界第二经济强国；明朝历史跌宕起伏，史料虽多但说法不一，需设身处地理解。
 # 访谈详细记录
 ## 《大奥》与日本文化
-- 当年明月认为《大奥》是继《大长今》之后最有影响的外国电视剧，三部曲中前两部对应中国晚明到清初，第三部在明治维新之前，是一部有跨越性的历史剧。
-- 当年明月表示，吸引他的是剧中体现的严谨精神，并对比说回头看《三国演义》会看到群众演员笑场，而日本历史剧看不到笑，每个人都特别认真、有专业精神。
-- 马先生介绍，大奥即后宫，日语中「奥」指屋子最深处，规矩严谨，后宫不许进人；幕府将军与约1000名女人生活在大奥中，全是伺候他一人。
-- 当年明月指出，日本天皇一直是摆设，实际权力掌握在幕府将军手中，德川家康开创德川幕府后权力集中；天皇曾因想办活动没钱向将军要钱被拒，最后以退位抗议。
-- 马先生认为，日本战后用30年时间成为世界第二经济强国（绝对量），是唯一没有资源的国家，这与其全民族的极端精神有关，是必然而非偶然。
-- 当年明月对比中日文化精神，认为中国文化精神是中庸，讲究融合、走最适合的路；日本精神则坚持一个原则、做事做到尽头，如炮手开炮时忘记一切只记得把炮开出去即达最高境界。
-- 马先生提到日本跳槽率最低，实行终身雇佣制，西方经济学家认为缺乏竞争会导致效率低下，但日本终身雇佣下积极性仍高，是经济学上的奇迹。
-- 马先生举例日本豆腐厂当天做当天卖，夜里11:45所有人坐好看表，12点整准时开工，4点多干完上市，无人闲聊，体现一丝不苟。
-- 当年明月认为日本作为岛国，没有资源、常火山地震，人本身有极强求生欲望，对世界悲观，必须融入团体按固定规则做事才能生存。
-- 马先生认为日本投机取巧者没有生存环境，社会文化鄙视使其无法生存；举例做绳子的人几年不赚钱铺市场，最后通过两边各加2%获利4%。
-- 当年明月表示不愿做日本人，因其常盲从且有寻死的潜在欲望，如看樱花只看落的那天，对死亡不惧怕甚至有点向往；马先生则认为日本民族不是藐视生命而是重视死亡，经济危机时身家万贯者剖腹自杀。
-## 明朝历史与《明朝那些事儿》
-- 马先生称赞《明朝那些事儿》写得好、写得放松，发行量在文学类排行榜第一；当年明月回应说主要原因是他不知道什么叫拘着，只能这么写。
-- 当年明月解释自己写明史是因为明史资料最多，但同一事件可能有7种不同说法，如罗生门；先秦因史料少难研究，明清因说法太多也难说清。
-- 马先生认为明朝260多年过程本身跌宕起伏，土木堡之变、夺门之变等怪事特别多，皇上被瓦剌军抓了又扶弟弟上位，构成现代版电视剧情节。
-- 当年明月推崇朱元璋，认为他从乞丐到皇帝独此一份，定下明朝规章制度且基本无大改动，是了不起的人才；马先生补充说朱元璋因要过饭、知道每层猫腻而疑心重。
-- 当年明月认为朱元璋参加起义军是逼上梁山，因信差送信被听到告发，没办法才去；他强调历史最重要的是弄明白这事是真的，旁观者觉得好玩，但当事人要掉脑袋，是很有风险的事。
-- 当年明月指出明末很多真相被掩盖，当时市民生活轻松舒服，江浙一带工商业兴起，给人当雇工活得很滋润，三言二拍这类娱乐产品出现说明有养活自己的资本。
-- 当年明月认为李自成起义是因为陕西一带发生大规模灾荒；马先生补充说明末江南富足，工艺精细，文征明、唐寅、董其昌都是那个时期的人，生活不好画不出小桥流水。
-- 当年明月引用名言「我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训」，认为历史事件发生时有背景，不能套用经验，否则一定要倒霉。
-- 当年明月说明朝皇帝有趣，宦官专政（魏忠贤、刘瑾）、文官专政（张居正）、皇帝专政（朱元璋、朱棣）都有，什么都能发生，皇帝出去了还能回来做皇帝。
-- 当年明月提到1644年明朝灭亡时北京闹瘟疫（疙瘩瘟，可能天花），李自成军打到京城无人抵抗；他曾与老师王佩奇交流，认为明朝亡得蹊跷，坏事衰事都赶上了。
-- 马先生认为中国王朝300年大限，宋朝因退让大半个国土延续319年，汉朝中间隔断14年，唐朝、明朝、清朝都没跨过界限；当年明月比喻说明朝像公司，摊子几千万人，能撑276年已不易。
-- 马先生对比宋明汉人文人政权与满族异族政权的审美差异，认为汉人审美素雅、非表象，满族审美表象，晚清民国初年收藏中素雅之物才值钱。
-- 当年明月说明武宗正德皇帝被写坏，因接班的嘉靖是其堂兄弟而非亲生，明武宗实录由嘉靖指派杨廷和等人编纂，有偏颇；正德皇帝从江南回来在通州停半天先派人打探京城情况，很有城府。
-- 马先生提到天启皇帝爱当木匠，做完家具差大臣去卖，还打听卖得怎么样，成就感特大；他认为这反映当时社会时尚，明式家具国际地位高绝非偶然。
-- 当年明月认为明神宗几十年不上朝但不出去；马先生补充说明武宗对宫廷内女人没兴趣，因禁忌太多，对宫廷外女人有兴趣，但史料无法证实其出宫行为。
+- **剧集评价**：马未都认为《大奥》是继《大长今》后最有影响的外国电视剧，三部曲中前两部对应中国晚明到清初，后一部在明治维新前。
+- **严谨精神**：当年明月表示，《大奥》吸引他的是严谨精神，日本历史剧中群众演员不会笑，而中国历史剧如《三国演义》会看到群众演员笑。
+- **大奥释义**：马未都解释，大奥即中文的“后宫”，日语“奥”指屋子最深处，如“堂奥”“深奥”保留此意，且一般人不准进入。
+- **幕府权力**：当年明月指出，日本天皇一直是摆设，实际权力在幕府将军手中；德川家康开创德川幕府后，权力集于一人，天皇曾因将军不给钱办不成活动，甚至以退位抗议。
+- **极端精神**：马未都认为日本文化体现极端精神，所有事情要做到尽头，且是发自内心的；战后日本用30年成为世界第二经济强国（绝对量），是唯一没有资源的国家，这不是偶然而是必然。
+- **文化对比**：当年明月认为中国文化精神是中庸，日本精神恰相反，坚持一个原则；他以马未都家具店中硬木刻云彩为例，说明中国讲究融合与最适合的路。
+- **忠诚文化**：马未都指出日本是忠诚文化的典型国度，跳槽率最低，终身雇佣制下效率仍高，西方经济学家难以理解；《大奥》中阿福25岁入宫当奶妈，65岁去世，40年不出于私心，被所有人视为楷模。
+- **豆腐厂见闻**：马未都讲述参观日本豆腐厂，规定当天做当天卖，夜里11:45所有人坐好等钟，12点整开始工作，4点多干完上市，无人闲聊。
+- **生存逻辑**：当年明月认为日本岛国无资源、多火山地震，人有极强求生欲望，必须融入团体按规则行事才能生存；投机取巧者无生存环境，文化鄙视使其难以立足。
+- **商人案例**：马未都举例日本做绳子做到全日本第一的人，几年不赚钱铺市场，后向两边各加2%利润，全国4%收益巨大。
+- **死亡观念**：当年明月认为日本文化有寻死欲望，看樱花只看落的那天，对死亡不惧怕甚至向往；马未都补充，日本民族不是藐视生命而是重视死亡，经济危机时身家万贯者剖腹自杀。
+## 明朝历史与《明朝那些事》
+- **作品成绩**：马未都提到《明朝那些事》发行量排行榜第一（文学类），各报都是第一。
+- **写作缘由**：当年明月表示，写明史是因为明史资料最多，但一个事件可能有7个不同说法，如罗生门；先秦史料太少，史记中孙武事迹仅一两篇，多为编造。
+- **历史趣味**：马未都认为明朝260多年过程跌宕起伏，土木堡之变、夺门之变等事件构成现代版电视剧情节，皇上被瓦剌军抓走后又扶弟弟即位。
+- **朱元璋评价**：当年明月推崇朱元璋，因其从乞丐到皇帝独此一份，定下明朝规章制度且基本无大改动；马未都补充，朱元璋要过饭，知道每一层猫腻，疑心重。
+- **起义动机**：当年明月讲述朱元璋参加起义军是被逼无奈，因信差送信被告发，怕被杀头才去；他强调历史最重要的是明白这事是真的，旁观者觉得好玩，但当事人面临掉脑袋风险。
+- **明末生活**：当年明月指出明末市民生活轻松，江浙工商业兴起，给人当雇工活得很滋润，三言二拍等娱乐产品出现说明有养活自己的资本；李自成起义因陕西大规模灾荒。
+- **艺术繁荣**：马未都提到明末江南富足，工艺变得精细，文征明、唐寅、董其昌等无门化派画家画小桥流水，心态轻松；八大山人画翻白眼是因对社会愤愤不平。
+- **经验教训**：当年明月引用名言“我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训”，认为历史事件有背景，不能套用经验，否则一定倒霉。
+- **朝代特点**：当年明月指出明朝什么事都有，宦官专政（魏忠贤、刘瑾）、文官专政（张居正）、皇帝专政（朱元璋、朱棣），皇帝出去还能回来做皇帝。
+- **灭亡原因**：当年明月提到1644年明朝灭亡时北京闹瘟疫（疙瘩瘟，可能天花），李自成军打来无人抵抗；吴三桂与满清合作入关，名义是为崇祯复仇。
+- **王朝周期**：马未都认为中国王朝300年大限，宋朝延续319年（南北宋接上），明朝未跨过；当年明月以公司类比，明朝几千万人摊子大，能撑276年已不易。
+- **审美差异**：马未都认为宋明是文人政权，审美素雅；满族异族审美表象，今天外在美直观的卖得贵，但晚清民国收藏素雅之物不值钱。
+- **正德皇帝**：当年明月认为正德皇帝被写坏，因嘉靖非其亲生（堂兄弟），编《明武宗实录》有偏颇；正德从江南回京在通州停半天打探京城情况，很有城府。
+- **天启皇帝**：马未都提到天启皇帝爱当木匠，干完活差大臣去卖，还打听卖得怎么样，反映明式家具在当时地位高，其国际地位绝非偶然。
 # 关键引语与金句
 &gt; 慢慢来才是最快的方法。
-&gt; 所有人按照自己的角色去做自己的事情，最节省成本了，就不会有互相的作用力互相抵消，大家都会有一个共同的目标往前走。
 &gt; 我们从历史中得到的唯一教训就是我们从来没有从历史中得到过教训。
-&gt; 历史它那个事儿发生的时候是有背景的，就是当你要明白你不比前人聪明，你甚至可能比前人笨，就是当那种情况出现的时候，你也得那么办。
-&gt; 史书上记载下来是什么？照片。我们实际的生活，古人的生活都是录像，在史书上下来的只是一个照片，咔嚓。但你不知道为那一幕之前跟之后是什么。
-&gt; 日本的文化跟中国的文化存在一个极大的不同。中国的文化精神是什么？是中庸。日本的精神就恰相反，他坚持一个原则，你看鞠一刀就知道。
+&gt; 日本的文化跟中国的文化存在一个极大的不同。中国的文化精神是什么？是中庸。
+&gt; 日本战后用30年的时间成为世界第二经济强国，它不是一个偶然，它是一个必然。
+&gt; 历史你回过头看谁都是一个聪明人，你站在一个历史的原点的时候，你前后都看不见，你必须撤出来，你才能看见他。
 &gt; 日本民族它不是藐视生命，它是重视死亡，它是翻着的。</t>
         </is>
       </c>
       <c r="D16" s="10" t="n">
-        <v>58.7</v>
+        <v>51.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>14719/2548</t>
+          <t>14719/2343</t>
         </is>
       </c>
     </row>
@@ -5187,27 +5257,41 @@
       <c r="C17" s="4" t="inlineStr">
         <is>
           <t># 就诊概况
-患者张学恒，男，48岁，因上腹反复疼痛4年、近3个月加重，于消化专科门诊就诊。疼痛位于心窝处，呈烧灼感，与进食冷、硬、辛辣食物及工作紧张劳累相关，白天发作，夜间无痛醒。近4年出现两次黑便，近两个月呕吐数次。初步判断需排除消化道出血及恶性病变可能，已安排大便潜血及胃镜检查。
+患者张学恒，男，48岁，因上腹心窝处烧灼样疼痛反复发作4年、近3个月加重，于消化专科就诊。疼痛诱因为进食冷、硬、辛辣食物及工作紧张劳累，白天发作、夜间无痛醒；近3个月出现呕吐黄水样酸味物，吐后舒适。近4年有两次黑便，分别发生于一年前和三个月前，均住院治疗。既往有甲肝病史及磺胺过敏史。医生初步判断需排查消化道出血及肿瘤可能，拟行大便潜血检查及胃镜活检。
 # 诊断与检查结果
-本次门诊未进行胃镜及大便潜血检查，医生根据病史初步判断需排除消化道出血及恶性病变可能。患者近4年出现两次黑便，均查大便示出血，**一年前**一次持续约一个月并住院10天，**三个月前**一次住院两三天。近三个月无黑便，大便黄色正常，小便正常。既往16岁患甲肝，在三医院住院一个月，出院及后续体检肝功能均正常；对磺胺药过敏（左手起红疹，持续约半个月）。
+**诊断结论**：初步考虑消化系统疾病，需进一步检查明确。
+**关键检查结果**：
+- **大便潜血检查**：已要求患者留大便送检，结果未出。
+- **胃镜及活检**：已预约后天进行，结果未出。
+**解读**：患者反复上腹疼痛、两次黑便、近期呕吐，需排查消化道出血及肿瘤可能；婶婶有胃癌史（无血缘关系），患者自身担忧，需检查排除。
 # 治疗方案与医嘱
-治疗计划：待大便潜血及胃镜检查结果明确后，再判断是否需要手术；若药物可控制病情则无需手术。生活注意事项：医生建议患者尽量少抽或不抽烟、少喝酒，因吸烟饮酒对胃部疾病不利；注意避免工作紧张、劳累及加班熬夜，因可能加重病情。用药说明：患者近期服用达喜、奥美拉唑、阿莫西林及胃炎合剂，均停药后复发，具体用药方案见下表。
+**治疗计划**：待检查资料全面后，由上一级张医生（指导教授）判断是否需要手术；若药物可控制病情则无需手术。
+**生活注意事项**：
+- **戒烟**：吸烟对疾病不利，应尽量少抽或不抽，现限制在10支以内，计划逐步戒除。
+- **限酒**：酒对胃病影响大，应尽量少喝。
+- **避免诱因**：减少进食冷、硬、辛辣食物，避免工作紧张、劳累、加班熬夜。
+**用药说明**：近期自行服药效果不佳，需遵医嘱调整，具体方案待检查后确定。
 | 药品名称 | 剂量 | 频次 | 用法 | 注意事项 |
 | --- | --- | --- | --- | --- |
-| 达喜 | 未明确 | 初始一天两次，每次一颗；后增至每天四五次 | 口服 | 初始有效，后效果不佳，停药后复发 |
-| 奥美拉唑（国产，武汉药厂） | 未明确 | 未明确 | 口服 | 停药后复发 |
-| 阿莫西林 | 未明确 | 未明确 | 口服 | 停药后复发 |
-| 胃炎合剂（医务室配制） | 未明确 | 未明确 | 口服 | 停药后复发 |
+| 大叔（可能为达喜） | 未明确 | 初始每天2次，每次1颗；后增至每天4-5次 | 口服 | 初服有效，后效果变差，自行加量 |
+| 奥美拉唑（武汉药厂国产） | 未明确 | 未明确 | 口服 | 初服有效，停药后复发 |
+| 阿莫西林 | 未明确 | 未明确 | 口服 | 与奥美拉唑同服，停药后复发 |
+| 胃炎合剂（医务室自配） | 未明确 | 未明确 | 口服 | 初服有效，停药后复发 |
 # 复诊与预警信号
-复诊时间：胃镜预约在后天进行，胃镜活检后由张大夫查房，医生将总结病情向上一级张医生汇报后再与患者商量下一步处理意见。⚠️ 预警症状：若再次出现黑便、呕血、剧烈腹痛或体重明显下降，需立即就医。</t>
+**复诊时间**：后天行胃镜及活检，届时张大夫查房；检查后与患者商量下一步处理意见。
+**预警信号**：
+- ⚠️ 出现黑便或大便带血
+- ⚠️ 呕吐物含红色或黑色物质
+- ⚠️ 腹痛加剧或持续不缓解
+- ⚠️ 头晕、乏力、面色苍白等贫血表现</t>
         </is>
       </c>
       <c r="D17" s="10" t="n">
-        <v>49.1</v>
+        <v>56.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>8519/846</t>
+          <t>8519/989</t>
         </is>
       </c>
     </row>
@@ -6162,39 +6246,23 @@
       <c r="C18" s="4" t="inlineStr">
         <is>
           <t># 庭审概况
-本案系上诉人国家开发银行与被上诉人云南东源电力股份有限公司、云南东源曲靖电力有限公司、招银金融租赁有限公司金融借款合同纠纷一案，因不服云南省高级人民法院云民初88号民事判决提起上诉。本院依法组成合议庭，依据《中华人民共和国民事诉讼法》第134条第一款、第169条的规定公开开庭审理。庭审围绕三个争议焦点展开：抵押权与融资租赁所有权冲突、罚息复利计算、违约金连带给付。各方对央行融资租赁登记性质存在分歧，国开行主张系行业强制性规范，招银租赁主张系行业指导性规范，东源公司认为不产生物权后果。合议庭询问查询方式，国开行称仅能按单位查询，招银租赁称可登记唯一识别码但非必填项。经合议庭评议，各方当事人自愿达成调解协议，法院予以确认，庭后出具调解书。
+本案系上诉人国家开发银行与被上诉人云南东源电力股份有限公司、云南东源曲靖电力有限公司、招银金融租赁有限公司金融借款合同纠纷一案，上诉人不服云南省高级人民法院云民初88号民事判决，向本院提起上诉。本院依法组成合议庭，依据《中华人民共和国民事诉讼法》第134条第一款、第169条的规定公开开庭审理。庭审中，合议庭围绕抵押权与融资租赁所有权冲突、罚息复利计算、违约金连带给付三个争议焦点展开法庭调查与辩论。各方当事人对一审判决第二项、第四项无争议。经合议庭主持调解，各方自愿达成调解协议，合议庭予以确认，庭后出具调解书。
 # 原告诉称与被告辩称
-上诉人国家开发银行请求确认对案涉设备享有抵押权，主张已尽审查义务，构成善意取得；被上诉人东源公司、曲靖电力公司、招银租赁对抵押权效力提出异议。
 | 方 | 诉讼请求/答辩意见 | 事实与理由 |
 | --- | --- | --- |
-| 上诉人（原审原告） | 确认对案涉设备享有抵押权，主张已尽审查义务，构成善意取得 | 抵押设备为通用设备无唯一标识，查询无登记；已按人民银行规定完成贷款抵押的刑事审查、资料审查、法律审查 |
-| 被上诉人（原审被告） | 主张国开行未尽审查义务，不构成善意取得 | 东源公司主张2015年12月2日邮件已告知抵押设备与招银租赁设备名称一致；招银租赁主张国开行未按央行规定查询融资租赁登记，东源煤电出资行为系无权处分 |
+| 上诉人（原审原告） | 请求确认对案涉93项设备享有抵押权，主张利息、罚息、复利及违约金，要求东源煤电连带给付违约金 | 主张已尽审查义务，抵押设备为通用设备无唯一标识，查询无登记结果，构成善意取得；合同第24条第三项约定违约金，东源煤电违反第13条、第14条约定，应支付千分之一违约金 |
+| 被上诉人（原审被告） | 主张国开行宣布贷款提前到期未给合理期限，罚息不应作为复利计算基数，违约金请求无依据 | 主张2015年12月2日邮件已告知抵押设备存在融资租赁，国开行未尽注意义务；引用《人民币利率管理规定》第21条及最高院判例；国开行未举证违约行为，且未按合同约定发出限期纠正通知 |
+| 第三人（原审第三人） | 主张对涉案六项设备享有所有权，国开行不构成善意取得 | 主张国开行未按央行规定查询融资租赁登记系统，不构成善意；招银租赁2012年已取得设备所有权，东源煤电出资行为系无权处分 |
 # 举证与法庭调查
-**证据与质证意见**
-- 国开行提交2018年9月融资租赁查询证书，招银租赁质证认为不符合201493号文要求，查询时点与操作抵押时点不符。
-- 国开行提交工商出资证明、权属证明等材料，主张已尽审慎义务；招银租赁认为东源煤电出资行为系无权处分，工商登记公示的是出资行为而非动产公示。
-- 东源公司提交2015年12月2日邮件及融资情况统计表，主张已告知抵押设备与招银租赁设备名称一致，并用红色标注；国开行认为统计表仅显示并列关系，无法得出告知结论。
-- 招银租赁提交回租设备清单（证据7页），载明设备名称、生产厂家，但无型号；国开行认为无法据此识别设备唯一性。
-- 招银租赁提交2013年、2015年审计报告（证据82页、95页），载明曲靖电力公司注册资本4亿元已实缴；国开行据此主张招银租赁知道或应当知道设备出资情况。
-**法官询问要点**
-- 合议庭询问各方对央行征信中心融资租赁登记性质及法律后果的理解。
-- 询问国开行贷款前审查是否有内部规定必须查询融资租赁登记，未查到结果是否需保留单证作为风控材料；国开行称无此规定，未保留查询记录。
-- 询问招银租赁融资租赁登记系统中设备唯一标识码是否必填项；招银租赁称非必填项，本案设备无唯一识别码故未登记。
-- 询问国开行和招银租赁关于查询通知的规范性质及违反后果。
-**双方辩论的争议焦点**
-- 国开行主张抵押设备为通用设备无唯一标识，查询无登记，构成善意取得；招银租赁主张国开行未按央行规定查询融资租赁登记，不构成善意。
-- 东源公司主张2015年12月2日邮件已告知抵押设备与招银租赁设备名称一致，国开行未尽注意义务。
-- 各方对央行融资租赁登记性质存在分歧：国开行认为系行业强制性规范，招银租赁认为系行业指导性规范，东源公司认为不产生物权后果。
-# 庭审结果
-本案争议焦点为：一、抵押权与融资租赁所有权冲突；二、罚息、复利计算；三、违约金连带给付。经合议庭评议，各方当事人自愿达成调解协议：确定国开行对东源公司债权扣除破产清偿本金后，利息、罚息、复利合计6474.4513万元；招银租赁对六项设备享有所有权，对应债权1377.4137万元；国开行对93项设备有抵押权。双方对案涉全部发电设备整体盘活处置，变现款各50%，费用各担50%；变现不足清偿时，招银租赁未实现债权按破产重整计划预留方案清偿。各方对调解方案均无异议，签字确认，法院予以确认，庭后出具调解书。</t>
+# 庭审结果</t>
         </is>
       </c>
       <c r="D18" s="10" t="n">
-        <v>52.3</v>
+        <v>39.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>30731/1699</t>
+          <t>30731/746</t>
         </is>
       </c>
     </row>
@@ -6300,17 +6368,26 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t># 公务员面试：四题综合考察公共服务能力
-公务员面试：四题综合考察公共服务能力
-会议要点：本次面试共20分钟，考生需回答4个问题，分别考察对公务员工作的理解、问题解决能力和公共服务意识。第一题中，考生将绳子比喻为鞭策、平衡和动力，分别对应骏马、风筝和陀螺：对骏马而言，绳子意味着自我反省，引用曾子“吾日三省吾身”，强调反思工作中的失误和拖延，并指出单位应形成紧张、活泼、团结、有趣的风气，同事之间比较能力和效率而非票子、车子、房子；对风筝而言，绳子意味着平衡，需建立权利清单、责任清单；对陀螺而言，绳子意味着动力，源于责任感和成就感，如撰写材料加班加点。；第二题中，考生作为小王提出AI企业调研方案：先完善统筹准备，利用课余时间补课，学习兄弟城市经验，查阅国务院和省厅关于人工智能的指导意见；制定包含客观（企业发展现状）和主观（政府服务需求）两方面的工作方案；调研分三部分：市场状况、服务需求、管理措施；具体实施包括与企业对接阅读发展报告、制定调查问卷并请专家修改、召开座谈会听取企业意见，询问人才引进、政策倾斜、用地审批、人才吸引和培养机制；管理措施通过问卷调查了解AI发展不完善之处，以便政策规范。；第三题中，考生模拟小王答复记者：承认管道问题，解释管道是90年代修建，老城区改造难度大，夏天用水高峰问题集中；已联系维修师傅准备现场维修，并将硬件问题汇报上级，计划通过城市综合保障工程改善；承认工作失职，请求媒体和居民给予改进机会，并希望媒体解释政府难处。；第四题中，考生分析存在主要矛盾（时间上的需求不满足）和次要矛盾（噪音、出行、舆论）；坚持推进城市建设，同时处理次要矛盾：督促施工方加快进度减少扰民，使用防噪墙、洒水降尘减少噪音灰尘，建议使用替代道路、通过交通广播推荐路线、鼓励公交出行并增加公交班次；通过公告形式在网络上发布信息，公开透明表达政府举措，获得市民理解。</t>
+          <t># 候选人概况与面试岗位
+考生参加公务员面试，面试时长20分钟，共回答4道结构化题目，考察综合分析、组织协调、应急应变和公共服务能力。整体表现思路清晰、表达流畅，能结合具体事例展开论述。第一题将绳子比喻为鞭策、平衡和动力，分别对应骏马、风筝和陀螺，引用曾子“吾日三省吾身”强调自我反省，并联系权利清单、责任清单及工作责任感。第二题提出AI企业调研方案，包括补课学习、借鉴兄弟城市经验、查阅中央和省厅文件，制定主客观结合的工作方案，分市场状况、服务需求、管理措施三部分实施。第三题模拟回应记者，承认管道问题，解释老城区改造难度，已联系维修并汇报上级，同时承认工作失职。第四题分析道路改造矛盾，提出督促施工进度、减少噪音灰尘、引导出行、加强沟通等措施。
+# 能力评估
+专业/技术能力：优。对AI调研提出补课学习、查阅国务院及省厅文件、制定调查问卷请专家修改等具体方法，体现政策理解与调研设计能力。项目经验：良。在AI调研中提出与企业对接阅读发展报告、召开座谈会、问卷调查等实操步骤；在管道问题中说明90年代老城区改造难点，体现项目背景分析能力。沟通协作：优。模拟回应记者时态度诚恳，承认失职并请求改进机会；在道路改造矛盾中提出通过公告公开透明沟通，体现沟通协调意识。岗位匹配度：优。四题均围绕公务员工作展开，如自我反省、权利责任平衡、服务群众、处理社会矛盾，契合岗位要求。
+| 评估维度 | 推荐评级 | 评估依据（具体事例） |
+| --- | --- | --- |
+| 专业/技术能力 | 优 | 对AI调研提出补课学习、查阅国务院及省厅文件、制定调查问卷请专家修改等具体方法，体现政策理解与调研设计能力。 |
+| 项目经验 | 良 | 在AI调研中提出与企业对接阅读发展报告、召开座谈会、问卷调查等实操步骤；在管道问题中说明90年代老城区改造难点，体现项目背景分析能力。 |
+| 沟通协作 | 优 | 模拟回应记者时态度诚恳，承认失职并请求改进机会；在道路改造矛盾中提出通过公告公开透明沟通，体现沟通协调意识。 |
+| 岗位匹配度 | 优 | 四题均围绕公务员工作展开，如自我反省、权利责任平衡、服务群众、处理社会矛盾，契合岗位要求。 |
+# 综合素质
+亮点：考生在第二题中主动承认自身知识盲区，提出利用课余时间补课，体现学习意识；在第三题中既承认工作失职，又解释客观困难，并请求媒体给予改进机会，态度诚恳。风险点：在第四题中，考生将矛盾分为主要矛盾和次要矛盾，但未明确说明如何平衡长期建设与短期扰民之间的冲突，可能在实际工作中面临执行难度。推进建议：建议考生在后续工作中加强政策执行与群众沟通的衔接，细化具体措施，如明确时间节点和责任人。</t>
         </is>
       </c>
       <c r="D19" s="10" t="n">
-        <v>41.9</v>
+        <v>34.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>5808/789</t>
+          <t>5808/1125</t>
         </is>
       </c>
     </row>
@@ -6379,45 +6456,38 @@
       <c r="C20" s="4" t="inlineStr">
         <is>
           <t># 参观概况
-本次参观为故宫中轴线及东西六宫、珍宝馆等区域的游览讲解，全程约12分钟，覆盖午门、太和门、太和殿、中和殿、保和殿、乾清门、乾清宫、交泰殿、坤宁宫、储秀宫、慈宁宫、断虹桥、武英殿、文华殿、箭亭、钟表馆、珍宝馆、御花园、神武门等景点。讲解重点包括午门明三暗五门洞及通行规则、太和殿为举行盛大典礼之地而非上朝处、乾清宫正大光明牌匾后藏立储诏书、珍宝馆即乾隆养老院宁寿全宫等历史典故，并介绍了七个免费盖章点及三条游览路线。整体过程按中轴线由南向北推进，穿插东西六宫与珍宝馆等支线，最后从神武门结束。
+本次讲解为故宫保姆级游览攻略，覆盖午门、太和殿、乾清宫、珍宝馆等主要景点，介绍历史背景与建筑特色。午门为明三暗五结构，中间正门仅供皇帝、皇后大婚及殿试前三名通行；太和殿为举行盛大典礼的金銮殿，文武百官文东武西站立；乾清宫为皇帝寝宫，正大光明牌匾后藏立储诏书；珍宝馆为乾隆养老院，皇极殿1:1复刻乾清宫，乐寿堂是唯一可进入参观的皇家寝室。讲解标注了七个免费盖章位置，并推荐三条游览路线，供游客按时间选择。
 # 核心看点与讲解
-- 午门：有三个门洞，进门后变五个，即明三暗五；中间正门仅供皇帝、皇后大婚、殿试前三名（状元、榜眼、探花）通行，旁门走皇亲国戚和文武百官。
-- 太和门广场：有五座金水桥，中间桥供皇帝，挨着中间的两座桥供黄金国器，最边上的桥供文武百官。
-- 太和门：明朝皇帝在此御门听政，即上朝的地方；门口铜狮子是故宫六对铜狮中最大的一对，脚踩寰宇象征权力，建议单独拍照，不要站在狮子底下。
-- 太和殿：即金銮殿，是举行盛大典礼的地方（皇帝登基、皇后册封），不是上朝处；文武百官在太和殿广场站列，文东武西。
-- 中和殿：举行盛大典礼时皇帝的休息室，文武百官站好后皇帝再过去。
-- 保和殿：从乾隆五十四年开始是殿试考场；东北角有汉字馆，内有4枚免费印章，可购买紫禁城100现场盖章。
-- 乾清门：后宫入口，东边九卿直房，西边军机处；门口狮子耳朵耷拉、眉毛遮眼，警示后宫不该看的不看、不该听的不听。
-- 乾清宫：皇帝睡觉的地方，有27张龙床防刺客；牌匾“正大光明”后藏立储诏书，皇帝写两份，驾崩后对比。
-- 交泰殿：放25块传国玉玺。
-- 坤宁宫：住皇后，明朝所有皇后都住这；东北角文创店有5枚免费印章。
-- 储秀宫：慈禧住了20多年，现为慈禧五十大寿原状陈列，其子在此出生；旁边文创店有3枚免费印章。
-- 翊坤宫、永寿宫：永寿宫西边是太极殿，是东西六宫唯一被称为殿的。
-- 慈宁宫：康熙给奶奶孝庄皇太后修建的养老院，旁边是寿康宫（甄嬛居住）。
-- 断虹桥：网红打卡地，有形态各异的石狮子，最有名的是武当狮。
-- 武英殿（西）：后改陶瓷馆，目前关闭状态；文华殿（东）：据说现在有展览。
-- 箭亭：清朝皇帝及子孙练习骑马射箭的地方，旁边商店可买文创雪糕。
-- 钟表馆：展示各种造型的钟表。
-- 珍宝馆：门口有我国现存三座古代九龙壁之一，左边数第三条白龙下有一块木头，因当年烧制琉璃砖瓦弄坏一块，工匠用木头刷白漆以假乱真；珍宝馆不是单独展厅，院子周围屋子都是展品；即宁寿全宫，为乾隆给自己修建的养老院，乾隆退休后未放权，每天照常上朝办公；皇极殿据说是1:1复刻乾清宫，宁寿宫对标坤宁宫；乐寿堂为故宫唯一能进去参观的皇家寝室，有二龙仙楼设计；珍妃井为当年慈禧把珍妃丢进去的地方，现上头是井口石，珍妃不是从那个小眼进去的。
-- 延禧宫：网红打卡地，旁边景仁宫是甄嬛被封熹妃时所住，珍妃也住过。
-- 御花园：有钦安殿供奉真武大帝；紫禁城靠山景山从天上看酷似闭目盘坐的人像，有人说就是真武大帝。
-- 神武门：故宫北门，出门左手边有角楼咖啡（2枚免费印章）和故宫文创（2枚免费印章）两个盖章点。
+**午门**：三个门洞，进门后变五个，即明三暗五；中间正门仅供皇帝、皇后大婚、殿试前三名通行，两侧门走皇亲国戚和文武百官。
+**太和门广场**：五座金水桥，中间桥供皇帝，两侧桥供皇亲国戚和文武百官；太和门为明朝御门听政处，门口铜狮子为故宫六对铜狮中最大一对。
+**太和殿**：金銮殿，举行皇帝登基、皇后册封等盛大典礼，文武百官文东武西站立；中和殿为皇帝休息室。
+**保和殿**：乾隆五十四年起为殿试考场，东北角汉字馆有4枚免费印章，可购买紫禁城100并现场盖章。
+**乾清门**：皇帝上早朝处，东侧九卿直房，西侧军机处，门口狮子耳朵耷拉、眉毛遮眼警示后宫。
+**乾清宫**：皇帝寝宫，27张龙床，正大光明牌匾后藏立储诏书；交泰殿放25块传国玉玺；坤宁宫为皇后住所，东北角文创店有5枚免费印章。
+**储秀宫**：慈禧住20多年，五十大寿原状陈列，旁边文创店有3枚免费印章；翊坤宫、永寿宫、太极殿为东西六宫，太极殿是唯一称殿的。
+**慈宁宫**：康熙为孝庄皇太后修建，旁边寿康宫为甄嬛居住；冰窖书吧有3枚免费印章。
+**断虹桥**：网红打卡地，石狮子形态各异，最有名武当狮；武英殿改陶瓷馆，目前关闭；文华殿我去时未开，据说有展览。
+**箭亭**：清朝皇帝练习骑马射箭，旁边商店有文创雪糕；钟表馆展示各种钟表。
+**珍宝馆**：宁寿全宫，乾隆养老院，皇极殿1:1复刻乾清宫，乐寿堂是唯一能进去参观的皇家寝室，珍妃井在出口附近。
+**东筒子夹道**：拍照出片；延禧宫、景仁宫为网红打卡地，甄嬛、珍妃曾住。
+**御花园**：钦安殿供奉真武大帝，景山酷似真武大帝；神武门为故宫北门，出门左手边角楼咖啡和故宫文创各有2枚免费印章。
 # 互动与体验
-- 盖章互动：共标注七个免费盖章位置，包括保和殿东北角汉字馆4枚、坤宁宫东北角文创店5枚、储秀宫边文创店3枚、冰窖书吧3枚、珍宝馆出口右手边商店3枚、神武门出门左手边角楼咖啡2枚、故宫文创2枚；汉字馆可购买紫禁城100现场盖章，每家店印章不同，买了不能去其他店铺盖章，汉字馆印章数量最多，可邮寄到家或背着走。
-- 文创雪糕：箭亭旁边商店可购买文创雪糕，讲解者提问雪糕造型是谁，欢迎评论区分享。
-- 个人感受：在冰窖书吧盖章时有批折子的感觉；钟表馆的钟表造型令人开眼；珍宝馆的宝贝每一样都能让人说出感叹词，但游客太多，尤其看凤冠的挤不进去；东筒子夹道拍照非常出片。
+**盖章互动**：讲解标注七个免费盖章位置，包括保和殿东北角汉字馆4枚、坤宁宫东北角文创店5枚、储秀宫旁文创店3枚、冰窖书吧3枚、珍宝馆出口右手边商店3枚、神武门出门左手边角楼咖啡2枚、故宫文创2枚。
+**文创体验**：在汉字馆可购买紫禁城100并现场盖章，每家店印章不同，购买后不能去其他店铺盖章；在冰窖书吧购买了冰溪图，盖章时有批折子的感觉。
+**拍照打卡**：太和门铜狮子造型威武，建议单独拍照；东筒子夹道拍照出片；断虹桥武当狮可寻找。
+**个人感受**：钟表馆的钟表造型令人开眼；珍宝馆宝贝惊艳，但游客太多，看凤冠需挤进去；一天走3万步，需适当休息和补充水分。
 # 收获与建议
-- 建议早起排队，一进门沿中轴线往后走，可错开大批旅游团人群，在人少时逛完最重要景点。
-- 三条游览路线：第一条走完视频内所有景点，适合待一整天的朋友，一天走3万步，需适当休息和补充水分；第二条看完坤宁宫去看景仁宫和延禧宫，接着逛钟表馆和珍宝馆，出来直奔御花园，从神武门出，大概半天时间；第三条看完坤宁宫去储秀宫，出来去御花园，从神武门出，最省力，预计2小时左右。
-- 盖章建议：喜欢盖章的朋友可截图保存七个免费盖章位置；买了紫禁城100后不能去其他店铺盖章，需有所取舍。</t>
+**知识增量**：午门明三暗五结构及通行规则；太和殿为典礼场所而非上朝处；乾清宫正大光明牌匾后藏立储诏书；珍宝馆为乾隆养老院，乐寿堂是唯一可进入参观的皇家寝室。
+**游览建议**：建议早起排队一进门沿中轴线往后走，可错开旅游团；三条路线按时间选择，第一条适合一整天，第二条约半天，第三条约2小时最省力。
+**盖章建议**：标注七个免费盖章位置，供章友截图保存；汉字馆印章数量最多，购买紫禁城100后不能去其他店铺盖章。</t>
         </is>
       </c>
       <c r="D20" s="10" t="n">
-        <v>72.59999999999999</v>
+        <v>41.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4497/1880</t>
+          <t>4497/1441</t>
         </is>
       </c>
     </row>
@@ -6562,52 +6632,41 @@
       <c r="C21" s="4" t="inlineStr">
         <is>
           <t># 访谈概况
-本次访谈以留守老人养老问题为核心议题，受访对象包括农村留守老人、村政府和民政局干部、城市社区社工等多元群体。访谈目的为梳理留守老人养老现状、政策落实困境及社区实践路径。据2021社区居家养老现状与未来趋势报告，65.5%的老人子女长期不在身边而独居，仅26.8%与子女同住；独居老人存在无人照料、无人慰藉、就医困难等问题，并列举了黑龙江绥滨独居老人因寂寞报警、上海与杭州各一名67岁独居老人去世多日后才被发现等案例。农村留守老人群体庞大，原因包括子女外出打工、经济压力大、老人适应能力降低及城市对农村老人的歧视等。整体反馈基调为：农村养老面临经济困难、子女不在身边、娱乐方式少等现实困境，政策覆盖有限且运营经费不足；城市社区通过志愿者制度、养老服务中心等实践取得一定成效，但社工行业面临供给不足、资金短缺、专业欠缺等困境。
+本次访谈围绕农村留守老人养老问题展开，访谈对象包括农村留守老人、村政府和民政局干部、城市社区养老社工。访谈目的是了解留守老人养老现状与困境，并寻求解决之道。整体反馈基调为：留守老人面临无人照料、就医困难、经济困难等突出问题，农村养老政策保障水平有限，城市社区志愿者制度与社工服务提供了有益经验，但社工行业面临供给不足、资金短缺、专业欠缺等困境。
 # 核心反馈
 ## 农村留守老人
-- 黑龙江绥滨一位独居老奶奶因独自在家太寂寞，报警称有人敲门，民警上门后老奶奶承认是想找人聊天才报警，反映独居老人无人慰藉的普遍困境。
-- 上海一名67岁独居老人去世多日后，家中溢出刺鼻气味才被邻居发现；杭州一名67岁独居老人同样在去世数天后才被发现，凸显独居老人无人照料的致命风险。
-- 农村留守老人群体庞大，原因包括子女外出打工、经济压力大、老人适应能力降低以及城市对农村老人的无形歧视，多重因素叠加导致留守老人愈发增多。
-- 有老人反映子女外出后无人照料，日常只能自己操持农活、喂猪养鱼，生病时也缺乏陪伴，生活孤独且辛苦。
+- **独居现状**：根据2021社区居家养老现状与未来趋势报告，**65.5%** 的老人子女长期不在身边，无奈独居，仅 **26.8%** 的老人与子女同住。
+- **生活困境**：独居老人存在无人平护照料、无人慰藉、就医困难等问题，甚至可能独自在家发生意外。
+- **典型案例**：黑龙江绥滨一位独居老奶奶因寂寞报警，承认“因为自己一个人在家太寂寞，所以想找个人聊聊天”；上海、杭州各有一名 **67岁** 独居老人去世多日后才被发现。
+- **经济压力**：农村老人反映子女外出打工，经济压力大，老人适应能力降低，城市对农村老人存在无形歧视。
+- **就医障碍**：一位视障老人说出了自己在就医上遇到的障碍。
 ## 村政府和民政局干部
-- 农村养老面临三大问题：经济困难（地方经济不发达）、子女不在身边（生病住院麻烦）、娱乐方式少（只能坐在一起聊天打牌）。
-- 此前探索在农村建养老公共设施，提供日托、休闲娱乐、沟通交友平台，但地方财政困难，运营经费后续无支持，设施难以持续发挥作用。
-- 五保户（三无人员）分集中供养和分散供养：集中供养将生活护理补贴直接发给敬老院护理人员，生活费直接发给敬老院；分散供养每月发475元生活费，另有护理补贴。
-- 残疾人一级二级纳入最低生活保障，有160、270、380三个标准，按家庭状况制定，最起码保证最低生活保障。
-- 农村老年人每月养老金118元，可能还要提高；但农村养老金与工人养老金待遇完全一样，对老年人不公平。
-- 村支两委和志愿者通过敲门串门、宣传政策、搞卫生等方式服务老人，每月开党员组织会，上午开会下午搞活动，到孤寡老人、留守老人家里走一圈。
-## 城市社区社工
-- 城市小区留守老人与外界社交机会更少，更容易产生孤独、抑郁等情绪，社区建立志愿者制度以就近帮扶方式传递善意。
-- 志愿者一对一帮扶，如发现老人住在楼下，上下楼时天天去看望，老人身体不好时天天送菜；通过定期表彰、志愿者积分兑换（年底可在雷锋超市兑换礼品）激励志愿者长期坚持。
-- 发掘中年志愿者，开展小手拉大手活动，从儿童青少年入手拉动家长参与；这周四准备开展送春联活动，邀请书法老师写对联，孩子们上门送对联。
-- 去年中秋节开展做月饼活动，还做过百家宴，让老人感觉社区就是大家庭；2023年目标是家长自己组织活动，社区作为协助者。
-- 每个社区成立养老服务中心，提供理疗、按摩、老年大学、心理咨询等服务。
-- 社工曾帮助一位有心理问题的老人：老人与邻里关系不和谐、半夜摔门，抗拒上门帮助，觉得周围人陌生、没有关心他的人；通过社工日复一日的关心和照料，老人心理问题逐渐好转，现在与邻里关系还算好，能接受一些意见。
-- 社工制度困境：社会需求量大而供给不足，政府和社区资金有限，难以承担长期专业社工服务费用；大量社工迫于生计转行，阻碍行业长期发展。
-- 每个街道和乡镇派两名社工驻点，围绕老人小孩服务，但很难坚持下来；社工工资低，影响就业率，很多同学做不超过一年就离开。
-- 长沙社工机构领域多，但专注力不集中，需花钱购买服务，项目不一定每年都有；一年服务成效不明显，资金拨不下来，项目结束，服务成效不一定达到。
-- 湖南省街道社工花费十来万，省里拨了钱，但很多社工不专业，专业上欠缺。
+- **五保户供养**：五保户分为集中供养和分散供养，分散供养五保户每月发 **475元** 生活费，另有护理补贴；集中供养则将生活护理补贴直接发给敬老院护理人员。
+- **低保标准**：残疾人一二级纳入最低生活保障，有 **160、270、380** 三个标准，根据家庭状况制定。
+- **养老金水平**：农村老年人每月养老金 **118元**，可能提高，但农村养老金与工人养老金待遇不完全相同。
+- **养老问题**：农村养老面临经济困难、子女不在身边、娱乐方式少等问题；之前探索过农村养老公共设施，但地方财政困难，运营经费后续无支持。
+- **现有做法**：村支两委和志愿者每月开展党员组织会，下午搞活动、清洁卫生，到孤寡老人、留守老人家里走访。
+## 城市社区养老社工
+- **志愿者制度**：社区建立志愿者制度，一对一帮扶，志愿者定期看望老人，提供帮助；志愿者积分兑换，年底可到雷锋超市兑换礼品。
+- **活动开展**：今年周四准备开展送春联活动，邀请书法老师写对联，孩子们上门送对联；去年中秋节开展做月饼活动，还做过百家宴。
+- **未来目标**：2023年目标是家长自己组织活动，社区作为协助者。
+- **养老服务中心**：每个社区成立养老服务中心，提供理疗、按摩、老年大学、心理咨询等服务。
+- **心理帮扶案例**：社工帮助过一位心理问题老人，通过日复一日关心照料，老人心理问题逐渐好转，与邻里关系改善。
+- **社工困境**：社工制度困境在于社会需求量大而供给不足，政府和社区资金有限，难以承担长期专业社工服务费用，大量社工迫于生计转行。
 # 关键洞察与建议
-## 洞察
-- 独居老人无人照料、无人慰藉、就医困难等问题普遍存在，且可能独自在家发生意外（如上海、杭州67岁独居老人去世多日后才被发现），说明独居老人安全与情感需求均未得到有效保障。
-- 农村留守老人群体庞大，原因包括子女外出打工、经济压力大、老人适应能力降低及城市对农村老人的歧视，说明养老问题与人口流动、城乡差距密切相关。
-- 农村养老公共设施因地方财政困难、运营经费无后续支持而难以持续，说明一次性投入不足以解决养老问题，需考虑长期运营经费。
-- 城市社区志愿者制度（一对一帮扶、积分兑换、小手拉大手）和养老服务中心（理疗、按摩、老年大学、心理咨询）取得一定成效，说明社区参与和多元服务模式有助于缓解养老困境。
-- 社工行业面临供给不足、资金短缺、专业欠缺、人员流失快（很多同学做不超过一年）等困境，说明社工制度需解决资金可持续性和专业人才培养问题。
-## 建议
-- 请专业施工人进行陪伴，为老人提供日常照料与陪伴。
-- 倡导在外务工的子女多与老人联系，缓解老人孤独感。
-- 丰富老人文化生活，增加娱乐方式。
-- 希望老年协会专项执行，专门建养老设施，有固定场地，定期开展宣传和健康知识讲座，并考虑持续运营经费。
-- 社区志愿者制度应长期坚持，通过表彰、积分兑换等激励志愿者，并发掘中年志愿者、开展小手拉大手活动，让家长自己组织活动，社区作为协助者。</t>
+**现状洞察**：根据2021社区居家养老现状与未来趋势报告，**65.5%** 的老人子女长期不在身边，独居老人基数庞大，且存在无人照料、就医困难等问题，说明农村留守老人养老问题具有普遍性和紧迫性。
+**政策局限**：农村养老金每月 **118元**，分散供养五保户每月 **475元**，保障水平有限；农村养老公共设施因地方财政困难，运营经费后续无支持，说明一次性投入难以持续。
+**社工困境**：社工工资低，很多同学做不超过一年就离职；服务领域多，专注力不集中，项目不一定每年都有，说明社工行业供给不足、专业欠缺，影响服务成效。
+**改善建议**：建议请专业施工人进行陪伴，倡导在外务工的子女多与老人联系，丰富老人的文化生活，增加娱乐方式；希望老年协会专项执行，专门建养老设施，有固定场地，定期开展宣传、健康知识讲座，并考虑持续运营经费。
+**社区经验**：城市社区通过志愿者一对一帮扶、积分兑换、小手拉大手等活动，让老人融入社区，说明社区参与和代际互动有助于缓解老人孤独感。</t>
         </is>
       </c>
       <c r="D21" s="10" t="n">
-        <v>56.2</v>
+        <v>45.4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>5309/2292</t>
+          <t>5309/1654</t>
         </is>
       </c>
     </row>
@@ -7211,7 +7270,47 @@
           <t>家校沟通</t>
         </is>
       </c>
-      <c r="C22" s="4" t="n"/>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t># 沟通概况
+2025年秋季学期，372班班主任林瑞（地理教师）主持召开家长会，与全班60名学生家长沟通班级管理与学生成长事宜。会议围绕班级基本情况、教师团队、存在问题及解决思路、费用说明、保险与电子学生证办理、家庭教育建议等议题展开。班主任指出班级整体班风纪律良好，但少数学生存在周末玩手机游戏、自习课效率低、个别学生书写不佳等问题，并提出加强手机管理、制定班规、加强班委培训等措施。会议明确费用由学生交给生活委员、不在微信群收取，建议家长关注学生社交账号与心理健康，并成立家委会（至少三人）。张宇波校长作为家长代表分享家庭教育经验，强调尊重孩子、多倾听多交流。
+# 沟通内容
+**班级亮点**：
+- **班风纪律**：372班共60人（男生25人、女生35人），整体时间观念、执行力强，班风班貌纪律良好，卫生干净。
+- **教师团队**：多为老教师、优秀教师，师范院校毕业，有3年以上教学经验，部分教师有6年以上经验；班主任林瑞教地理学科。
+**需关注之处**：
+- **手机管理**：少数同学周末玩手机游戏，有网瘾，充生活费400元用于游戏；发现学生看直播、不健康内容，需家长关注。
+- **自习效率**：自习课效率低，思考能力差，班主任不在时纪律松散，需加强班委培训。
+- **书写习惯**：个别学生书写不好，已与家长沟通，建议买字帖练字。
+- **行为规范**：发现学生带镜子，要求全部收掉；有学生谈恋爱，需家长关注QQ、抖音、快手等社交账号。
+# 家长反馈
+张宇波校长作为家长代表分享家庭教育经验，强调关注孩子身体健康和心理健康，尊重孩子，多倾听多交流，配合学校制度。班主任林瑞转述家长反馈：个别学生书写问题已与家长沟通；有家长反映孩子生活费使用不当，建议控制零花钱。班主任提醒家长注意孩子社交账号动态，防止早恋和不良内容影响。
+# 共识与配合事项
+**家校共识**：
+- 费用由学生交给生活委员，不在微信群收取，防止诈骗。
+- 要求收掉镜子，加强手机管理，家长配合处理多余手机。
+- 成立家委会，至少三人，有家长自愿报名。
+**后续配合事项**：
+- [ ] 家长：周一到周五不定时打电话检查孩子手机是否开机。
+- [ ] 家长：处理孩子多余手机，不留多部。
+- [ ] 家长：关注孩子QQ、抖音、快手等社交账号，防止早恋和不良内容。
+- [ ] 家长：督促孩子练字，购买字帖。
+- [ ] 班主任：制定详细班规，严格扣分、写检讨、罚站。
+- [ ] 班主任：加强班委培训，提高自习课效率。
+- [ ] 班主任：定期与科任老师沟通，了解学生表现。
+- [ ] 家长：关注孩子心理健康，发现异常及时心理辅导。
+- [ ] 家长：提醒孩子注意交通安全，未满16周岁不骑电动车。
+- [ ] 家长：配合学校防溺水、防诈骗、防校园欺凌教育。</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>17334/1178</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="13.5" customHeight="1" s="9">
       <c r="A23" s="6" t="inlineStr">
@@ -7287,7 +7386,42 @@
           <t>团队例会</t>
         </is>
       </c>
-      <c r="C23" s="4" t="n"/>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t># 例会概况
+本次周会于10月28日召开，会议等级为自愿级，会议资料包括工作报告、这班看法、这班型社区介绍。会议目标是初步统一成员意见，统一对社区的认识，总结工作并安排下周任务。会议讨论了社区建设与教育方向，提出将服务定价权交给消费者，变成代购；建设教育办的师范学校；参加互联网加创业大赛；根据学校为学府学习所需技能，实现教师上的改革；并邀请同事加入制作解决方案。下周工作安排需确定路线，修订纲领章程；组建教育团队，确定路线；任务包括课程开发、组建执法队伍、大运发放等，其中组建执法队伍为下月主要任务，任务分配需考虑工作量。待遇方面，上班5000元，额外有奖励，还有提成；休假为周五半天加周末两天。营销工作先发介绍，提高了解程度；抖音任务，可视化学习方案和工具；每月充值赞助；根据数据配热情况。
+# 工作进展
+## 工作方向与任务安排
+- **确定路线**：🔄进行中，需修订纲领章程，下一步安排任务分配，时间节点未明确。
+- **组建教育团队**：🔄进行中，需确定路线，下一步邀请同事加入，时间节点未明确。
+- **组建执法队伍**：🔄进行中，为下月主要任务，需招聘20多位师傅，时间节点未明确。
+- **课程开发**：🔄进行中，作为任务之一，具体进展未明确。
+- **大运发放**：🔄进行中，需要调试，具体进展未明确。
+## 社区建设与教育
+- **定价权交给消费者**：🔄进行中，将服务变成代购，具体进展未明确。
+- **建设教育办的师范学校**：🔄进行中，具体进展未明确。
+- **参加互联网加创业大赛**：🔄进行中，具体进展未明确。
+- **实现教师上的改革**：🔄进行中，根据学校为学府学习所需技能，具体进展未明确。
+## 营销与宣传
+- **营销工作先发介绍**：🔄进行中，提高了解程度，下一步继续推进，时间节点未明确。
+- **抖音任务**：🔄进行中，可视化学习方案和工具，具体进展未明确。
+- **每月充值赞助**：🔄进行中，具体进展未明确。
+- **根据数据配热情况**：🔄进行中，具体进展未明确。
+# 协作需求
+- **邀请同事加入**：提出方为会议主持人，配合方为全体成员，用于共同制作解决方案，时间节点未明确。
+- **任务分配需考虑工作量**：提出方为会议主持人，配合方为任务负责人，需评估工作量，时间节点未明确。
+- **大运发放调试**：提出方为会议主持人，配合方为负责调试的成员，需完成调试，时间节点未明确。
+- **营销工作先发介绍**：提出方为会议主持人，配合方为营销相关成员，需先发介绍，时间节点未明确。</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>4999/1075</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="13.5" customHeight="1" s="9">
       <c r="A24" s="6" t="inlineStr">
